--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G18">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G30">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G48">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G60">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G84">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G86">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G96">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G100">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G103">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G128">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G134">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G140">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G147">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU151"/>
+  <dimension ref="A1:AU154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-23 10:15:00</t>
+          <t>2026-10-23 10:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-10-23 10:30:00</t>
+          <t>2026-10-23 10:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-10-23 11:00:00</t>
+          <t>2026-10-23 10:00:00</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-23 11:00:00</t>
+          <t>2026-10-23 10:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-23 11:15:00</t>
+          <t>2026-10-23 10:15:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-10-23 11:15:00</t>
+          <t>2026-10-23 10:30:00</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-23 11:30:00</t>
+          <t>2026-10-23 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-23 12:00:00</t>
+          <t>2026-10-23 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-10-23 12:00:00</t>
+          <t>2026-10-23 11:15:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-10-23 12:00:00</t>
+          <t>2026-10-23 11:15:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-10-23 12:20:00</t>
+          <t>2026-10-23 11:30:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-10-23 12:20:00</t>
+          <t>2026-10-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-10-23 12:30:00</t>
+          <t>2026-10-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-10-23 12:30:00</t>
+          <t>2026-10-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-10-23 13:00:00</t>
+          <t>2026-10-23 12:20:00</t>
         </is>
       </c>
     </row>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-23 13:00:00</t>
+          <t>2026-10-23 12:20:00</t>
         </is>
       </c>
     </row>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-23 13:00:00</t>
+          <t>2026-10-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-23 13:00:00</t>
+          <t>2026-10-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-10-23 13:45:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:45:00</t>
         </is>
       </c>
     </row>
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,27 +10694,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="O67">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="P67">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-10-23 14:45:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="G68">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G69">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G70">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:45:00</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P76">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12905,10 +12905,10 @@
         <v>0</v>
       </c>
       <c r="AC77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD77">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE77">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G86">
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O97">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="P97">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16165,10 +16165,10 @@
         <v>0</v>
       </c>
       <c r="AC97">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD97">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE97">
         <v>0</v>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G98">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB99">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16562,27 +16562,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16725,27 +16725,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16817,10 +16817,10 @@
         <v>0</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16893,22 +16893,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O104">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB104">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G105">
@@ -17540,27 +17540,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB106">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G109">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-23 16:30:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O111">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P111">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-10-23 16:45:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18518,27 +18518,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G112">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-10-23 17:30:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18681,27 +18681,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-10-23 19:00:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18844,27 +18844,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-10-23 19:30:00</t>
+          <t>2026-10-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 16:45:00</t>
         </is>
       </c>
     </row>
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 19:00:00</t>
         </is>
       </c>
     </row>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 19:30:00</t>
         </is>
       </c>
     </row>
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,22 +22924,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,22 +24554,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G149">
@@ -24712,27 +24712,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G150">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-10-23 22:30:00</t>
+          <t>2026-10-23 21:00:00</t>
         </is>
       </c>
     </row>
@@ -24875,156 +24875,645 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Grafičar</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Spartak Subotica</t>
+        </is>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+      <c r="Q151">
+        <v>0</v>
+      </c>
+      <c r="R151">
+        <v>0</v>
+      </c>
+      <c r="S151">
+        <v>0</v>
+      </c>
+      <c r="T151">
+        <v>0</v>
+      </c>
+      <c r="U151">
+        <v>0</v>
+      </c>
+      <c r="V151">
+        <v>0</v>
+      </c>
+      <c r="W151">
+        <v>0</v>
+      </c>
+      <c r="X151">
+        <v>0</v>
+      </c>
+      <c r="Y151">
+        <v>0</v>
+      </c>
+      <c r="Z151">
+        <v>0</v>
+      </c>
+      <c r="AA151">
+        <v>0</v>
+      </c>
+      <c r="AB151">
+        <v>0</v>
+      </c>
+      <c r="AC151">
+        <v>0</v>
+      </c>
+      <c r="AD151">
+        <v>0</v>
+      </c>
+      <c r="AE151">
+        <v>0</v>
+      </c>
+      <c r="AF151">
+        <v>0</v>
+      </c>
+      <c r="AG151">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ151">
+        <v>0</v>
+      </c>
+      <c r="AK151">
+        <v>0</v>
+      </c>
+      <c r="AL151">
+        <v>0</v>
+      </c>
+      <c r="AM151">
+        <v>-1</v>
+      </c>
+      <c r="AN151">
+        <v>-1</v>
+      </c>
+      <c r="AO151">
+        <v>-1</v>
+      </c>
+      <c r="AP151">
+        <v>-1</v>
+      </c>
+      <c r="AQ151">
+        <v>0</v>
+      </c>
+      <c r="AR151">
+        <v>0</v>
+      </c>
+      <c r="AS151">
+        <v>0</v>
+      </c>
+      <c r="AT151">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>2026-10-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+      <c r="Q152">
+        <v>0</v>
+      </c>
+      <c r="R152">
+        <v>0</v>
+      </c>
+      <c r="S152">
+        <v>0</v>
+      </c>
+      <c r="T152">
+        <v>0</v>
+      </c>
+      <c r="U152">
+        <v>0</v>
+      </c>
+      <c r="V152">
+        <v>0</v>
+      </c>
+      <c r="W152">
+        <v>0</v>
+      </c>
+      <c r="X152">
+        <v>0</v>
+      </c>
+      <c r="Y152">
+        <v>0</v>
+      </c>
+      <c r="Z152">
+        <v>0</v>
+      </c>
+      <c r="AA152">
+        <v>0</v>
+      </c>
+      <c r="AB152">
+        <v>0</v>
+      </c>
+      <c r="AC152">
+        <v>0</v>
+      </c>
+      <c r="AD152">
+        <v>0</v>
+      </c>
+      <c r="AE152">
+        <v>0</v>
+      </c>
+      <c r="AF152">
+        <v>0</v>
+      </c>
+      <c r="AG152">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ152">
+        <v>0</v>
+      </c>
+      <c r="AK152">
+        <v>0</v>
+      </c>
+      <c r="AL152">
+        <v>0</v>
+      </c>
+      <c r="AM152">
+        <v>-1</v>
+      </c>
+      <c r="AN152">
+        <v>-1</v>
+      </c>
+      <c r="AO152">
+        <v>-1</v>
+      </c>
+      <c r="AP152">
+        <v>-1</v>
+      </c>
+      <c r="AQ152">
+        <v>0</v>
+      </c>
+      <c r="AR152">
+        <v>0</v>
+      </c>
+      <c r="AS152">
+        <v>0</v>
+      </c>
+      <c r="AT152">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>2026-10-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153">
+        <v>0</v>
+      </c>
+      <c r="R153">
+        <v>0</v>
+      </c>
+      <c r="S153">
+        <v>0</v>
+      </c>
+      <c r="T153">
+        <v>0</v>
+      </c>
+      <c r="U153">
+        <v>0</v>
+      </c>
+      <c r="V153">
+        <v>0</v>
+      </c>
+      <c r="W153">
+        <v>0</v>
+      </c>
+      <c r="X153">
+        <v>0</v>
+      </c>
+      <c r="Y153">
+        <v>0</v>
+      </c>
+      <c r="Z153">
+        <v>0</v>
+      </c>
+      <c r="AA153">
+        <v>0</v>
+      </c>
+      <c r="AB153">
+        <v>0</v>
+      </c>
+      <c r="AC153">
+        <v>0</v>
+      </c>
+      <c r="AD153">
+        <v>0</v>
+      </c>
+      <c r="AE153">
+        <v>0</v>
+      </c>
+      <c r="AF153">
+        <v>0</v>
+      </c>
+      <c r="AG153">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ153">
+        <v>0</v>
+      </c>
+      <c r="AK153">
+        <v>0</v>
+      </c>
+      <c r="AL153">
+        <v>0</v>
+      </c>
+      <c r="AM153">
+        <v>-1</v>
+      </c>
+      <c r="AN153">
+        <v>-1</v>
+      </c>
+      <c r="AO153">
+        <v>-1</v>
+      </c>
+      <c r="AP153">
+        <v>-1</v>
+      </c>
+      <c r="AQ153">
+        <v>0</v>
+      </c>
+      <c r="AR153">
+        <v>0</v>
+      </c>
+      <c r="AS153">
+        <v>0</v>
+      </c>
+      <c r="AT153">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>2026-10-23 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>Portland Thorns</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>North Carolina Courage</t>
         </is>
       </c>
-      <c r="G151">
-        <v>0</v>
-      </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
-      <c r="I151">
-        <v>0</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151">
-        <v>0</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151" t="inlineStr">
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="O151">
-        <v>0</v>
-      </c>
-      <c r="P151">
-        <v>0</v>
-      </c>
-      <c r="Q151">
-        <v>0</v>
-      </c>
-      <c r="R151">
-        <v>0</v>
-      </c>
-      <c r="S151">
-        <v>0</v>
-      </c>
-      <c r="T151">
-        <v>0</v>
-      </c>
-      <c r="U151">
-        <v>0</v>
-      </c>
-      <c r="V151">
-        <v>0</v>
-      </c>
-      <c r="W151">
-        <v>0</v>
-      </c>
-      <c r="X151">
-        <v>0</v>
-      </c>
-      <c r="Y151">
-        <v>0</v>
-      </c>
-      <c r="Z151">
-        <v>0</v>
-      </c>
-      <c r="AA151">
-        <v>0</v>
-      </c>
-      <c r="AB151">
-        <v>0</v>
-      </c>
-      <c r="AC151">
-        <v>0</v>
-      </c>
-      <c r="AD151">
-        <v>0</v>
-      </c>
-      <c r="AE151">
-        <v>0</v>
-      </c>
-      <c r="AF151">
-        <v>0</v>
-      </c>
-      <c r="AG151">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ151">
-        <v>0</v>
-      </c>
-      <c r="AK151">
-        <v>0</v>
-      </c>
-      <c r="AL151">
-        <v>0</v>
-      </c>
-      <c r="AM151">
-        <v>-1</v>
-      </c>
-      <c r="AN151">
-        <v>-1</v>
-      </c>
-      <c r="AO151">
-        <v>-1</v>
-      </c>
-      <c r="AP151">
-        <v>-1</v>
-      </c>
-      <c r="AQ151">
-        <v>0</v>
-      </c>
-      <c r="AR151">
-        <v>0</v>
-      </c>
-      <c r="AS151">
-        <v>0</v>
-      </c>
-      <c r="AT151">
-        <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>0</v>
+      </c>
+      <c r="R154">
+        <v>0</v>
+      </c>
+      <c r="S154">
+        <v>0</v>
+      </c>
+      <c r="T154">
+        <v>0</v>
+      </c>
+      <c r="U154">
+        <v>0</v>
+      </c>
+      <c r="V154">
+        <v>0</v>
+      </c>
+      <c r="W154">
+        <v>0</v>
+      </c>
+      <c r="X154">
+        <v>0</v>
+      </c>
+      <c r="Y154">
+        <v>0</v>
+      </c>
+      <c r="Z154">
+        <v>0</v>
+      </c>
+      <c r="AA154">
+        <v>0</v>
+      </c>
+      <c r="AB154">
+        <v>0</v>
+      </c>
+      <c r="AC154">
+        <v>0</v>
+      </c>
+      <c r="AD154">
+        <v>0</v>
+      </c>
+      <c r="AE154">
+        <v>0</v>
+      </c>
+      <c r="AF154">
+        <v>0</v>
+      </c>
+      <c r="AG154">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ154">
+        <v>0</v>
+      </c>
+      <c r="AK154">
+        <v>0</v>
+      </c>
+      <c r="AL154">
+        <v>0</v>
+      </c>
+      <c r="AM154">
+        <v>-1</v>
+      </c>
+      <c r="AN154">
+        <v>-1</v>
+      </c>
+      <c r="AO154">
+        <v>-1</v>
+      </c>
+      <c r="AP154">
+        <v>-1</v>
+      </c>
+      <c r="AQ154">
+        <v>0</v>
+      </c>
+      <c r="AR154">
+        <v>0</v>
+      </c>
+      <c r="AS154">
+        <v>0</v>
+      </c>
+      <c r="AT154">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
         <is>
           <t>2026-10-23 23:00:00</t>
         </is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G52">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G90">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G151">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G90">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU154"/>
+  <dimension ref="A1:AU156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G18">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G26">
@@ -4663,27 +4663,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-10-23 11:15:00</t>
+          <t>2026-10-23 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-10-23 11:15:00</t>
+          <t>2026-10-23 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-10-23 11:30:00</t>
+          <t>2026-10-23 11:15:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-10-23 12:00:00</t>
+          <t>2026-10-23 11:15:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-10-23 12:00:00</t>
+          <t>2026-10-23 11:30:00</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-10-23 12:20:00</t>
+          <t>2026-10-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-23 12:20:00</t>
+          <t>2026-10-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-23 12:30:00</t>
+          <t>2026-10-23 12:20:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-23 12:30:00</t>
+          <t>2026-10-23 12:20:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-23 13:00:00</t>
+          <t>2026-10-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-23 13:00:00</t>
+          <t>2026-10-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,22 +7276,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-23 13:45:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:45:00</t>
         </is>
       </c>
     </row>
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G62">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G63">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="G70">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-10-23 14:45:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G72">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:45:00</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD81">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G90">
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O96">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="P96">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16817,10 +16817,10 @@
         <v>0</v>
       </c>
       <c r="AC101">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD101">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE101">
         <v>0</v>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.19</v>
+        <v>1.44</v>
       </c>
       <c r="O103">
-        <v>3.74</v>
+        <v>5.65</v>
       </c>
       <c r="P103">
-        <v>3.43</v>
+        <v>6.98</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,16 +17137,16 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB103">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P108">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB108">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109">
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.96</v>
+        <v>2.15</v>
       </c>
       <c r="O110">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="P110">
-        <v>2.55</v>
+        <v>3.64</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB110">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G111">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G113">
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-10-23 16:30:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P115">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-10-23 16:45:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-10-23 17:30:00</t>
+          <t>2026-10-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-23 19:00:00</t>
+          <t>2026-10-23 16:45:00</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-23 19:30:00</t>
+          <t>2026-10-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 19:00:00</t>
         </is>
       </c>
     </row>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O120">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="P120">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 19:30:00</t>
         </is>
       </c>
     </row>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G121">
@@ -20148,27 +20148,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20311,27 +20311,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,22 +22924,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,22 +23250,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,22 +25043,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G152">
@@ -25201,27 +25201,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G153">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>2026-10-23 22:30:00</t>
+          <t>2026-10-23 21:00:00</t>
         </is>
       </c>
     </row>
@@ -25364,156 +25364,482 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>0</v>
+      </c>
+      <c r="R154">
+        <v>0</v>
+      </c>
+      <c r="S154">
+        <v>0</v>
+      </c>
+      <c r="T154">
+        <v>0</v>
+      </c>
+      <c r="U154">
+        <v>0</v>
+      </c>
+      <c r="V154">
+        <v>0</v>
+      </c>
+      <c r="W154">
+        <v>0</v>
+      </c>
+      <c r="X154">
+        <v>0</v>
+      </c>
+      <c r="Y154">
+        <v>0</v>
+      </c>
+      <c r="Z154">
+        <v>0</v>
+      </c>
+      <c r="AA154">
+        <v>0</v>
+      </c>
+      <c r="AB154">
+        <v>0</v>
+      </c>
+      <c r="AC154">
+        <v>0</v>
+      </c>
+      <c r="AD154">
+        <v>0</v>
+      </c>
+      <c r="AE154">
+        <v>0</v>
+      </c>
+      <c r="AF154">
+        <v>0</v>
+      </c>
+      <c r="AG154">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ154">
+        <v>0</v>
+      </c>
+      <c r="AK154">
+        <v>0</v>
+      </c>
+      <c r="AL154">
+        <v>0</v>
+      </c>
+      <c r="AM154">
+        <v>-1</v>
+      </c>
+      <c r="AN154">
+        <v>-1</v>
+      </c>
+      <c r="AO154">
+        <v>-1</v>
+      </c>
+      <c r="AP154">
+        <v>-1</v>
+      </c>
+      <c r="AQ154">
+        <v>0</v>
+      </c>
+      <c r="AR154">
+        <v>0</v>
+      </c>
+      <c r="AS154">
+        <v>0</v>
+      </c>
+      <c r="AT154">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>2026-10-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
+        <v>0</v>
+      </c>
+      <c r="R155">
+        <v>0</v>
+      </c>
+      <c r="S155">
+        <v>0</v>
+      </c>
+      <c r="T155">
+        <v>0</v>
+      </c>
+      <c r="U155">
+        <v>0</v>
+      </c>
+      <c r="V155">
+        <v>0</v>
+      </c>
+      <c r="W155">
+        <v>0</v>
+      </c>
+      <c r="X155">
+        <v>0</v>
+      </c>
+      <c r="Y155">
+        <v>0</v>
+      </c>
+      <c r="Z155">
+        <v>0</v>
+      </c>
+      <c r="AA155">
+        <v>0</v>
+      </c>
+      <c r="AB155">
+        <v>0</v>
+      </c>
+      <c r="AC155">
+        <v>0</v>
+      </c>
+      <c r="AD155">
+        <v>0</v>
+      </c>
+      <c r="AE155">
+        <v>0</v>
+      </c>
+      <c r="AF155">
+        <v>0</v>
+      </c>
+      <c r="AG155">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
+        <v>0</v>
+      </c>
+      <c r="AK155">
+        <v>0</v>
+      </c>
+      <c r="AL155">
+        <v>0</v>
+      </c>
+      <c r="AM155">
+        <v>-1</v>
+      </c>
+      <c r="AN155">
+        <v>-1</v>
+      </c>
+      <c r="AO155">
+        <v>-1</v>
+      </c>
+      <c r="AP155">
+        <v>-1</v>
+      </c>
+      <c r="AQ155">
+        <v>0</v>
+      </c>
+      <c r="AR155">
+        <v>0</v>
+      </c>
+      <c r="AS155">
+        <v>0</v>
+      </c>
+      <c r="AT155">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>2026-10-23 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>Portland Thorns</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>North Carolina Courage</t>
         </is>
       </c>
-      <c r="G154">
-        <v>0</v>
-      </c>
-      <c r="H154">
-        <v>0</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
-      </c>
-      <c r="J154">
-        <v>0</v>
-      </c>
-      <c r="K154">
-        <v>0</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154" t="inlineStr">
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
-      <c r="O154">
-        <v>0</v>
-      </c>
-      <c r="P154">
-        <v>0</v>
-      </c>
-      <c r="Q154">
-        <v>0</v>
-      </c>
-      <c r="R154">
-        <v>0</v>
-      </c>
-      <c r="S154">
-        <v>0</v>
-      </c>
-      <c r="T154">
-        <v>0</v>
-      </c>
-      <c r="U154">
-        <v>0</v>
-      </c>
-      <c r="V154">
-        <v>0</v>
-      </c>
-      <c r="W154">
-        <v>0</v>
-      </c>
-      <c r="X154">
-        <v>0</v>
-      </c>
-      <c r="Y154">
-        <v>0</v>
-      </c>
-      <c r="Z154">
-        <v>0</v>
-      </c>
-      <c r="AA154">
-        <v>0</v>
-      </c>
-      <c r="AB154">
-        <v>0</v>
-      </c>
-      <c r="AC154">
-        <v>0</v>
-      </c>
-      <c r="AD154">
-        <v>0</v>
-      </c>
-      <c r="AE154">
-        <v>0</v>
-      </c>
-      <c r="AF154">
-        <v>0</v>
-      </c>
-      <c r="AG154">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ154">
-        <v>0</v>
-      </c>
-      <c r="AK154">
-        <v>0</v>
-      </c>
-      <c r="AL154">
-        <v>0</v>
-      </c>
-      <c r="AM154">
-        <v>-1</v>
-      </c>
-      <c r="AN154">
-        <v>-1</v>
-      </c>
-      <c r="AO154">
-        <v>-1</v>
-      </c>
-      <c r="AP154">
-        <v>-1</v>
-      </c>
-      <c r="AQ154">
-        <v>0</v>
-      </c>
-      <c r="AR154">
-        <v>0</v>
-      </c>
-      <c r="AS154">
-        <v>0</v>
-      </c>
-      <c r="AT154">
-        <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+      <c r="Q156">
+        <v>0</v>
+      </c>
+      <c r="R156">
+        <v>0</v>
+      </c>
+      <c r="S156">
+        <v>0</v>
+      </c>
+      <c r="T156">
+        <v>0</v>
+      </c>
+      <c r="U156">
+        <v>0</v>
+      </c>
+      <c r="V156">
+        <v>0</v>
+      </c>
+      <c r="W156">
+        <v>0</v>
+      </c>
+      <c r="X156">
+        <v>0</v>
+      </c>
+      <c r="Y156">
+        <v>0</v>
+      </c>
+      <c r="Z156">
+        <v>0</v>
+      </c>
+      <c r="AA156">
+        <v>0</v>
+      </c>
+      <c r="AB156">
+        <v>0</v>
+      </c>
+      <c r="AC156">
+        <v>0</v>
+      </c>
+      <c r="AD156">
+        <v>0</v>
+      </c>
+      <c r="AE156">
+        <v>0</v>
+      </c>
+      <c r="AF156">
+        <v>0</v>
+      </c>
+      <c r="AG156">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
+        <v>0</v>
+      </c>
+      <c r="AK156">
+        <v>0</v>
+      </c>
+      <c r="AL156">
+        <v>0</v>
+      </c>
+      <c r="AM156">
+        <v>-1</v>
+      </c>
+      <c r="AN156">
+        <v>-1</v>
+      </c>
+      <c r="AO156">
+        <v>-1</v>
+      </c>
+      <c r="AP156">
+        <v>-1</v>
+      </c>
+      <c r="AQ156">
+        <v>0</v>
+      </c>
+      <c r="AR156">
+        <v>0</v>
+      </c>
+      <c r="AS156">
+        <v>0</v>
+      </c>
+      <c r="AT156">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
         <is>
           <t>2026-10-23 23:00:00</t>
         </is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G18">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G152">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G18">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G92">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G134">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G151">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G153">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU156"/>
+  <dimension ref="A1:AU151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G18">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G79">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-23 19:00:00</t>
+          <t>2026-10-23 19:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-23 19:30:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O122">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="P122">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20311,27 +20311,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 21:00:00</t>
         </is>
       </c>
     </row>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G128">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G130">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,22 +23250,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,22 +24554,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G149">
@@ -24712,27 +24712,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G150">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 22:30:00</t>
         </is>
       </c>
     </row>
@@ -24875,27 +24875,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G151">
@@ -25025,821 +25025,6 @@
         <v>0</v>
       </c>
       <c r="AU151" t="inlineStr">
-        <is>
-          <t>2026-10-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152">
-        <v>0</v>
-      </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-      <c r="J152">
-        <v>0</v>
-      </c>
-      <c r="K152">
-        <v>0</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N152">
-        <v>0</v>
-      </c>
-      <c r="O152">
-        <v>0</v>
-      </c>
-      <c r="P152">
-        <v>0</v>
-      </c>
-      <c r="Q152">
-        <v>0</v>
-      </c>
-      <c r="R152">
-        <v>0</v>
-      </c>
-      <c r="S152">
-        <v>0</v>
-      </c>
-      <c r="T152">
-        <v>0</v>
-      </c>
-      <c r="U152">
-        <v>0</v>
-      </c>
-      <c r="V152">
-        <v>0</v>
-      </c>
-      <c r="W152">
-        <v>0</v>
-      </c>
-      <c r="X152">
-        <v>0</v>
-      </c>
-      <c r="Y152">
-        <v>0</v>
-      </c>
-      <c r="Z152">
-        <v>0</v>
-      </c>
-      <c r="AA152">
-        <v>0</v>
-      </c>
-      <c r="AB152">
-        <v>0</v>
-      </c>
-      <c r="AC152">
-        <v>0</v>
-      </c>
-      <c r="AD152">
-        <v>0</v>
-      </c>
-      <c r="AE152">
-        <v>0</v>
-      </c>
-      <c r="AF152">
-        <v>0</v>
-      </c>
-      <c r="AG152">
-        <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ152">
-        <v>0</v>
-      </c>
-      <c r="AK152">
-        <v>0</v>
-      </c>
-      <c r="AL152">
-        <v>0</v>
-      </c>
-      <c r="AM152">
-        <v>-1</v>
-      </c>
-      <c r="AN152">
-        <v>-1</v>
-      </c>
-      <c r="AO152">
-        <v>-1</v>
-      </c>
-      <c r="AP152">
-        <v>-1</v>
-      </c>
-      <c r="AQ152">
-        <v>0</v>
-      </c>
-      <c r="AR152">
-        <v>0</v>
-      </c>
-      <c r="AS152">
-        <v>0</v>
-      </c>
-      <c r="AT152">
-        <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>2026-10-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="G153">
-        <v>0</v>
-      </c>
-      <c r="H153">
-        <v>0</v>
-      </c>
-      <c r="I153">
-        <v>0</v>
-      </c>
-      <c r="J153">
-        <v>0</v>
-      </c>
-      <c r="K153">
-        <v>0</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
-      <c r="O153">
-        <v>0</v>
-      </c>
-      <c r="P153">
-        <v>0</v>
-      </c>
-      <c r="Q153">
-        <v>0</v>
-      </c>
-      <c r="R153">
-        <v>0</v>
-      </c>
-      <c r="S153">
-        <v>0</v>
-      </c>
-      <c r="T153">
-        <v>0</v>
-      </c>
-      <c r="U153">
-        <v>0</v>
-      </c>
-      <c r="V153">
-        <v>0</v>
-      </c>
-      <c r="W153">
-        <v>0</v>
-      </c>
-      <c r="X153">
-        <v>0</v>
-      </c>
-      <c r="Y153">
-        <v>0</v>
-      </c>
-      <c r="Z153">
-        <v>0</v>
-      </c>
-      <c r="AA153">
-        <v>0</v>
-      </c>
-      <c r="AB153">
-        <v>0</v>
-      </c>
-      <c r="AC153">
-        <v>0</v>
-      </c>
-      <c r="AD153">
-        <v>0</v>
-      </c>
-      <c r="AE153">
-        <v>0</v>
-      </c>
-      <c r="AF153">
-        <v>0</v>
-      </c>
-      <c r="AG153">
-        <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ153">
-        <v>0</v>
-      </c>
-      <c r="AK153">
-        <v>0</v>
-      </c>
-      <c r="AL153">
-        <v>0</v>
-      </c>
-      <c r="AM153">
-        <v>-1</v>
-      </c>
-      <c r="AN153">
-        <v>-1</v>
-      </c>
-      <c r="AO153">
-        <v>-1</v>
-      </c>
-      <c r="AP153">
-        <v>-1</v>
-      </c>
-      <c r="AQ153">
-        <v>0</v>
-      </c>
-      <c r="AR153">
-        <v>0</v>
-      </c>
-      <c r="AS153">
-        <v>0</v>
-      </c>
-      <c r="AT153">
-        <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>2026-10-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G154">
-        <v>0</v>
-      </c>
-      <c r="H154">
-        <v>0</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
-      </c>
-      <c r="J154">
-        <v>0</v>
-      </c>
-      <c r="K154">
-        <v>0</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
-      <c r="O154">
-        <v>0</v>
-      </c>
-      <c r="P154">
-        <v>0</v>
-      </c>
-      <c r="Q154">
-        <v>0</v>
-      </c>
-      <c r="R154">
-        <v>0</v>
-      </c>
-      <c r="S154">
-        <v>0</v>
-      </c>
-      <c r="T154">
-        <v>0</v>
-      </c>
-      <c r="U154">
-        <v>0</v>
-      </c>
-      <c r="V154">
-        <v>0</v>
-      </c>
-      <c r="W154">
-        <v>0</v>
-      </c>
-      <c r="X154">
-        <v>0</v>
-      </c>
-      <c r="Y154">
-        <v>0</v>
-      </c>
-      <c r="Z154">
-        <v>0</v>
-      </c>
-      <c r="AA154">
-        <v>0</v>
-      </c>
-      <c r="AB154">
-        <v>0</v>
-      </c>
-      <c r="AC154">
-        <v>0</v>
-      </c>
-      <c r="AD154">
-        <v>0</v>
-      </c>
-      <c r="AE154">
-        <v>0</v>
-      </c>
-      <c r="AF154">
-        <v>0</v>
-      </c>
-      <c r="AG154">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ154">
-        <v>0</v>
-      </c>
-      <c r="AK154">
-        <v>0</v>
-      </c>
-      <c r="AL154">
-        <v>0</v>
-      </c>
-      <c r="AM154">
-        <v>-1</v>
-      </c>
-      <c r="AN154">
-        <v>-1</v>
-      </c>
-      <c r="AO154">
-        <v>-1</v>
-      </c>
-      <c r="AP154">
-        <v>-1</v>
-      </c>
-      <c r="AQ154">
-        <v>0</v>
-      </c>
-      <c r="AR154">
-        <v>0</v>
-      </c>
-      <c r="AS154">
-        <v>0</v>
-      </c>
-      <c r="AT154">
-        <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>2026-10-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="G155">
-        <v>0</v>
-      </c>
-      <c r="H155">
-        <v>0</v>
-      </c>
-      <c r="I155">
-        <v>0</v>
-      </c>
-      <c r="J155">
-        <v>0</v>
-      </c>
-      <c r="K155">
-        <v>0</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N155">
-        <v>0</v>
-      </c>
-      <c r="O155">
-        <v>0</v>
-      </c>
-      <c r="P155">
-        <v>0</v>
-      </c>
-      <c r="Q155">
-        <v>0</v>
-      </c>
-      <c r="R155">
-        <v>0</v>
-      </c>
-      <c r="S155">
-        <v>0</v>
-      </c>
-      <c r="T155">
-        <v>0</v>
-      </c>
-      <c r="U155">
-        <v>0</v>
-      </c>
-      <c r="V155">
-        <v>0</v>
-      </c>
-      <c r="W155">
-        <v>0</v>
-      </c>
-      <c r="X155">
-        <v>0</v>
-      </c>
-      <c r="Y155">
-        <v>0</v>
-      </c>
-      <c r="Z155">
-        <v>0</v>
-      </c>
-      <c r="AA155">
-        <v>0</v>
-      </c>
-      <c r="AB155">
-        <v>0</v>
-      </c>
-      <c r="AC155">
-        <v>0</v>
-      </c>
-      <c r="AD155">
-        <v>0</v>
-      </c>
-      <c r="AE155">
-        <v>0</v>
-      </c>
-      <c r="AF155">
-        <v>0</v>
-      </c>
-      <c r="AG155">
-        <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>0</v>
-      </c>
-      <c r="AK155">
-        <v>0</v>
-      </c>
-      <c r="AL155">
-        <v>0</v>
-      </c>
-      <c r="AM155">
-        <v>-1</v>
-      </c>
-      <c r="AN155">
-        <v>-1</v>
-      </c>
-      <c r="AO155">
-        <v>-1</v>
-      </c>
-      <c r="AP155">
-        <v>-1</v>
-      </c>
-      <c r="AQ155">
-        <v>0</v>
-      </c>
-      <c r="AR155">
-        <v>0</v>
-      </c>
-      <c r="AS155">
-        <v>0</v>
-      </c>
-      <c r="AT155">
-        <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>2026-10-23 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G156">
-        <v>0</v>
-      </c>
-      <c r="H156">
-        <v>0</v>
-      </c>
-      <c r="I156">
-        <v>0</v>
-      </c>
-      <c r="J156">
-        <v>0</v>
-      </c>
-      <c r="K156">
-        <v>0</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N156">
-        <v>0</v>
-      </c>
-      <c r="O156">
-        <v>0</v>
-      </c>
-      <c r="P156">
-        <v>0</v>
-      </c>
-      <c r="Q156">
-        <v>0</v>
-      </c>
-      <c r="R156">
-        <v>0</v>
-      </c>
-      <c r="S156">
-        <v>0</v>
-      </c>
-      <c r="T156">
-        <v>0</v>
-      </c>
-      <c r="U156">
-        <v>0</v>
-      </c>
-      <c r="V156">
-        <v>0</v>
-      </c>
-      <c r="W156">
-        <v>0</v>
-      </c>
-      <c r="X156">
-        <v>0</v>
-      </c>
-      <c r="Y156">
-        <v>0</v>
-      </c>
-      <c r="Z156">
-        <v>0</v>
-      </c>
-      <c r="AA156">
-        <v>0</v>
-      </c>
-      <c r="AB156">
-        <v>0</v>
-      </c>
-      <c r="AC156">
-        <v>0</v>
-      </c>
-      <c r="AD156">
-        <v>0</v>
-      </c>
-      <c r="AE156">
-        <v>0</v>
-      </c>
-      <c r="AF156">
-        <v>0</v>
-      </c>
-      <c r="AG156">
-        <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>0</v>
-      </c>
-      <c r="AK156">
-        <v>0</v>
-      </c>
-      <c r="AL156">
-        <v>0</v>
-      </c>
-      <c r="AM156">
-        <v>-1</v>
-      </c>
-      <c r="AN156">
-        <v>-1</v>
-      </c>
-      <c r="AO156">
-        <v>-1</v>
-      </c>
-      <c r="AP156">
-        <v>-1</v>
-      </c>
-      <c r="AQ156">
-        <v>0</v>
-      </c>
-      <c r="AR156">
-        <v>0</v>
-      </c>
-      <c r="AS156">
-        <v>0</v>
-      </c>
-      <c r="AT156">
-        <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
         <is>
           <t>2026-10-23 23:00:00</t>
         </is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G126">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G133">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G139">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU151"/>
+  <dimension ref="A1:AU149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bắc Ninh</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15:00</t>
+          <t>2026-10-23 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Bắc Ninh</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30:00</t>
+          <t>2026-10-23 09:15:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G8">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:50:00</t>
+          <t>2026-10-23 09:30:00</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Musannah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:00</t>
+          <t>2026-10-23 09:50:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Al Musannah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-23 10:00:00</t>
+          <t>2026-10-23 09:55:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G22">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-23 10:15:00</t>
+          <t>2026-10-23 10:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-10-23 10:30:00</t>
+          <t>2026-10-23 10:15:00</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-23 11:00:00</t>
+          <t>2026-10-23 10:30:00</t>
         </is>
       </c>
     </row>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,22 +4831,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G28">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-10-23 11:15:00</t>
+          <t>2026-10-23 11:00:00</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G30">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-10-23 11:30:00</t>
+          <t>2026-10-23 11:15:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-10-23 12:00:00</t>
+          <t>2026-10-23 11:30:00</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-23 12:20:00</t>
+          <t>2026-10-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-23 12:30:00</t>
+          <t>2026-10-23 12:20:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G38">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-23 13:00:00</t>
+          <t>2026-10-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7276,22 +7276,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="O55">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P55">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="O56">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AC56">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-10-23 13:45:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:45:00</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P66">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11188,22 +11188,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.39</v>
+        <v>3.39</v>
       </c>
       <c r="O69">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="P69">
-        <v>2.78</v>
+        <v>2.03</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.09</v>
+        <v>1.55</v>
       </c>
       <c r="O72">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="P72">
-        <v>2.79</v>
+        <v>4.58</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.65</v>
+        <v>2.09</v>
       </c>
       <c r="O73">
-        <v>3.24</v>
+        <v>3.72</v>
       </c>
       <c r="P73">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-10-23 14:45:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:45:00</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G75">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="O82">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="P82">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.54</v>
+        <v>3.04</v>
       </c>
       <c r="O83">
-        <v>4.69</v>
+        <v>3.25</v>
       </c>
       <c r="P83">
-        <v>5.62</v>
+        <v>2.22</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G92">
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="O99">
-        <v>3.38</v>
+        <v>5.27</v>
       </c>
       <c r="P99">
-        <v>3.53</v>
+        <v>3.19</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="O100">
         <v>3.38</v>
       </c>
       <c r="P100">
-        <v>2.64</v>
+        <v>3.53</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17143,10 +17143,10 @@
         <v>0</v>
       </c>
       <c r="AC103">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD103">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE103">
         <v>0</v>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17306,10 +17306,10 @@
         <v>0</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O105">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P105">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="AA105">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB105">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.9</v>
+        <v>2.19</v>
       </c>
       <c r="O106">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="P106">
-        <v>1.84</v>
+        <v>3.43</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="O107">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="P107">
-        <v>4.61</v>
+        <v>1.84</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="O108">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="P108">
-        <v>3.16</v>
+        <v>4.61</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="O109">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P109">
-        <v>4.18</v>
+        <v>3.16</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="P110">
-        <v>3.64</v>
+        <v>4.18</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB110">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="P111">
-        <v>2.76</v>
+        <v>3.64</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AB111">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="O112">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="P112">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB112">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.22</v>
+        <v>2.96</v>
       </c>
       <c r="O113">
-        <v>6.2</v>
+        <v>3.52</v>
       </c>
       <c r="P113">
-        <v>10.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G115">
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-10-23 16:30:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-23 16:45:00</t>
+          <t>2026-10-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-23 17:30:00</t>
+          <t>2026-10-23 16:45:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-23 19:30:00</t>
+          <t>2026-10-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 19:30:00</t>
         </is>
       </c>
     </row>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O121">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="P121">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20311,27 +20311,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,22 +22761,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,22 +24228,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G147">
@@ -24386,27 +24386,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G148">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 22:30:00</t>
         </is>
       </c>
     </row>
@@ -24549,12 +24549,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G149">
@@ -24699,332 +24699,6 @@
         <v>0</v>
       </c>
       <c r="AU149" t="inlineStr">
-        <is>
-          <t>2026-10-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="G150">
-        <v>0</v>
-      </c>
-      <c r="H150">
-        <v>0</v>
-      </c>
-      <c r="I150">
-        <v>0</v>
-      </c>
-      <c r="J150">
-        <v>0</v>
-      </c>
-      <c r="K150">
-        <v>0</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>0</v>
-      </c>
-      <c r="R150">
-        <v>0</v>
-      </c>
-      <c r="S150">
-        <v>0</v>
-      </c>
-      <c r="T150">
-        <v>0</v>
-      </c>
-      <c r="U150">
-        <v>0</v>
-      </c>
-      <c r="V150">
-        <v>0</v>
-      </c>
-      <c r="W150">
-        <v>0</v>
-      </c>
-      <c r="X150">
-        <v>0</v>
-      </c>
-      <c r="Y150">
-        <v>0</v>
-      </c>
-      <c r="Z150">
-        <v>0</v>
-      </c>
-      <c r="AA150">
-        <v>0</v>
-      </c>
-      <c r="AB150">
-        <v>0</v>
-      </c>
-      <c r="AC150">
-        <v>0</v>
-      </c>
-      <c r="AD150">
-        <v>0</v>
-      </c>
-      <c r="AE150">
-        <v>0</v>
-      </c>
-      <c r="AF150">
-        <v>0</v>
-      </c>
-      <c r="AG150">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ150">
-        <v>0</v>
-      </c>
-      <c r="AK150">
-        <v>0</v>
-      </c>
-      <c r="AL150">
-        <v>0</v>
-      </c>
-      <c r="AM150">
-        <v>-1</v>
-      </c>
-      <c r="AN150">
-        <v>-1</v>
-      </c>
-      <c r="AO150">
-        <v>-1</v>
-      </c>
-      <c r="AP150">
-        <v>-1</v>
-      </c>
-      <c r="AQ150">
-        <v>0</v>
-      </c>
-      <c r="AR150">
-        <v>0</v>
-      </c>
-      <c r="AS150">
-        <v>0</v>
-      </c>
-      <c r="AT150">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>2026-10-23 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G151">
-        <v>0</v>
-      </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
-      <c r="I151">
-        <v>0</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151">
-        <v>0</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="O151">
-        <v>0</v>
-      </c>
-      <c r="P151">
-        <v>0</v>
-      </c>
-      <c r="Q151">
-        <v>0</v>
-      </c>
-      <c r="R151">
-        <v>0</v>
-      </c>
-      <c r="S151">
-        <v>0</v>
-      </c>
-      <c r="T151">
-        <v>0</v>
-      </c>
-      <c r="U151">
-        <v>0</v>
-      </c>
-      <c r="V151">
-        <v>0</v>
-      </c>
-      <c r="W151">
-        <v>0</v>
-      </c>
-      <c r="X151">
-        <v>0</v>
-      </c>
-      <c r="Y151">
-        <v>0</v>
-      </c>
-      <c r="Z151">
-        <v>0</v>
-      </c>
-      <c r="AA151">
-        <v>0</v>
-      </c>
-      <c r="AB151">
-        <v>0</v>
-      </c>
-      <c r="AC151">
-        <v>0</v>
-      </c>
-      <c r="AD151">
-        <v>0</v>
-      </c>
-      <c r="AE151">
-        <v>0</v>
-      </c>
-      <c r="AF151">
-        <v>0</v>
-      </c>
-      <c r="AG151">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ151">
-        <v>0</v>
-      </c>
-      <c r="AK151">
-        <v>0</v>
-      </c>
-      <c r="AL151">
-        <v>0</v>
-      </c>
-      <c r="AM151">
-        <v>-1</v>
-      </c>
-      <c r="AN151">
-        <v>-1</v>
-      </c>
-      <c r="AO151">
-        <v>-1</v>
-      </c>
-      <c r="AP151">
-        <v>-1</v>
-      </c>
-      <c r="AQ151">
-        <v>0</v>
-      </c>
-      <c r="AR151">
-        <v>0</v>
-      </c>
-      <c r="AS151">
-        <v>0</v>
-      </c>
-      <c r="AT151">
-        <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
         <is>
           <t>2026-10-23 23:00:00</t>
         </is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G131">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G134">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU149"/>
+  <dimension ref="A1:AU148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,22 +22598,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,22 +22761,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,22 +24065,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G146">
@@ -24223,12 +24223,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G147">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 22:30:00</t>
         </is>
       </c>
     </row>
@@ -24386,7 +24386,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G148">
@@ -24536,169 +24536,6 @@
         <v>0</v>
       </c>
       <c r="AU148" t="inlineStr">
-        <is>
-          <t>2026-10-23 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
-      </c>
-      <c r="I149">
-        <v>0</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149">
-        <v>0</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="O149">
-        <v>0</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>0</v>
-      </c>
-      <c r="R149">
-        <v>0</v>
-      </c>
-      <c r="S149">
-        <v>0</v>
-      </c>
-      <c r="T149">
-        <v>0</v>
-      </c>
-      <c r="U149">
-        <v>0</v>
-      </c>
-      <c r="V149">
-        <v>0</v>
-      </c>
-      <c r="W149">
-        <v>0</v>
-      </c>
-      <c r="X149">
-        <v>0</v>
-      </c>
-      <c r="Y149">
-        <v>0</v>
-      </c>
-      <c r="Z149">
-        <v>0</v>
-      </c>
-      <c r="AA149">
-        <v>0</v>
-      </c>
-      <c r="AB149">
-        <v>0</v>
-      </c>
-      <c r="AC149">
-        <v>0</v>
-      </c>
-      <c r="AD149">
-        <v>0</v>
-      </c>
-      <c r="AE149">
-        <v>0</v>
-      </c>
-      <c r="AF149">
-        <v>0</v>
-      </c>
-      <c r="AG149">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ149">
-        <v>0</v>
-      </c>
-      <c r="AK149">
-        <v>0</v>
-      </c>
-      <c r="AL149">
-        <v>0</v>
-      </c>
-      <c r="AM149">
-        <v>-1</v>
-      </c>
-      <c r="AN149">
-        <v>-1</v>
-      </c>
-      <c r="AO149">
-        <v>-1</v>
-      </c>
-      <c r="AP149">
-        <v>-1</v>
-      </c>
-      <c r="AQ149">
-        <v>0</v>
-      </c>
-      <c r="AR149">
-        <v>0</v>
-      </c>
-      <c r="AS149">
-        <v>0</v>
-      </c>
-      <c r="AT149">
-        <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
         <is>
           <t>2026-10-23 23:00:00</t>
         </is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10134,10 +10134,10 @@
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE60">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU148"/>
+  <dimension ref="A1:AU146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,22 +22598,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,22 +23739,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G144">
@@ -23897,27 +23897,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G145">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 22:30:00</t>
         </is>
       </c>
     </row>
@@ -24060,12 +24060,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G146">
@@ -24210,332 +24210,6 @@
         <v>0</v>
       </c>
       <c r="AU146" t="inlineStr">
-        <is>
-          <t>2026-10-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147">
-        <v>0</v>
-      </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>0</v>
-      </c>
-      <c r="R147">
-        <v>0</v>
-      </c>
-      <c r="S147">
-        <v>0</v>
-      </c>
-      <c r="T147">
-        <v>0</v>
-      </c>
-      <c r="U147">
-        <v>0</v>
-      </c>
-      <c r="V147">
-        <v>0</v>
-      </c>
-      <c r="W147">
-        <v>0</v>
-      </c>
-      <c r="X147">
-        <v>0</v>
-      </c>
-      <c r="Y147">
-        <v>0</v>
-      </c>
-      <c r="Z147">
-        <v>0</v>
-      </c>
-      <c r="AA147">
-        <v>0</v>
-      </c>
-      <c r="AB147">
-        <v>0</v>
-      </c>
-      <c r="AC147">
-        <v>0</v>
-      </c>
-      <c r="AD147">
-        <v>0</v>
-      </c>
-      <c r="AE147">
-        <v>0</v>
-      </c>
-      <c r="AF147">
-        <v>0</v>
-      </c>
-      <c r="AG147">
-        <v>0</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>0</v>
-      </c>
-      <c r="AK147">
-        <v>0</v>
-      </c>
-      <c r="AL147">
-        <v>0</v>
-      </c>
-      <c r="AM147">
-        <v>-1</v>
-      </c>
-      <c r="AN147">
-        <v>-1</v>
-      </c>
-      <c r="AO147">
-        <v>-1</v>
-      </c>
-      <c r="AP147">
-        <v>-1</v>
-      </c>
-      <c r="AQ147">
-        <v>0</v>
-      </c>
-      <c r="AR147">
-        <v>0</v>
-      </c>
-      <c r="AS147">
-        <v>0</v>
-      </c>
-      <c r="AT147">
-        <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>2026-10-23 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
-        <v>0</v>
-      </c>
-      <c r="I148">
-        <v>0</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="O148">
-        <v>0</v>
-      </c>
-      <c r="P148">
-        <v>0</v>
-      </c>
-      <c r="Q148">
-        <v>0</v>
-      </c>
-      <c r="R148">
-        <v>0</v>
-      </c>
-      <c r="S148">
-        <v>0</v>
-      </c>
-      <c r="T148">
-        <v>0</v>
-      </c>
-      <c r="U148">
-        <v>0</v>
-      </c>
-      <c r="V148">
-        <v>0</v>
-      </c>
-      <c r="W148">
-        <v>0</v>
-      </c>
-      <c r="X148">
-        <v>0</v>
-      </c>
-      <c r="Y148">
-        <v>0</v>
-      </c>
-      <c r="Z148">
-        <v>0</v>
-      </c>
-      <c r="AA148">
-        <v>0</v>
-      </c>
-      <c r="AB148">
-        <v>0</v>
-      </c>
-      <c r="AC148">
-        <v>0</v>
-      </c>
-      <c r="AD148">
-        <v>0</v>
-      </c>
-      <c r="AE148">
-        <v>0</v>
-      </c>
-      <c r="AF148">
-        <v>0</v>
-      </c>
-      <c r="AG148">
-        <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ148">
-        <v>0</v>
-      </c>
-      <c r="AK148">
-        <v>0</v>
-      </c>
-      <c r="AL148">
-        <v>0</v>
-      </c>
-      <c r="AM148">
-        <v>-1</v>
-      </c>
-      <c r="AN148">
-        <v>-1</v>
-      </c>
-      <c r="AO148">
-        <v>-1</v>
-      </c>
-      <c r="AP148">
-        <v>-1</v>
-      </c>
-      <c r="AQ148">
-        <v>0</v>
-      </c>
-      <c r="AR148">
-        <v>0</v>
-      </c>
-      <c r="AS148">
-        <v>0</v>
-      </c>
-      <c r="AT148">
-        <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
         <is>
           <t>2026-10-23 23:00:00</t>
         </is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G134">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU146"/>
+  <dimension ref="A1:AU143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,49 +9111,49 @@
         </is>
       </c>
       <c r="N54">
+        <v>2.04</v>
+      </c>
+      <c r="O54">
+        <v>3.52</v>
+      </c>
+      <c r="P54">
+        <v>3.28</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
         <v>1.8</v>
       </c>
-      <c r="O54">
-        <v>3.5</v>
-      </c>
-      <c r="P54">
-        <v>4.04</v>
-      </c>
-      <c r="Q54">
-        <v>0</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>0</v>
-      </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54">
-        <v>0</v>
-      </c>
-      <c r="V54">
-        <v>0</v>
-      </c>
-      <c r="W54">
-        <v>0</v>
-      </c>
-      <c r="X54">
-        <v>0</v>
-      </c>
-      <c r="Y54">
-        <v>0</v>
-      </c>
-      <c r="Z54">
-        <v>0</v>
-      </c>
-      <c r="AA54">
-        <v>1.9</v>
-      </c>
       <c r="AB54">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-23 13:30:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.66</v>
+        <v>1.47</v>
       </c>
       <c r="O56">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="P56">
-        <v>2.22</v>
+        <v>5.51</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="AC57">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.87</v>
+        <v>3.12</v>
       </c>
       <c r="O59">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P59">
-        <v>4.62</v>
+        <v>2.03</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>7.85</v>
+        <v>2.66</v>
       </c>
       <c r="O60">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="P60">
-        <v>1.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10134,10 +10134,10 @@
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-23 13:45:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="O63">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="P63">
-        <v>6.69</v>
+        <v>4.62</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10786,10 +10786,10 @@
         <v>0</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-10-23 14:00:00</t>
+          <t>2026-10-23 13:45:00</t>
         </is>
       </c>
     </row>
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P67">
-        <v>4.35</v>
+        <v>6.69</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11672,27 +11672,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="O70">
-        <v>3.36</v>
+        <v>3.45</v>
       </c>
       <c r="P70">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11835,27 +11835,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.09</v>
+        <v>3.39</v>
       </c>
       <c r="O73">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="P73">
-        <v>2.79</v>
+        <v>2.03</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="O74">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="P74">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-10-23 14:45:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="G75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="O76">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="P76">
-        <v>4.32</v>
+        <v>4.58</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.86</v>
+        <v>2.09</v>
       </c>
       <c r="O77">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="P77">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="O78">
-        <v>3.58</v>
+        <v>3.24</v>
       </c>
       <c r="P78">
-        <v>4.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00:00</t>
+          <t>2026-10-23 14:45:00</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="O82">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="P82">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="O84">
-        <v>4.69</v>
+        <v>3.58</v>
       </c>
       <c r="P84">
-        <v>5.62</v>
+        <v>4.28</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,16 +14040,16 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE84">
         <v>0</v>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14698,10 +14698,10 @@
         <v>0</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G93">
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P95">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB95">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -16073,12 +16073,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-10-23 15:30:00</t>
+          <t>2026-10-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="O99">
-        <v>5.27</v>
+        <v>3.35</v>
       </c>
       <c r="P99">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="O104">
-        <v>5.65</v>
+        <v>3.38</v>
       </c>
       <c r="P104">
-        <v>6.98</v>
+        <v>3.53</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17306,10 +17306,10 @@
         <v>0</v>
       </c>
       <c r="AC104">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE104">
         <v>0</v>
@@ -17377,12 +17377,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB106">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17703,27 +17703,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17866,27 +17866,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="O108">
-        <v>3.95</v>
+        <v>5.65</v>
       </c>
       <c r="P108">
-        <v>4.61</v>
+        <v>6.98</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-10-23 15:45:00</t>
+          <t>2026-10-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="O110">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="P110">
-        <v>4.18</v>
+        <v>3.43</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="O111">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="P111">
-        <v>3.64</v>
+        <v>1.84</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB111">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.48</v>
+        <v>1.67</v>
       </c>
       <c r="O112">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="P112">
-        <v>2.76</v>
+        <v>4.61</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB112">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18681,27 +18681,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="O113">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="P113">
-        <v>2.55</v>
+        <v>3.16</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB113">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18844,7 +18844,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="O114">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="P114">
-        <v>10.8</v>
+        <v>4.18</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>4.12</v>
+        <v>2.48</v>
       </c>
       <c r="O116">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="P116">
-        <v>1.71</v>
+        <v>2.76</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-10-23 16:00:00</t>
+          <t>2026-10-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>0</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-23 16:30:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="O118">
-        <v>3.71</v>
+        <v>6.2</v>
       </c>
       <c r="P118">
-        <v>4.9</v>
+        <v>10.8</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-23 16:45:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-23 17:30:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-23 19:30:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,27 +20148,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="O122">
-        <v>5.37</v>
+        <v>3.71</v>
       </c>
       <c r="P122">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 16:45:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:00</t>
+          <t>2026-10-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -20474,27 +20474,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 19:30:00</t>
         </is>
       </c>
     </row>
@@ -20637,27 +20637,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20800,27 +20800,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20963,27 +20963,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G127">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,22 +21783,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,22 +23250,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G141">
@@ -23408,27 +23408,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G142">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-10-23 21:00:00</t>
+          <t>2026-10-23 22:30:00</t>
         </is>
       </c>
     </row>
@@ -23571,27 +23571,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G143">
@@ -23721,495 +23721,6 @@
         <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
-        <is>
-          <t>2026-10-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-      <c r="H144">
-        <v>0</v>
-      </c>
-      <c r="I144">
-        <v>0</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>0</v>
-      </c>
-      <c r="R144">
-        <v>0</v>
-      </c>
-      <c r="S144">
-        <v>0</v>
-      </c>
-      <c r="T144">
-        <v>0</v>
-      </c>
-      <c r="U144">
-        <v>0</v>
-      </c>
-      <c r="V144">
-        <v>0</v>
-      </c>
-      <c r="W144">
-        <v>0</v>
-      </c>
-      <c r="X144">
-        <v>0</v>
-      </c>
-      <c r="Y144">
-        <v>0</v>
-      </c>
-      <c r="Z144">
-        <v>0</v>
-      </c>
-      <c r="AA144">
-        <v>0</v>
-      </c>
-      <c r="AB144">
-        <v>0</v>
-      </c>
-      <c r="AC144">
-        <v>0</v>
-      </c>
-      <c r="AD144">
-        <v>0</v>
-      </c>
-      <c r="AE144">
-        <v>0</v>
-      </c>
-      <c r="AF144">
-        <v>0</v>
-      </c>
-      <c r="AG144">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>0</v>
-      </c>
-      <c r="AK144">
-        <v>0</v>
-      </c>
-      <c r="AL144">
-        <v>0</v>
-      </c>
-      <c r="AM144">
-        <v>-1</v>
-      </c>
-      <c r="AN144">
-        <v>-1</v>
-      </c>
-      <c r="AO144">
-        <v>-1</v>
-      </c>
-      <c r="AP144">
-        <v>-1</v>
-      </c>
-      <c r="AQ144">
-        <v>0</v>
-      </c>
-      <c r="AR144">
-        <v>0</v>
-      </c>
-      <c r="AS144">
-        <v>0</v>
-      </c>
-      <c r="AT144">
-        <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>2026-10-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145">
-        <v>0</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
-      </c>
-      <c r="J145">
-        <v>0</v>
-      </c>
-      <c r="K145">
-        <v>0</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>0</v>
-      </c>
-      <c r="R145">
-        <v>0</v>
-      </c>
-      <c r="S145">
-        <v>0</v>
-      </c>
-      <c r="T145">
-        <v>0</v>
-      </c>
-      <c r="U145">
-        <v>0</v>
-      </c>
-      <c r="V145">
-        <v>0</v>
-      </c>
-      <c r="W145">
-        <v>0</v>
-      </c>
-      <c r="X145">
-        <v>0</v>
-      </c>
-      <c r="Y145">
-        <v>0</v>
-      </c>
-      <c r="Z145">
-        <v>0</v>
-      </c>
-      <c r="AA145">
-        <v>0</v>
-      </c>
-      <c r="AB145">
-        <v>0</v>
-      </c>
-      <c r="AC145">
-        <v>0</v>
-      </c>
-      <c r="AD145">
-        <v>0</v>
-      </c>
-      <c r="AE145">
-        <v>0</v>
-      </c>
-      <c r="AF145">
-        <v>0</v>
-      </c>
-      <c r="AG145">
-        <v>0</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ145">
-        <v>0</v>
-      </c>
-      <c r="AK145">
-        <v>0</v>
-      </c>
-      <c r="AL145">
-        <v>0</v>
-      </c>
-      <c r="AM145">
-        <v>-1</v>
-      </c>
-      <c r="AN145">
-        <v>-1</v>
-      </c>
-      <c r="AO145">
-        <v>-1</v>
-      </c>
-      <c r="AP145">
-        <v>-1</v>
-      </c>
-      <c r="AQ145">
-        <v>0</v>
-      </c>
-      <c r="AR145">
-        <v>0</v>
-      </c>
-      <c r="AS145">
-        <v>0</v>
-      </c>
-      <c r="AT145">
-        <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>2026-10-23 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="I146">
-        <v>0</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>0</v>
-      </c>
-      <c r="R146">
-        <v>0</v>
-      </c>
-      <c r="S146">
-        <v>0</v>
-      </c>
-      <c r="T146">
-        <v>0</v>
-      </c>
-      <c r="U146">
-        <v>0</v>
-      </c>
-      <c r="V146">
-        <v>0</v>
-      </c>
-      <c r="W146">
-        <v>0</v>
-      </c>
-      <c r="X146">
-        <v>0</v>
-      </c>
-      <c r="Y146">
-        <v>0</v>
-      </c>
-      <c r="Z146">
-        <v>0</v>
-      </c>
-      <c r="AA146">
-        <v>0</v>
-      </c>
-      <c r="AB146">
-        <v>0</v>
-      </c>
-      <c r="AC146">
-        <v>0</v>
-      </c>
-      <c r="AD146">
-        <v>0</v>
-      </c>
-      <c r="AE146">
-        <v>0</v>
-      </c>
-      <c r="AF146">
-        <v>0</v>
-      </c>
-      <c r="AG146">
-        <v>0</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>0</v>
-      </c>
-      <c r="AK146">
-        <v>0</v>
-      </c>
-      <c r="AL146">
-        <v>0</v>
-      </c>
-      <c r="AM146">
-        <v>-1</v>
-      </c>
-      <c r="AN146">
-        <v>-1</v>
-      </c>
-      <c r="AO146">
-        <v>-1</v>
-      </c>
-      <c r="AP146">
-        <v>-1</v>
-      </c>
-      <c r="AQ146">
-        <v>0</v>
-      </c>
-      <c r="AR146">
-        <v>0</v>
-      </c>
-      <c r="AS146">
-        <v>0</v>
-      </c>
-      <c r="AT146">
-        <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
         <is>
           <t>2026-10-23 23:00:00</t>
         </is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q57">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G19">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G97">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G45">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G97">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20560,10 +20560,10 @@
         <v>0</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC124">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="AA141">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC141">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q143">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -644,34 +644,34 @@
         <v>3.32</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA2">
         <v>1.8</v>
@@ -680,19 +680,19 @@
         <v>2</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1622,16 +1622,16 @@
         <v>4.3</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1667,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,22 +1785,22 @@
         <v>3.21</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1809,16 +1809,16 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1830,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4230,22 +4230,22 @@
         <v>2.1</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W24">
         <v>0</v>
@@ -4254,16 +4254,16 @@
         <v>0</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4275,10 +4275,10 @@
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>3.85</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>4.11</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>2.97</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>3.31</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O48">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O49">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -9120,34 +9120,34 @@
         <v>3.28</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA54">
         <v>1.8</v>
@@ -9156,19 +9156,19 @@
         <v>2</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>5.51</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9772,34 +9772,34 @@
         <v>4.04</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA58">
         <v>1.9</v>
@@ -9808,19 +9808,19 @@
         <v>1.85</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>2.22</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,40 +10261,40 @@
         <v>2.12</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC61">
         <v>2.2</v>
@@ -10303,13 +10303,13 @@
         <v>1.57</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>4.62</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,40 +10750,40 @@
         <v>1.26</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AC64">
         <v>1.88</v>
@@ -10792,13 +10792,13 @@
         <v>1.87</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12217,10 +12217,10 @@
         <v>2.03</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -12229,10 +12229,10 @@
         <v>0</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W73">
         <v>0</v>
@@ -12241,31 +12241,31 @@
         <v>0</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,34 +12380,34 @@
         <v>2.78</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AA74">
         <v>1.93</v>
@@ -12416,19 +12416,19 @@
         <v>1.88</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.55</v>
+        <v>2.09</v>
       </c>
       <c r="O76">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="P76">
-        <v>4.58</v>
+        <v>2.79</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.09</v>
+        <v>1.55</v>
       </c>
       <c r="O77">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="P77">
-        <v>2.79</v>
+        <v>4.58</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,55 +13032,55 @@
         <v>2.5</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -14499,55 +14499,55 @@
         <v>2.22</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,40 +14662,40 @@
         <v>5.62</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC88">
         <v>2</v>
@@ -14704,13 +14704,13 @@
         <v>1.8</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16292,55 +16292,55 @@
         <v>10.8</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16455,34 +16455,34 @@
         <v>2.95</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AA99">
         <v>1.93</v>
@@ -16491,19 +16491,19 @@
         <v>1.77</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>3.53</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17922,40 +17922,40 @@
         <v>6.98</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC108">
         <v>1.78</v>
@@ -17964,13 +17964,13 @@
         <v>1.93</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -19063,34 +19063,34 @@
         <v>3.64</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA115">
         <v>2.05</v>
@@ -19099,19 +19099,19 @@
         <v>1.8</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19226,34 +19226,34 @@
         <v>2.76</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA116">
         <v>1.73</v>
@@ -19262,19 +19262,19 @@
         <v>1.98</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19878,55 +19878,55 @@
         <v>1.71</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20204,55 +20204,55 @@
         <v>4.9</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20530,34 +20530,34 @@
         <v>4</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA124">
         <v>1.98</v>
@@ -20566,19 +20566,19 @@
         <v>1.72</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G140">
@@ -23301,34 +23301,34 @@
         <v>3.11</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S141">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T141">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U141">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V141">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W141">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X141">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y141">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z141">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA141">
         <v>2.1</v>
@@ -23337,19 +23337,19 @@
         <v>1.65</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD141">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE141">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF141">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG141">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK141">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q142">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -7979,55 +7979,55 @@
         <v>3.16</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.8</v>
+        <v>3.12</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>4.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q58">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U58">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V58">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z58">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA58">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC58">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG58">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK58">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.12</v>
+        <v>1.8</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P59">
-        <v>2.03</v>
+        <v>4.04</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>6.69</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11728,55 +11728,55 @@
         <v>2.95</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,55 +11891,55 @@
         <v>4.35</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.73</v>
+        <v>2.86</v>
       </c>
       <c r="O80">
-        <v>3.84</v>
+        <v>3.34</v>
       </c>
       <c r="P80">
-        <v>4.32</v>
+        <v>2.37</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.86</v>
+        <v>2.35</v>
       </c>
       <c r="O81">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="P81">
-        <v>2.37</v>
+        <v>3.02</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.73</v>
+        <v>1.8</v>
       </c>
       <c r="O82">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P82">
-        <v>2.35</v>
+        <v>4.28</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA82">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AB82">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="O83">
-        <v>3.15</v>
+        <v>3.84</v>
       </c>
       <c r="P83">
-        <v>3.02</v>
+        <v>4.32</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.8</v>
+        <v>2.73</v>
       </c>
       <c r="O84">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P84">
-        <v>4.28</v>
+        <v>2.35</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA84">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB84">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>2.04</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G102">
@@ -17433,55 +17433,55 @@
         <v>2.64</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18248,34 +18248,34 @@
         <v>3.43</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA110">
         <v>1.83</v>
@@ -18284,19 +18284,19 @@
         <v>1.98</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18574,55 +18574,55 @@
         <v>4.61</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19389,34 +19389,34 @@
         <v>2.55</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA117">
         <v>1.85</v>
@@ -19425,19 +19425,19 @@
         <v>1.85</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19552,55 +19552,55 @@
         <v>10.8</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X118">
         <v>0</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20856,55 +20856,55 @@
         <v>8.6</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21834,55 +21834,55 @@
         <v>1.62</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -23464,55 +23464,55 @@
         <v>2.51</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23627,55 +23627,55 @@
         <v>2.2</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL143">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G104">

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="O5">
         <v>4.5</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.27</v>
+        <v>3.12</v>
       </c>
       <c r="O58">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>2.77</v>
+        <v>2.03</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.12</v>
+        <v>1.47</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P59">
-        <v>2.03</v>
+        <v>5.51</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="O61">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="P61">
-        <v>5.51</v>
+        <v>1.67</v>
       </c>
       <c r="Q61">
-        <v>1.85</v>
+        <v>5.54</v>
       </c>
       <c r="R61">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="S61">
         <v>1.22</v>
       </c>
       <c r="T61">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U61">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB61">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="AC61">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AD61">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE61">
         <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>2.5</v>
+        <v>1.15</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12549,10 +12549,10 @@
         <v>2.3</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U75">
         <v>2.49</v>
@@ -12561,10 +12561,10 @@
         <v>1.52</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
         <v>1.21</v>
@@ -13847,55 +13847,55 @@
         <v>3.02</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>2.55</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>3.75</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15640,55 +15640,55 @@
         <v>2.72</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="O95">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="P95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O96">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P96">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="O97">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P97">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="Q97">
-        <v>2.16</v>
+        <v>2.69</v>
       </c>
       <c r="R97">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="S97">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T97">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U97">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="V97">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="W97">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z97">
-        <v>6.15</v>
+        <v>4.75</v>
       </c>
       <c r="AA97">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AB97">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AC97">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD97">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AE97">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AF97">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG97">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK97">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="O98">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="P98">
-        <v>2.58</v>
+        <v>5</v>
       </c>
       <c r="Q98">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="R98">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="S98">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T98">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="U98">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="V98">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="W98">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X98">
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z98">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA98">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AB98">
-        <v>2.31</v>
+        <v>2.87</v>
       </c>
       <c r="AC98">
-        <v>2.33</v>
+        <v>1.92</v>
       </c>
       <c r="AD98">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AE98">
+        <v>1.3</v>
+      </c>
+      <c r="AF98">
+        <v>1.4</v>
+      </c>
+      <c r="AG98">
+        <v>2.73</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
         <v>1.16</v>
       </c>
-      <c r="AF98">
-        <v>1.44</v>
-      </c>
-      <c r="AG98">
-        <v>2.5</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.3</v>
-      </c>
       <c r="AK98">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="O99">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P99">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q99">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="R99">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S99">
         <v>1.22</v>
       </c>
       <c r="T99">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U99">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V99">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W99">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X99">
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z99">
-        <v>4.75</v>
+        <v>5.95</v>
       </c>
       <c r="AA99">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB99">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AC99">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AD99">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AE99">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF99">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG99">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -5521,7 +5521,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N32">
@@ -6032,10 +6032,10 @@
         <v>1.2</v>
       </c>
       <c r="T35">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="U35">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="V35">
         <v>1.67</v>
@@ -6047,16 +6047,16 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>5.55</v>
+        <v>6.26</v>
       </c>
       <c r="AA35">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB35">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AC35">
         <v>1.96</v>
@@ -6065,7 +6065,7 @@
         <v>1.76</v>
       </c>
       <c r="AE35">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF35">
         <v>1.4</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6503,25 +6503,25 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O38">
         <v>3.4</v>
       </c>
       <c r="P38">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q38">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S38">
         <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U38">
         <v>2.8</v>
@@ -6536,22 +6536,22 @@
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z38">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA38">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB38">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC38">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD38">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
         <v>1.05</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7327,25 +7327,25 @@
         <v>3.05</v>
       </c>
       <c r="Q43">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R43">
         <v>2.31</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
         <v>3.75</v>
       </c>
       <c r="U43">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V43">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7354,19 +7354,19 @@
         <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="AA43">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB43">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="AC43">
         <v>2.33</v>
       </c>
       <c r="AD43">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE43">
         <v>1.2</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9612,16 +9612,16 @@
         <v>2.63</v>
       </c>
       <c r="R57">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="S57">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T57">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U57">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="V57">
         <v>1.44</v>
@@ -9633,7 +9633,7 @@
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z57">
         <v>3.77</v>
@@ -9642,7 +9642,7 @@
         <v>1.8</v>
       </c>
       <c r="AB57">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC57">
         <v>2.95</v>
@@ -9654,10 +9654,10 @@
         <v>1.09</v>
       </c>
       <c r="AF57">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG57">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="O63">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q63">
-        <v>3.53</v>
+        <v>3.46</v>
       </c>
       <c r="R63">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="U63">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="V63">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z63">
-        <v>4.48</v>
+        <v>5.25</v>
       </c>
       <c r="AA63">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AB63">
-        <v>2.17</v>
+        <v>2.59</v>
       </c>
       <c r="AC63">
         <v>2.2</v>
       </c>
       <c r="AD63">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE63">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF63">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P64">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q64">
-        <v>3.46</v>
+        <v>3.53</v>
       </c>
       <c r="R64">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="S64">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="U64">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="V64">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W64">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z64">
-        <v>5.25</v>
+        <v>4.48</v>
       </c>
       <c r="AA64">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AB64">
-        <v>2.59</v>
+        <v>2.17</v>
       </c>
       <c r="AC64">
         <v>2.2</v>
       </c>
       <c r="AD64">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE64">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -11239,46 +11239,46 @@
         <v>1.26</v>
       </c>
       <c r="Q67">
-        <v>6.43</v>
+        <v>6.72</v>
       </c>
       <c r="R67">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T67">
         <v>4</v>
       </c>
       <c r="U67">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="V67">
         <v>1.7</v>
       </c>
       <c r="W67">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z67">
-        <v>5.58</v>
+        <v>5.71</v>
       </c>
       <c r="AA67">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB67">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AC67">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AD67">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AE67">
         <v>1.26</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK67">
         <v>1.04</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="O83">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P83">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q83">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S83">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T83">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U83">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="V83">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W83">
         <v>1.08</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z83">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AA83">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB83">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC83">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="AD83">
         <v>1.3</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF83">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG83">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK83">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O84">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="Q84">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R84">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="S84">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T84">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U84">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V84">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W84">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X84">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z84">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AA84">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB84">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AC84">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AD84">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE84">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF84">
         <v>1.85</v>
       </c>
       <c r="AG84">
+        <v>1.83</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
+        <v>1.28</v>
+      </c>
+      <c r="AK84">
         <v>1.94</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.3</v>
-      </c>
-      <c r="AK84">
-        <v>1.95</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.73</v>
+        <v>2.34</v>
       </c>
       <c r="O85">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="P85">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="Q85">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="R85">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S85">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T85">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U85">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="V85">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W85">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Z85">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="AA85">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB85">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC85">
-        <v>2.52</v>
+        <v>3.83</v>
       </c>
       <c r="AD85">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE85">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
+        <v>1.8</v>
+      </c>
+      <c r="AG85">
+        <v>1.91</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <v>1.36</v>
+      </c>
+      <c r="AK85">
         <v>1.57</v>
-      </c>
-      <c r="AG85">
-        <v>2.25</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.3</v>
-      </c>
-      <c r="AK85">
-        <v>1.4</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,31 +14327,31 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O86">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P86">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="Q86">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="R86">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S86">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T86">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="U86">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="V86">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W86">
         <v>1.1</v>
@@ -14360,31 +14360,31 @@
         <v>1</v>
       </c>
       <c r="Y86">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z86">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="AA86">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB86">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC86">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="AD86">
         <v>1.36</v>
       </c>
       <c r="AE86">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF86">
         <v>1.7</v>
       </c>
       <c r="AG86">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,65 +14490,65 @@
         </is>
       </c>
       <c r="N87">
+        <v>2.62</v>
+      </c>
+      <c r="O87">
+        <v>3.4</v>
+      </c>
+      <c r="P87">
+        <v>2.3</v>
+      </c>
+      <c r="Q87">
+        <v>3.02</v>
+      </c>
+      <c r="R87">
+        <v>2.14</v>
+      </c>
+      <c r="S87">
+        <v>1.34</v>
+      </c>
+      <c r="T87">
+        <v>3.25</v>
+      </c>
+      <c r="U87">
+        <v>2.36</v>
+      </c>
+      <c r="V87">
+        <v>1.5</v>
+      </c>
+      <c r="W87">
+        <v>1.08</v>
+      </c>
+      <c r="X87">
+        <v>1.01</v>
+      </c>
+      <c r="Y87">
+        <v>1.21</v>
+      </c>
+      <c r="Z87">
+        <v>4.1</v>
+      </c>
+      <c r="AA87">
+        <v>1.67</v>
+      </c>
+      <c r="AB87">
+        <v>2.04</v>
+      </c>
+      <c r="AC87">
+        <v>2.83</v>
+      </c>
+      <c r="AD87">
+        <v>1.42</v>
+      </c>
+      <c r="AE87">
+        <v>1.16</v>
+      </c>
+      <c r="AF87">
+        <v>1.53</v>
+      </c>
+      <c r="AG87">
         <v>2.35</v>
       </c>
-      <c r="O87">
-        <v>3.15</v>
-      </c>
-      <c r="P87">
-        <v>3.02</v>
-      </c>
-      <c r="Q87">
-        <v>2.88</v>
-      </c>
-      <c r="R87">
-        <v>2</v>
-      </c>
-      <c r="S87">
-        <v>1.4</v>
-      </c>
-      <c r="T87">
-        <v>2.75</v>
-      </c>
-      <c r="U87">
-        <v>2.9</v>
-      </c>
-      <c r="V87">
-        <v>1.33</v>
-      </c>
-      <c r="W87">
-        <v>1.06</v>
-      </c>
-      <c r="X87">
-        <v>1.02</v>
-      </c>
-      <c r="Y87">
-        <v>1.35</v>
-      </c>
-      <c r="Z87">
-        <v>3.12</v>
-      </c>
-      <c r="AA87">
-        <v>2.15</v>
-      </c>
-      <c r="AB87">
-        <v>1.7</v>
-      </c>
-      <c r="AC87">
-        <v>3.83</v>
-      </c>
-      <c r="AD87">
-        <v>1.25</v>
-      </c>
-      <c r="AE87">
-        <v>1.06</v>
-      </c>
-      <c r="AF87">
-        <v>1.8</v>
-      </c>
-      <c r="AG87">
-        <v>1.91</v>
-      </c>
       <c r="AH87" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK87">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="O90">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P90">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="Q90">
-        <v>3.66</v>
+        <v>3.07</v>
       </c>
       <c r="R90">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="S90">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T90">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="U90">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="V90">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z90">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="AA90">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AB90">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AC90">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="AD90">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AE90">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AG90">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AK90">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,58 +15142,58 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="O91">
-        <v>4.69</v>
+        <v>4.5</v>
       </c>
       <c r="P91">
-        <v>5.62</v>
+        <v>4.45</v>
       </c>
       <c r="Q91">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="R91">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="S91">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T91">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="U91">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="V91">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W91">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>6.15</v>
+        <v>6.04</v>
       </c>
       <c r="AA91">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB91">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AC91">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AD91">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE91">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AF91">
         <v>1.44</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK91">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.43</v>
+        <v>1.6</v>
       </c>
       <c r="O92">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="P92">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="Q92">
-        <v>2.73</v>
+        <v>2.07</v>
       </c>
       <c r="R92">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S92">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T92">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="U92">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="V92">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="W92">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z92">
-        <v>5.8</v>
+        <v>6.45</v>
       </c>
       <c r="AA92">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AB92">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="AC92">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AD92">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AE92">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF92">
         <v>1.4</v>
       </c>
       <c r="AG92">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>1.22</v>
       </c>
       <c r="AK92">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O93">
-        <v>4.35</v>
+        <v>3.65</v>
       </c>
       <c r="P93">
-        <v>4.5</v>
+        <v>2.72</v>
       </c>
       <c r="Q93">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
       <c r="R93">
+        <v>2.41</v>
+      </c>
+      <c r="S93">
+        <v>1.2</v>
+      </c>
+      <c r="T93">
+        <v>3.74</v>
+      </c>
+      <c r="U93">
+        <v>2.1</v>
+      </c>
+      <c r="V93">
+        <v>1.67</v>
+      </c>
+      <c r="W93">
+        <v>1.18</v>
+      </c>
+      <c r="X93">
+        <v>1.02</v>
+      </c>
+      <c r="Y93">
+        <v>1.09</v>
+      </c>
+      <c r="Z93">
+        <v>5.3</v>
+      </c>
+      <c r="AA93">
+        <v>1.47</v>
+      </c>
+      <c r="AB93">
         <v>2.6</v>
       </c>
-      <c r="S93">
-        <v>1.16</v>
-      </c>
-      <c r="T93">
-        <v>4.33</v>
-      </c>
-      <c r="U93">
-        <v>1.91</v>
-      </c>
-      <c r="V93">
-        <v>1.79</v>
-      </c>
-      <c r="W93">
-        <v>1.19</v>
-      </c>
-      <c r="X93">
-        <v>1.01</v>
-      </c>
-      <c r="Y93">
-        <v>1.05</v>
-      </c>
-      <c r="Z93">
-        <v>6.45</v>
-      </c>
-      <c r="AA93">
-        <v>1.3</v>
-      </c>
-      <c r="AB93">
-        <v>2.97</v>
-      </c>
       <c r="AC93">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AD93">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AE93">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF93">
         <v>1.4</v>
       </c>
       <c r="AG93">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O94">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P94">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="Q94">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="R94">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="S94">
         <v>1.2</v>
       </c>
       <c r="T94">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="U94">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="V94">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W94">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z94">
-        <v>5.3</v>
+        <v>6.15</v>
       </c>
       <c r="AA94">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AB94">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AC94">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AD94">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AE94">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AF94">
         <v>1.4</v>
       </c>
       <c r="AG94">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK94">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="O95">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P95">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="Q95">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="R95">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="S95">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="U95">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="V95">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="W95">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z95">
-        <v>6.15</v>
+        <v>4.7</v>
       </c>
       <c r="AA95">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AB95">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="AC95">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="AD95">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AE95">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AF95">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG95">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
+        <v>2.22</v>
+      </c>
+      <c r="O96">
+        <v>3.6</v>
+      </c>
+      <c r="P96">
+        <v>2.7</v>
+      </c>
+      <c r="Q96">
+        <v>2.69</v>
+      </c>
+      <c r="R96">
         <v>2.3</v>
       </c>
-      <c r="O96">
-        <v>3.65</v>
-      </c>
-      <c r="P96">
-        <v>2.58</v>
-      </c>
-      <c r="Q96">
-        <v>2.75</v>
-      </c>
-      <c r="R96">
-        <v>2.4</v>
-      </c>
       <c r="S96">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T96">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U96">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V96">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W96">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
         <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA96">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AB96">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC96">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD96">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AE96">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF96">
         <v>1.44</v>
       </c>
       <c r="AG96">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK96">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,19 +16120,19 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="O97">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P97">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q97">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="R97">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S97">
         <v>1.22</v>
@@ -16141,43 +16141,43 @@
         <v>3.8</v>
       </c>
       <c r="U97">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V97">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W97">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z97">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA97">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB97">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC97">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD97">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AE97">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF97">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG97">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK97">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="O99">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P99">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q99">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="R99">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S99">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T99">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="U99">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V99">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="W99">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z99">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA99">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AB99">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC99">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="AD99">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AE99">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AF99">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG99">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>1.22</v>
       </c>
       <c r="AK99">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O107">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P107">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="Q107">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="R107">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S107">
         <v>1.4</v>
       </c>
       <c r="T107">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="U107">
         <v>3</v>
       </c>
       <c r="V107">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z107">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="AA107">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AB107">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC107">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD107">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE107">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF107">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG107">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="O111">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="P111">
-        <v>6.98</v>
+        <v>6.1</v>
       </c>
       <c r="Q111">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R111">
-        <v>3.16</v>
+        <v>2.74</v>
       </c>
       <c r="S111">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T111">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="U111">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="V111">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="W111">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z111">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AA111">
         <v>1.28</v>
       </c>
       <c r="AB111">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AC111">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AD111">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AE111">
         <v>1.46</v>
       </c>
       <c r="AF111">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG111">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK111">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18728,22 +18728,22 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O113">
-        <v>3.74</v>
+        <v>3.36</v>
       </c>
       <c r="P113">
-        <v>3.43</v>
+        <v>2.77</v>
       </c>
       <c r="Q113">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="R113">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S113">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T113">
         <v>3.3</v>
@@ -18752,40 +18752,40 @@
         <v>2.4</v>
       </c>
       <c r="V113">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W113">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z113">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA113">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AB113">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="AC113">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="AD113">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE113">
         <v>1.13</v>
       </c>
       <c r="AF113">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG113">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK113">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
+        <v>1.73</v>
+      </c>
+      <c r="O114">
         <v>3.9</v>
       </c>
-      <c r="O114">
-        <v>3.65</v>
-      </c>
       <c r="P114">
-        <v>1.84</v>
+        <v>4.18</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="O115">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="P115">
-        <v>3.16</v>
+        <v>5</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
+        <v>3.9</v>
+      </c>
+      <c r="O116">
+        <v>3.65</v>
+      </c>
+      <c r="P116">
+        <v>1.84</v>
+      </c>
+      <c r="Q116">
+        <v>5.45</v>
+      </c>
+      <c r="R116">
+        <v>2.31</v>
+      </c>
+      <c r="S116">
+        <v>1.27</v>
+      </c>
+      <c r="T116">
+        <v>3.32</v>
+      </c>
+      <c r="U116">
+        <v>2.38</v>
+      </c>
+      <c r="V116">
+        <v>1.5</v>
+      </c>
+      <c r="W116">
+        <v>1.09</v>
+      </c>
+      <c r="X116">
+        <v>1.02</v>
+      </c>
+      <c r="Y116">
+        <v>1.17</v>
+      </c>
+      <c r="Z116">
+        <v>4</v>
+      </c>
+      <c r="AA116">
+        <v>1.69</v>
+      </c>
+      <c r="AB116">
+        <v>2.09</v>
+      </c>
+      <c r="AC116">
+        <v>2.66</v>
+      </c>
+      <c r="AD116">
+        <v>1.37</v>
+      </c>
+      <c r="AE116">
+        <v>1.11</v>
+      </c>
+      <c r="AF116">
         <v>1.73</v>
       </c>
-      <c r="O116">
-        <v>3.9</v>
-      </c>
-      <c r="P116">
-        <v>4.18</v>
-      </c>
-      <c r="Q116">
-        <v>0</v>
-      </c>
-      <c r="R116">
-        <v>0</v>
-      </c>
-      <c r="S116">
-        <v>0</v>
-      </c>
-      <c r="T116">
-        <v>0</v>
-      </c>
-      <c r="U116">
-        <v>0</v>
-      </c>
-      <c r="V116">
-        <v>0</v>
-      </c>
-      <c r="W116">
-        <v>0</v>
-      </c>
-      <c r="X116">
-        <v>0</v>
-      </c>
-      <c r="Y116">
-        <v>0</v>
-      </c>
-      <c r="Z116">
-        <v>0</v>
-      </c>
-      <c r="AA116">
-        <v>0</v>
-      </c>
-      <c r="AB116">
-        <v>0</v>
-      </c>
-      <c r="AC116">
-        <v>0</v>
-      </c>
-      <c r="AD116">
-        <v>0</v>
-      </c>
-      <c r="AE116">
-        <v>0</v>
-      </c>
-      <c r="AF116">
-        <v>0</v>
-      </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="O117">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="P117">
-        <v>4.61</v>
+        <v>3.16</v>
       </c>
       <c r="Q117">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S117">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T117">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U117">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V117">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W117">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
         <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z117">
-        <v>3.92</v>
+        <v>4.37</v>
       </c>
       <c r="AA117">
         <v>1.68</v>
       </c>
       <c r="AB117">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AC117">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AD117">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE117">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF117">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG117">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK117">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,46 +19543,46 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O118">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="P118">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="Q118">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R118">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="S118">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T118">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="U118">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="V118">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W118">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
         <v>1.3</v>
       </c>
       <c r="Z118">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AA118">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB118">
         <v>1.8</v>
@@ -19591,16 +19591,16 @@
         <v>3.44</v>
       </c>
       <c r="AD118">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE118">
         <v>1.05</v>
       </c>
       <c r="AF118">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG118">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK118">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19715,40 +19715,40 @@
         <v>2.76</v>
       </c>
       <c r="Q119">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="R119">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S119">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T119">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U119">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V119">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W119">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X119">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y119">
         <v>1.18</v>
       </c>
       <c r="Z119">
-        <v>3.82</v>
+        <v>4.03</v>
       </c>
       <c r="AA119">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB119">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AC119">
         <v>2.7</v>
@@ -19760,10 +19760,10 @@
         <v>1.1</v>
       </c>
       <c r="AF119">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG119">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK119">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,52 +19869,52 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O120">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P120">
+        <v>2.15</v>
+      </c>
+      <c r="Q120">
+        <v>3.4</v>
+      </c>
+      <c r="R120">
+        <v>2.25</v>
+      </c>
+      <c r="S120">
+        <v>1.29</v>
+      </c>
+      <c r="T120">
+        <v>3.3</v>
+      </c>
+      <c r="U120">
         <v>2.55</v>
       </c>
-      <c r="Q120">
-        <v>3.67</v>
-      </c>
-      <c r="R120">
-        <v>2.39</v>
-      </c>
-      <c r="S120">
-        <v>1.3</v>
-      </c>
-      <c r="T120">
-        <v>3.25</v>
-      </c>
-      <c r="U120">
-        <v>2.61</v>
-      </c>
       <c r="V120">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W120">
         <v>1.08</v>
       </c>
       <c r="X120">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z120">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA120">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB120">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC120">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="AD120">
         <v>1.45</v>
@@ -19926,7 +19926,7 @@
         <v>1.57</v>
       </c>
       <c r="AG120">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20032,31 +20032,31 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="O121">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="P121">
-        <v>10.8</v>
+        <v>12</v>
       </c>
       <c r="Q121">
         <v>1.5</v>
       </c>
       <c r="R121">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="S121">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T121">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="U121">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="V121">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W121">
         <v>1.18</v>
@@ -20068,28 +20068,28 @@
         <v>1.08</v>
       </c>
       <c r="Z121">
-        <v>5.72</v>
+        <v>5.7</v>
       </c>
       <c r="AA121">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AB121">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="AC121">
         <v>2.08</v>
       </c>
       <c r="AD121">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AE121">
         <v>1.29</v>
       </c>
       <c r="AF121">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG121">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20195,31 +20195,31 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O122">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P122">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="Q122">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R122">
         <v>2.1</v>
       </c>
       <c r="S122">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T122">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U122">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V122">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W122">
         <v>1.05</v>
@@ -20228,31 +20228,31 @@
         <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z122">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA122">
         <v>2.1</v>
       </c>
       <c r="AB122">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC122">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD122">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE122">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF122">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG122">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK122">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20684,22 +20684,22 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="O125">
-        <v>3.71</v>
+        <v>4.12</v>
       </c>
       <c r="P125">
-        <v>4.9</v>
+        <v>5.75</v>
       </c>
       <c r="Q125">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R125">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S125">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T125">
         <v>3</v>
@@ -20711,10 +20711,10 @@
         <v>1.42</v>
       </c>
       <c r="W125">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X125">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y125">
         <v>1.24</v>
@@ -20723,10 +20723,10 @@
         <v>3.34</v>
       </c>
       <c r="AA125">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AB125">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AC125">
         <v>2.92</v>
@@ -20735,13 +20735,13 @@
         <v>1.31</v>
       </c>
       <c r="AE125">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF125">
         <v>1.95</v>
       </c>
       <c r="AG125">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK125">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="AL125">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O5">
         <v>4.94</v>
       </c>
       <c r="P5">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -6355,7 +6355,7 @@
         <v>2.01</v>
       </c>
       <c r="S37">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T37">
         <v>2.67</v>
@@ -6397,7 +6397,7 @@
         <v>1.95</v>
       </c>
       <c r="AG37">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -8471,22 +8471,22 @@
         <v>2.5</v>
       </c>
       <c r="R50">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="U50">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="V50">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
         <v>1.04</v>
@@ -8498,16 +8498,16 @@
         <v>3.8</v>
       </c>
       <c r="AA50">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB50">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC50">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE50">
         <v>1.15</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="O58">
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -10092,16 +10092,16 @@
         <v>1.8</v>
       </c>
       <c r="O60">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P60">
-        <v>4.04</v>
+        <v>3.7</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
       </c>
       <c r="R60">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
         <v>1.35</v>
@@ -10110,13 +10110,13 @@
         <v>3</v>
       </c>
       <c r="U60">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V60">
         <v>1.4</v>
       </c>
       <c r="W60">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X60">
         <v>1.01</v>
@@ -10128,10 +10128,10 @@
         <v>3.28</v>
       </c>
       <c r="AA60">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB60">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC60">
         <v>3.04</v>
@@ -10146,7 +10146,7 @@
         <v>1.75</v>
       </c>
       <c r="AG60">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
         <v>1.91</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O61">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P61">
-        <v>5.51</v>
+        <v>4.8</v>
       </c>
       <c r="Q61">
         <v>1.85</v>
@@ -10279,7 +10279,7 @@
         <v>1.67</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
+        <v>4.8</v>
+      </c>
+      <c r="O62">
         <v>4.2</v>
       </c>
-      <c r="O62">
-        <v>3.8</v>
-      </c>
       <c r="P62">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="Q62">
-        <v>5.54</v>
+        <v>5.36</v>
       </c>
       <c r="R62">
-        <v>2.67</v>
+        <v>2.49</v>
       </c>
       <c r="S62">
         <v>1.22</v>
@@ -10436,34 +10436,34 @@
         <v>3.75</v>
       </c>
       <c r="U62">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V62">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W62">
         <v>1.17</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
         <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>5.27</v>
+        <v>4.95</v>
       </c>
       <c r="AA62">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AB62">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="AC62">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AD62">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE62">
         <v>1.24</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="O63">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="P63">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="Q63">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="U63">
         <v>2.1</v>
       </c>
       <c r="V63">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W63">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z63">
-        <v>5.25</v>
+        <v>5.55</v>
       </c>
       <c r="AA63">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB63">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AC63">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AD63">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE63">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF63">
         <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK63">
         <v>1.36</v>
@@ -10741,61 +10741,61 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="O64">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="P64">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q64">
-        <v>3.53</v>
+        <v>3.13</v>
       </c>
       <c r="R64">
-        <v>2.39</v>
+        <v>2.19</v>
       </c>
       <c r="S64">
         <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U64">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="V64">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W64">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z64">
-        <v>4.48</v>
+        <v>4.15</v>
       </c>
       <c r="AA64">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB64">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AC64">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="AD64">
+        <v>1.4</v>
+      </c>
+      <c r="AE64">
+        <v>1.12</v>
+      </c>
+      <c r="AF64">
         <v>1.57</v>
-      </c>
-      <c r="AE64">
-        <v>1.14</v>
-      </c>
-      <c r="AF64">
-        <v>1.5</v>
       </c>
       <c r="AG64">
         <v>2.38</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="O66">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="P66">
-        <v>4.62</v>
+        <v>3.74</v>
       </c>
       <c r="Q66">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R66">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S66">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T66">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U66">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="V66">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z66">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AA66">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AB66">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC66">
-        <v>3.44</v>
+        <v>3.16</v>
       </c>
       <c r="AD66">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE66">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF66">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AG66">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK66">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11405,22 +11405,22 @@
         <v>2.5</v>
       </c>
       <c r="R68">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="S68">
         <v>1.4</v>
       </c>
       <c r="T68">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="U68">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V68">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
         <v>1.02</v>
@@ -11429,10 +11429,10 @@
         <v>1.35</v>
       </c>
       <c r="Z68">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA68">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB68">
         <v>1.61</v>
@@ -11444,10 +11444,10 @@
         <v>1.16</v>
       </c>
       <c r="AE68">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF68">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG68">
         <v>1.75</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK68">
         <v>1.83</v>
@@ -11731,25 +11731,25 @@
         <v>1.8</v>
       </c>
       <c r="R70">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="S70">
         <v>1.22</v>
       </c>
       <c r="T70">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="U70">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V70">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W70">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
         <v>1.16</v>
@@ -11767,7 +11767,7 @@
         <v>2.33</v>
       </c>
       <c r="AD70">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE70">
         <v>1.16</v>
@@ -11776,7 +11776,7 @@
         <v>1.75</v>
       </c>
       <c r="AG70">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK70">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11885,28 +11885,28 @@
         <v>1.57</v>
       </c>
       <c r="O71">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="P71">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="Q71">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R71">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
         <v>1.16</v>
       </c>
       <c r="T71">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U71">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V71">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="W71">
         <v>1.18</v>
@@ -11921,25 +11921,25 @@
         <v>5.68</v>
       </c>
       <c r="AA71">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB71">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="AC71">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AD71">
         <v>1.73</v>
       </c>
       <c r="AE71">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF71">
         <v>1.44</v>
       </c>
       <c r="AG71">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.06</v>
       </c>
       <c r="AK71">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,34 +12208,34 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="O73">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P73">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q73">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="R73">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S73">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U73">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V73">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W73">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X73">
         <v>1.03</v>
@@ -12247,10 +12247,10 @@
         <v>3.85</v>
       </c>
       <c r="AA73">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB73">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC73">
         <v>2.88</v>
@@ -12259,7 +12259,7 @@
         <v>1.4</v>
       </c>
       <c r="AE73">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF73">
         <v>1.62</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,34 +12371,34 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="O74">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P74">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="Q74">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R74">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="S74">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T74">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U74">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V74">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W74">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
         <v>1.02</v>
@@ -12422,7 +12422,7 @@
         <v>1.42</v>
       </c>
       <c r="AE74">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF74">
         <v>1.62</v>
@@ -12444,7 +12444,7 @@
         <v>1.2</v>
       </c>
       <c r="AK74">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O75">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P75">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q75">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="R75">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T75">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="U75">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V75">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
         <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA75">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB75">
         <v>1.83</v>
       </c>
       <c r="AC75">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AD75">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE75">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG75">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12860,49 +12860,49 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="O77">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="P77">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="Q77">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R77">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
         <v>1.33</v>
       </c>
       <c r="T77">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U77">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V77">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W77">
         <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="AA77">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AB77">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
         <v>3.1</v>
@@ -12911,13 +12911,13 @@
         <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF77">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG77">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="O81">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="P81">
         <v>2.5</v>
       </c>
       <c r="Q81">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R81">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S81">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T81">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="U81">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="V81">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W81">
+        <v>1.08</v>
+      </c>
+      <c r="X81">
+        <v>1.03</v>
+      </c>
+      <c r="Y81">
+        <v>1.29</v>
+      </c>
+      <c r="Z81">
+        <v>3.3</v>
+      </c>
+      <c r="AA81">
+        <v>1.93</v>
+      </c>
+      <c r="AB81">
+        <v>1.83</v>
+      </c>
+      <c r="AC81">
+        <v>3.42</v>
+      </c>
+      <c r="AD81">
+        <v>1.31</v>
+      </c>
+      <c r="AE81">
         <v>1.05</v>
       </c>
-      <c r="X81">
-        <v>1.04</v>
-      </c>
-      <c r="Y81">
-        <v>1.3</v>
-      </c>
-      <c r="Z81">
-        <v>3.2</v>
-      </c>
-      <c r="AA81">
-        <v>1.94</v>
-      </c>
-      <c r="AB81">
-        <v>1.74</v>
-      </c>
-      <c r="AC81">
-        <v>3.6</v>
-      </c>
-      <c r="AD81">
+      <c r="AF81">
+        <v>1.76</v>
+      </c>
+      <c r="AG81">
+        <v>2</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
         <v>1.25</v>
       </c>
-      <c r="AE81">
-        <v>1.06</v>
-      </c>
-      <c r="AF81">
-        <v>1.75</v>
-      </c>
-      <c r="AG81">
-        <v>1.95</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.33</v>
-      </c>
       <c r="AK81">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK83">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
       <c r="O85">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="Q85">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="R85">
+        <v>2.25</v>
+      </c>
+      <c r="S85">
+        <v>1.35</v>
+      </c>
+      <c r="T85">
+        <v>2.86</v>
+      </c>
+      <c r="U85">
+        <v>2.46</v>
+      </c>
+      <c r="V85">
+        <v>1.46</v>
+      </c>
+      <c r="W85">
+        <v>1.1</v>
+      </c>
+      <c r="X85">
+        <v>1</v>
+      </c>
+      <c r="Y85">
+        <v>1.22</v>
+      </c>
+      <c r="Z85">
+        <v>4.02</v>
+      </c>
+      <c r="AA85">
+        <v>1.81</v>
+      </c>
+      <c r="AB85">
+        <v>2.01</v>
+      </c>
+      <c r="AC85">
+        <v>2.9</v>
+      </c>
+      <c r="AD85">
+        <v>1.36</v>
+      </c>
+      <c r="AE85">
+        <v>1.11</v>
+      </c>
+      <c r="AF85">
+        <v>1.7</v>
+      </c>
+      <c r="AG85">
         <v>2</v>
       </c>
-      <c r="S85">
-        <v>1.4</v>
-      </c>
-      <c r="T85">
-        <v>2.75</v>
-      </c>
-      <c r="U85">
-        <v>2.9</v>
-      </c>
-      <c r="V85">
-        <v>1.33</v>
-      </c>
-      <c r="W85">
-        <v>1.05</v>
-      </c>
-      <c r="X85">
-        <v>1.02</v>
-      </c>
-      <c r="Y85">
-        <v>1.35</v>
-      </c>
-      <c r="Z85">
-        <v>3.12</v>
-      </c>
-      <c r="AA85">
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <v>1.21</v>
+      </c>
+      <c r="AK85">
         <v>2.1</v>
-      </c>
-      <c r="AB85">
-        <v>1.7</v>
-      </c>
-      <c r="AC85">
-        <v>3.83</v>
-      </c>
-      <c r="AD85">
-        <v>1.25</v>
-      </c>
-      <c r="AE85">
-        <v>1.06</v>
-      </c>
-      <c r="AF85">
-        <v>1.8</v>
-      </c>
-      <c r="AG85">
-        <v>1.91</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.36</v>
-      </c>
-      <c r="AK85">
-        <v>1.57</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="O86">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P86">
-        <v>4.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q86">
+        <v>2.88</v>
+      </c>
+      <c r="R86">
+        <v>2</v>
+      </c>
+      <c r="S86">
+        <v>1.4</v>
+      </c>
+      <c r="T86">
+        <v>2.75</v>
+      </c>
+      <c r="U86">
+        <v>2.9</v>
+      </c>
+      <c r="V86">
+        <v>1.33</v>
+      </c>
+      <c r="W86">
+        <v>1.05</v>
+      </c>
+      <c r="X86">
+        <v>1.02</v>
+      </c>
+      <c r="Y86">
+        <v>1.35</v>
+      </c>
+      <c r="Z86">
+        <v>3.12</v>
+      </c>
+      <c r="AA86">
         <v>2.15</v>
       </c>
-      <c r="R86">
-        <v>2.25</v>
-      </c>
-      <c r="S86">
-        <v>1.35</v>
-      </c>
-      <c r="T86">
-        <v>2.86</v>
-      </c>
-      <c r="U86">
-        <v>2.46</v>
-      </c>
-      <c r="V86">
-        <v>1.46</v>
-      </c>
-      <c r="W86">
-        <v>1.1</v>
-      </c>
-      <c r="X86">
-        <v>1</v>
-      </c>
-      <c r="Y86">
-        <v>1.22</v>
-      </c>
-      <c r="Z86">
-        <v>4.02</v>
-      </c>
-      <c r="AA86">
-        <v>1.81</v>
-      </c>
       <c r="AB86">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC86">
-        <v>2.9</v>
+        <v>3.83</v>
       </c>
       <c r="AD86">
+        <v>1.25</v>
+      </c>
+      <c r="AE86">
+        <v>1.06</v>
+      </c>
+      <c r="AF86">
+        <v>1.8</v>
+      </c>
+      <c r="AG86">
+        <v>1.91</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
         <v>1.36</v>
       </c>
-      <c r="AE86">
-        <v>1.11</v>
-      </c>
-      <c r="AF86">
-        <v>1.7</v>
-      </c>
-      <c r="AG86">
-        <v>2</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.21</v>
-      </c>
       <c r="AK86">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,10 +14490,10 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O87">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P87">
         <v>2.3</v>
@@ -14816,34 +14816,34 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="O89">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P89">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q89">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="R89">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S89">
         <v>1.28</v>
       </c>
       <c r="T89">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V89">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W89">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X89">
         <v>1</v>
@@ -14852,16 +14852,16 @@
         <v>1.2</v>
       </c>
       <c r="Z89">
-        <v>3.72</v>
+        <v>3.89</v>
       </c>
       <c r="AA89">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB89">
         <v>1.96</v>
       </c>
       <c r="AC89">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="AD89">
         <v>1.35</v>
@@ -14870,10 +14870,10 @@
         <v>1.1</v>
       </c>
       <c r="AF89">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG89">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK89">
         <v>1.3</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="O97">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P97">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q97">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="R97">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S97">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T97">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="U97">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V97">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="W97">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z97">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA97">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AB97">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC97">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="AD97">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AE97">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AF97">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG97">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.22</v>
       </c>
       <c r="AK97">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="O98">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="P98">
+        <v>5</v>
+      </c>
+      <c r="Q98">
+        <v>2.03</v>
+      </c>
+      <c r="R98">
+        <v>2.61</v>
+      </c>
+      <c r="S98">
+        <v>1.15</v>
+      </c>
+      <c r="T98">
+        <v>4.25</v>
+      </c>
+      <c r="U98">
+        <v>1.95</v>
+      </c>
+      <c r="V98">
+        <v>1.76</v>
+      </c>
+      <c r="W98">
+        <v>1.17</v>
+      </c>
+      <c r="X98">
+        <v>1.01</v>
+      </c>
+      <c r="Y98">
+        <v>1.05</v>
+      </c>
+      <c r="Z98">
+        <v>6.5</v>
+      </c>
+      <c r="AA98">
+        <v>1.4</v>
+      </c>
+      <c r="AB98">
         <v>2.87</v>
       </c>
-      <c r="Q98">
-        <v>2.62</v>
-      </c>
-      <c r="R98">
-        <v>2.5</v>
-      </c>
-      <c r="S98">
-        <v>1.22</v>
-      </c>
-      <c r="T98">
-        <v>3.9</v>
-      </c>
-      <c r="U98">
-        <v>2.1</v>
-      </c>
-      <c r="V98">
-        <v>1.67</v>
-      </c>
-      <c r="W98">
-        <v>1.18</v>
-      </c>
-      <c r="X98">
-        <v>1.02</v>
-      </c>
-      <c r="Y98">
-        <v>1.07</v>
-      </c>
-      <c r="Z98">
-        <v>5.95</v>
-      </c>
-      <c r="AA98">
-        <v>1.44</v>
-      </c>
-      <c r="AB98">
-        <v>2.7</v>
-      </c>
       <c r="AC98">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AD98">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AE98">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF98">
         <v>1.4</v>
       </c>
       <c r="AG98">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK98">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="O99">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P99">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q99">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="R99">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S99">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T99">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="U99">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="V99">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="W99">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z99">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA99">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB99">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AC99">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="AD99">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AE99">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AF99">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG99">
-        <v>2.94</v>
+        <v>2.3</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>1.22</v>
       </c>
       <c r="AK99">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="O100">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="P100">
-        <v>5</v>
+        <v>2.87</v>
       </c>
       <c r="Q100">
-        <v>2.03</v>
+        <v>2.62</v>
       </c>
       <c r="R100">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S100">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T100">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="U100">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V100">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="W100">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z100">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA100">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB100">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC100">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AD100">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AE100">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF100">
         <v>1.4</v>
       </c>
       <c r="AG100">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="O102">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P102">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q102">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="R102">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T102">
-        <v>3.09</v>
+        <v>2.73</v>
       </c>
       <c r="U102">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V102">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W102">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z102">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="AA102">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AB102">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC102">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="AD102">
         <v>1.34</v>
       </c>
       <c r="AE102">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AG102">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.3</v>
       </c>
       <c r="AK102">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="O106">
-        <v>5.27</v>
+        <v>3.6</v>
       </c>
       <c r="P106">
-        <v>3.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17913,31 +17913,31 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O108">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>2.64</v>
+        <v>2.37</v>
       </c>
       <c r="Q108">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="R108">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S108">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T108">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="U108">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="V108">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W108">
         <v>1.07</v>
@@ -17952,22 +17952,22 @@
         <v>3.6</v>
       </c>
       <c r="AA108">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB108">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC108">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD108">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF108">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG108">
         <v>2.1</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O111">
         <v>5.6</v>
@@ -18574,25 +18574,25 @@
         <v>1.44</v>
       </c>
       <c r="Q112">
-        <v>5.99</v>
+        <v>5.5</v>
       </c>
       <c r="R112">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S112">
         <v>1.28</v>
       </c>
       <c r="T112">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U112">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V112">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W112">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X112">
         <v>1.01</v>
@@ -18607,7 +18607,7 @@
         <v>1.66</v>
       </c>
       <c r="AB112">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC112">
         <v>2.66</v>
@@ -18622,7 +18622,7 @@
         <v>1.78</v>
       </c>
       <c r="AG112">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK112">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -20358,61 +20358,61 @@
         </is>
       </c>
       <c r="N123">
-        <v>4.12</v>
+        <v>4.6</v>
       </c>
       <c r="O123">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="P123">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="Q123">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="R123">
         <v>2.5</v>
       </c>
       <c r="S123">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T123">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U123">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V123">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W123">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X123">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
         <v>1.11</v>
       </c>
       <c r="Z123">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="AA123">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB123">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="AC123">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="AD123">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE123">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF123">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG123">
         <v>2.45</v>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK123">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21010,34 +21010,34 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O127">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P127">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q127">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="R127">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S127">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T127">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="U127">
         <v>2.73</v>
       </c>
       <c r="V127">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W127">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
         <v>1.01</v>
@@ -21049,41 +21049,41 @@
         <v>3.04</v>
       </c>
       <c r="AA127">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB127">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC127">
         <v>3.48</v>
       </c>
       <c r="AD127">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE127">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF127">
         <v>1.85</v>
       </c>
       <c r="AG127">
+        <v>1.91</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127">
+        <v>1.3</v>
+      </c>
+      <c r="AK127">
         <v>1.85</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>1.27</v>
-      </c>
-      <c r="AK127">
-        <v>1.84</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22323,25 +22323,25 @@
         <v>1.62</v>
       </c>
       <c r="Q135">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="R135">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S135">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T135">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U135">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="V135">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W135">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
         <v>1.04</v>
@@ -22356,7 +22356,7 @@
         <v>1.69</v>
       </c>
       <c r="AB135">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AC135">
         <v>2.7</v>
@@ -22365,7 +22365,7 @@
         <v>1.42</v>
       </c>
       <c r="AE135">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
         <v>1.65</v>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AL135">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O38">
         <v>3.4</v>
       </c>
       <c r="P38">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q38">
         <v>2.47</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O54">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P54">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9603,10 +9603,10 @@
         <v>2.05</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q57">
         <v>2.63</v>
@@ -9769,7 +9769,7 @@
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -10430,19 +10430,19 @@
         <v>2.49</v>
       </c>
       <c r="S62">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T62">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U62">
         <v>2.12</v>
       </c>
       <c r="V62">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X62">
         <v>1.02</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="O63">
-        <v>3.78</v>
+        <v>3.62</v>
       </c>
       <c r="P63">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="Q63">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="R63">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="U63">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="V63">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z63">
-        <v>5.55</v>
+        <v>4.15</v>
       </c>
       <c r="AA63">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB63">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="AC63">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="AD63">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AE63">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AF63">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O64">
-        <v>3.62</v>
+        <v>3.83</v>
       </c>
       <c r="P64">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="Q64">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="R64">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="S64">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T64">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="V64">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W64">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z64">
-        <v>4.15</v>
+        <v>5.55</v>
       </c>
       <c r="AA64">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB64">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AC64">
-        <v>2.56</v>
+        <v>2.11</v>
       </c>
       <c r="AD64">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AE64">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AF64">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG64">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK64">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -12211,7 +12211,7 @@
         <v>2.05</v>
       </c>
       <c r="O73">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P73">
         <v>3.3</v>
@@ -12247,10 +12247,10 @@
         <v>3.85</v>
       </c>
       <c r="AA73">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB73">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC73">
         <v>2.88</v>
@@ -13515,10 +13515,10 @@
         <v>2.45</v>
       </c>
       <c r="O81">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P81">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="O85">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P85">
-        <v>4.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q85">
+        <v>2.88</v>
+      </c>
+      <c r="R85">
+        <v>2</v>
+      </c>
+      <c r="S85">
+        <v>1.4</v>
+      </c>
+      <c r="T85">
+        <v>2.75</v>
+      </c>
+      <c r="U85">
+        <v>2.9</v>
+      </c>
+      <c r="V85">
+        <v>1.33</v>
+      </c>
+      <c r="W85">
+        <v>1.05</v>
+      </c>
+      <c r="X85">
+        <v>1.02</v>
+      </c>
+      <c r="Y85">
+        <v>1.35</v>
+      </c>
+      <c r="Z85">
+        <v>3.12</v>
+      </c>
+      <c r="AA85">
         <v>2.15</v>
       </c>
-      <c r="R85">
-        <v>2.25</v>
-      </c>
-      <c r="S85">
-        <v>1.35</v>
-      </c>
-      <c r="T85">
-        <v>2.86</v>
-      </c>
-      <c r="U85">
-        <v>2.46</v>
-      </c>
-      <c r="V85">
-        <v>1.46</v>
-      </c>
-      <c r="W85">
-        <v>1.1</v>
-      </c>
-      <c r="X85">
-        <v>1</v>
-      </c>
-      <c r="Y85">
-        <v>1.22</v>
-      </c>
-      <c r="Z85">
-        <v>4.02</v>
-      </c>
-      <c r="AA85">
-        <v>1.81</v>
-      </c>
       <c r="AB85">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AC85">
-        <v>2.9</v>
+        <v>3.83</v>
       </c>
       <c r="AD85">
+        <v>1.25</v>
+      </c>
+      <c r="AE85">
+        <v>1.06</v>
+      </c>
+      <c r="AF85">
+        <v>1.8</v>
+      </c>
+      <c r="AG85">
+        <v>1.91</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
         <v>1.36</v>
       </c>
-      <c r="AE85">
-        <v>1.11</v>
-      </c>
-      <c r="AF85">
-        <v>1.7</v>
-      </c>
-      <c r="AG85">
-        <v>2</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.21</v>
-      </c>
       <c r="AK85">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="O86">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="Q86">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="R86">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="S86">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T86">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U86">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="V86">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W86">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z86">
-        <v>3.12</v>
+        <v>4.1</v>
       </c>
       <c r="AA86">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AB86">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AC86">
-        <v>3.83</v>
+        <v>2.83</v>
       </c>
       <c r="AD86">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AE86">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF86">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK86">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,80 +14490,80 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="O87">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P87">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q87">
-        <v>3.02</v>
+        <v>2.15</v>
       </c>
       <c r="R87">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S87">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T87">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="U87">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="V87">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y87">
+        <v>1.22</v>
+      </c>
+      <c r="Z87">
+        <v>4.02</v>
+      </c>
+      <c r="AA87">
+        <v>1.81</v>
+      </c>
+      <c r="AB87">
+        <v>2.01</v>
+      </c>
+      <c r="AC87">
+        <v>2.9</v>
+      </c>
+      <c r="AD87">
+        <v>1.36</v>
+      </c>
+      <c r="AE87">
+        <v>1.11</v>
+      </c>
+      <c r="AF87">
+        <v>1.7</v>
+      </c>
+      <c r="AG87">
+        <v>2</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
         <v>1.21</v>
       </c>
-      <c r="Z87">
-        <v>4.1</v>
-      </c>
-      <c r="AA87">
-        <v>1.67</v>
-      </c>
-      <c r="AB87">
-        <v>2.04</v>
-      </c>
-      <c r="AC87">
-        <v>2.83</v>
-      </c>
-      <c r="AD87">
-        <v>1.42</v>
-      </c>
-      <c r="AE87">
-        <v>1.16</v>
-      </c>
-      <c r="AF87">
-        <v>1.53</v>
-      </c>
-      <c r="AG87">
-        <v>2.35</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.26</v>
-      </c>
       <c r="AK87">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -17931,7 +17931,7 @@
         <v>1.3</v>
       </c>
       <c r="T108">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U108">
         <v>2.75</v>
@@ -17986,7 +17986,7 @@
         <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18731,7 +18731,7 @@
         <v>2.15</v>
       </c>
       <c r="O113">
-        <v>3.36</v>
+        <v>3.67</v>
       </c>
       <c r="P113">
         <v>2.77</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="O116">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P116">
-        <v>1.84</v>
+        <v>3.16</v>
       </c>
       <c r="Q116">
-        <v>5.45</v>
+        <v>2.4</v>
       </c>
       <c r="R116">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S116">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T116">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U116">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V116">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W116">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X116">
         <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z116">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="AA116">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB116">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="AC116">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AD116">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AE116">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF116">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG116">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK116">
-        <v>1.13</v>
+        <v>1.88</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,80 +19380,80 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="O117">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P117">
-        <v>3.16</v>
+        <v>1.84</v>
       </c>
       <c r="Q117">
-        <v>2.4</v>
+        <v>5.45</v>
       </c>
       <c r="R117">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="S117">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T117">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U117">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="V117">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W117">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X117">
         <v>1.02</v>
       </c>
       <c r="Y117">
+        <v>1.17</v>
+      </c>
+      <c r="Z117">
+        <v>4</v>
+      </c>
+      <c r="AA117">
+        <v>1.69</v>
+      </c>
+      <c r="AB117">
+        <v>2.09</v>
+      </c>
+      <c r="AC117">
+        <v>2.66</v>
+      </c>
+      <c r="AD117">
+        <v>1.37</v>
+      </c>
+      <c r="AE117">
+        <v>1.11</v>
+      </c>
+      <c r="AF117">
+        <v>1.73</v>
+      </c>
+      <c r="AG117">
+        <v>2</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ117">
         <v>1.2</v>
       </c>
-      <c r="Z117">
-        <v>4.37</v>
-      </c>
-      <c r="AA117">
-        <v>1.68</v>
-      </c>
-      <c r="AB117">
-        <v>2.19</v>
-      </c>
-      <c r="AC117">
-        <v>2.64</v>
-      </c>
-      <c r="AD117">
-        <v>1.47</v>
-      </c>
-      <c r="AE117">
-        <v>1.12</v>
-      </c>
-      <c r="AF117">
-        <v>1.57</v>
-      </c>
-      <c r="AG117">
-        <v>2.26</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>1.24</v>
-      </c>
       <c r="AK117">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="O118">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P118">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="Q118">
         <v>2.56</v>
@@ -19558,16 +19558,16 @@
         <v>2.08</v>
       </c>
       <c r="S118">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T118">
-        <v>2.92</v>
+        <v>3.01</v>
       </c>
       <c r="U118">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="V118">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W118">
         <v>1.06</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O122">
         <v>3.6</v>
       </c>
       <c r="P122">
-        <v>3.88</v>
+        <v>4.6</v>
       </c>
       <c r="Q122">
         <v>2.28</v>
@@ -20234,7 +20234,7 @@
         <v>3.08</v>
       </c>
       <c r="AA122">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB122">
         <v>1.78</v>
@@ -20364,7 +20364,7 @@
         <v>4.3</v>
       </c>
       <c r="P123">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="Q123">
         <v>4.5</v>
@@ -20693,19 +20693,19 @@
         <v>5.75</v>
       </c>
       <c r="Q125">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="R125">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="S125">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T125">
         <v>3</v>
       </c>
       <c r="U125">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V125">
         <v>1.42</v>
@@ -20726,7 +20726,7 @@
         <v>1.89</v>
       </c>
       <c r="AB125">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC125">
         <v>2.92</v>
@@ -20898,7 +20898,7 @@
         <v>1.4</v>
       </c>
       <c r="AE126">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF126">
         <v>1.7</v>
@@ -21336,31 +21336,31 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O129">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="P129">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Q129">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R129">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S129">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T129">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="U129">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="V129">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W129">
         <v>1.14</v>
@@ -21369,31 +21369,31 @@
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z129">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="AA129">
         <v>1.49</v>
       </c>
       <c r="AB129">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="AC129">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD129">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE129">
         <v>1.25</v>
       </c>
       <c r="AF129">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG129">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK129">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21505,55 +21505,55 @@
         <v>3.3</v>
       </c>
       <c r="P130">
+        <v>3.3</v>
+      </c>
+      <c r="Q130">
+        <v>2.6</v>
+      </c>
+      <c r="R130">
+        <v>2.2</v>
+      </c>
+      <c r="S130">
+        <v>1.3</v>
+      </c>
+      <c r="T130">
         <v>3.2</v>
       </c>
-      <c r="Q130">
-        <v>2.5</v>
-      </c>
-      <c r="R130">
-        <v>2.25</v>
-      </c>
-      <c r="S130">
-        <v>1.33</v>
-      </c>
-      <c r="T130">
-        <v>3.1</v>
-      </c>
       <c r="U130">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V130">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W130">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X130">
         <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z130">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA130">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB130">
         <v>1.9</v>
       </c>
       <c r="AC130">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD130">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE130">
         <v>1.08</v>
       </c>
       <c r="AF130">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG130">
         <v>2</v>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK130">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL130">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="O5">
         <v>4.94</v>
       </c>
       <c r="P5">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O38">
         <v>3.4</v>
@@ -9609,7 +9609,7 @@
         <v>3</v>
       </c>
       <c r="Q57">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R57">
         <v>2.29</v>
@@ -9639,7 +9639,7 @@
         <v>3.77</v>
       </c>
       <c r="AA57">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB57">
         <v>1.96</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK57">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10421,13 +10421,13 @@
         <v>4.2</v>
       </c>
       <c r="P62">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q62">
-        <v>5.36</v>
+        <v>5.05</v>
       </c>
       <c r="R62">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="S62">
         <v>1.19</v>
@@ -10448,7 +10448,7 @@
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z62">
         <v>4.95</v>
@@ -10460,13 +10460,13 @@
         <v>2.41</v>
       </c>
       <c r="AC62">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD62">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE62">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF62">
         <v>1.57</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="O63">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="P63">
         <v>2.18</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="O64">
         <v>3.83</v>
       </c>
       <c r="P64">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O73">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P73">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q73">
         <v>2.49</v>
@@ -12226,13 +12226,13 @@
         <v>1.3</v>
       </c>
       <c r="T73">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U73">
         <v>2.5</v>
       </c>
       <c r="V73">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
         <v>1.06</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O74">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P74">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -13515,10 +13515,10 @@
         <v>2.45</v>
       </c>
       <c r="O81">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P81">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -13841,22 +13841,22 @@
         <v>2.75</v>
       </c>
       <c r="O83">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
         <v>2.25</v>
       </c>
       <c r="Q83">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="R83">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S83">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T83">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U83">
         <v>2.59</v>
@@ -14369,7 +14369,7 @@
         <v>1.67</v>
       </c>
       <c r="AB86">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC86">
         <v>2.83</v>
@@ -14982,10 +14982,10 @@
         <v>2.45</v>
       </c>
       <c r="O90">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q90">
         <v>3.07</v>
@@ -15006,7 +15006,7 @@
         <v>1.43</v>
       </c>
       <c r="W90">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
         <v>1.01</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O91">
         <v>4.5</v>
       </c>
       <c r="P91">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="Q91">
         <v>2.04</v>
@@ -16953,7 +16953,7 @@
         <v>1.38</v>
       </c>
       <c r="T102">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U102">
         <v>2.45</v>
@@ -16977,16 +16977,16 @@
         <v>1.76</v>
       </c>
       <c r="AB102">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC102">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD102">
         <v>1.34</v>
       </c>
       <c r="AE102">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF102">
         <v>1.59</v>
@@ -17756,7 +17756,7 @@
         <v>3.1</v>
       </c>
       <c r="P107">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q107">
         <v>2.91</v>
@@ -17916,10 +17916,10 @@
         <v>2.6</v>
       </c>
       <c r="O108">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P108">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q108">
         <v>2.97</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="O111">
         <v>5.6</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,80 +19217,80 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="O116">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P116">
-        <v>3.16</v>
+        <v>1.84</v>
       </c>
       <c r="Q116">
-        <v>2.4</v>
+        <v>5.45</v>
       </c>
       <c r="R116">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="S116">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T116">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U116">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="V116">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W116">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X116">
         <v>1.02</v>
       </c>
       <c r="Y116">
+        <v>1.17</v>
+      </c>
+      <c r="Z116">
+        <v>4</v>
+      </c>
+      <c r="AA116">
+        <v>1.69</v>
+      </c>
+      <c r="AB116">
+        <v>2.09</v>
+      </c>
+      <c r="AC116">
+        <v>2.66</v>
+      </c>
+      <c r="AD116">
+        <v>1.37</v>
+      </c>
+      <c r="AE116">
+        <v>1.11</v>
+      </c>
+      <c r="AF116">
+        <v>1.73</v>
+      </c>
+      <c r="AG116">
+        <v>2</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ116">
         <v>1.2</v>
       </c>
-      <c r="Z116">
-        <v>4.37</v>
-      </c>
-      <c r="AA116">
-        <v>1.68</v>
-      </c>
-      <c r="AB116">
-        <v>2.19</v>
-      </c>
-      <c r="AC116">
-        <v>2.64</v>
-      </c>
-      <c r="AD116">
-        <v>1.47</v>
-      </c>
-      <c r="AE116">
-        <v>1.12</v>
-      </c>
-      <c r="AF116">
-        <v>1.57</v>
-      </c>
-      <c r="AG116">
-        <v>2.26</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>1.24</v>
-      </c>
       <c r="AK116">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="O117">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P117">
-        <v>1.84</v>
+        <v>3.16</v>
       </c>
       <c r="Q117">
-        <v>5.45</v>
+        <v>2.4</v>
       </c>
       <c r="R117">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S117">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T117">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U117">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V117">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W117">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
         <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z117">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="AA117">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB117">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="AC117">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AD117">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AE117">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF117">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG117">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK117">
-        <v>1.13</v>
+        <v>1.88</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19546,10 +19546,10 @@
         <v>2.11</v>
       </c>
       <c r="O118">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="P118">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="Q118">
         <v>2.56</v>
@@ -19561,7 +19561,7 @@
         <v>1.39</v>
       </c>
       <c r="T118">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="U118">
         <v>2.96</v>
@@ -19763,7 +19763,7 @@
         <v>1.57</v>
       </c>
       <c r="AG119">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O122">
         <v>3.6</v>
@@ -20358,7 +20358,7 @@
         </is>
       </c>
       <c r="N123">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O123">
         <v>4.3</v>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK126">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AL126">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>4.94</v>
+        <v>5.2</v>
       </c>
       <c r="P5">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -10783,13 +10783,13 @@
         <v>1.88</v>
       </c>
       <c r="AB64">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC64">
         <v>3.04</v>
       </c>
       <c r="AD64">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE64">
         <v>1.11</v>
@@ -10928,10 +10928,10 @@
         <v>2.12</v>
       </c>
       <c r="V65">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X65">
         <v>1.02</v>
@@ -12380,7 +12380,7 @@
         <v>6.69</v>
       </c>
       <c r="Q74">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R74">
         <v>2.49</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="O102">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="P102">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q102">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="R102">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="S102">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T102">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U102">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="V102">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="W102">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z102">
-        <v>5.61</v>
+        <v>4.45</v>
       </c>
       <c r="AA102">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AB102">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="AC102">
-        <v>2.11</v>
+        <v>2.53</v>
       </c>
       <c r="AD102">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AE102">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AF102">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AG102">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="O103">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P103">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q103">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="R103">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="S103">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T103">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U103">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="V103">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="W103">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="Z103">
-        <v>4.45</v>
+        <v>6.25</v>
       </c>
       <c r="AA103">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AB103">
-        <v>2.23</v>
+        <v>2.93</v>
       </c>
       <c r="AC103">
-        <v>2.53</v>
+        <v>1.93</v>
       </c>
       <c r="AD103">
-        <v>1.49</v>
+        <v>1.86</v>
       </c>
       <c r="AE103">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AF103">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AG103">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK103">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O104">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P104">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q104">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R104">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="S104">
         <v>1.2</v>
       </c>
       <c r="T104">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U104">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V104">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="W104">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z104">
-        <v>6.25</v>
+        <v>5.15</v>
       </c>
       <c r="AA104">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="AC104">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AD104">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AE104">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AF104">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AG104">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AK104">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,65 +17424,65 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P105">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q105">
-        <v>2.7</v>
+        <v>2.09</v>
       </c>
       <c r="R105">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="S105">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T105">
         <v>4</v>
       </c>
       <c r="U105">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V105">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W105">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z105">
-        <v>5.15</v>
+        <v>5.61</v>
       </c>
       <c r="AA105">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AB105">
+        <v>2.7</v>
+      </c>
+      <c r="AC105">
+        <v>2.11</v>
+      </c>
+      <c r="AD105">
+        <v>1.7</v>
+      </c>
+      <c r="AE105">
+        <v>1.28</v>
+      </c>
+      <c r="AF105">
+        <v>1.44</v>
+      </c>
+      <c r="AG105">
         <v>2.5</v>
       </c>
-      <c r="AC105">
-        <v>2.09</v>
-      </c>
-      <c r="AD105">
-        <v>1.68</v>
-      </c>
-      <c r="AE105">
-        <v>1.25</v>
-      </c>
-      <c r="AF105">
-        <v>1.39</v>
-      </c>
-      <c r="AG105">
-        <v>2.77</v>
-      </c>
       <c r="AH105" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AK105">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O107">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P107">
         <v>2.8</v>
@@ -17768,7 +17768,7 @@
         <v>1.38</v>
       </c>
       <c r="T107">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U107">
         <v>2.45</v>
@@ -17795,7 +17795,7 @@
         <v>1.95</v>
       </c>
       <c r="AC107">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AD107">
         <v>1.34</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,7 +19217,7 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="O116">
         <v>5.6</v>
@@ -19229,7 +19229,7 @@
         <v>1.75</v>
       </c>
       <c r="R116">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="S116">
         <v>1.13</v>
@@ -19262,10 +19262,10 @@
         <v>3.6</v>
       </c>
       <c r="AC116">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AD116">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AE116">
         <v>1.46</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK116">
         <v>3.1</v>
@@ -19727,10 +19727,10 @@
         <v>3.32</v>
       </c>
       <c r="U119">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V119">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W119">
         <v>1.08</v>
@@ -20059,7 +20059,7 @@
         <v>1.52</v>
       </c>
       <c r="W121">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X121">
         <v>1.02</v>
@@ -20204,25 +20204,25 @@
         <v>1.84</v>
       </c>
       <c r="Q122">
-        <v>5.45</v>
+        <v>5.29</v>
       </c>
       <c r="R122">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="S122">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T122">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="U122">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V122">
         <v>1.5</v>
       </c>
       <c r="W122">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
         <v>1.02</v>
@@ -20231,28 +20231,28 @@
         <v>1.17</v>
       </c>
       <c r="Z122">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AA122">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB122">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AC122">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD122">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE122">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF122">
         <v>1.73</v>
       </c>
       <c r="AG122">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK122">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20373,16 +20373,16 @@
         <v>2.08</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T123">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="U123">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="V123">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W123">
         <v>1.06</v>
@@ -20391,10 +20391,10 @@
         <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z123">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AA123">
         <v>1.91</v>
@@ -20403,13 +20403,13 @@
         <v>1.8</v>
       </c>
       <c r="AC123">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="AD123">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE123">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF123">
         <v>1.75</v>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20859,19 +20859,19 @@
         <v>1.5</v>
       </c>
       <c r="R126">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="S126">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T126">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="U126">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="V126">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W126">
         <v>1.18</v>
@@ -20880,31 +20880,31 @@
         <v>0</v>
       </c>
       <c r="Y126">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z126">
-        <v>5.7</v>
+        <v>5.76</v>
       </c>
       <c r="AA126">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AB126">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="AC126">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AD126">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE126">
         <v>1.29</v>
       </c>
       <c r="AF126">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AG126">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK126">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21671,55 +21671,55 @@
         <v>0</v>
       </c>
       <c r="Q131">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="R131">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S131">
         <v>1.28</v>
       </c>
       <c r="T131">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U131">
         <v>2.5</v>
       </c>
       <c r="V131">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W131">
         <v>1.11</v>
       </c>
       <c r="X131">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y131">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z131">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="AA131">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB131">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC131">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD131">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE131">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF131">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG131">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK131">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -22335,10 +22335,10 @@
         <v>3.2</v>
       </c>
       <c r="U135">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="V135">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W135">
         <v>1.1</v>
@@ -22516,16 +22516,16 @@
         <v>3</v>
       </c>
       <c r="AA136">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AB136">
         <v>2.05</v>
       </c>
       <c r="AC136">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD136">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE136">
         <v>1.11</v>
@@ -22975,71 +22975,71 @@
         <v>2.51</v>
       </c>
       <c r="Q139">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R139">
         <v>2.15</v>
       </c>
       <c r="S139">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T139">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="U139">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V139">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W139">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X139">
         <v>1.03</v>
       </c>
       <c r="Y139">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z139">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA139">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB139">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AC139">
         <v>2.38</v>
       </c>
       <c r="AD139">
+        <v>1.49</v>
+      </c>
+      <c r="AE139">
+        <v>1.16</v>
+      </c>
+      <c r="AF139">
+        <v>1.44</v>
+      </c>
+      <c r="AG139">
+        <v>2.5</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>1.25</v>
+      </c>
+      <c r="AK139">
         <v>1.53</v>
-      </c>
-      <c r="AE139">
-        <v>1.14</v>
-      </c>
-      <c r="AF139">
-        <v>1.36</v>
-      </c>
-      <c r="AG139">
-        <v>2.15</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>1.08</v>
-      </c>
-      <c r="AK139">
-        <v>1.5</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23138,25 +23138,25 @@
         <v>2.2</v>
       </c>
       <c r="Q140">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R140">
         <v>2.4</v>
       </c>
       <c r="S140">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T140">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="U140">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="V140">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="W140">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X140">
         <v>1.01</v>
@@ -23168,10 +23168,10 @@
         <v>5.5</v>
       </c>
       <c r="AA140">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AB140">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AC140">
         <v>2.05</v>
@@ -23183,10 +23183,10 @@
         <v>1.24</v>
       </c>
       <c r="AF140">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG140">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AK140">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL140">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -665,13 +665,13 @@
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
         <v>1.26</v>
       </c>
       <c r="Z2">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA2">
         <v>1.85</v>
@@ -689,7 +689,7 @@
         <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG2">
         <v>2.1</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P42">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="Q42">
         <v>2.47</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7982,7 +7982,7 @@
         <v>2.4</v>
       </c>
       <c r="R47">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="S47">
         <v>1.22</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -9120,7 +9120,7 @@
         <v>3.3</v>
       </c>
       <c r="Q54">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R54">
         <v>2.25</v>
@@ -9283,55 +9283,55 @@
         <v>2.5</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>2.95</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10255,7 +10255,7 @@
         <v>2.05</v>
       </c>
       <c r="O61">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P61">
         <v>3</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="O67">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P67">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q67">
-        <v>3.13</v>
+        <v>3.02</v>
       </c>
       <c r="R67">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="S67">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T67">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="U67">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="V67">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W67">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z67">
-        <v>4.15</v>
+        <v>5.55</v>
       </c>
       <c r="AA67">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB67">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="AC67">
-        <v>2.56</v>
+        <v>2.11</v>
       </c>
       <c r="AD67">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AE67">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AF67">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG67">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK67">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="O68">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P68">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q68">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="R68">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S68">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="U68">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="V68">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W68">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z68">
-        <v>5.55</v>
+        <v>4.2</v>
       </c>
       <c r="AA68">
+        <v>1.6</v>
+      </c>
+      <c r="AB68">
+        <v>2.19</v>
+      </c>
+      <c r="AC68">
+        <v>2.52</v>
+      </c>
+      <c r="AD68">
         <v>1.44</v>
       </c>
-      <c r="AB68">
-        <v>2.6</v>
-      </c>
-      <c r="AC68">
-        <v>2.11</v>
-      </c>
-      <c r="AD68">
-        <v>1.68</v>
-      </c>
       <c r="AE68">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG68">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O70">
         <v>3.54</v>
       </c>
       <c r="P70">
-        <v>3.74</v>
+        <v>3.38</v>
       </c>
       <c r="Q70">
         <v>2.55</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>7.85</v>
+        <v>1.21</v>
       </c>
       <c r="O71">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="P71">
-        <v>1.26</v>
+        <v>6.6</v>
       </c>
       <c r="Q71">
         <v>6.72</v>
@@ -12048,10 +12048,10 @@
         <v>1.93</v>
       </c>
       <c r="O72">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -12537,13 +12537,13 @@
         <v>1.57</v>
       </c>
       <c r="O75">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="P75">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q75">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="R75">
         <v>2.3</v>
@@ -12555,10 +12555,10 @@
         <v>4</v>
       </c>
       <c r="U75">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V75">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W75">
         <v>1.18</v>
@@ -12607,7 +12607,7 @@
         <v>1.06</v>
       </c>
       <c r="AK75">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>3.4</v>
       </c>
       <c r="Q77">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="R77">
         <v>2.17</v>
@@ -12933,7 +12933,7 @@
         <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK78">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13355,7 +13355,7 @@
         <v>3.5</v>
       </c>
       <c r="P80">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -13518,7 +13518,7 @@
         <v>3.48</v>
       </c>
       <c r="P81">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -13880,7 +13880,7 @@
         <v>1.44</v>
       </c>
       <c r="AB83">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AC83">
         <v>1.97</v>
@@ -14010,25 +14010,25 @@
         <v>4.4</v>
       </c>
       <c r="Q84">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R84">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="S84">
         <v>1.22</v>
       </c>
       <c r="T84">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V84">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W84">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X84">
         <v>1.02</v>
@@ -14040,7 +14040,7 @@
         <v>5.01</v>
       </c>
       <c r="AA84">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB84">
         <v>2.37</v>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK84">
         <v>2.09</v>
@@ -14167,10 +14167,10 @@
         <v>2.45</v>
       </c>
       <c r="O85">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P85">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O88">
         <v>3.2</v>
@@ -14662,10 +14662,10 @@
         <v>2.25</v>
       </c>
       <c r="Q88">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="R88">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S88">
         <v>1.38</v>
@@ -14692,10 +14692,10 @@
         <v>3.4</v>
       </c>
       <c r="AA88">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB88">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC88">
         <v>3.3</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK88">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14852,7 +14852,7 @@
         <v>1.27</v>
       </c>
       <c r="Z89">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA89">
         <v>1.97</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK89">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="O90">
         <v>3.1</v>
@@ -15003,10 +15003,10 @@
         <v>2.9</v>
       </c>
       <c r="V90">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X90">
         <v>1.02</v>
@@ -15015,22 +15015,22 @@
         <v>1.35</v>
       </c>
       <c r="Z90">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="AA90">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB90">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC90">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="AD90">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF90">
         <v>1.8</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK90">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15184,7 +15184,7 @@
         <v>1.67</v>
       </c>
       <c r="AB91">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC91">
         <v>2.83</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK91">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         <v>4.4</v>
       </c>
       <c r="Q92">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="R92">
         <v>2.25</v>
@@ -15341,7 +15341,7 @@
         <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="AA92">
         <v>1.81</v>
@@ -15378,7 +15378,7 @@
         <v>1.21</v>
       </c>
       <c r="AK92">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="O95">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P95">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="Q95">
         <v>3.07</v>
@@ -15963,7 +15963,7 @@
         <v>4.5</v>
       </c>
       <c r="P96">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="Q96">
         <v>2.04</v>
@@ -16002,7 +16002,7 @@
         <v>2.66</v>
       </c>
       <c r="AC96">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD96">
         <v>1.74</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O97">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P97">
         <v>4.1</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O99">
         <v>4</v>
@@ -16612,7 +16612,7 @@
         <v>2.3</v>
       </c>
       <c r="O100">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P100">
         <v>2.55</v>
@@ -16775,7 +16775,7 @@
         <v>2.4</v>
       </c>
       <c r="O101">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P101">
         <v>2.37</v>
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O102">
         <v>3.78</v>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="O103">
         <v>3.8</v>
@@ -17303,7 +17303,7 @@
         <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC104">
         <v>2.09</v>
@@ -17427,7 +17427,7 @@
         <v>1.61</v>
       </c>
       <c r="O105">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P105">
         <v>4.2</v>
@@ -17436,7 +17436,7 @@
         <v>2.09</v>
       </c>
       <c r="R105">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="S105">
         <v>1.17</v>
@@ -17457,25 +17457,25 @@
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z105">
-        <v>5.61</v>
+        <v>5.86</v>
       </c>
       <c r="AA105">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB105">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AC105">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="AD105">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AE105">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF105">
         <v>1.44</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK105">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="O106">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="P106">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q106">
         <v>1.48</v>
@@ -17605,13 +17605,13 @@
         <v>1.14</v>
       </c>
       <c r="T106">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U106">
         <v>1.97</v>
       </c>
       <c r="V106">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W106">
         <v>1.22</v>
@@ -17629,7 +17629,7 @@
         <v>1.33</v>
       </c>
       <c r="AB106">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC106">
         <v>1.92</v>
@@ -17765,10 +17765,10 @@
         <v>2.1</v>
       </c>
       <c r="S107">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T107">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U107">
         <v>2.45</v>
@@ -17823,7 +17823,7 @@
         <v>1.3</v>
       </c>
       <c r="AK107">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18565,19 +18565,19 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O112">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P112">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q112">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="R112">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S112">
         <v>1.4</v>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK112">
         <v>1.63</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O113">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P113">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q113">
         <v>2.97</v>
@@ -18761,22 +18761,22 @@
         <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z113">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA113">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB113">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AC113">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD113">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE113">
         <v>1.12</v>
@@ -18785,7 +18785,7 @@
         <v>1.67</v>
       </c>
       <c r="AG113">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>3.63</v>
       </c>
       <c r="P118">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="Q118">
         <v>2.52</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK118">
         <v>1.68</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O120">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="P120">
-        <v>5</v>
+        <v>3.16</v>
       </c>
       <c r="Q120">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="R120">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S120">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T120">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U120">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V120">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W120">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X120">
         <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z120">
-        <v>3.92</v>
+        <v>4.37</v>
       </c>
       <c r="AA120">
         <v>1.68</v>
       </c>
       <c r="AB120">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AC120">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="AD120">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE120">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF120">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG120">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK120">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="O121">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P121">
-        <v>3.16</v>
+        <v>1.84</v>
       </c>
       <c r="Q121">
-        <v>2.4</v>
+        <v>5.29</v>
       </c>
       <c r="R121">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S121">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T121">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="U121">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V121">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W121">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
         <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z121">
-        <v>4.37</v>
+        <v>3.94</v>
       </c>
       <c r="AA121">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB121">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC121">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AD121">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE121">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF121">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG121">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK121">
-        <v>1.88</v>
+        <v>1.14</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,31 +20195,31 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="O122">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="P122">
-        <v>1.84</v>
+        <v>5</v>
       </c>
       <c r="Q122">
-        <v>5.29</v>
+        <v>2.05</v>
       </c>
       <c r="R122">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S122">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U122">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="V122">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W122">
         <v>1.08</v>
@@ -20228,31 +20228,31 @@
         <v>1.02</v>
       </c>
       <c r="Y122">
+        <v>1.18</v>
+      </c>
+      <c r="Z122">
+        <v>3.92</v>
+      </c>
+      <c r="AA122">
+        <v>1.68</v>
+      </c>
+      <c r="AB122">
+        <v>2.11</v>
+      </c>
+      <c r="AC122">
+        <v>2.71</v>
+      </c>
+      <c r="AD122">
+        <v>1.45</v>
+      </c>
+      <c r="AE122">
         <v>1.17</v>
       </c>
-      <c r="Z122">
-        <v>3.94</v>
-      </c>
-      <c r="AA122">
-        <v>1.71</v>
-      </c>
-      <c r="AB122">
-        <v>2.06</v>
-      </c>
-      <c r="AC122">
-        <v>2.7</v>
-      </c>
-      <c r="AD122">
-        <v>1.36</v>
-      </c>
-      <c r="AE122">
-        <v>1.16</v>
-      </c>
       <c r="AF122">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG122">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>1.14</v>
+        <v>2.14</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20693,7 +20693,7 @@
         <v>2.15</v>
       </c>
       <c r="Q125">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R125">
         <v>2.25</v>
@@ -20723,10 +20723,10 @@
         <v>3.74</v>
       </c>
       <c r="AA125">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB125">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC125">
         <v>2.76</v>
@@ -20741,7 +20741,7 @@
         <v>1.61</v>
       </c>
       <c r="AG125">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK125">
         <v>1.33</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O127">
         <v>3.6</v>
       </c>
       <c r="P127">
-        <v>3.88</v>
+        <v>4.6</v>
       </c>
       <c r="Q127">
         <v>2.28</v>
@@ -21083,7 +21083,7 @@
         <v>1.23</v>
       </c>
       <c r="AK127">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21499,19 +21499,19 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="O130">
-        <v>4.12</v>
+        <v>3.75</v>
       </c>
       <c r="P130">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="Q130">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="R130">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="S130">
         <v>1.38</v>
@@ -21520,37 +21520,37 @@
         <v>3</v>
       </c>
       <c r="U130">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V130">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W130">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z130">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AA130">
         <v>1.89</v>
       </c>
       <c r="AB130">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC130">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AD130">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE130">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF130">
         <v>1.95</v>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK130">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21716,7 +21716,7 @@
         <v>1.12</v>
       </c>
       <c r="AF131">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG131">
         <v>1.95</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="O132">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P132">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q132">
         <v>2.38</v>
@@ -21870,7 +21870,7 @@
         <v>1.71</v>
       </c>
       <c r="AC132">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AD132">
         <v>1.25</v>
@@ -21898,7 +21898,7 @@
         <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22812,13 +22812,13 @@
         <v>2.9</v>
       </c>
       <c r="Q138">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="R138">
         <v>1.95</v>
       </c>
       <c r="S138">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T138">
         <v>2.75</v>
@@ -22830,7 +22830,7 @@
         <v>1.3</v>
       </c>
       <c r="W138">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X138">
         <v>1.05</v>
@@ -22876,7 +22876,7 @@
         <v>1.35</v>
       </c>
       <c r="AK138">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22993,7 +22993,7 @@
         <v>1.57</v>
       </c>
       <c r="W139">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X139">
         <v>1.03</v>
@@ -23138,7 +23138,7 @@
         <v>2.2</v>
       </c>
       <c r="Q140">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R140">
         <v>2.4</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O5">
         <v>5.2</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
+        <v>2.2</v>
+      </c>
+      <c r="O55">
+        <v>3.35</v>
+      </c>
+      <c r="P55">
+        <v>2.95</v>
+      </c>
+      <c r="Q55">
+        <v>2.7</v>
+      </c>
+      <c r="R55">
         <v>2.3</v>
       </c>
-      <c r="O55">
-        <v>3.75</v>
-      </c>
-      <c r="P55">
-        <v>2.5</v>
-      </c>
-      <c r="Q55">
-        <v>2.63</v>
-      </c>
-      <c r="R55">
-        <v>2.5</v>
-      </c>
       <c r="S55">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T55">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="U55">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="V55">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="W55">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z55">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA55">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="AB55">
-        <v>2.74</v>
+        <v>2.13</v>
       </c>
       <c r="AC55">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="AD55">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AE55">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AG55">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O56">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q56">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S56">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T56">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="U56">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="V56">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="W56">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z56">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA56">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AB56">
-        <v>2.13</v>
+        <v>2.74</v>
       </c>
       <c r="AC56">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="AD56">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AE56">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AF56">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AG56">
-        <v>2.28</v>
+        <v>2.84</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK56">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -19893,7 +19893,7 @@
         <v>2.46</v>
       </c>
       <c r="V120">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W120">
         <v>1.12</v>
@@ -20041,16 +20041,16 @@
         <v>1.84</v>
       </c>
       <c r="Q121">
-        <v>5.29</v>
+        <v>5.78</v>
       </c>
       <c r="R121">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S121">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T121">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U121">
         <v>2.45</v>
@@ -20059,7 +20059,7 @@
         <v>1.5</v>
       </c>
       <c r="W121">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X121">
         <v>1.02</v>
@@ -20068,13 +20068,13 @@
         <v>1.17</v>
       </c>
       <c r="Z121">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="AA121">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB121">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC121">
         <v>2.7</v>
@@ -20083,13 +20083,13 @@
         <v>1.36</v>
       </c>
       <c r="AE121">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF121">
         <v>1.73</v>
       </c>
       <c r="AG121">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.21</v>
+        <v>2.3</v>
       </c>
       <c r="AK121">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20207,43 +20207,43 @@
         <v>2.05</v>
       </c>
       <c r="R122">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S122">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T122">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U122">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V122">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X122">
         <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z122">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AA122">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB122">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC122">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AD122">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE122">
         <v>1.17</v>
@@ -20252,7 +20252,7 @@
         <v>1.67</v>
       </c>
       <c r="AG122">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK122">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="O126">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="P126">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q126">
         <v>1.5</v>
@@ -20871,13 +20871,13 @@
         <v>2.02</v>
       </c>
       <c r="V126">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="W126">
         <v>1.18</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
         <v>1.07</v>
@@ -20886,7 +20886,7 @@
         <v>5.76</v>
       </c>
       <c r="AA126">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB126">
         <v>2.84</v>
@@ -20898,7 +20898,7 @@
         <v>1.75</v>
       </c>
       <c r="AE126">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF126">
         <v>1.91</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1127,10 +1127,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="P5">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="P26">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB26">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="O41">
         <v>3.3</v>
@@ -7010,13 +7010,13 @@
         <v>1.43</v>
       </c>
       <c r="T41">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="U41">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="V41">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W41">
         <v>1.01</v>
@@ -7025,22 +7025,22 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z41">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="AA41">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB41">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC41">
         <v>3.95</v>
       </c>
       <c r="AD41">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE41">
         <v>1.02</v>
@@ -7164,55 +7164,55 @@
         <v>3.44</v>
       </c>
       <c r="Q42">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="R42">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V42">
         <v>1.4</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z42">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AA42">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AB42">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AC42">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="AD42">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
         <v>1.91</v>
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="O45">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="P45">
         <v>3.02</v>
       </c>
       <c r="Q45">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="R45">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="S45">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T45">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="U45">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="V45">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W45">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7680,28 +7680,28 @@
         <v>1.12</v>
       </c>
       <c r="Z45">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA45">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB45">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AC45">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AD45">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE45">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF45">
         <v>1.46</v>
       </c>
       <c r="AG45">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK45">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>2.37</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7988,7 +7988,7 @@
         <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
         <v>2.28</v>
@@ -8009,10 +8009,10 @@
         <v>4.85</v>
       </c>
       <c r="AA47">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AC47">
         <v>2.33</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="O49">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="O50">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P50">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="O52">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="P52">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9132,10 +9132,10 @@
         <v>3.02</v>
       </c>
       <c r="U54">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V54">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W54">
         <v>1.08</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O55">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q55">
         <v>2.7</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O56">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
         <v>2.5</v>
       </c>
       <c r="Q56">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="R56">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S56">
         <v>1.17</v>
@@ -9473,7 +9473,7 @@
         <v>1.07</v>
       </c>
       <c r="Z56">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA56">
         <v>1.35</v>
@@ -9482,19 +9482,19 @@
         <v>2.74</v>
       </c>
       <c r="AC56">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD56">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE56">
         <v>1.28</v>
       </c>
       <c r="AF56">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AG56">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK56">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.17</v>
+        <v>1.52</v>
       </c>
       <c r="O58">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="P58">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="O60">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P60">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,7 +10255,7 @@
         <v>2.05</v>
       </c>
       <c r="O61">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P61">
         <v>3</v>
@@ -10279,7 +10279,7 @@
         <v>1.44</v>
       </c>
       <c r="W61">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O62">
         <v>3.6</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,65 +10741,65 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="O64">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P64">
+        <v>4.8</v>
+      </c>
+      <c r="Q64">
+        <v>1.85</v>
+      </c>
+      <c r="R64">
+        <v>2.62</v>
+      </c>
+      <c r="S64">
+        <v>1.22</v>
+      </c>
+      <c r="T64">
         <v>4</v>
       </c>
-      <c r="Q64">
+      <c r="U64">
+        <v>2.1</v>
+      </c>
+      <c r="V64">
+        <v>1.67</v>
+      </c>
+      <c r="W64">
+        <v>1.17</v>
+      </c>
+      <c r="X64">
+        <v>1.02</v>
+      </c>
+      <c r="Y64">
+        <v>1.09</v>
+      </c>
+      <c r="Z64">
+        <v>5.71</v>
+      </c>
+      <c r="AA64">
+        <v>1.44</v>
+      </c>
+      <c r="AB64">
+        <v>2.74</v>
+      </c>
+      <c r="AC64">
+        <v>2.11</v>
+      </c>
+      <c r="AD64">
+        <v>1.67</v>
+      </c>
+      <c r="AE64">
+        <v>1.24</v>
+      </c>
+      <c r="AF64">
+        <v>1.55</v>
+      </c>
+      <c r="AG64">
         <v>2.3</v>
       </c>
-      <c r="R64">
-        <v>2.17</v>
-      </c>
-      <c r="S64">
-        <v>1.35</v>
-      </c>
-      <c r="T64">
-        <v>3</v>
-      </c>
-      <c r="U64">
-        <v>2.81</v>
-      </c>
-      <c r="V64">
-        <v>1.4</v>
-      </c>
-      <c r="W64">
-        <v>1.08</v>
-      </c>
-      <c r="X64">
-        <v>1</v>
-      </c>
-      <c r="Y64">
-        <v>1.25</v>
-      </c>
-      <c r="Z64">
-        <v>3.49</v>
-      </c>
-      <c r="AA64">
-        <v>1.88</v>
-      </c>
-      <c r="AB64">
-        <v>1.9</v>
-      </c>
-      <c r="AC64">
-        <v>3.04</v>
-      </c>
-      <c r="AD64">
-        <v>1.33</v>
-      </c>
-      <c r="AE64">
-        <v>1.11</v>
-      </c>
-      <c r="AF64">
-        <v>1.75</v>
-      </c>
-      <c r="AG64">
-        <v>1.93</v>
-      </c>
       <c r="AH64" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.48</v>
+        <v>4.6</v>
       </c>
       <c r="O65">
         <v>4.2</v>
       </c>
       <c r="P65">
-        <v>4.8</v>
+        <v>1.53</v>
       </c>
       <c r="Q65">
-        <v>1.85</v>
+        <v>5.05</v>
       </c>
       <c r="R65">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="S65">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T65">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U65">
         <v>2.12</v>
       </c>
       <c r="V65">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W65">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z65">
-        <v>5.71</v>
+        <v>4.95</v>
       </c>
       <c r="AA65">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB65">
-        <v>2.74</v>
+        <v>2.41</v>
       </c>
       <c r="AC65">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AD65">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AE65">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF65">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>4.6</v>
+        <v>1.73</v>
       </c>
       <c r="O66">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="Q66">
-        <v>5.05</v>
+        <v>2.3</v>
       </c>
       <c r="R66">
-        <v>2.46</v>
+        <v>2.17</v>
       </c>
       <c r="S66">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="T66">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="V66">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y66">
+        <v>1.25</v>
+      </c>
+      <c r="Z66">
+        <v>3.49</v>
+      </c>
+      <c r="AA66">
+        <v>1.88</v>
+      </c>
+      <c r="AB66">
+        <v>1.9</v>
+      </c>
+      <c r="AC66">
+        <v>3.04</v>
+      </c>
+      <c r="AD66">
+        <v>1.33</v>
+      </c>
+      <c r="AE66">
         <v>1.11</v>
       </c>
-      <c r="Z66">
-        <v>4.95</v>
-      </c>
-      <c r="AA66">
-        <v>1.45</v>
-      </c>
-      <c r="AB66">
-        <v>2.41</v>
-      </c>
-      <c r="AC66">
-        <v>2.25</v>
-      </c>
-      <c r="AD66">
-        <v>1.59</v>
-      </c>
-      <c r="AE66">
-        <v>1.23</v>
-      </c>
       <c r="AF66">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="O67">
-        <v>3.85</v>
+        <v>3.48</v>
       </c>
       <c r="P67">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q67">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="R67">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S67">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="U67">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="V67">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W67">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z67">
-        <v>5.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA67">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AB67">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="AC67">
-        <v>2.11</v>
+        <v>2.63</v>
       </c>
       <c r="AD67">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AE67">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AF67">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG67">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="O68">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P68">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q68">
-        <v>3.13</v>
+        <v>3.02</v>
       </c>
       <c r="R68">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="U68">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="V68">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z68">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AA68">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB68">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="AC68">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="AD68">
+        <v>1.65</v>
+      </c>
+      <c r="AE68">
+        <v>1.29</v>
+      </c>
+      <c r="AF68">
         <v>1.44</v>
       </c>
-      <c r="AE68">
-        <v>1.12</v>
-      </c>
-      <c r="AF68">
-        <v>1.57</v>
-      </c>
       <c r="AG68">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK68">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O70">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P70">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="Q70">
         <v>2.55</v>
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="O71">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="P71">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="Q71">
         <v>6.72</v>
       </c>
       <c r="R71">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="S71">
         <v>1.2</v>
@@ -11903,10 +11903,10 @@
         <v>4</v>
       </c>
       <c r="U71">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V71">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W71">
         <v>1.17</v>
@@ -11924,7 +11924,7 @@
         <v>1.4</v>
       </c>
       <c r="AB71">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AC71">
         <v>2.08</v>
@@ -11933,7 +11933,7 @@
         <v>1.72</v>
       </c>
       <c r="AE71">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF71">
         <v>1.62</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.13</v>
+        <v>2.95</v>
       </c>
       <c r="AK71">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12099,7 +12099,7 @@
         <v>1.01</v>
       </c>
       <c r="AF72">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG72">
         <v>1.75</v>
@@ -12217,55 +12217,55 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="O74">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P74">
-        <v>6.69</v>
+        <v>6.5</v>
       </c>
       <c r="Q74">
         <v>1.78</v>
@@ -12416,13 +12416,13 @@
         <v>2.31</v>
       </c>
       <c r="AC74">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AD74">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE74">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
         <v>1.75</v>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O75">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P75">
         <v>4.33</v>
@@ -12546,13 +12546,13 @@
         <v>1.95</v>
       </c>
       <c r="R75">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S75">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U75">
         <v>2.16</v>
@@ -12567,31 +12567,31 @@
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z75">
-        <v>5.68</v>
+        <v>5.64</v>
       </c>
       <c r="AA75">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AB75">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AC75">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AD75">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AE75">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF75">
         <v>1.44</v>
       </c>
       <c r="AG75">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK75">
         <v>2.17</v>
@@ -12860,22 +12860,22 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O77">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P77">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q77">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="R77">
         <v>2.17</v>
       </c>
       <c r="S77">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T77">
         <v>3.2</v>
@@ -12887,7 +12887,7 @@
         <v>1.44</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X77">
         <v>1.03</v>
@@ -12899,10 +12899,10 @@
         <v>3.85</v>
       </c>
       <c r="AA77">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB77">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC77">
         <v>2.88</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O78">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P78">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -13192,7 +13192,7 @@
         <v>3.5</v>
       </c>
       <c r="P79">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q79">
         <v>4.8</v>
@@ -13204,7 +13204,7 @@
         <v>1.38</v>
       </c>
       <c r="T79">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="U79">
         <v>2.56</v>
@@ -13213,7 +13213,7 @@
         <v>1.43</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X79">
         <v>1.03</v>
@@ -13530,7 +13530,7 @@
         <v>1.33</v>
       </c>
       <c r="T81">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U81">
         <v>2.75</v>
@@ -14197,10 +14197,10 @@
         <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z85">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA85">
         <v>1.93</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="P87">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="Q87">
-        <v>3.18</v>
+        <v>3.67</v>
       </c>
       <c r="R87">
-        <v>2.39</v>
+        <v>2.57</v>
       </c>
       <c r="S87">
+        <v>1.18</v>
+      </c>
+      <c r="T87">
+        <v>3.84</v>
+      </c>
+      <c r="U87">
+        <v>2.1</v>
+      </c>
+      <c r="V87">
+        <v>1.67</v>
+      </c>
+      <c r="W87">
         <v>1.17</v>
       </c>
-      <c r="T87">
-        <v>3.98</v>
-      </c>
-      <c r="U87">
-        <v>1.98</v>
-      </c>
-      <c r="V87">
-        <v>1.71</v>
-      </c>
-      <c r="W87">
-        <v>1.18</v>
-      </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z87">
-        <v>5.25</v>
+        <v>5.63</v>
       </c>
       <c r="AA87">
+        <v>1.44</v>
+      </c>
+      <c r="AB87">
+        <v>2.67</v>
+      </c>
+      <c r="AC87">
+        <v>2.12</v>
+      </c>
+      <c r="AD87">
+        <v>1.69</v>
+      </c>
+      <c r="AE87">
+        <v>1.28</v>
+      </c>
+      <c r="AF87">
         <v>1.4</v>
       </c>
-      <c r="AB87">
-        <v>2.56</v>
-      </c>
-      <c r="AC87">
-        <v>2.08</v>
-      </c>
-      <c r="AD87">
-        <v>1.7</v>
-      </c>
-      <c r="AE87">
-        <v>1.25</v>
-      </c>
-      <c r="AF87">
-        <v>1.38</v>
-      </c>
       <c r="AG87">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK87">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O88">
         <v>3.2</v>
@@ -14668,7 +14668,7 @@
         <v>2.06</v>
       </c>
       <c r="S88">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T88">
         <v>2.72</v>
@@ -14677,7 +14677,7 @@
         <v>2.59</v>
       </c>
       <c r="V88">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W88">
         <v>1.08</v>
@@ -14819,10 +14819,10 @@
         <v>1.75</v>
       </c>
       <c r="O89">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P89">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Q89">
         <v>2.41</v>
@@ -14979,10 +14979,10 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="O90">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="P90">
         <v>2.87</v>
@@ -15018,7 +15018,7 @@
         <v>3.14</v>
       </c>
       <c r="AA90">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB90">
         <v>1.71</v>
@@ -15157,13 +15157,13 @@
         <v>2.14</v>
       </c>
       <c r="S91">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T91">
         <v>3.25</v>
       </c>
       <c r="U91">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V91">
         <v>1.5</v>
@@ -15320,13 +15320,13 @@
         <v>2.25</v>
       </c>
       <c r="S92">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T92">
         <v>2.87</v>
       </c>
       <c r="U92">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="V92">
         <v>1.47</v>
@@ -15344,10 +15344,10 @@
         <v>3.99</v>
       </c>
       <c r="AA92">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB92">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC92">
         <v>2.9</v>
@@ -15658,7 +15658,7 @@
         <v>1.44</v>
       </c>
       <c r="W94">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X94">
         <v>1</v>
@@ -15673,7 +15673,7 @@
         <v>1.78</v>
       </c>
       <c r="AB94">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC94">
         <v>2.82</v>
@@ -15797,7 +15797,7 @@
         <v>2.32</v>
       </c>
       <c r="O95">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="P95">
         <v>2.57</v>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="O96">
         <v>4.5</v>
@@ -17916,61 +17916,61 @@
         <v>2.45</v>
       </c>
       <c r="O108">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P108">
         <v>2.5</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O109">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P109">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA109">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB109">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O110">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P110">
-        <v>4.43</v>
+        <v>3.9</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA110">
         <v>2.2</v>
       </c>
       <c r="AB110">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18571,7 +18571,7 @@
         <v>3.2</v>
       </c>
       <c r="P112">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -18580,10 +18580,10 @@
         <v>2.16</v>
       </c>
       <c r="S112">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T112">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="U112">
         <v>3</v>
@@ -18734,7 +18734,7 @@
         <v>3.25</v>
       </c>
       <c r="P113">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q113">
         <v>2.97</v>
@@ -18761,22 +18761,22 @@
         <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z113">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA113">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB113">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC113">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD113">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE113">
         <v>1.12</v>
@@ -18785,7 +18785,7 @@
         <v>1.67</v>
       </c>
       <c r="AG113">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>5.6</v>
       </c>
       <c r="P116">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Q116">
         <v>1.75</v>
@@ -19250,16 +19250,16 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z116">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA116">
         <v>1.28</v>
       </c>
       <c r="AB116">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AC116">
         <v>1.69</v>
@@ -19268,7 +19268,7 @@
         <v>2.2</v>
       </c>
       <c r="AE116">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AF116">
         <v>1.44</v>
@@ -19380,31 +19380,31 @@
         </is>
       </c>
       <c r="N117">
-        <v>5.5</v>
+        <v>6.42</v>
       </c>
       <c r="O117">
-        <v>4.2</v>
+        <v>4.57</v>
       </c>
       <c r="P117">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Q117">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R117">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S117">
         <v>1.28</v>
       </c>
       <c r="T117">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U117">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V117">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W117">
         <v>1.11</v>
@@ -19416,28 +19416,28 @@
         <v>1.17</v>
       </c>
       <c r="Z117">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA117">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB117">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC117">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD117">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE117">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF117">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG117">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>1.17</v>
       </c>
       <c r="AK117">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19549,7 +19549,7 @@
         <v>3.63</v>
       </c>
       <c r="P118">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="Q118">
         <v>2.52</v>
@@ -19570,10 +19570,10 @@
         <v>1.5</v>
       </c>
       <c r="W118">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
         <v>1.19</v>
@@ -19594,7 +19594,7 @@
         <v>1.43</v>
       </c>
       <c r="AE118">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF118">
         <v>1.55</v>
@@ -20358,7 +20358,7 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="O123">
         <v>3.45</v>
@@ -20376,40 +20376,40 @@
         <v>1.38</v>
       </c>
       <c r="T123">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U123">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V123">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W123">
         <v>1.06</v>
       </c>
       <c r="X123">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z123">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA123">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB123">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC123">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD123">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE123">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF123">
         <v>1.75</v>
@@ -20539,7 +20539,7 @@
         <v>1.3</v>
       </c>
       <c r="T124">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U124">
         <v>2.63</v>
@@ -20563,7 +20563,7 @@
         <v>1.72</v>
       </c>
       <c r="AB124">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC124">
         <v>2.7</v>
@@ -20696,7 +20696,7 @@
         <v>3.4</v>
       </c>
       <c r="R125">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S125">
         <v>1.29</v>
@@ -20705,16 +20705,16 @@
         <v>3.3</v>
       </c>
       <c r="U125">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V125">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W125">
         <v>1.08</v>
       </c>
       <c r="X125">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y125">
         <v>1.22</v>
@@ -20732,7 +20732,7 @@
         <v>2.76</v>
       </c>
       <c r="AD125">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE125">
         <v>1.13</v>
@@ -20741,7 +20741,7 @@
         <v>1.61</v>
       </c>
       <c r="AG125">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK125">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21034,7 +21034,7 @@
         <v>3</v>
       </c>
       <c r="V127">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W127">
         <v>1.05</v>
@@ -21058,10 +21058,10 @@
         <v>3.4</v>
       </c>
       <c r="AD127">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE127">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF127">
         <v>1.85</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="O128">
         <v>4.3</v>
       </c>
       <c r="P128">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="Q128">
         <v>4.5</v>
@@ -21514,7 +21514,7 @@
         <v>2.31</v>
       </c>
       <c r="S130">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T130">
         <v>3</v>
@@ -21828,10 +21828,10 @@
         <v>1.89</v>
       </c>
       <c r="O132">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P132">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q132">
         <v>2.38</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22151,10 +22151,10 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="O134">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="P134">
         <v>8</v>
@@ -22809,7 +22809,7 @@
         <v>3.1</v>
       </c>
       <c r="P138">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q138">
         <v>2.8</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="O5">
         <v>5.1</v>
       </c>
       <c r="P5">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="O26">
         <v>6.5</v>
       </c>
       <c r="P26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>6.26</v>
       </c>
       <c r="AA39">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB39">
         <v>2.89</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O42">
-        <v>3.64</v>
+        <v>3.15</v>
       </c>
       <c r="P42">
         <v>3.44</v>
@@ -7197,7 +7197,7 @@
         <v>1.8</v>
       </c>
       <c r="AB42">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC42">
         <v>2.87</v>
@@ -7206,7 +7206,7 @@
         <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
         <v>1.67</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="O45">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="P45">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="Q45">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="R45">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="S45">
         <v>1.19</v>
@@ -7680,16 +7680,16 @@
         <v>1.12</v>
       </c>
       <c r="Z45">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA45">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB45">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AC45">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AD45">
         <v>1.57</v>
@@ -7698,10 +7698,10 @@
         <v>1.18</v>
       </c>
       <c r="AF45">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG45">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK45">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7822,19 +7822,19 @@
         <v>2.27</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
         <v>1.57</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7861,10 +7861,10 @@
         <v>1.16</v>
       </c>
       <c r="AF46">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P49">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="Q49">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="R49">
+        <v>2.09</v>
+      </c>
+      <c r="S49">
+        <v>1.33</v>
+      </c>
+      <c r="T49">
+        <v>2.85</v>
+      </c>
+      <c r="U49">
+        <v>2.64</v>
+      </c>
+      <c r="V49">
+        <v>1.38</v>
+      </c>
+      <c r="W49">
+        <v>1.04</v>
+      </c>
+      <c r="X49">
+        <v>1</v>
+      </c>
+      <c r="Y49">
+        <v>1.22</v>
+      </c>
+      <c r="Z49">
+        <v>3.5</v>
+      </c>
+      <c r="AA49">
+        <v>1.95</v>
+      </c>
+      <c r="AB49">
+        <v>1.85</v>
+      </c>
+      <c r="AC49">
+        <v>2.97</v>
+      </c>
+      <c r="AD49">
+        <v>1.3</v>
+      </c>
+      <c r="AE49">
+        <v>1.07</v>
+      </c>
+      <c r="AF49">
+        <v>1.64</v>
+      </c>
+      <c r="AG49">
         <v>2.1</v>
-      </c>
-      <c r="S49">
-        <v>1.36</v>
-      </c>
-      <c r="T49">
-        <v>2.88</v>
-      </c>
-      <c r="U49">
-        <v>2.85</v>
-      </c>
-      <c r="V49">
-        <v>1.33</v>
-      </c>
-      <c r="W49">
-        <v>1.05</v>
-      </c>
-      <c r="X49">
-        <v>1.02</v>
-      </c>
-      <c r="Y49">
-        <v>1.26</v>
-      </c>
-      <c r="Z49">
-        <v>3.2</v>
-      </c>
-      <c r="AA49">
-        <v>2.05</v>
-      </c>
-      <c r="AB49">
-        <v>1.75</v>
-      </c>
-      <c r="AC49">
-        <v>3.34</v>
-      </c>
-      <c r="AD49">
-        <v>1.24</v>
-      </c>
-      <c r="AE49">
-        <v>1.04</v>
-      </c>
-      <c r="AF49">
-        <v>1.72</v>
-      </c>
-      <c r="AG49">
-        <v>1.98</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="O50">
-        <v>3.46</v>
+        <v>3.33</v>
       </c>
       <c r="P50">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="Q50">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="R50">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U50">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="V50">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA50">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB50">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC50">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="AD50">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AG50">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK50">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P51">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="Q51">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
+        <v>1.36</v>
+      </c>
+      <c r="T51">
+        <v>2.88</v>
+      </c>
+      <c r="U51">
+        <v>2.85</v>
+      </c>
+      <c r="V51">
         <v>1.33</v>
       </c>
-      <c r="T51">
-        <v>2.85</v>
-      </c>
-      <c r="U51">
-        <v>2.68</v>
-      </c>
-      <c r="V51">
-        <v>1.37</v>
-      </c>
       <c r="W51">
+        <v>1.05</v>
+      </c>
+      <c r="X51">
+        <v>1.02</v>
+      </c>
+      <c r="Y51">
+        <v>1.26</v>
+      </c>
+      <c r="Z51">
+        <v>3.2</v>
+      </c>
+      <c r="AA51">
+        <v>2.05</v>
+      </c>
+      <c r="AB51">
+        <v>1.75</v>
+      </c>
+      <c r="AC51">
+        <v>3.34</v>
+      </c>
+      <c r="AD51">
+        <v>1.24</v>
+      </c>
+      <c r="AE51">
         <v>1.04</v>
       </c>
-      <c r="X51">
-        <v>1</v>
-      </c>
-      <c r="Y51">
-        <v>1.22</v>
-      </c>
-      <c r="Z51">
-        <v>3.5</v>
-      </c>
-      <c r="AA51">
-        <v>1.95</v>
-      </c>
-      <c r="AB51">
-        <v>1.85</v>
-      </c>
-      <c r="AC51">
-        <v>3.05</v>
-      </c>
-      <c r="AD51">
-        <v>1.28</v>
-      </c>
-      <c r="AE51">
-        <v>1.06</v>
-      </c>
       <c r="AF51">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AG51">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="O52">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q52">
-        <v>3.2</v>
+        <v>2.49</v>
       </c>
       <c r="R52">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U52">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="V52">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W52">
+        <v>1.04</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52">
+        <v>1.22</v>
+      </c>
+      <c r="Z52">
+        <v>3.5</v>
+      </c>
+      <c r="AA52">
+        <v>1.95</v>
+      </c>
+      <c r="AB52">
+        <v>1.85</v>
+      </c>
+      <c r="AC52">
+        <v>3.05</v>
+      </c>
+      <c r="AD52">
+        <v>1.28</v>
+      </c>
+      <c r="AE52">
         <v>1.06</v>
       </c>
-      <c r="X52">
-        <v>1.02</v>
-      </c>
-      <c r="Y52">
-        <v>1.3</v>
-      </c>
-      <c r="Z52">
-        <v>2.97</v>
-      </c>
-      <c r="AA52">
-        <v>2.15</v>
-      </c>
-      <c r="AB52">
-        <v>1.66</v>
-      </c>
-      <c r="AC52">
-        <v>3.42</v>
-      </c>
-      <c r="AD52">
-        <v>1.23</v>
-      </c>
-      <c r="AE52">
-        <v>1.05</v>
-      </c>
       <c r="AF52">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AG52">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK52">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.17</v>
+        <v>1.52</v>
       </c>
       <c r="O57">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="P57">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="Q57">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S57">
         <v>1.25</v>
       </c>
       <c r="T57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U57">
         <v>2.25</v>
@@ -9630,34 +9630,34 @@
         <v>1.15</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
         <v>1.15</v>
       </c>
       <c r="Z57">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA57">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB57">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AD57">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE57">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF57">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG57">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK57">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="O58">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="Q58">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="R58">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S58">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T58">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U58">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="V58">
         <v>1.5</v>
       </c>
       <c r="W58">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA58">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB58">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AC58">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="AD58">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE58">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG58">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK58">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9935,22 +9935,22 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R59">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S59">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="U59">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="V59">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W59">
         <v>1.12</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
         <v>1.67</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="O60">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P60">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="R60">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S60">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="T60">
-        <v>3.08</v>
+        <v>3.46</v>
       </c>
       <c r="U60">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="V60">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W60">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AA60">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB60">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AC60">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AD60">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AE60">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF60">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AG60">
-        <v>1.99</v>
+        <v>2.39</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11891,7 +11891,7 @@
         <v>7.1</v>
       </c>
       <c r="Q71">
-        <v>6.72</v>
+        <v>6</v>
       </c>
       <c r="R71">
         <v>2.71</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q73">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S73">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U73">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V73">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W73">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y73">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z73">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB73">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC73">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD73">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF73">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG73">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,10 +12374,10 @@
         <v>1.35</v>
       </c>
       <c r="O74">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P74">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q74">
         <v>1.78</v>
@@ -12410,10 +12410,10 @@
         <v>4.5</v>
       </c>
       <c r="AA74">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB74">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC74">
         <v>2.27</v>
@@ -14490,19 +14490,19 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="O87">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="P87">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q87">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="R87">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="S87">
         <v>1.18</v>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="O95">
         <v>3.32</v>
@@ -15963,7 +15963,7 @@
         <v>4.5</v>
       </c>
       <c r="P96">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q96">
         <v>2.04</v>
@@ -15999,7 +15999,7 @@
         <v>1.4</v>
       </c>
       <c r="AB96">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC96">
         <v>2.12</v>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O108">
         <v>3.25</v>
@@ -17955,7 +17955,7 @@
         <v>1.87</v>
       </c>
       <c r="AB108">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC108">
         <v>2.92</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="O109">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P109">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="Q109">
-        <v>2.81</v>
+        <v>2.42</v>
       </c>
       <c r="R109">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S109">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T109">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U109">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="V109">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X109">
+        <v>1.02</v>
+      </c>
+      <c r="Y109">
+        <v>1.36</v>
+      </c>
+      <c r="Z109">
+        <v>2.7</v>
+      </c>
+      <c r="AA109">
+        <v>2.2</v>
+      </c>
+      <c r="AB109">
+        <v>1.57</v>
+      </c>
+      <c r="AC109">
+        <v>4.15</v>
+      </c>
+      <c r="AD109">
+        <v>1.16</v>
+      </c>
+      <c r="AE109">
         <v>1.01</v>
       </c>
-      <c r="Y109">
-        <v>1.28</v>
-      </c>
-      <c r="Z109">
-        <v>3.05</v>
-      </c>
-      <c r="AA109">
-        <v>2.1</v>
-      </c>
-      <c r="AB109">
-        <v>1.75</v>
-      </c>
-      <c r="AC109">
-        <v>3.42</v>
-      </c>
-      <c r="AD109">
-        <v>1.23</v>
-      </c>
-      <c r="AE109">
-        <v>1.04</v>
-      </c>
       <c r="AF109">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="AG109">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK109">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="O110">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P110">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="Q110">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="R110">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S110">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U110">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="V110">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
         <v>1.01</v>
       </c>
-      <c r="X110">
-        <v>1.02</v>
-      </c>
       <c r="Y110">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z110">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AA110">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB110">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AC110">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="AD110">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE110">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>2.01</v>
+        <v>1.76</v>
       </c>
       <c r="AG110">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK110">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O114">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P114">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="O115">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q115">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="R115">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S115">
         <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="U115">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V115">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W115">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z115">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA115">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AB115">
         <v>1.67</v>
       </c>
       <c r="AC115">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="AD115">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE115">
         <v>1.03</v>
       </c>
       <c r="AF115">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG115">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AK115">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,10 +19217,10 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="O116">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="P116">
         <v>6</v>
@@ -19256,10 +19256,10 @@
         <v>8</v>
       </c>
       <c r="AA116">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AB116">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AC116">
         <v>1.69</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O123">
         <v>3.45</v>
       </c>
       <c r="P123">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="Q123">
         <v>2.56</v>
@@ -20400,7 +20400,7 @@
         <v>1.9</v>
       </c>
       <c r="AB123">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC123">
         <v>3.4</v>
@@ -20563,7 +20563,7 @@
         <v>1.72</v>
       </c>
       <c r="AB124">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC124">
         <v>2.7</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="O133">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P133">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22172,7 +22172,7 @@
         <v>3.48</v>
       </c>
       <c r="U134">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="V134">
         <v>1.62</v>
@@ -22187,13 +22187,13 @@
         <v>1.12</v>
       </c>
       <c r="Z134">
-        <v>5.39</v>
+        <v>4.75</v>
       </c>
       <c r="AA134">
         <v>1.49</v>
       </c>
       <c r="AB134">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AC134">
         <v>2.29</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="O138">
         <v>3.1</v>
       </c>
       <c r="P138">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="Q138">
         <v>2.8</v>
@@ -22842,7 +22842,7 @@
         <v>2.83</v>
       </c>
       <c r="AA138">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB138">
         <v>1.66</v>
@@ -22876,7 +22876,7 @@
         <v>1.35</v>
       </c>
       <c r="AK138">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AL138">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O2">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="P2">
         <v>3.05</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
         <v>3.5</v>
@@ -7025,16 +7025,16 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z41">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="AA41">
         <v>2.17</v>
       </c>
       <c r="AB41">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC41">
         <v>3.95</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="O50">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="P50">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="Q50">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R50">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S50">
         <v>1.36</v>
       </c>
       <c r="T50">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U50">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
+        <v>1.26</v>
+      </c>
+      <c r="Z50">
+        <v>3.2</v>
+      </c>
+      <c r="AA50">
+        <v>2.05</v>
+      </c>
+      <c r="AB50">
+        <v>1.75</v>
+      </c>
+      <c r="AC50">
+        <v>3.34</v>
+      </c>
+      <c r="AD50">
+        <v>1.24</v>
+      </c>
+      <c r="AE50">
+        <v>1.04</v>
+      </c>
+      <c r="AF50">
+        <v>1.72</v>
+      </c>
+      <c r="AG50">
+        <v>1.98</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.3</v>
       </c>
-      <c r="Z50">
-        <v>2.97</v>
-      </c>
-      <c r="AA50">
-        <v>2.15</v>
-      </c>
-      <c r="AB50">
-        <v>1.66</v>
-      </c>
-      <c r="AC50">
-        <v>3.42</v>
-      </c>
-      <c r="AD50">
-        <v>1.23</v>
-      </c>
-      <c r="AE50">
-        <v>1.05</v>
-      </c>
-      <c r="AF50">
-        <v>1.76</v>
-      </c>
-      <c r="AG50">
-        <v>1.94</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.32</v>
-      </c>
       <c r="AK50">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="Q51">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="R51">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U51">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB51">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC51">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE51">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AG51">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="P52">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q52">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="R52">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="S52">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U52">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="V52">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA52">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB52">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC52">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AD52">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE52">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG52">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK52">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9132,7 +9132,7 @@
         <v>3.02</v>
       </c>
       <c r="U54">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V54">
         <v>1.44</v>
@@ -9150,13 +9150,13 @@
         <v>3.8</v>
       </c>
       <c r="AA54">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB54">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC54">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD54">
         <v>1.34</v>
@@ -9184,7 +9184,7 @@
         <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9280,7 +9280,7 @@
         <v>3.5</v>
       </c>
       <c r="P55">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q55">
         <v>2.7</v>
@@ -9476,7 +9476,7 @@
         <v>5.9</v>
       </c>
       <c r="AA56">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB56">
         <v>2.74</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -9941,49 +9941,49 @@
         <v>2.3</v>
       </c>
       <c r="S59">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T59">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="U59">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="V59">
         <v>1.55</v>
       </c>
       <c r="W59">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
         <v>1.14</v>
       </c>
       <c r="Z59">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="AA59">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB59">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AC59">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AD59">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE59">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF59">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG59">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK59">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -10104,50 +10104,50 @@
         <v>2.3</v>
       </c>
       <c r="S60">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="U60">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="V60">
         <v>1.55</v>
       </c>
       <c r="W60">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
         <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA60">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB60">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AC60">
+        <v>2.43</v>
+      </c>
+      <c r="AD60">
+        <v>1.44</v>
+      </c>
+      <c r="AE60">
+        <v>1.14</v>
+      </c>
+      <c r="AF60">
+        <v>1.53</v>
+      </c>
+      <c r="AG60">
         <v>2.38</v>
       </c>
-      <c r="AD60">
-        <v>1.46</v>
-      </c>
-      <c r="AE60">
-        <v>1.16</v>
-      </c>
-      <c r="AF60">
-        <v>1.49</v>
-      </c>
-      <c r="AG60">
-        <v>2.39</v>
-      </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK60">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O64">
         <v>4.2</v>
@@ -10750,10 +10750,10 @@
         <v>4.8</v>
       </c>
       <c r="Q64">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="R64">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="S64">
         <v>1.22</v>
@@ -10774,16 +10774,16 @@
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z64">
-        <v>5.71</v>
+        <v>5.64</v>
       </c>
       <c r="AA64">
         <v>1.44</v>
       </c>
       <c r="AB64">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="AC64">
         <v>2.11</v>
@@ -10792,7 +10792,7 @@
         <v>1.67</v>
       </c>
       <c r="AE64">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF64">
         <v>1.55</v>
@@ -10946,7 +10946,7 @@
         <v>1.45</v>
       </c>
       <c r="AB65">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AC65">
         <v>2.25</v>
@@ -11073,7 +11073,7 @@
         <v>3.5</v>
       </c>
       <c r="P66">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q66">
         <v>2.3</v>
@@ -11082,7 +11082,7 @@
         <v>2.17</v>
       </c>
       <c r="S66">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T66">
         <v>3</v>
@@ -11287,7 +11287,7 @@
         <v>1.57</v>
       </c>
       <c r="AG67">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>3.85</v>
       </c>
       <c r="P68">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q68">
         <v>3.02</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O72">
         <v>3.3</v>
@@ -12217,34 +12217,34 @@
         <v>2.66</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA73">
         <v>1.93</v>
@@ -12253,19 +12253,19 @@
         <v>1.88</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,7 +12374,7 @@
         <v>1.35</v>
       </c>
       <c r="O74">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P74">
         <v>6.75</v>
@@ -12410,10 +12410,10 @@
         <v>4.5</v>
       </c>
       <c r="AA74">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB74">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC74">
         <v>2.27</v>
@@ -12573,10 +12573,10 @@
         <v>5.64</v>
       </c>
       <c r="AA75">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB75">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC75">
         <v>2.01</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O78">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P78">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -13041,7 +13041,7 @@
         <v>1.33</v>
       </c>
       <c r="T78">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U78">
         <v>2.4</v>
@@ -13062,10 +13062,10 @@
         <v>4.3</v>
       </c>
       <c r="AA78">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB78">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC78">
         <v>2.49</v>
@@ -13358,10 +13358,10 @@
         <v>1.91</v>
       </c>
       <c r="Q80">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R80">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S80">
         <v>1.25</v>
@@ -13388,10 +13388,10 @@
         <v>4.3</v>
       </c>
       <c r="AA80">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB80">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC80">
         <v>2.35</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O81">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P81">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -13551,7 +13551,7 @@
         <v>3.5</v>
       </c>
       <c r="AA81">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB81">
         <v>1.95</v>
@@ -13859,7 +13859,7 @@
         <v>4.5</v>
       </c>
       <c r="U83">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V83">
         <v>1.7</v>
@@ -13877,7 +13877,7 @@
         <v>6.5</v>
       </c>
       <c r="AA83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB83">
         <v>2.62</v>
@@ -13892,7 +13892,7 @@
         <v>1.29</v>
       </c>
       <c r="AF83">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG83">
         <v>3</v>
@@ -14055,7 +14055,7 @@
         <v>1.24</v>
       </c>
       <c r="AF84">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG84">
         <v>2.34</v>
@@ -14203,10 +14203,10 @@
         <v>3.25</v>
       </c>
       <c r="AA85">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB85">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC85">
         <v>3.42</v>
@@ -14671,10 +14671,10 @@
         <v>1.33</v>
       </c>
       <c r="T88">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="U88">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="V88">
         <v>1.4</v>
@@ -14692,10 +14692,10 @@
         <v>3.4</v>
       </c>
       <c r="AA88">
+        <v>1.95</v>
+      </c>
+      <c r="AB88">
         <v>1.85</v>
-      </c>
-      <c r="AB88">
-        <v>1.82</v>
       </c>
       <c r="AC88">
         <v>3.3</v>
@@ -14704,7 +14704,7 @@
         <v>1.3</v>
       </c>
       <c r="AE88">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF88">
         <v>1.7</v>
@@ -14855,10 +14855,10 @@
         <v>3.14</v>
       </c>
       <c r="AA89">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB89">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC89">
         <v>3.6</v>
@@ -14985,7 +14985,7 @@
         <v>3.38</v>
       </c>
       <c r="P90">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="Q90">
         <v>2.88</v>
@@ -15018,10 +15018,10 @@
         <v>3.14</v>
       </c>
       <c r="AA90">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB90">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC90">
         <v>3.8</v>
@@ -15181,10 +15181,10 @@
         <v>4.1</v>
       </c>
       <c r="AA91">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB91">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC91">
         <v>2.83</v>
@@ -15305,10 +15305,10 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="O92">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P92">
         <v>4.4</v>
@@ -15347,7 +15347,7 @@
         <v>1.8</v>
       </c>
       <c r="AB92">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC92">
         <v>2.9</v>
@@ -15634,10 +15634,10 @@
         <v>3.1</v>
       </c>
       <c r="O94">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P94">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q94">
         <v>3.81</v>
@@ -15670,7 +15670,7 @@
         <v>3.89</v>
       </c>
       <c r="AA94">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB94">
         <v>2.05</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="O97">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P97">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -16138,7 +16138,7 @@
         <v>1.14</v>
       </c>
       <c r="T97">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U97">
         <v>1.91</v>
@@ -16162,7 +16162,7 @@
         <v>1.3</v>
       </c>
       <c r="AB97">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AC97">
         <v>1.87</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P98">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Q98">
         <v>2.46</v>
@@ -16301,7 +16301,7 @@
         <v>1.22</v>
       </c>
       <c r="T98">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="U98">
         <v>2.1</v>
@@ -16325,7 +16325,7 @@
         <v>1.42</v>
       </c>
       <c r="AB98">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AC98">
         <v>2.06</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="O99">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P99">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q99">
         <v>2.1</v>
@@ -16461,10 +16461,10 @@
         <v>2.63</v>
       </c>
       <c r="S99">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T99">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="U99">
         <v>1.91</v>
@@ -16473,7 +16473,7 @@
         <v>1.8</v>
       </c>
       <c r="W99">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X99">
         <v>1.01</v>
@@ -16612,10 +16612,10 @@
         <v>2.3</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="Q100">
         <v>2.8</v>
@@ -16636,7 +16636,7 @@
         <v>1.58</v>
       </c>
       <c r="W100">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X100">
         <v>1.01</v>
@@ -16772,10 +16772,10 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O101">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P101">
         <v>2.37</v>
@@ -16787,7 +16787,7 @@
         <v>2.46</v>
       </c>
       <c r="S101">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T101">
         <v>3.98</v>
@@ -16811,10 +16811,10 @@
         <v>6.16</v>
       </c>
       <c r="AA101">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB101">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AC101">
         <v>1.98</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="O102">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q102">
         <v>2.33</v>
@@ -16956,10 +16956,10 @@
         <v>3.6</v>
       </c>
       <c r="U102">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="V102">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W102">
         <v>1.11</v>
@@ -16977,7 +16977,7 @@
         <v>1.63</v>
       </c>
       <c r="AB102">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC102">
         <v>2.53</v>
@@ -17098,34 +17098,34 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="O103">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="Q103">
         <v>2.63</v>
       </c>
       <c r="R103">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="S103">
         <v>1.2</v>
       </c>
       <c r="T103">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U103">
         <v>1.95</v>
       </c>
       <c r="V103">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W103">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X103">
         <v>1.01</v>
@@ -17137,7 +17137,7 @@
         <v>6.25</v>
       </c>
       <c r="AA103">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB103">
         <v>2.93</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="O104">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P104">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -17282,28 +17282,28 @@
         <v>4</v>
       </c>
       <c r="U104">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V104">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W104">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X104">
         <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z104">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="AA104">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB104">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AC104">
         <v>2.09</v>
@@ -17318,7 +17318,7 @@
         <v>1.39</v>
       </c>
       <c r="AG104">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17427,10 +17427,10 @@
         <v>1.61</v>
       </c>
       <c r="O105">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P105">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q105">
         <v>2.09</v>
@@ -17457,16 +17457,16 @@
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z105">
         <v>5.86</v>
       </c>
       <c r="AA105">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB105">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AC105">
         <v>2.03</v>
@@ -17626,7 +17626,7 @@
         <v>7.5</v>
       </c>
       <c r="AA106">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB106">
         <v>3</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="O108">
         <v>3.25</v>
       </c>
       <c r="P108">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q108">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="R108">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="S108">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T108">
-        <v>2.85</v>
+        <v>2.48</v>
       </c>
       <c r="U108">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="V108">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="W108">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X108">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z108">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AA108">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AB108">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC108">
-        <v>2.92</v>
+        <v>4.15</v>
       </c>
       <c r="AD108">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AE108">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF108">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="AG108">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK108">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O109">
         <v>3.25</v>
       </c>
       <c r="P109">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q109">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="R109">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="S109">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T109">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="U109">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="V109">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="W109">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y109">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z109">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="AA109">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AB109">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC109">
-        <v>4.15</v>
+        <v>2.92</v>
       </c>
       <c r="AD109">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AE109">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF109">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AG109">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK109">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O111">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P111">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18571,7 +18571,7 @@
         <v>3.2</v>
       </c>
       <c r="P112">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -18589,10 +18589,10 @@
         <v>3</v>
       </c>
       <c r="V112">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
         <v>1.02</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="O113">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P113">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q113">
         <v>2.97</v>
@@ -18767,7 +18767,7 @@
         <v>3.6</v>
       </c>
       <c r="AA113">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB113">
         <v>1.88</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="O114">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P114">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="Q114">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="R114">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="S114">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T114">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U114">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="V114">
+        <v>1.33</v>
+      </c>
+      <c r="W114">
+        <v>1.06</v>
+      </c>
+      <c r="X114">
+        <v>1.02</v>
+      </c>
+      <c r="Y114">
+        <v>1.33</v>
+      </c>
+      <c r="Z114">
+        <v>2.83</v>
+      </c>
+      <c r="AA114">
+        <v>2.15</v>
+      </c>
+      <c r="AB114">
+        <v>1.67</v>
+      </c>
+      <c r="AC114">
+        <v>3.84</v>
+      </c>
+      <c r="AD114">
+        <v>1.18</v>
+      </c>
+      <c r="AE114">
+        <v>1.03</v>
+      </c>
+      <c r="AF114">
+        <v>1.82</v>
+      </c>
+      <c r="AG114">
+        <v>1.85</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
         <v>1.42</v>
       </c>
-      <c r="W114">
-        <v>1.1</v>
-      </c>
-      <c r="X114">
-        <v>1</v>
-      </c>
-      <c r="Y114">
-        <v>1.23</v>
-      </c>
-      <c r="Z114">
-        <v>3.42</v>
-      </c>
-      <c r="AA114">
-        <v>1.9</v>
-      </c>
-      <c r="AB114">
-        <v>1.9</v>
-      </c>
-      <c r="AC114">
-        <v>2.92</v>
-      </c>
-      <c r="AD114">
-        <v>1.31</v>
-      </c>
-      <c r="AE114">
-        <v>1.08</v>
-      </c>
-      <c r="AF114">
-        <v>1.69</v>
-      </c>
-      <c r="AG114">
-        <v>2</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.21</v>
-      </c>
       <c r="AK114">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="O115">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P115">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="Q115">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="R115">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="S115">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T115">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U115">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="V115">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y115">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z115">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="AA115">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB115">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC115">
-        <v>3.84</v>
+        <v>2.92</v>
       </c>
       <c r="AD115">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AE115">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AG115">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AK115">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19223,16 +19223,16 @@
         <v>5.7</v>
       </c>
       <c r="P116">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="Q116">
         <v>1.75</v>
       </c>
       <c r="R116">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="S116">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T116">
         <v>4.8</v>
@@ -19250,7 +19250,7 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z116">
         <v>8</v>
@@ -19271,10 +19271,10 @@
         <v>1.47</v>
       </c>
       <c r="AF116">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG116">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19395,10 +19395,10 @@
         <v>2.33</v>
       </c>
       <c r="S117">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T117">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U117">
         <v>2.45</v>
@@ -19410,7 +19410,7 @@
         <v>1.11</v>
       </c>
       <c r="X117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
         <v>1.17</v>
@@ -19419,10 +19419,10 @@
         <v>3.98</v>
       </c>
       <c r="AA117">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB117">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC117">
         <v>2.7</v>
@@ -19434,10 +19434,10 @@
         <v>1.1</v>
       </c>
       <c r="AF117">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG117">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>1.43</v>
       </c>
       <c r="AE118">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF118">
         <v>1.55</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="O119">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P119">
-        <v>4.18</v>
+        <v>3.45</v>
       </c>
       <c r="Q119">
         <v>2.31</v>
@@ -19745,10 +19745,10 @@
         <v>4.5</v>
       </c>
       <c r="AA119">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB119">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AC119">
         <v>2.41</v>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK119">
         <v>1.98</v>
@@ -19869,19 +19869,19 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="O120">
         <v>3.55</v>
       </c>
       <c r="P120">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
       </c>
       <c r="R120">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S120">
         <v>1.26</v>
@@ -19890,7 +19890,7 @@
         <v>3.4</v>
       </c>
       <c r="U120">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V120">
         <v>1.53</v>
@@ -19902,22 +19902,22 @@
         <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z120">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AA120">
         <v>1.68</v>
       </c>
       <c r="AB120">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC120">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AD120">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE120">
         <v>1.12</v>
@@ -19926,7 +19926,7 @@
         <v>1.57</v>
       </c>
       <c r="AG120">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20032,19 +20032,19 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="O121">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P121">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="Q121">
-        <v>5.78</v>
+        <v>4.39</v>
       </c>
       <c r="R121">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S121">
         <v>1.32</v>
@@ -20062,16 +20062,16 @@
         <v>1.09</v>
       </c>
       <c r="X121">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
         <v>1.17</v>
       </c>
       <c r="Z121">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="AA121">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB121">
         <v>2.08</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK121">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,19 +20195,19 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O122">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="P122">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Q122">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R122">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="S122">
         <v>1.29</v>
@@ -20234,10 +20234,10 @@
         <v>4</v>
       </c>
       <c r="AA122">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB122">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC122">
         <v>2.68</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20723,10 +20723,10 @@
         <v>3.74</v>
       </c>
       <c r="AA125">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB125">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC125">
         <v>2.76</v>
@@ -20847,31 +20847,31 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="O126">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="P126">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="Q126">
         <v>1.5</v>
       </c>
       <c r="R126">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="S126">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T126">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="U126">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="V126">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W126">
         <v>1.18</v>
@@ -20880,31 +20880,31 @@
         <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z126">
-        <v>5.76</v>
+        <v>6</v>
       </c>
       <c r="AA126">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB126">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="AC126">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AD126">
         <v>1.75</v>
       </c>
       <c r="AE126">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF126">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AG126">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK126">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O127">
         <v>3.6</v>
@@ -21049,7 +21049,7 @@
         <v>3.08</v>
       </c>
       <c r="AA127">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AB127">
         <v>1.78</v>
@@ -21173,10 +21173,10 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="O128">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P128">
         <v>1.48</v>
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="O130">
         <v>3.75</v>
@@ -21511,7 +21511,7 @@
         <v>2.19</v>
       </c>
       <c r="R130">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S130">
         <v>1.33</v>
@@ -21538,7 +21538,7 @@
         <v>3.14</v>
       </c>
       <c r="AA130">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB130">
         <v>1.85</v>
@@ -22190,10 +22190,10 @@
         <v>4.75</v>
       </c>
       <c r="AA134">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB134">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC134">
         <v>2.29</v>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK134">
         <v>3.1</v>
@@ -22492,7 +22492,7 @@
         <v>2.3</v>
       </c>
       <c r="S136">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T136">
         <v>3.3</v>
@@ -22501,40 +22501,40 @@
         <v>2.4</v>
       </c>
       <c r="V136">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W136">
         <v>1.08</v>
       </c>
       <c r="X136">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z136">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA136">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB136">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC136">
-        <v>2.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD136">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AE136">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF136">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG136">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22975,10 +22975,10 @@
         <v>2.51</v>
       </c>
       <c r="Q139">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R139">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S139">
         <v>1.22</v>
@@ -23011,7 +23011,7 @@
         <v>2.31</v>
       </c>
       <c r="AC139">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AD139">
         <v>1.49</v>
@@ -23183,10 +23183,10 @@
         <v>1.24</v>
       </c>
       <c r="AF140">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG140">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -970,25 +970,25 @@
         <v>2.66</v>
       </c>
       <c r="Q4">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="R4">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1000,10 +1000,10 @@
         <v>3.2</v>
       </c>
       <c r="AA4">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
         <v>3.14</v>
@@ -1018,7 +1018,7 @@
         <v>1.69</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1130,58 +1130,58 @@
         <v>5.1</v>
       </c>
       <c r="P5">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA5">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB5">
         <v>2.3</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>2.2</v>
       </c>
       <c r="O25">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P25">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         <v>6.1</v>
       </c>
       <c r="P27">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6029,10 +6029,10 @@
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U35">
         <v>3</v>
@@ -6835,7 +6835,7 @@
         <v>3.8</v>
       </c>
       <c r="P40">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="Q40">
         <v>2.1</v>
@@ -6847,7 +6847,7 @@
         <v>1.2</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="U40">
         <v>2.1</v>
@@ -6868,10 +6868,10 @@
         <v>6.26</v>
       </c>
       <c r="AA40">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB40">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AC40">
         <v>1.96</v>
@@ -6880,7 +6880,7 @@
         <v>1.76</v>
       </c>
       <c r="AE40">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF40">
         <v>1.4</v>
@@ -7001,25 +7001,25 @@
         <v>4.57</v>
       </c>
       <c r="Q41">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R41">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="U41">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="V41">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.03</v>
@@ -7034,7 +7034,7 @@
         <v>2.01</v>
       </c>
       <c r="AB41">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC41">
         <v>3.42</v>
@@ -7049,7 +7049,7 @@
         <v>1.9</v>
       </c>
       <c r="AG41">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>3.04</v>
       </c>
       <c r="AA42">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AB42">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC42">
         <v>3.95</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK42">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="O43">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="Q43">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="R43">
         <v>2.18</v>
@@ -7357,22 +7357,22 @@
         <v>3.7</v>
       </c>
       <c r="AA43">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC43">
         <v>2.87</v>
       </c>
       <c r="AD43">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG43">
         <v>2.1</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
         <v>1.91</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="O46">
-        <v>3.76</v>
+        <v>3.88</v>
       </c>
       <c r="P46">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="Q46">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R46">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
         <v>1.19</v>
@@ -7828,10 +7828,10 @@
         <v>3.74</v>
       </c>
       <c r="U46">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="V46">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W46">
         <v>1.14</v>
@@ -7843,28 +7843,28 @@
         <v>1.12</v>
       </c>
       <c r="Z46">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA46">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AB46">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AC46">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AD46">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE46">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF46">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG46">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK46">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8012,7 +8012,7 @@
         <v>1.57</v>
       </c>
       <c r="AB47">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AC47">
         <v>2.35</v>
@@ -8043,7 +8043,7 @@
         <v>1.62</v>
       </c>
       <c r="AK47">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8145,25 +8145,25 @@
         <v>2.4</v>
       </c>
       <c r="R48">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T48">
         <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="V48">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.11</v>
@@ -8184,7 +8184,7 @@
         <v>1.56</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF48">
         <v>1.44</v>
@@ -8516,7 +8516,7 @@
         <v>1.64</v>
       </c>
       <c r="AG50">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8637,49 +8637,49 @@
         <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="U51">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AA51">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AB51">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AC51">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8794,55 +8794,55 @@
         <v>2.65</v>
       </c>
       <c r="Q52">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R52">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="U52">
-        <v>2.73</v>
+        <v>2.34</v>
       </c>
       <c r="V52">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="AA52">
         <v>2.15</v>
       </c>
       <c r="AB52">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AC52">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="AD52">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE52">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF52">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AK52">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>2.5</v>
       </c>
       <c r="R53">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S53">
         <v>1.33</v>
@@ -8981,10 +8981,10 @@
         <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA53">
         <v>1.95</v>
@@ -8993,19 +8993,19 @@
         <v>1.85</v>
       </c>
       <c r="AC53">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD53">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE53">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="O55">
         <v>3.55</v>
       </c>
       <c r="P55">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q55">
         <v>2.4</v>
@@ -9289,7 +9289,7 @@
         <v>2.25</v>
       </c>
       <c r="S55">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T55">
         <v>3.02</v>
@@ -9304,7 +9304,7 @@
         <v>1.08</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
         <v>1.22</v>
@@ -9319,13 +9319,13 @@
         <v>2</v>
       </c>
       <c r="AC55">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AD55">
         <v>1.34</v>
       </c>
       <c r="AE55">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF55">
         <v>1.65</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK55">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,10 +9446,10 @@
         <v>2.87</v>
       </c>
       <c r="Q56">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK56">
         <v>1.62</v>
@@ -9642,7 +9642,7 @@
         <v>1.4</v>
       </c>
       <c r="AB57">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AC57">
         <v>1.94</v>
@@ -9657,7 +9657,7 @@
         <v>1.34</v>
       </c>
       <c r="AG57">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9772,16 +9772,16 @@
         <v>6</v>
       </c>
       <c r="Q58">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R58">
         <v>2.35</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T58">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="U58">
         <v>2.25</v>
@@ -9790,7 +9790,7 @@
         <v>1.57</v>
       </c>
       <c r="W58">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
         <v>1.02</v>
@@ -9820,7 +9820,7 @@
         <v>1.62</v>
       </c>
       <c r="AG58">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK58">
         <v>2.2</v>
@@ -9965,10 +9965,10 @@
         <v>3.9</v>
       </c>
       <c r="AA59">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB59">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC59">
         <v>2.66</v>
@@ -10294,7 +10294,7 @@
         <v>1.57</v>
       </c>
       <c r="AB61">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AC61">
         <v>2.38</v>
@@ -10436,10 +10436,10 @@
         <v>3.15</v>
       </c>
       <c r="U62">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="V62">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W62">
         <v>1.08</v>
@@ -10451,7 +10451,7 @@
         <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="AA62">
         <v>1.85</v>
@@ -10460,10 +10460,10 @@
         <v>1.96</v>
       </c>
       <c r="AC62">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AD62">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE62">
         <v>1.09</v>
@@ -10472,7 +10472,7 @@
         <v>1.65</v>
       </c>
       <c r="AG62">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>2.3</v>
       </c>
       <c r="O63">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P63">
         <v>2.88</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="P64">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10904,43 +10904,43 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="O65">
+        <v>3.5</v>
+      </c>
+      <c r="P65">
+        <v>2.15</v>
+      </c>
+      <c r="Q65">
+        <v>2.93</v>
+      </c>
+      <c r="R65">
+        <v>2.3</v>
+      </c>
+      <c r="S65">
+        <v>1.22</v>
+      </c>
+      <c r="T65">
         <v>3.75</v>
       </c>
-      <c r="P65">
-        <v>2.03</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA65">
         <v>1.57</v>
@@ -10949,19 +10949,19 @@
         <v>2.35</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11079,19 +11079,19 @@
         <v>1.95</v>
       </c>
       <c r="R66">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T66">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U66">
         <v>2.1</v>
       </c>
       <c r="V66">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W66">
         <v>1.18</v>
@@ -11100,16 +11100,16 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z66">
-        <v>5.64</v>
+        <v>5.4</v>
       </c>
       <c r="AA66">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB66">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AC66">
         <v>2.11</v>
@@ -11118,13 +11118,13 @@
         <v>1.67</v>
       </c>
       <c r="AE66">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF66">
         <v>1.55</v>
       </c>
       <c r="AG66">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>4.81</v>
+        <v>4.85</v>
       </c>
       <c r="O67">
-        <v>4.08</v>
+        <v>4.4</v>
       </c>
       <c r="P67">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q67">
         <v>5.05</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11408,10 +11408,10 @@
         <v>2.17</v>
       </c>
       <c r="S68">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U68">
         <v>2.75</v>
@@ -11420,7 +11420,7 @@
         <v>1.4</v>
       </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
         <v>1</v>
@@ -11432,7 +11432,7 @@
         <v>3.49</v>
       </c>
       <c r="AA68">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB68">
         <v>1.9</v>
@@ -11562,13 +11562,13 @@
         <v>3.6</v>
       </c>
       <c r="P69">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q69">
-        <v>3.02</v>
+        <v>3.56</v>
       </c>
       <c r="R69">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S69">
         <v>1.2</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK69">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="O70">
         <v>3.4</v>
@@ -12048,10 +12048,10 @@
         <v>1.95</v>
       </c>
       <c r="O72">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q72">
         <v>2.55</v>
@@ -12259,7 +12259,7 @@
         <v>1.72</v>
       </c>
       <c r="AE73">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF73">
         <v>1.62</v>
@@ -12371,19 +12371,19 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O74">
         <v>3.3</v>
       </c>
       <c r="P74">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q74">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R74">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S74">
         <v>1.44</v>
@@ -12395,7 +12395,7 @@
         <v>3.2</v>
       </c>
       <c r="V74">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W74">
         <v>1.03</v>
@@ -12444,7 +12444,7 @@
         <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,25 +12543,25 @@
         <v>2.66</v>
       </c>
       <c r="Q75">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R75">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S75">
         <v>1.33</v>
       </c>
       <c r="T75">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U75">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="V75">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W75">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK75">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12700,10 +12700,10 @@
         <v>1.35</v>
       </c>
       <c r="O76">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P76">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q76">
         <v>1.78</v>
@@ -12718,16 +12718,16 @@
         <v>3.56</v>
       </c>
       <c r="U76">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V76">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W76">
         <v>1.13</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
         <v>1.16</v>
@@ -12736,22 +12736,22 @@
         <v>4.5</v>
       </c>
       <c r="AA76">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB76">
         <v>2.4</v>
       </c>
       <c r="AC76">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AD76">
         <v>1.54</v>
       </c>
       <c r="AE76">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF76">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG76">
         <v>1.95</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AK76">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12866,34 +12866,34 @@
         <v>3.95</v>
       </c>
       <c r="P77">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q77">
         <v>1.95</v>
       </c>
       <c r="R77">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S77">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U77">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="V77">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W77">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X77">
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z77">
         <v>5.64</v>
@@ -12917,7 +12917,7 @@
         <v>1.44</v>
       </c>
       <c r="AG77">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.17</v>
       </c>
       <c r="AK77">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13204,7 +13204,7 @@
         <v>1.29</v>
       </c>
       <c r="T79">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U79">
         <v>2.5</v>
@@ -13219,28 +13219,28 @@
         <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z79">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA79">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB79">
         <v>2.05</v>
       </c>
       <c r="AC79">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD79">
         <v>1.4</v>
       </c>
       <c r="AE79">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF79">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG79">
         <v>2.2</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,25 +13349,25 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O80">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P80">
-        <v>4.35</v>
+        <v>3.95</v>
       </c>
       <c r="Q80">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R80">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="S80">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="U80">
         <v>2.4</v>
@@ -13376,7 +13376,7 @@
         <v>1.5</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X80">
         <v>1.02</v>
@@ -13400,13 +13400,13 @@
         <v>1.42</v>
       </c>
       <c r="AE80">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF80">
         <v>1.62</v>
       </c>
       <c r="AG80">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.19</v>
       </c>
       <c r="AK80">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>3.6</v>
       </c>
       <c r="AA81">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB81">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC81">
         <v>3.2</v>
@@ -13871,13 +13871,13 @@
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
         <v>3.5</v>
       </c>
       <c r="AA83">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB83">
         <v>1.95</v>
@@ -14529,10 +14529,10 @@
         <v>3.25</v>
       </c>
       <c r="AA87">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB87">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC87">
         <v>3.42</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14855,7 +14855,7 @@
         <v>5.63</v>
       </c>
       <c r="AA89">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB89">
         <v>2.67</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O90">
         <v>3.2</v>
@@ -14988,16 +14988,16 @@
         <v>2.25</v>
       </c>
       <c r="Q90">
-        <v>3.21</v>
+        <v>3.58</v>
       </c>
       <c r="R90">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
         <v>1.33</v>
       </c>
       <c r="T90">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="U90">
         <v>2.57</v>
@@ -15021,7 +15021,7 @@
         <v>1.95</v>
       </c>
       <c r="AB90">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC90">
         <v>3.3</v>
@@ -15030,13 +15030,13 @@
         <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF90">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG90">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>1.27</v>
       </c>
       <c r="AK90">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15157,10 +15157,10 @@
         <v>2.06</v>
       </c>
       <c r="S91">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T91">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U91">
         <v>2.75</v>
@@ -15172,19 +15172,19 @@
         <v>1.04</v>
       </c>
       <c r="X91">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
         <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
         <v>1.97</v>
       </c>
       <c r="AB91">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC91">
         <v>3.6</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O92">
         <v>3.38</v>
@@ -15314,10 +15314,10 @@
         <v>3.05</v>
       </c>
       <c r="Q92">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R92">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S92">
         <v>1.4</v>
@@ -15329,7 +15329,7 @@
         <v>2.9</v>
       </c>
       <c r="V92">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W92">
         <v>1.06</v>
@@ -15338,22 +15338,22 @@
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z92">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA92">
         <v>2.14</v>
       </c>
       <c r="AB92">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC92">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AD92">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE92">
         <v>1.05</v>
@@ -15474,7 +15474,7 @@
         <v>3.6</v>
       </c>
       <c r="P93">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q93">
         <v>3.02</v>
@@ -15483,16 +15483,16 @@
         <v>2.14</v>
       </c>
       <c r="S93">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T93">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U93">
         <v>2.4</v>
       </c>
       <c r="V93">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W93">
         <v>1.08</v>
@@ -15501,25 +15501,25 @@
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
         <v>4.1</v>
       </c>
       <c r="AA93">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB93">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC93">
-        <v>2.83</v>
+        <v>2.52</v>
       </c>
       <c r="AD93">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE93">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF93">
         <v>1.57</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AK93">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15634,13 +15634,13 @@
         <v>1.68</v>
       </c>
       <c r="O94">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P94">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q94">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R94">
         <v>2.25</v>
@@ -15676,16 +15676,16 @@
         <v>2</v>
       </c>
       <c r="AC94">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AD94">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE94">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF94">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG94">
         <v>2</v>
@@ -15704,7 +15704,7 @@
         <v>1.21</v>
       </c>
       <c r="AK94">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="O95">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P95">
+        <v>2.05</v>
+      </c>
+      <c r="Q95">
+        <v>3.81</v>
+      </c>
+      <c r="R95">
+        <v>2.15</v>
+      </c>
+      <c r="S95">
+        <v>1.28</v>
+      </c>
+      <c r="T95">
         <v>3.08</v>
       </c>
-      <c r="Q95">
-        <v>0</v>
-      </c>
-      <c r="R95">
-        <v>0</v>
-      </c>
-      <c r="S95">
-        <v>0</v>
-      </c>
-      <c r="T95">
-        <v>0</v>
-      </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="O96">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P96">
-        <v>1.98</v>
+        <v>3.08</v>
       </c>
       <c r="Q96">
-        <v>3.81</v>
+        <v>3.2</v>
       </c>
       <c r="R96">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S96">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U96">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V96">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X96">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z96">
-        <v>3.89</v>
+        <v>4.5</v>
       </c>
       <c r="AA96">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB96">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AC96">
-        <v>2.82</v>
+        <v>2.36</v>
       </c>
       <c r="AD96">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AE96">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AF96">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AG96">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK96">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="O97">
         <v>3.3</v>
       </c>
       <c r="P97">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="Q97">
         <v>3.07</v>
@@ -16162,7 +16162,7 @@
         <v>1.81</v>
       </c>
       <c r="AB97">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC97">
         <v>3.05</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK97">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16316,10 +16316,10 @@
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z98">
-        <v>6.04</v>
+        <v>6</v>
       </c>
       <c r="AA98">
         <v>1.44</v>
@@ -16337,7 +16337,7 @@
         <v>1.29</v>
       </c>
       <c r="AF98">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG98">
         <v>2.6</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O109">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q109">
         <v>2.69</v>
@@ -18106,7 +18106,7 @@
         <v>1.06</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
         <v>1.19</v>
@@ -18121,7 +18121,7 @@
         <v>1.95</v>
       </c>
       <c r="AC109">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AD109">
         <v>1.34</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK109">
         <v>1.51</v>
@@ -18257,7 +18257,7 @@
         <v>1.43</v>
       </c>
       <c r="T110">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="U110">
         <v>3.18</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O111">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P111">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="Q111">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="R111">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S111">
+        <v>1.33</v>
+      </c>
+      <c r="T111">
+        <v>2.85</v>
+      </c>
+      <c r="U111">
+        <v>2.75</v>
+      </c>
+      <c r="V111">
         <v>1.4</v>
-      </c>
-      <c r="T111">
-        <v>2.75</v>
-      </c>
-      <c r="U111">
-        <v>3</v>
-      </c>
-      <c r="V111">
-        <v>1.33</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z111">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AA111">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB111">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC111">
-        <v>3.42</v>
+        <v>2.92</v>
       </c>
       <c r="AD111">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF111">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AG111">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P112">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q112">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="R112">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S112">
+        <v>1.4</v>
+      </c>
+      <c r="T112">
+        <v>2.75</v>
+      </c>
+      <c r="U112">
+        <v>3</v>
+      </c>
+      <c r="V112">
         <v>1.33</v>
-      </c>
-      <c r="T112">
-        <v>2.85</v>
-      </c>
-      <c r="U112">
-        <v>2.75</v>
-      </c>
-      <c r="V112">
-        <v>1.4</v>
       </c>
       <c r="W112">
         <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
+        <v>1.28</v>
+      </c>
+      <c r="Z112">
+        <v>3.05</v>
+      </c>
+      <c r="AA112">
+        <v>2.05</v>
+      </c>
+      <c r="AB112">
+        <v>1.75</v>
+      </c>
+      <c r="AC112">
+        <v>3.42</v>
+      </c>
+      <c r="AD112">
         <v>1.23</v>
       </c>
-      <c r="Z112">
-        <v>3.42</v>
-      </c>
-      <c r="AA112">
-        <v>1.85</v>
-      </c>
-      <c r="AB112">
-        <v>1.95</v>
-      </c>
-      <c r="AC112">
-        <v>2.92</v>
-      </c>
-      <c r="AD112">
-        <v>1.31</v>
-      </c>
       <c r="AE112">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF112">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AG112">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK112">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="O114">
         <v>3.2</v>
@@ -18930,7 +18930,7 @@
         <v>3.08</v>
       </c>
       <c r="AA114">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB114">
         <v>1.77</v>
@@ -18948,7 +18948,7 @@
         <v>1.76</v>
       </c>
       <c r="AG114">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19054,34 +19054,34 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O115">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P115">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Q115">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="R115">
         <v>2.08</v>
       </c>
       <c r="S115">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
         <v>3.05</v>
       </c>
       <c r="U115">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="V115">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W115">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
         <v>1.03</v>
@@ -19090,13 +19090,13 @@
         <v>1.25</v>
       </c>
       <c r="Z115">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA115">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB115">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC115">
         <v>3.2</v>
@@ -19127,7 +19127,7 @@
         <v>1.3</v>
       </c>
       <c r="AK115">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="O118">
         <v>5.7</v>
@@ -19552,7 +19552,7 @@
         <v>6.7</v>
       </c>
       <c r="Q118">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R118">
         <v>3.19</v>
@@ -19582,10 +19582,10 @@
         <v>8</v>
       </c>
       <c r="AA118">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AB118">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AC118">
         <v>1.69</v>
@@ -19594,7 +19594,7 @@
         <v>2.2</v>
       </c>
       <c r="AE118">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AF118">
         <v>1.4</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK118">
         <v>3.1</v>
@@ -19733,7 +19733,7 @@
         <v>1.44</v>
       </c>
       <c r="W119">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X119">
         <v>1.03</v>
@@ -19745,7 +19745,7 @@
         <v>3.98</v>
       </c>
       <c r="AA119">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB119">
         <v>2.03</v>
@@ -19878,28 +19878,28 @@
         <v>2.83</v>
       </c>
       <c r="Q120">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="R120">
         <v>2.13</v>
       </c>
       <c r="S120">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T120">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="U120">
         <v>2.4</v>
       </c>
       <c r="V120">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W120">
         <v>1.12</v>
       </c>
       <c r="X120">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
         <v>1.19</v>
@@ -19908,10 +19908,10 @@
         <v>4.1</v>
       </c>
       <c r="AA120">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AB120">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AC120">
         <v>2.58</v>
@@ -19926,7 +19926,7 @@
         <v>1.55</v>
       </c>
       <c r="AG120">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK120">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20693,19 +20693,19 @@
         <v>3.08</v>
       </c>
       <c r="Q125">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="R125">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S125">
         <v>1.38</v>
       </c>
       <c r="T125">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U125">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V125">
         <v>1.41</v>
@@ -20714,7 +20714,7 @@
         <v>1.06</v>
       </c>
       <c r="X125">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y125">
         <v>1.29</v>
@@ -20726,7 +20726,7 @@
         <v>1.9</v>
       </c>
       <c r="AB125">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC125">
         <v>3.4</v>
@@ -20738,7 +20738,7 @@
         <v>1.1</v>
       </c>
       <c r="AF125">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG125">
         <v>2</v>
@@ -20847,16 +20847,16 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="O126">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="P126">
-        <v>2.76</v>
+        <v>2.47</v>
       </c>
       <c r="Q126">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="R126">
         <v>2.15</v>
@@ -20871,13 +20871,13 @@
         <v>2.63</v>
       </c>
       <c r="V126">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W126">
         <v>1.11</v>
       </c>
       <c r="X126">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
         <v>1.18</v>
@@ -20886,13 +20886,13 @@
         <v>4.03</v>
       </c>
       <c r="AA126">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB126">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC126">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD126">
         <v>1.36</v>
@@ -20901,7 +20901,7 @@
         <v>1.1</v>
       </c>
       <c r="AF126">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG126">
         <v>2.2</v>
@@ -20920,7 +20920,7 @@
         <v>1.27</v>
       </c>
       <c r="AK126">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21016,31 +21016,31 @@
         <v>3.5</v>
       </c>
       <c r="P127">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q127">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R127">
         <v>2.2</v>
       </c>
       <c r="S127">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T127">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U127">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V127">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W127">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
         <v>1.22</v>
@@ -21058,7 +21058,7 @@
         <v>2.76</v>
       </c>
       <c r="AD127">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE127">
         <v>1.13</v>
@@ -21067,7 +21067,7 @@
         <v>1.61</v>
       </c>
       <c r="AG127">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AK127">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21345,13 +21345,13 @@
         <v>4.8</v>
       </c>
       <c r="Q129">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R129">
         <v>2.1</v>
       </c>
       <c r="S129">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T129">
         <v>2.88</v>
@@ -21360,7 +21360,7 @@
         <v>3</v>
       </c>
       <c r="V129">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W129">
         <v>1.05</v>
@@ -21499,10 +21499,10 @@
         </is>
       </c>
       <c r="N130">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="O130">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="P130">
         <v>1.48</v>
@@ -21514,22 +21514,22 @@
         <v>2.5</v>
       </c>
       <c r="S130">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T130">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U130">
         <v>2.2</v>
       </c>
       <c r="V130">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W130">
         <v>1.14</v>
       </c>
       <c r="X130">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y130">
         <v>1.11</v>
@@ -21541,19 +21541,19 @@
         <v>1.5</v>
       </c>
       <c r="AB130">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AC130">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="AD130">
         <v>1.63</v>
       </c>
       <c r="AE130">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF130">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG130">
         <v>2.45</v>
@@ -21828,10 +21828,10 @@
         <v>1.48</v>
       </c>
       <c r="O132">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="P132">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q132">
         <v>2.19</v>
@@ -21846,7 +21846,7 @@
         <v>3</v>
       </c>
       <c r="U132">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="V132">
         <v>1.44</v>
@@ -21861,7 +21861,7 @@
         <v>1.27</v>
       </c>
       <c r="Z132">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA132">
         <v>1.95</v>
@@ -21876,7 +21876,7 @@
         <v>1.27</v>
       </c>
       <c r="AE132">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF132">
         <v>1.95</v>
@@ -22027,13 +22027,13 @@
         <v>3.84</v>
       </c>
       <c r="AA133">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB133">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC133">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AD133">
         <v>1.39</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="O135">
         <v>3.4</v>
       </c>
       <c r="P135">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22480,7 +22480,7 @@
         <v>1.36</v>
       </c>
       <c r="O136">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="P136">
         <v>8</v>
@@ -22525,7 +22525,7 @@
         <v>2.29</v>
       </c>
       <c r="AD136">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE136">
         <v>1.25</v>
@@ -22534,7 +22534,7 @@
         <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O2">
         <v>3.52</v>
@@ -680,10 +680,10 @@
         <v>1.98</v>
       </c>
       <c r="AC2">
-        <v>3.06</v>
+        <v>2.83</v>
       </c>
       <c r="AD2">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
         <v>1.14</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK2">
         <v>1.7</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O4">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -1003,7 +1003,7 @@
         <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC4">
         <v>3.14</v>
@@ -1130,7 +1130,7 @@
         <v>5.1</v>
       </c>
       <c r="P5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q5">
         <v>6.09</v>
@@ -1157,31 +1157,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AC5">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD5">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE5">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF5">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G22">
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G24">
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>2.2</v>
       </c>
       <c r="O25">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P25">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -7001,10 +7001,10 @@
         <v>4.57</v>
       </c>
       <c r="Q41">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S41">
         <v>1.36</v>
@@ -7013,10 +7013,10 @@
         <v>2.88</v>
       </c>
       <c r="U41">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
         <v>1.06</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
         <v>3.4</v>
@@ -7333,16 +7333,16 @@
         <v>2.18</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
         <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="V43">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W43">
         <v>1.07</v>
@@ -7357,10 +7357,10 @@
         <v>3.7</v>
       </c>
       <c r="AA43">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC43">
         <v>2.87</v>
@@ -7816,16 +7816,16 @@
         <v>3.26</v>
       </c>
       <c r="Q46">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R46">
         <v>2.4</v>
       </c>
       <c r="S46">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="U46">
         <v>2.23</v>
@@ -7991,7 +7991,7 @@
         <v>3.5</v>
       </c>
       <c r="U47">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V47">
         <v>1.57</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="O52">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q52">
+        <v>2.5</v>
+      </c>
+      <c r="R52">
+        <v>2</v>
+      </c>
+      <c r="S52">
+        <v>1.33</v>
+      </c>
+      <c r="T52">
         <v>3</v>
       </c>
-      <c r="R52">
-        <v>1.91</v>
-      </c>
-      <c r="S52">
-        <v>1.35</v>
-      </c>
-      <c r="T52">
-        <v>2.18</v>
-      </c>
       <c r="U52">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W52">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y52">
+        <v>1.2</v>
+      </c>
+      <c r="Z52">
+        <v>2.75</v>
+      </c>
+      <c r="AA52">
+        <v>1.95</v>
+      </c>
+      <c r="AB52">
+        <v>1.85</v>
+      </c>
+      <c r="AC52">
+        <v>2.63</v>
+      </c>
+      <c r="AD52">
+        <v>1.22</v>
+      </c>
+      <c r="AE52">
+        <v>1.05</v>
+      </c>
+      <c r="AF52">
+        <v>1.57</v>
+      </c>
+      <c r="AG52">
+        <v>1.78</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.25</v>
       </c>
-      <c r="Z52">
-        <v>2.45</v>
-      </c>
-      <c r="AA52">
-        <v>2.15</v>
-      </c>
-      <c r="AB52">
-        <v>1.54</v>
-      </c>
-      <c r="AC52">
-        <v>2.9</v>
-      </c>
-      <c r="AD52">
-        <v>1.17</v>
-      </c>
-      <c r="AE52">
-        <v>1.03</v>
-      </c>
-      <c r="AF52">
-        <v>1.65</v>
-      </c>
-      <c r="AG52">
-        <v>1.7</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.11</v>
-      </c>
       <c r="AK52">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="P53">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q53">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R53">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S53">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="V53">
+        <v>1.29</v>
+      </c>
+      <c r="W53">
+        <v>1.03</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
+        <v>1.25</v>
+      </c>
+      <c r="Z53">
+        <v>2.45</v>
+      </c>
+      <c r="AA53">
+        <v>2.15</v>
+      </c>
+      <c r="AB53">
+        <v>1.54</v>
+      </c>
+      <c r="AC53">
+        <v>2.9</v>
+      </c>
+      <c r="AD53">
+        <v>1.17</v>
+      </c>
+      <c r="AE53">
+        <v>1.03</v>
+      </c>
+      <c r="AF53">
+        <v>1.65</v>
+      </c>
+      <c r="AG53">
+        <v>1.7</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.11</v>
+      </c>
+      <c r="AK53">
         <v>1.4</v>
-      </c>
-      <c r="W53">
-        <v>1.07</v>
-      </c>
-      <c r="X53">
-        <v>1</v>
-      </c>
-      <c r="Y53">
-        <v>1.2</v>
-      </c>
-      <c r="Z53">
-        <v>2.75</v>
-      </c>
-      <c r="AA53">
-        <v>1.95</v>
-      </c>
-      <c r="AB53">
-        <v>1.85</v>
-      </c>
-      <c r="AC53">
-        <v>2.63</v>
-      </c>
-      <c r="AD53">
-        <v>1.22</v>
-      </c>
-      <c r="AE53">
-        <v>1.05</v>
-      </c>
-      <c r="AF53">
-        <v>1.57</v>
-      </c>
-      <c r="AG53">
-        <v>1.78</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.25</v>
-      </c>
-      <c r="AK53">
-        <v>1.83</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>2.02</v>
       </c>
       <c r="O55">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
         <v>3.3</v>
@@ -9295,7 +9295,7 @@
         <v>3.02</v>
       </c>
       <c r="U55">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="V55">
         <v>1.45</v>
@@ -9316,7 +9316,7 @@
         <v>1.74</v>
       </c>
       <c r="AB55">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC55">
         <v>2.78</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O57">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q57">
         <v>2.68</v>
@@ -9642,7 +9642,7 @@
         <v>1.4</v>
       </c>
       <c r="AB57">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AC57">
         <v>1.94</v>
@@ -10294,7 +10294,7 @@
         <v>1.57</v>
       </c>
       <c r="AB61">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="AC61">
         <v>2.38</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="O63">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="P63">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="O64">
         <v>3.37</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="O65">
         <v>3.5</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="O67">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P67">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q67">
         <v>5.05</v>
@@ -11399,10 +11399,10 @@
         <v>3.5</v>
       </c>
       <c r="P68">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q68">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R68">
         <v>2.17</v>
@@ -11429,7 +11429,7 @@
         <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="AA68">
         <v>1.86</v>
@@ -11466,7 +11466,7 @@
         <v>1.24</v>
       </c>
       <c r="AK68">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O69">
         <v>3.6</v>
@@ -11583,37 +11583,37 @@
         <v>1.65</v>
       </c>
       <c r="W69">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X69">
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z69">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA69">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB69">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC69">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD69">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE69">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF69">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG69">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK69">
         <v>1.29</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P70">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q70">
         <v>3.13</v>
@@ -11749,25 +11749,25 @@
         <v>1.07</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
         <v>1.2</v>
       </c>
       <c r="Z70">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA70">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB70">
         <v>2.19</v>
       </c>
       <c r="AC70">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD70">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE70">
         <v>1.17</v>
@@ -11792,7 +11792,7 @@
         <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12226,7 +12226,7 @@
         <v>1.2</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U73">
         <v>2.1</v>
@@ -12700,7 +12700,7 @@
         <v>1.35</v>
       </c>
       <c r="O76">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P76">
         <v>6.5</v>
@@ -12739,7 +12739,7 @@
         <v>1.56</v>
       </c>
       <c r="AB76">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AC76">
         <v>2.26</v>
@@ -12869,7 +12869,7 @@
         <v>4.2</v>
       </c>
       <c r="Q77">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="R77">
         <v>2.5</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK77">
         <v>2.12</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O79">
         <v>3.55</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -13391,7 +13391,7 @@
         <v>1.66</v>
       </c>
       <c r="AB80">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC80">
         <v>2.49</v>
@@ -13844,7 +13844,7 @@
         <v>3.48</v>
       </c>
       <c r="P83">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q83">
         <v>2.75</v>
@@ -13880,7 +13880,7 @@
         <v>1.85</v>
       </c>
       <c r="AB83">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC83">
         <v>3.1</v>
@@ -14360,16 +14360,16 @@
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>5.01</v>
+        <v>5.4</v>
       </c>
       <c r="AA86">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB86">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AC86">
         <v>2.17</v>
@@ -14378,13 +14378,13 @@
         <v>1.59</v>
       </c>
       <c r="AE86">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
         <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14662,55 +14662,55 @@
         <v>10</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA88">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB88">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O91">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P91">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q91">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="R91">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S91">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U91">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V91">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z91">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA91">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AB91">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AC91">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD91">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF91">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG91">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK91">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="O92">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P92">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q92">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="R92">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S92">
+        <v>1.27</v>
+      </c>
+      <c r="T92">
+        <v>3.32</v>
+      </c>
+      <c r="U92">
+        <v>2.4</v>
+      </c>
+      <c r="V92">
+        <v>1.52</v>
+      </c>
+      <c r="W92">
+        <v>1.08</v>
+      </c>
+      <c r="X92">
+        <v>1.01</v>
+      </c>
+      <c r="Y92">
+        <v>1.2</v>
+      </c>
+      <c r="Z92">
+        <v>4.1</v>
+      </c>
+      <c r="AA92">
+        <v>1.65</v>
+      </c>
+      <c r="AB92">
+        <v>2.1</v>
+      </c>
+      <c r="AC92">
+        <v>2.52</v>
+      </c>
+      <c r="AD92">
         <v>1.4</v>
       </c>
-      <c r="T92">
-        <v>2.75</v>
-      </c>
-      <c r="U92">
-        <v>2.9</v>
-      </c>
-      <c r="V92">
+      <c r="AE92">
+        <v>1.13</v>
+      </c>
+      <c r="AF92">
+        <v>1.57</v>
+      </c>
+      <c r="AG92">
+        <v>2.25</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <v>1.55</v>
+      </c>
+      <c r="AK92">
         <v>1.38</v>
-      </c>
-      <c r="W92">
-        <v>1.06</v>
-      </c>
-      <c r="X92">
-        <v>1.02</v>
-      </c>
-      <c r="Y92">
-        <v>1.29</v>
-      </c>
-      <c r="Z92">
-        <v>3.04</v>
-      </c>
-      <c r="AA92">
-        <v>2.14</v>
-      </c>
-      <c r="AB92">
-        <v>1.7</v>
-      </c>
-      <c r="AC92">
-        <v>3.34</v>
-      </c>
-      <c r="AD92">
-        <v>1.24</v>
-      </c>
-      <c r="AE92">
-        <v>1.05</v>
-      </c>
-      <c r="AF92">
-        <v>1.8</v>
-      </c>
-      <c r="AG92">
-        <v>1.91</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.28</v>
-      </c>
-      <c r="AK92">
-        <v>1.62</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="O93">
         <v>3.6</v>
       </c>
       <c r="P93">
+        <v>4.55</v>
+      </c>
+      <c r="Q93">
+        <v>2.16</v>
+      </c>
+      <c r="R93">
         <v>2.25</v>
       </c>
-      <c r="Q93">
-        <v>3.02</v>
-      </c>
-      <c r="R93">
-        <v>2.14</v>
-      </c>
       <c r="S93">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>3.32</v>
+        <v>2.87</v>
       </c>
       <c r="U93">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V93">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z93">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="AA93">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB93">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC93">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="AD93">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE93">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF93">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG93">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AK93">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="O94">
+        <v>3.5</v>
+      </c>
+      <c r="P94">
+        <v>3.9</v>
+      </c>
+      <c r="Q94">
+        <v>2.41</v>
+      </c>
+      <c r="R94">
+        <v>2.06</v>
+      </c>
+      <c r="S94">
+        <v>1.42</v>
+      </c>
+      <c r="T94">
+        <v>2.59</v>
+      </c>
+      <c r="U94">
+        <v>2.75</v>
+      </c>
+      <c r="V94">
+        <v>1.35</v>
+      </c>
+      <c r="W94">
+        <v>1.04</v>
+      </c>
+      <c r="X94">
+        <v>1.04</v>
+      </c>
+      <c r="Y94">
+        <v>1.27</v>
+      </c>
+      <c r="Z94">
+        <v>3.25</v>
+      </c>
+      <c r="AA94">
+        <v>1.97</v>
+      </c>
+      <c r="AB94">
+        <v>1.78</v>
+      </c>
+      <c r="AC94">
         <v>3.6</v>
       </c>
-      <c r="P94">
-        <v>4.45</v>
-      </c>
-      <c r="Q94">
-        <v>2.16</v>
-      </c>
-      <c r="R94">
-        <v>2.25</v>
-      </c>
-      <c r="S94">
-        <v>1.3</v>
-      </c>
-      <c r="T94">
-        <v>2.87</v>
-      </c>
-      <c r="U94">
-        <v>2.6</v>
-      </c>
-      <c r="V94">
-        <v>1.47</v>
-      </c>
-      <c r="W94">
-        <v>1.1</v>
-      </c>
-      <c r="X94">
-        <v>1</v>
-      </c>
-      <c r="Y94">
-        <v>1.22</v>
-      </c>
-      <c r="Z94">
-        <v>3.99</v>
-      </c>
-      <c r="AA94">
-        <v>1.8</v>
-      </c>
-      <c r="AB94">
-        <v>2</v>
-      </c>
-      <c r="AC94">
-        <v>2.66</v>
-      </c>
       <c r="AD94">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AE94">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF94">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG94">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15800,7 +15800,7 @@
         <v>3.25</v>
       </c>
       <c r="P95">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q95">
         <v>3.81</v>
@@ -15966,16 +15966,16 @@
         <v>3.08</v>
       </c>
       <c r="Q96">
+        <v>3</v>
+      </c>
+      <c r="R96">
+        <v>2.38</v>
+      </c>
+      <c r="S96">
+        <v>1.26</v>
+      </c>
+      <c r="T96">
         <v>3.2</v>
-      </c>
-      <c r="R96">
-        <v>2.32</v>
-      </c>
-      <c r="S96">
-        <v>1.25</v>
-      </c>
-      <c r="T96">
-        <v>3.5</v>
       </c>
       <c r="U96">
         <v>2.25</v>
@@ -15984,7 +15984,7 @@
         <v>1.57</v>
       </c>
       <c r="W96">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
         <v>1.01</v>
@@ -15993,28 +15993,28 @@
         <v>1.15</v>
       </c>
       <c r="Z96">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA96">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB96">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AC96">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AD96">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AE96">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF96">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AG96">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.22</v>
       </c>
       <c r="AK96">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16123,7 +16123,7 @@
         <v>2.37</v>
       </c>
       <c r="O97">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P97">
         <v>2.6</v>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK97">
         <v>1.44</v>
@@ -17937,7 +17937,7 @@
         <v>1.97</v>
       </c>
       <c r="V108">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W108">
         <v>1.22</v>
@@ -17961,7 +17961,7 @@
         <v>1.92</v>
       </c>
       <c r="AD108">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AE108">
         <v>1.33</v>
@@ -18248,25 +18248,25 @@
         <v>3.9</v>
       </c>
       <c r="Q110">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="R110">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S110">
         <v>1.43</v>
       </c>
       <c r="T110">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="U110">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="V110">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W110">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X110">
         <v>1.02</v>
@@ -18284,7 +18284,7 @@
         <v>1.57</v>
       </c>
       <c r="AC110">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD110">
         <v>1.16</v>
@@ -18293,10 +18293,10 @@
         <v>1.01</v>
       </c>
       <c r="AF110">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AG110">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK110">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O111">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q111">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="R111">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S111">
+        <v>1.4</v>
+      </c>
+      <c r="T111">
+        <v>2.75</v>
+      </c>
+      <c r="U111">
+        <v>3</v>
+      </c>
+      <c r="V111">
         <v>1.33</v>
-      </c>
-      <c r="T111">
-        <v>2.85</v>
-      </c>
-      <c r="U111">
-        <v>2.75</v>
-      </c>
-      <c r="V111">
-        <v>1.4</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
+        <v>1.28</v>
+      </c>
+      <c r="Z111">
+        <v>3.05</v>
+      </c>
+      <c r="AA111">
+        <v>2.05</v>
+      </c>
+      <c r="AB111">
+        <v>1.75</v>
+      </c>
+      <c r="AC111">
+        <v>3.42</v>
+      </c>
+      <c r="AD111">
         <v>1.23</v>
       </c>
-      <c r="Z111">
-        <v>3.42</v>
-      </c>
-      <c r="AA111">
-        <v>1.85</v>
-      </c>
-      <c r="AB111">
-        <v>1.95</v>
-      </c>
-      <c r="AC111">
-        <v>2.92</v>
-      </c>
-      <c r="AD111">
-        <v>1.31</v>
-      </c>
       <c r="AE111">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AG111">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK111">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O112">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P112">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="Q112">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="R112">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S112">
+        <v>1.33</v>
+      </c>
+      <c r="T112">
+        <v>2.85</v>
+      </c>
+      <c r="U112">
+        <v>2.75</v>
+      </c>
+      <c r="V112">
         <v>1.4</v>
-      </c>
-      <c r="T112">
-        <v>2.75</v>
-      </c>
-      <c r="U112">
-        <v>3</v>
-      </c>
-      <c r="V112">
-        <v>1.33</v>
       </c>
       <c r="W112">
         <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z112">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AA112">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB112">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC112">
-        <v>3.42</v>
+        <v>2.92</v>
       </c>
       <c r="AD112">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE112">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF112">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AG112">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18897,7 +18897,7 @@
         <v>3.2</v>
       </c>
       <c r="P114">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q114">
         <v>2.96</v>
@@ -18933,7 +18933,7 @@
         <v>2.03</v>
       </c>
       <c r="AB114">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC114">
         <v>3.28</v>
@@ -19072,7 +19072,7 @@
         <v>1.33</v>
       </c>
       <c r="T115">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="U115">
         <v>2.64</v>
@@ -19093,13 +19093,13 @@
         <v>3.5</v>
       </c>
       <c r="AA115">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB115">
         <v>1.86</v>
       </c>
       <c r="AC115">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD115">
         <v>1.3</v>
@@ -19111,7 +19111,7 @@
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19226,16 +19226,16 @@
         <v>2.35</v>
       </c>
       <c r="Q116">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R116">
         <v>1.97</v>
       </c>
       <c r="S116">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T116">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U116">
         <v>3</v>
@@ -19256,16 +19256,16 @@
         <v>2.83</v>
       </c>
       <c r="AA116">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB116">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AC116">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AD116">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE116">
         <v>1.03</v>
@@ -19274,7 +19274,7 @@
         <v>1.82</v>
       </c>
       <c r="AG116">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.42</v>
       </c>
       <c r="AK116">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19389,22 +19389,22 @@
         <v>1.78</v>
       </c>
       <c r="Q117">
-        <v>4.25</v>
+        <v>4.49</v>
       </c>
       <c r="R117">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S117">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T117">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="U117">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="V117">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W117">
         <v>1.1</v>
@@ -19413,31 +19413,31 @@
         <v>1</v>
       </c>
       <c r="Y117">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z117">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA117">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB117">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC117">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AD117">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE117">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF117">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AG117">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK117">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19576,10 +19576,10 @@
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z118">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA118">
         <v>1.28</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O125">
         <v>3.45</v>
       </c>
       <c r="P125">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="Q125">
         <v>2.74</v>
@@ -20699,7 +20699,7 @@
         <v>2.12</v>
       </c>
       <c r="S125">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T125">
         <v>2.9</v>
@@ -20714,7 +20714,7 @@
         <v>1.06</v>
       </c>
       <c r="X125">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y125">
         <v>1.29</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O126">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="P126">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="Q126">
         <v>2.82</v>
@@ -21387,7 +21387,7 @@
         <v>1.29</v>
       </c>
       <c r="AE129">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF129">
         <v>1.85</v>
@@ -21499,16 +21499,16 @@
         </is>
       </c>
       <c r="N130">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O130">
         <v>4.3</v>
       </c>
       <c r="P130">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="Q130">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R130">
         <v>2.5</v>
@@ -21538,7 +21538,7 @@
         <v>4.95</v>
       </c>
       <c r="AA130">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB130">
         <v>2.46</v>
@@ -21572,7 +21572,7 @@
         <v>1.17</v>
       </c>
       <c r="AK130">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O132">
         <v>3.96</v>
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q133">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R133">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S133">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T133">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U133">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V133">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W133">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X133">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z133">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA133">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB133">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC133">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AD133">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE133">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF133">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG133">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK133">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL133">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G21">
@@ -3741,16 +3741,16 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
         <v>2.89</v>
@@ -3759,22 +3759,22 @@
         <v>1.32</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z21">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA21">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AB21">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC21">
         <v>3.5</v>
@@ -3786,10 +3786,10 @@
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG21">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S22">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T22">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="U22">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="V22">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
         <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
         <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AD22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE22">
         <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG22">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4109,7 +4109,7 @@
         <v>1.24</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
         <v>1.72</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G24">
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R24">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T24">
         <v>2.57</v>
       </c>
       <c r="U24">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="V24">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
+        <v>1.05</v>
+      </c>
+      <c r="X24">
         <v>1.04</v>
       </c>
-      <c r="X24">
-        <v>1.03</v>
-      </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA24">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AB24">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC24">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG24">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O25">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P25">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>3.4</v>
       </c>
       <c r="Q43">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="R43">
         <v>2.18</v>
@@ -7357,10 +7357,10 @@
         <v>3.7</v>
       </c>
       <c r="AA43">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC43">
         <v>2.87</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O47">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q47">
         <v>3.42</v>
@@ -7991,7 +7991,7 @@
         <v>3.5</v>
       </c>
       <c r="U47">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V47">
         <v>1.57</v>
@@ -8015,13 +8015,13 @@
         <v>2.27</v>
       </c>
       <c r="AC47">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AD47">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE47">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
         <v>1.5</v>
@@ -8184,7 +8184,7 @@
         <v>1.56</v>
       </c>
       <c r="AE48">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
         <v>1.44</v>
@@ -8498,7 +8498,7 @@
         <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
         <v>1.85</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="P52">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R52">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S52">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="V52">
+        <v>1.29</v>
+      </c>
+      <c r="W52">
+        <v>1.03</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
+        <v>1.25</v>
+      </c>
+      <c r="Z52">
+        <v>2.45</v>
+      </c>
+      <c r="AA52">
+        <v>2.15</v>
+      </c>
+      <c r="AB52">
+        <v>1.54</v>
+      </c>
+      <c r="AC52">
+        <v>2.9</v>
+      </c>
+      <c r="AD52">
+        <v>1.17</v>
+      </c>
+      <c r="AE52">
+        <v>1.03</v>
+      </c>
+      <c r="AF52">
+        <v>1.65</v>
+      </c>
+      <c r="AG52">
+        <v>1.7</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.11</v>
+      </c>
+      <c r="AK52">
         <v>1.4</v>
-      </c>
-      <c r="W52">
-        <v>1.07</v>
-      </c>
-      <c r="X52">
-        <v>1</v>
-      </c>
-      <c r="Y52">
-        <v>1.2</v>
-      </c>
-      <c r="Z52">
-        <v>2.75</v>
-      </c>
-      <c r="AA52">
-        <v>1.95</v>
-      </c>
-      <c r="AB52">
-        <v>1.85</v>
-      </c>
-      <c r="AC52">
-        <v>2.63</v>
-      </c>
-      <c r="AD52">
-        <v>1.22</v>
-      </c>
-      <c r="AE52">
-        <v>1.05</v>
-      </c>
-      <c r="AF52">
-        <v>1.57</v>
-      </c>
-      <c r="AG52">
-        <v>1.78</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.25</v>
-      </c>
-      <c r="AK52">
-        <v>1.83</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="O53">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q53">
+        <v>2.5</v>
+      </c>
+      <c r="R53">
+        <v>2</v>
+      </c>
+      <c r="S53">
+        <v>1.33</v>
+      </c>
+      <c r="T53">
         <v>3</v>
       </c>
-      <c r="R53">
-        <v>1.91</v>
-      </c>
-      <c r="S53">
-        <v>1.35</v>
-      </c>
-      <c r="T53">
-        <v>2.18</v>
-      </c>
       <c r="U53">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W53">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y53">
+        <v>1.2</v>
+      </c>
+      <c r="Z53">
+        <v>2.75</v>
+      </c>
+      <c r="AA53">
+        <v>1.68</v>
+      </c>
+      <c r="AB53">
+        <v>1.9</v>
+      </c>
+      <c r="AC53">
+        <v>2.63</v>
+      </c>
+      <c r="AD53">
+        <v>1.22</v>
+      </c>
+      <c r="AE53">
+        <v>1.05</v>
+      </c>
+      <c r="AF53">
+        <v>1.57</v>
+      </c>
+      <c r="AG53">
+        <v>1.78</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
         <v>1.25</v>
       </c>
-      <c r="Z53">
-        <v>2.45</v>
-      </c>
-      <c r="AA53">
-        <v>2.15</v>
-      </c>
-      <c r="AB53">
-        <v>1.54</v>
-      </c>
-      <c r="AC53">
-        <v>2.9</v>
-      </c>
-      <c r="AD53">
-        <v>1.17</v>
-      </c>
-      <c r="AE53">
-        <v>1.03</v>
-      </c>
-      <c r="AF53">
-        <v>1.65</v>
-      </c>
-      <c r="AG53">
-        <v>1.7</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.11</v>
-      </c>
       <c r="AK53">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9443,7 +9443,7 @@
         <v>3.4</v>
       </c>
       <c r="P56">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="Q56">
         <v>2.59</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="O58">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P58">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
         <v>2.04</v>
@@ -9805,7 +9805,7 @@
         <v>1.61</v>
       </c>
       <c r="AB58">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC58">
         <v>2.42</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q59">
         <v>2.15</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -10294,7 +10294,7 @@
         <v>1.57</v>
       </c>
       <c r="AB61">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AC61">
         <v>2.38</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="O62">
         <v>3.3</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="O64">
         <v>3.37</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q65">
-        <v>2.93</v>
+        <v>3.34</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S65">
         <v>1.22</v>
@@ -10943,10 +10943,10 @@
         <v>4.55</v>
       </c>
       <c r="AA65">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB65">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC65">
         <v>2.33</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O66">
         <v>4.1</v>
       </c>
       <c r="P66">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q66">
         <v>1.95</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O67">
         <v>4.2</v>
@@ -11435,7 +11435,7 @@
         <v>1.86</v>
       </c>
       <c r="AB68">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC68">
         <v>3.04</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -12392,7 +12392,7 @@
         <v>2.62</v>
       </c>
       <c r="U74">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V74">
         <v>1.31</v>
@@ -12410,10 +12410,10 @@
         <v>2.7</v>
       </c>
       <c r="AA74">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB74">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC74">
         <v>4.15</v>
@@ -12425,7 +12425,7 @@
         <v>1.01</v>
       </c>
       <c r="AF74">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG74">
         <v>1.75</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK74">
         <v>1.85</v>
@@ -12700,7 +12700,7 @@
         <v>1.35</v>
       </c>
       <c r="O76">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P76">
         <v>6.5</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O79">
         <v>3.55</v>
@@ -13195,7 +13195,7 @@
         <v>3.1</v>
       </c>
       <c r="Q79">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="R79">
         <v>2.17</v>
@@ -13210,7 +13210,7 @@
         <v>2.5</v>
       </c>
       <c r="V79">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W79">
         <v>1.08</v>
@@ -13678,16 +13678,16 @@
         <v>3.25</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P82">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q82">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R82">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S82">
         <v>1.25</v>
@@ -13714,10 +13714,10 @@
         <v>4.3</v>
       </c>
       <c r="AA82">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB82">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC82">
         <v>2.35</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AK82">
         <v>1.27</v>
@@ -14532,7 +14532,7 @@
         <v>1.93</v>
       </c>
       <c r="AB87">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC87">
         <v>3.42</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O89">
         <v>3.8</v>
       </c>
       <c r="P89">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -14846,7 +14846,7 @@
         <v>1.17</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
         <v>1.13</v>
@@ -16193,7 +16193,7 @@
         <v>1.44</v>
       </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O98">
         <v>4.4</v>
@@ -16322,13 +16322,13 @@
         <v>6</v>
       </c>
       <c r="AA98">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB98">
         <v>2.66</v>
       </c>
       <c r="AC98">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD98">
         <v>1.74</v>
@@ -16340,7 +16340,7 @@
         <v>1.45</v>
       </c>
       <c r="AG98">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK98">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O99">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P99">
         <v>3.85</v>
@@ -16479,7 +16479,7 @@
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z99">
         <v>6.45</v>
@@ -16488,7 +16488,7 @@
         <v>1.3</v>
       </c>
       <c r="AB99">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AC99">
         <v>1.87</v>
@@ -16609,22 +16609,22 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P100">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Q100">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="R100">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T100">
         <v>4</v>
@@ -16633,7 +16633,7 @@
         <v>2.1</v>
       </c>
       <c r="V100">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W100">
         <v>1.14</v>
@@ -16654,13 +16654,13 @@
         <v>2.88</v>
       </c>
       <c r="AC100">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AD100">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE100">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF100">
         <v>1.4</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK100">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16775,10 +16775,10 @@
         <v>1.71</v>
       </c>
       <c r="O101">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P101">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q101">
         <v>2.1</v>
@@ -16790,7 +16790,7 @@
         <v>1.17</v>
       </c>
       <c r="T101">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="U101">
         <v>1.91</v>
@@ -16814,13 +16814,13 @@
         <v>1.32</v>
       </c>
       <c r="AB101">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AC101">
         <v>1.91</v>
       </c>
       <c r="AD101">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE101">
         <v>1.35</v>
@@ -16938,10 +16938,10 @@
         <v>2.3</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q102">
         <v>2.8</v>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="O103">
         <v>3.5</v>
@@ -17107,25 +17107,25 @@
         <v>2.37</v>
       </c>
       <c r="Q103">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="R103">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S103">
         <v>1.17</v>
       </c>
       <c r="T103">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="U103">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V103">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W103">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X103">
         <v>1.01</v>
@@ -17143,7 +17143,7 @@
         <v>2.88</v>
       </c>
       <c r="AC103">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD103">
         <v>1.81</v>
@@ -17152,7 +17152,7 @@
         <v>1.35</v>
       </c>
       <c r="AF103">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG103">
         <v>3</v>
@@ -17261,25 +17261,25 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="O104">
         <v>3.6</v>
       </c>
       <c r="P104">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q104">
         <v>2.33</v>
       </c>
       <c r="R104">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="S104">
         <v>1.25</v>
       </c>
       <c r="T104">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U104">
         <v>2.25</v>
@@ -17288,7 +17288,7 @@
         <v>1.57</v>
       </c>
       <c r="W104">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X104">
         <v>1.01</v>
@@ -17303,7 +17303,7 @@
         <v>1.63</v>
       </c>
       <c r="AB104">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC104">
         <v>2.53</v>
@@ -17315,7 +17315,7 @@
         <v>1.19</v>
       </c>
       <c r="AF104">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG104">
         <v>2.3</v>
@@ -17424,34 +17424,34 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="O105">
         <v>3.5</v>
       </c>
       <c r="P105">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="Q105">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="R105">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S105">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T105">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="U105">
         <v>1.95</v>
       </c>
       <c r="V105">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W105">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X105">
         <v>1.01</v>
@@ -17460,22 +17460,22 @@
         <v>1.06</v>
       </c>
       <c r="Z105">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="AA105">
         <v>1.36</v>
       </c>
       <c r="AB105">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="AC105">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AD105">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AE105">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF105">
         <v>1.33</v>
@@ -17587,19 +17587,19 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O106">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P106">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q106">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R106">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="S106">
         <v>1.2</v>
@@ -17620,16 +17620,16 @@
         <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z106">
-        <v>5.75</v>
+        <v>5.15</v>
       </c>
       <c r="AA106">
         <v>1.47</v>
       </c>
       <c r="AB106">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AC106">
         <v>2.09</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AK106">
         <v>1.57</v>
@@ -17753,16 +17753,16 @@
         <v>1.61</v>
       </c>
       <c r="O107">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P107">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="Q107">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="R107">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="S107">
         <v>1.17</v>
@@ -17783,28 +17783,28 @@
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z107">
-        <v>5.86</v>
+        <v>6.5</v>
       </c>
       <c r="AA107">
         <v>1.44</v>
       </c>
       <c r="AB107">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC107">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AD107">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE107">
         <v>1.31</v>
       </c>
       <c r="AF107">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG107">
         <v>2.5</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK107">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18118,7 +18118,7 @@
         <v>1.76</v>
       </c>
       <c r="AB109">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC109">
         <v>3.2</v>
@@ -18149,7 +18149,7 @@
         <v>1.27</v>
       </c>
       <c r="AK109">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18731,7 +18731,7 @@
         <v>3.02</v>
       </c>
       <c r="O113">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P113">
         <v>2.06</v>
@@ -19920,7 +19920,7 @@
         <v>1.43</v>
       </c>
       <c r="AE120">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF120">
         <v>1.55</v>
@@ -20071,10 +20071,10 @@
         <v>4.5</v>
       </c>
       <c r="AA121">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB121">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AC121">
         <v>2.41</v>
@@ -20207,7 +20207,7 @@
         <v>2.4</v>
       </c>
       <c r="R122">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
         <v>1.26</v>
@@ -20222,7 +20222,7 @@
         <v>1.53</v>
       </c>
       <c r="W122">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
         <v>1.02</v>
@@ -20237,7 +20237,7 @@
         <v>1.68</v>
       </c>
       <c r="AB122">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC122">
         <v>2.56</v>
@@ -20252,7 +20252,7 @@
         <v>1.57</v>
       </c>
       <c r="AG122">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>1.17</v>
       </c>
       <c r="Z123">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AA123">
         <v>1.72</v>
@@ -20524,10 +20524,10 @@
         <v>1.61</v>
       </c>
       <c r="O124">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P124">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q124">
         <v>2.06</v>
@@ -20560,25 +20560,25 @@
         <v>4</v>
       </c>
       <c r="AA124">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB124">
         <v>2.2</v>
       </c>
       <c r="AC124">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AD124">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE124">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF124">
         <v>1.67</v>
       </c>
       <c r="AG124">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK124">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20687,7 +20687,7 @@
         <v>2.15</v>
       </c>
       <c r="O125">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="P125">
         <v>3.3</v>
@@ -20847,10 +20847,10 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O126">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P126">
         <v>2.75</v>
@@ -21010,25 +21010,25 @@
         </is>
       </c>
       <c r="N127">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O127">
         <v>3.5</v>
       </c>
       <c r="P127">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q127">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R127">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S127">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T127">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U127">
         <v>2.55</v>
@@ -21037,16 +21037,16 @@
         <v>1.45</v>
       </c>
       <c r="W127">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z127">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AA127">
         <v>1.72</v>
@@ -21055,19 +21055,19 @@
         <v>2.1</v>
       </c>
       <c r="AC127">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AD127">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE127">
         <v>1.13</v>
       </c>
       <c r="AF127">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG127">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="AK127">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="O128">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="P128">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Q128">
         <v>1.5</v>
       </c>
       <c r="R128">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="S128">
         <v>1.14</v>
@@ -21209,28 +21209,28 @@
         <v>1.06</v>
       </c>
       <c r="Z128">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="AA128">
         <v>1.44</v>
       </c>
       <c r="AB128">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AC128">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD128">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE128">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AF128">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AG128">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK128">
         <v>5</v>
@@ -21997,34 +21997,34 @@
         <v>4.33</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA133">
         <v>1.7</v>
@@ -22033,19 +22033,19 @@
         <v>2</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O134">
         <v>3.4</v>
@@ -22169,16 +22169,16 @@
         <v>1.36</v>
       </c>
       <c r="T134">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="U134">
         <v>2.77</v>
       </c>
       <c r="V134">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W134">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X134">
         <v>1.01</v>
@@ -22193,19 +22193,19 @@
         <v>2.05</v>
       </c>
       <c r="AB134">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC134">
         <v>3.48</v>
       </c>
       <c r="AD134">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE134">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF134">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG134">
         <v>1.91</v>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK134">
         <v>1.83</v>
@@ -22670,7 +22670,7 @@
         <v>1.1</v>
       </c>
       <c r="X137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
         <v>1.22</v>
@@ -22836,13 +22836,13 @@
         <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z138">
         <v>2.9</v>
       </c>
       <c r="AA138">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB138">
         <v>1.96</v>
@@ -22854,7 +22854,7 @@
         <v>1.29</v>
       </c>
       <c r="AE138">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF138">
         <v>1.55</v>
@@ -22966,16 +22966,16 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="O139">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P139">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q139">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="R139">
         <v>1.95</v>
@@ -22993,7 +22993,7 @@
         <v>1.3</v>
       </c>
       <c r="W139">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X139">
         <v>1.05</v>
@@ -23008,10 +23008,10 @@
         <v>2.15</v>
       </c>
       <c r="AB139">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC139">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD139">
         <v>1.19</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK139">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23150,7 +23150,7 @@
         <v>3.8</v>
       </c>
       <c r="U140">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V140">
         <v>1.57</v>
@@ -23165,7 +23165,7 @@
         <v>1.12</v>
       </c>
       <c r="Z140">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA140">
         <v>1.52</v>
@@ -23301,10 +23301,10 @@
         <v>2.2</v>
       </c>
       <c r="Q141">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R141">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S141">
         <v>1.2</v>
@@ -23313,13 +23313,13 @@
         <v>4</v>
       </c>
       <c r="U141">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V141">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W141">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X141">
         <v>1.01</v>
@@ -23346,10 +23346,10 @@
         <v>1.24</v>
       </c>
       <c r="AF141">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG141">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>1.18</v>
       </c>
       <c r="AK141">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL141">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -970,55 +970,55 @@
         <v>2.9</v>
       </c>
       <c r="Q4">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U4">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA4">
         <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AC4">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG4">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>7.5</v>
       </c>
       <c r="O5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>1.28</v>
@@ -1197,7 +1197,7 @@
         <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AK26">
         <v>1.24</v>
@@ -6044,13 +6044,13 @@
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z35">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA35">
         <v>2.15</v>
@@ -6059,19 +6059,19 @@
         <v>1.64</v>
       </c>
       <c r="AC35">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="AD35">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="O41">
-        <v>3.28</v>
+        <v>3.69</v>
       </c>
       <c r="P41">
-        <v>4.57</v>
+        <v>5.07</v>
       </c>
       <c r="Q41">
         <v>2.32</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="O42">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="P42">
         <v>3.5</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="O55">
         <v>3.5</v>
       </c>
       <c r="P55">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q55">
         <v>2.4</v>
@@ -9295,10 +9295,10 @@
         <v>3.02</v>
       </c>
       <c r="U55">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V55">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W55">
         <v>1.08</v>
@@ -11559,7 +11559,7 @@
         <v>2.87</v>
       </c>
       <c r="O69">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P69">
         <v>2.11</v>
@@ -11568,7 +11568,7 @@
         <v>3.56</v>
       </c>
       <c r="R69">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S69">
         <v>1.2</v>
@@ -11629,7 +11629,7 @@
         <v>1.19</v>
       </c>
       <c r="AK69">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,16 +11719,16 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.62</v>
+        <v>3.03</v>
       </c>
       <c r="O70">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="P70">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="Q70">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="R70">
         <v>2.18</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK70">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O77">
         <v>3.95</v>
@@ -13554,7 +13554,7 @@
         <v>1.9</v>
       </c>
       <c r="AB81">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC81">
         <v>3.2</v>
@@ -14502,7 +14502,7 @@
         <v>3.1</v>
       </c>
       <c r="R87">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S87">
         <v>1.36</v>
@@ -14532,7 +14532,7 @@
         <v>1.93</v>
       </c>
       <c r="AB87">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC87">
         <v>3.42</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK87">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14665,37 +14665,37 @@
         <v>1.57</v>
       </c>
       <c r="R88">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="S88">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T88">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U88">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V88">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W88">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z88">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA88">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB88">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC88">
         <v>2.62</v>
@@ -14707,10 +14707,10 @@
         <v>1.11</v>
       </c>
       <c r="AF88">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AG88">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK88">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O90">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q90">
         <v>3.58</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O91">
         <v>3.1</v>
@@ -15305,10 +15305,10 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O92">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
         <v>2.25</v>
@@ -15347,7 +15347,7 @@
         <v>1.65</v>
       </c>
       <c r="AB92">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC92">
         <v>2.52</v>
@@ -15378,7 +15378,7 @@
         <v>1.55</v>
       </c>
       <c r="AK92">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15510,7 +15510,7 @@
         <v>1.81</v>
       </c>
       <c r="AB93">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC93">
         <v>2.66</v>
@@ -15541,7 +15541,7 @@
         <v>1.21</v>
       </c>
       <c r="AK93">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -18076,10 +18076,10 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O109">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P109">
         <v>2.86</v>
@@ -18118,7 +18118,7 @@
         <v>1.76</v>
       </c>
       <c r="AB109">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC109">
         <v>3.2</v>
@@ -18127,7 +18127,7 @@
         <v>1.34</v>
       </c>
       <c r="AE109">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF109">
         <v>1.59</v>
@@ -18149,7 +18149,7 @@
         <v>1.27</v>
       </c>
       <c r="AK109">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK110">
         <v>1.91</v>
@@ -18444,7 +18444,7 @@
         <v>2.05</v>
       </c>
       <c r="AB111">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC111">
         <v>3.42</v>
@@ -18565,7 +18565,7 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O112">
         <v>3.25</v>
@@ -18933,7 +18933,7 @@
         <v>2.03</v>
       </c>
       <c r="AB114">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC114">
         <v>3.28</v>
@@ -19099,7 +19099,7 @@
         <v>1.86</v>
       </c>
       <c r="AC115">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="AD115">
         <v>1.3</v>
@@ -19111,7 +19111,7 @@
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19555,13 +19555,13 @@
         <v>1.77</v>
       </c>
       <c r="R118">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="S118">
         <v>1.11</v>
       </c>
       <c r="T118">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U118">
         <v>1.85</v>
@@ -19582,10 +19582,10 @@
         <v>8.5</v>
       </c>
       <c r="AA118">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB118">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AC118">
         <v>1.69</v>
@@ -19594,13 +19594,13 @@
         <v>2.2</v>
       </c>
       <c r="AE118">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AF118">
         <v>1.4</v>
       </c>
       <c r="AG118">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19706,16 +19706,16 @@
         </is>
       </c>
       <c r="N119">
-        <v>6.42</v>
+        <v>5.5</v>
       </c>
       <c r="O119">
-        <v>4.57</v>
+        <v>4.2</v>
       </c>
       <c r="P119">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q119">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="R119">
         <v>2.33</v>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK119">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -21016,13 +21016,13 @@
         <v>3.5</v>
       </c>
       <c r="P127">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q127">
         <v>3.24</v>
       </c>
       <c r="R127">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S127">
         <v>1.29</v>
@@ -21037,7 +21037,7 @@
         <v>1.45</v>
       </c>
       <c r="W127">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X127">
         <v>1.01</v>
@@ -21052,7 +21052,7 @@
         <v>1.72</v>
       </c>
       <c r="AB127">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC127">
         <v>2.8</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK127">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK129">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,61 +21499,61 @@
         </is>
       </c>
       <c r="N130">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O130">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P130">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="Q130">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R130">
         <v>2.5</v>
       </c>
       <c r="S130">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T130">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U130">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V130">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W130">
         <v>1.14</v>
       </c>
       <c r="X130">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
         <v>1.11</v>
       </c>
       <c r="Z130">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA130">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB130">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AC130">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AD130">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE130">
         <v>1.22</v>
       </c>
       <c r="AF130">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG130">
         <v>2.45</v>
@@ -21572,7 +21572,7 @@
         <v>1.17</v>
       </c>
       <c r="AK130">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21867,7 +21867,7 @@
         <v>1.95</v>
       </c>
       <c r="AB132">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC132">
         <v>3.14</v>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK132">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O133">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P133">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q133">
         <v>2.12</v>
@@ -22027,10 +22027,10 @@
         <v>3.84</v>
       </c>
       <c r="AA133">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB133">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC133">
         <v>2.77</v>
@@ -22323,55 +22323,55 @@
         <v>3.41</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL135">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -976,10 +976,10 @@
         <v>2.04</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U4">
         <v>2.65</v>
@@ -991,7 +991,7 @@
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.29</v>
@@ -1003,7 +1003,7 @@
         <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AC4">
         <v>3.2</v>
@@ -1015,10 +1015,10 @@
         <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
         <v>6.09</v>
@@ -1163,10 +1163,10 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB5">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AC5">
         <v>2.55</v>
@@ -3783,7 +3783,7 @@
         <v>1.22</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
         <v>1.79</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T22">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="U22">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
         <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z22">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AA22">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB22">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC22">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="AD22">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE22">
         <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4097,7 +4097,7 @@
         <v>3.14</v>
       </c>
       <c r="AA23">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB23">
         <v>1.75</v>
@@ -4109,7 +4109,7 @@
         <v>1.24</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
         <v>1.72</v>
@@ -4236,16 +4236,16 @@
         <v>2.05</v>
       </c>
       <c r="S24">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="U24">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="V24">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
         <v>1.05</v>
@@ -4254,16 +4254,16 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA24">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB24">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
         <v>3.6</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>3</v>
       </c>
       <c r="P25">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -6023,34 +6023,34 @@
         <v>2.33</v>
       </c>
       <c r="Q35">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U35">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="V35">
+        <v>1.34</v>
+      </c>
+      <c r="W35">
+        <v>1.04</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
         <v>1.33</v>
       </c>
-      <c r="W35">
-        <v>1.06</v>
-      </c>
-      <c r="X35">
-        <v>1.06</v>
-      </c>
-      <c r="Y35">
-        <v>1.36</v>
-      </c>
       <c r="Z35">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AA35">
         <v>2.15</v>
@@ -6059,19 +6059,19 @@
         <v>1.64</v>
       </c>
       <c r="AC35">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="AD35">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6841,19 +6841,19 @@
         <v>2.1</v>
       </c>
       <c r="R40">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="S40">
         <v>1.2</v>
       </c>
       <c r="T40">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="U40">
         <v>2.1</v>
       </c>
       <c r="V40">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W40">
         <v>1.18</v>
@@ -6862,31 +6862,31 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
-        <v>6.26</v>
+        <v>6.5</v>
       </c>
       <c r="AA40">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC40">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD40">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE40">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF40">
         <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7001,55 +7001,55 @@
         <v>5.07</v>
       </c>
       <c r="Q41">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="R41">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U41">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z41">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA41">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AB41">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AC41">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD41">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE41">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF41">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG41">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>2.57</v>
       </c>
       <c r="U42">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="V42">
         <v>1.29</v>
@@ -7191,7 +7191,7 @@
         <v>1.35</v>
       </c>
       <c r="Z42">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AA42">
         <v>2.23</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O43">
         <v>3.45</v>
@@ -7327,7 +7327,7 @@
         <v>3.4</v>
       </c>
       <c r="Q43">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="R43">
         <v>2.18</v>
@@ -7336,7 +7336,7 @@
         <v>1.33</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U43">
         <v>2.49</v>
@@ -7852,13 +7852,13 @@
         <v>2.33</v>
       </c>
       <c r="AC46">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AD46">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE46">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF46">
         <v>1.46</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="O47">
         <v>3.4</v>
@@ -7979,19 +7979,19 @@
         <v>2.1</v>
       </c>
       <c r="Q47">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="R47">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
         <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V47">
         <v>1.57</v>
@@ -8003,16 +8003,16 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z47">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA47">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB47">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AC47">
         <v>2.45</v>
@@ -8024,10 +8024,10 @@
         <v>1.2</v>
       </c>
       <c r="AF47">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG47">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8145,28 +8145,28 @@
         <v>2.4</v>
       </c>
       <c r="R48">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="S48">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
         <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="V48">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z48">
         <v>4.85</v>
@@ -8181,7 +8181,7 @@
         <v>2.33</v>
       </c>
       <c r="AD48">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE48">
         <v>1.2</v>
@@ -8459,25 +8459,25 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="O50">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="P50">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="Q50">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="R50">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>2.85</v>
+        <v>2.27</v>
       </c>
       <c r="U50">
         <v>2.64</v>
@@ -8489,25 +8489,25 @@
         <v>1.04</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
         <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB50">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC50">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AD50">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE50">
         <v>1.07</v>
@@ -8516,7 +8516,7 @@
         <v>1.64</v>
       </c>
       <c r="AG50">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK50">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P51">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="Q51">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R51">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S51">
+        <v>1.36</v>
+      </c>
+      <c r="T51">
+        <v>2.15</v>
+      </c>
+      <c r="U51">
+        <v>2.39</v>
+      </c>
+      <c r="V51">
+        <v>1.28</v>
+      </c>
+      <c r="W51">
+        <v>1.03</v>
+      </c>
+      <c r="X51">
+        <v>1.03</v>
+      </c>
+      <c r="Y51">
+        <v>1.3</v>
+      </c>
+      <c r="Z51">
+        <v>2.97</v>
+      </c>
+      <c r="AA51">
+        <v>2.11</v>
+      </c>
+      <c r="AB51">
+        <v>1.73</v>
+      </c>
+      <c r="AC51">
+        <v>3.58</v>
+      </c>
+      <c r="AD51">
+        <v>1.21</v>
+      </c>
+      <c r="AE51">
+        <v>1.03</v>
+      </c>
+      <c r="AF51">
+        <v>1.78</v>
+      </c>
+      <c r="AG51">
+        <v>1.91</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.34</v>
       </c>
-      <c r="T51">
-        <v>2.2</v>
-      </c>
-      <c r="U51">
-        <v>2.32</v>
-      </c>
-      <c r="V51">
-        <v>1.3</v>
-      </c>
-      <c r="W51">
-        <v>1.04</v>
-      </c>
-      <c r="X51">
-        <v>1.02</v>
-      </c>
-      <c r="Y51">
-        <v>1.25</v>
-      </c>
-      <c r="Z51">
-        <v>2.55</v>
-      </c>
-      <c r="AA51">
-        <v>1.75</v>
-      </c>
-      <c r="AB51">
-        <v>1.59</v>
-      </c>
-      <c r="AC51">
-        <v>2.75</v>
-      </c>
-      <c r="AD51">
-        <v>1.2</v>
-      </c>
-      <c r="AE51">
-        <v>1.04</v>
-      </c>
-      <c r="AF51">
-        <v>1.6</v>
-      </c>
-      <c r="AG51">
-        <v>1.75</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.3</v>
-      </c>
       <c r="AK51">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="O52">
-        <v>3.33</v>
+        <v>3.52</v>
       </c>
       <c r="P52">
-        <v>2.65</v>
+        <v>4.66</v>
       </c>
       <c r="Q52">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="R52">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T52">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="U52">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AA52">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB52">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD52">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AE52">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG52">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,58 +8948,58 @@
         </is>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P53">
-        <v>3.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q53">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="R53">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S53">
         <v>1.33</v>
       </c>
       <c r="T53">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="V53">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
         <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z53">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA53">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AB53">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC53">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="AD53">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE53">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF53">
         <v>1.57</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK53">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9289,10 +9289,10 @@
         <v>2.25</v>
       </c>
       <c r="S55">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T55">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U55">
         <v>2.6</v>
@@ -9313,16 +9313,16 @@
         <v>3.8</v>
       </c>
       <c r="AA55">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB55">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC55">
         <v>2.78</v>
       </c>
       <c r="AD55">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE55">
         <v>1.1</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.85</v>
       </c>
       <c r="Q56">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="R56">
         <v>2.24</v>
@@ -9458,7 +9458,7 @@
         <v>3.25</v>
       </c>
       <c r="U56">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V56">
         <v>1.53</v>
@@ -9479,7 +9479,7 @@
         <v>1.61</v>
       </c>
       <c r="AB56">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AC56">
         <v>2.49</v>
@@ -9603,61 +9603,61 @@
         <v>2.2</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q57">
         <v>2.68</v>
       </c>
       <c r="R57">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="S57">
+        <v>1.19</v>
+      </c>
+      <c r="T57">
+        <v>3.74</v>
+      </c>
+      <c r="U57">
+        <v>2.1</v>
+      </c>
+      <c r="V57">
+        <v>1.67</v>
+      </c>
+      <c r="W57">
         <v>1.17</v>
       </c>
-      <c r="T57">
-        <v>4.5</v>
-      </c>
-      <c r="U57">
-        <v>2</v>
-      </c>
-      <c r="V57">
-        <v>1.73</v>
-      </c>
-      <c r="W57">
-        <v>1.2</v>
-      </c>
       <c r="X57">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z57">
-        <v>5.9</v>
+        <v>5.25</v>
       </c>
       <c r="AA57">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB57">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC57">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AD57">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AE57">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF57">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AG57">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK57">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9766,28 +9766,28 @@
         <v>1.57</v>
       </c>
       <c r="O58">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q58">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R58">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S58">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="U58">
         <v>2.25</v>
       </c>
       <c r="V58">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W58">
         <v>1.1</v>
@@ -9796,19 +9796,19 @@
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z58">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA58">
         <v>1.61</v>
       </c>
       <c r="AB58">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AC58">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD58">
         <v>1.44</v>
@@ -9820,7 +9820,7 @@
         <v>1.62</v>
       </c>
       <c r="AG58">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK58">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,80 +9926,80 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="O59">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P59">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q59">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="R59">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U59">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V59">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W59">
         <v>1.12</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z59">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA59">
+        <v>1.61</v>
+      </c>
+      <c r="AB59">
+        <v>2.25</v>
+      </c>
+      <c r="AC59">
+        <v>2.47</v>
+      </c>
+      <c r="AD59">
+        <v>1.48</v>
+      </c>
+      <c r="AE59">
+        <v>1.15</v>
+      </c>
+      <c r="AF59">
+        <v>1.53</v>
+      </c>
+      <c r="AG59">
+        <v>2.38</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <v>1.22</v>
+      </c>
+      <c r="AK59">
         <v>1.67</v>
-      </c>
-      <c r="AB59">
-        <v>2.04</v>
-      </c>
-      <c r="AC59">
-        <v>2.66</v>
-      </c>
-      <c r="AD59">
-        <v>1.37</v>
-      </c>
-      <c r="AE59">
-        <v>1.11</v>
-      </c>
-      <c r="AF59">
-        <v>1.67</v>
-      </c>
-      <c r="AG59">
-        <v>2.05</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ59">
-        <v>1.16</v>
-      </c>
-      <c r="AK59">
-        <v>2.07</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O60">
         <v>3.4</v>
       </c>
       <c r="P60">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -10104,16 +10104,16 @@
         <v>2.3</v>
       </c>
       <c r="S60">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T60">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U60">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="V60">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W60">
         <v>1.12</v>
@@ -10125,13 +10125,13 @@
         <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA60">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB60">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC60">
         <v>2.43</v>
@@ -10143,10 +10143,10 @@
         <v>1.14</v>
       </c>
       <c r="AF60">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG60">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,80 +10252,80 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.17</v>
+        <v>1.61</v>
       </c>
       <c r="O61">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q61">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="R61">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S61">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="V61">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W61">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z61">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="AA61">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB61">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="AC61">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AD61">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE61">
+        <v>1.11</v>
+      </c>
+      <c r="AF61">
+        <v>1.67</v>
+      </c>
+      <c r="AG61">
+        <v>2.05</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
         <v>1.16</v>
       </c>
-      <c r="AF61">
-        <v>1.49</v>
-      </c>
-      <c r="AG61">
-        <v>2.39</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.19</v>
-      </c>
       <c r="AK61">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,49 +10415,49 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="O62">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
       </c>
       <c r="R62">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
         <v>1.33</v>
       </c>
       <c r="T62">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="U62">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="V62">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W62">
         <v>1.08</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z62">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA62">
         <v>1.85</v>
       </c>
       <c r="AB62">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC62">
         <v>2.83</v>
@@ -10469,10 +10469,10 @@
         <v>1.09</v>
       </c>
       <c r="AF62">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG62">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="O63">
         <v>3.08</v>
       </c>
       <c r="P63">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10747,7 +10747,7 @@
         <v>3.37</v>
       </c>
       <c r="P64">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10913,10 +10913,10 @@
         <v>2.25</v>
       </c>
       <c r="Q65">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R65">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S65">
         <v>1.22</v>
@@ -10943,7 +10943,7 @@
         <v>4.55</v>
       </c>
       <c r="AA65">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB65">
         <v>2.28</v>
@@ -10961,7 +10961,7 @@
         <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11079,19 +11079,19 @@
         <v>1.95</v>
       </c>
       <c r="R66">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="S66">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T66">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="U66">
         <v>2.1</v>
       </c>
       <c r="V66">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W66">
         <v>1.18</v>
@@ -11106,10 +11106,10 @@
         <v>5.4</v>
       </c>
       <c r="AA66">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB66">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AC66">
         <v>2.11</v>
@@ -11118,10 +11118,10 @@
         <v>1.67</v>
       </c>
       <c r="AE66">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF66">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG66">
         <v>2.34</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK66">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,10 +11239,10 @@
         <v>1.53</v>
       </c>
       <c r="Q67">
-        <v>5.05</v>
+        <v>3.85</v>
       </c>
       <c r="R67">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="S67">
         <v>1.19</v>
@@ -11263,7 +11263,7 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z67">
         <v>4.95</v>
@@ -11281,7 +11281,7 @@
         <v>1.59</v>
       </c>
       <c r="AE67">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF67">
         <v>1.57</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
+        <v>1.13</v>
+      </c>
+      <c r="AK67">
         <v>1.17</v>
-      </c>
-      <c r="AK67">
-        <v>1.13</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,25 +11393,25 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q68">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R68">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="S68">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T68">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="U68">
         <v>2.75</v>
@@ -11420,37 +11420,37 @@
         <v>1.4</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z68">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="AA68">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB68">
         <v>1.88</v>
       </c>
       <c r="AC68">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD68">
         <v>1.33</v>
       </c>
       <c r="AE68">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF68">
         <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK70">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,10 +11891,10 @@
         <v>1.33</v>
       </c>
       <c r="Q71">
-        <v>6.5</v>
+        <v>7.12</v>
       </c>
       <c r="R71">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="S71">
         <v>1.25</v>
@@ -11909,7 +11909,7 @@
         <v>1.53</v>
       </c>
       <c r="W71">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X71">
         <v>1.02</v>
@@ -11939,7 +11939,7 @@
         <v>1.82</v>
       </c>
       <c r="AG71">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK71">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12048,10 +12048,10 @@
         <v>1.95</v>
       </c>
       <c r="O72">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P72">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q72">
         <v>2.55</v>
@@ -12060,7 +12060,7 @@
         <v>2.15</v>
       </c>
       <c r="S72">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T72">
         <v>3.08</v>
@@ -12118,7 +12118,7 @@
         <v>1.32</v>
       </c>
       <c r="AK72">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,43 +12208,43 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="O73">
-        <v>5.15</v>
+        <v>4.8</v>
       </c>
       <c r="P73">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="Q73">
         <v>6</v>
       </c>
       <c r="R73">
-        <v>2.71</v>
+        <v>2.89</v>
       </c>
       <c r="S73">
         <v>1.2</v>
       </c>
       <c r="T73">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U73">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V73">
         <v>1.67</v>
       </c>
       <c r="W73">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z73">
-        <v>5.71</v>
+        <v>5.77</v>
       </c>
       <c r="AA73">
         <v>1.4</v>
@@ -12253,10 +12253,10 @@
         <v>2.88</v>
       </c>
       <c r="AC73">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AD73">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE73">
         <v>1.27</v>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AK73">
         <v>1.06</v>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="N74">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O74">
         <v>3.25</v>
@@ -12404,7 +12404,7 @@
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z74">
         <v>2.7</v>
@@ -12419,7 +12419,7 @@
         <v>4.15</v>
       </c>
       <c r="AD74">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE74">
         <v>1.01</v>
@@ -12428,7 +12428,7 @@
         <v>1.98</v>
       </c>
       <c r="AG74">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12534,43 +12534,43 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O75">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P75">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q75">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R75">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U75">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V75">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W75">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X75">
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA75">
         <v>1.9</v>
@@ -12588,10 +12588,10 @@
         <v>1.05</v>
       </c>
       <c r="AF75">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG75">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK75">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O76">
         <v>4.8</v>
@@ -12715,7 +12715,7 @@
         <v>1.22</v>
       </c>
       <c r="T76">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
         <v>2.23</v>
@@ -12742,7 +12742,7 @@
         <v>2.31</v>
       </c>
       <c r="AC76">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="AD76">
         <v>1.54</v>
@@ -12751,7 +12751,7 @@
         <v>1.16</v>
       </c>
       <c r="AF76">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
         <v>1.95</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK76">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12881,13 +12881,13 @@
         <v>4</v>
       </c>
       <c r="U77">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="V77">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="W77">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X77">
         <v>1.01</v>
@@ -12917,7 +12917,7 @@
         <v>1.44</v>
       </c>
       <c r="AG77">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.14</v>
       </c>
       <c r="AK77">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="O79">
         <v>3.55</v>
@@ -13195,7 +13195,7 @@
         <v>3.1</v>
       </c>
       <c r="Q79">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="R79">
         <v>2.17</v>
@@ -13204,16 +13204,16 @@
         <v>1.29</v>
       </c>
       <c r="T79">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U79">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V79">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W79">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
         <v>1.03</v>
@@ -13225,7 +13225,7 @@
         <v>3.9</v>
       </c>
       <c r="AA79">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB79">
         <v>2.05</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
         <v>1.72</v>
@@ -13358,7 +13358,7 @@
         <v>3.95</v>
       </c>
       <c r="Q80">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="R80">
         <v>2.32</v>
@@ -13370,13 +13370,13 @@
         <v>3.46</v>
       </c>
       <c r="U80">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V80">
         <v>1.5</v>
       </c>
       <c r="W80">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
         <v>1.02</v>
@@ -13385,13 +13385,13 @@
         <v>1.14</v>
       </c>
       <c r="Z80">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="AA80">
         <v>1.66</v>
       </c>
       <c r="AB80">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC80">
         <v>2.49</v>
@@ -13406,7 +13406,7 @@
         <v>1.62</v>
       </c>
       <c r="AG80">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O81">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="Q81">
         <v>4.8</v>
       </c>
       <c r="R81">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T81">
         <v>3</v>
       </c>
       <c r="U81">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="V81">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W81">
         <v>1.08</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y81">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA81">
+        <v>1.72</v>
+      </c>
+      <c r="AB81">
         <v>1.9</v>
       </c>
-      <c r="AB81">
-        <v>1.83</v>
-      </c>
       <c r="AC81">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="AD81">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE81">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF81">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG81">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.2</v>
       </c>
       <c r="AK81">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O83">
         <v>3.48</v>
@@ -13853,7 +13853,7 @@
         <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T83">
         <v>2.96</v>
@@ -13868,10 +13868,10 @@
         <v>1.07</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z83">
         <v>3.5</v>
@@ -13883,7 +13883,7 @@
         <v>1.97</v>
       </c>
       <c r="AC83">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD83">
         <v>1.33</v>
@@ -14499,7 +14499,7 @@
         <v>2.6</v>
       </c>
       <c r="Q87">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R87">
         <v>2.04</v>
@@ -14508,7 +14508,7 @@
         <v>1.36</v>
       </c>
       <c r="T87">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U87">
         <v>2.88</v>
@@ -14517,13 +14517,13 @@
         <v>1.36</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X87">
         <v>1.03</v>
       </c>
       <c r="Y87">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
         <v>3.25</v>
@@ -14547,7 +14547,7 @@
         <v>1.76</v>
       </c>
       <c r="AG87">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,7 +14662,7 @@
         <v>10</v>
       </c>
       <c r="Q88">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R88">
         <v>2.7</v>
@@ -14683,13 +14683,13 @@
         <v>1.11</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z88">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA88">
         <v>1.67</v>
@@ -14698,19 +14698,19 @@
         <v>2.15</v>
       </c>
       <c r="AC88">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="AD88">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE88">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF88">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="AG88">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14825,10 +14825,10 @@
         <v>2.02</v>
       </c>
       <c r="Q89">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="R89">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S89">
         <v>1.2</v>
@@ -14837,7 +14837,7 @@
         <v>3.9</v>
       </c>
       <c r="U89">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="V89">
         <v>1.67</v>
@@ -14849,22 +14849,22 @@
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z89">
-        <v>5.63</v>
+        <v>5.15</v>
       </c>
       <c r="AA89">
         <v>1.47</v>
       </c>
       <c r="AB89">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="AC89">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD89">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE89">
         <v>1.28</v>
@@ -15009,13 +15009,13 @@
         <v>1.08</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
         <v>1.29</v>
       </c>
       <c r="Z90">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="AA90">
         <v>1.95</v>
@@ -15030,10 +15030,10 @@
         <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF90">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG90">
         <v>2.11</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK90">
         <v>1.39</v>
@@ -15151,25 +15151,25 @@
         <v>3.1</v>
       </c>
       <c r="Q91">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R91">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S91">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T91">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U91">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="V91">
         <v>1.38</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X91">
         <v>1.02</v>
@@ -15181,10 +15181,10 @@
         <v>3.04</v>
       </c>
       <c r="AA91">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AB91">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC91">
         <v>3.34</v>
@@ -15196,10 +15196,10 @@
         <v>1.05</v>
       </c>
       <c r="AF91">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG91">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK91">
         <v>1.62</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P92">
+        <v>4.6</v>
+      </c>
+      <c r="Q92">
+        <v>2.16</v>
+      </c>
+      <c r="R92">
         <v>2.25</v>
       </c>
-      <c r="Q92">
-        <v>3.02</v>
-      </c>
-      <c r="R92">
-        <v>2.14</v>
-      </c>
       <c r="S92">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T92">
-        <v>3.32</v>
+        <v>2.87</v>
       </c>
       <c r="U92">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="V92">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z92">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="AA92">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB92">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC92">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="AD92">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE92">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG92">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AK92">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="O93">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>4.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q93">
-        <v>2.16</v>
+        <v>3.02</v>
       </c>
       <c r="R93">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T93">
-        <v>2.87</v>
+        <v>3.32</v>
       </c>
       <c r="U93">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V93">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W93">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="AA93">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB93">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC93">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AD93">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE93">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF93">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG93">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AK93">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15643,7 +15643,7 @@
         <v>2.41</v>
       </c>
       <c r="R94">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S94">
         <v>1.42</v>
@@ -15655,13 +15655,13 @@
         <v>2.75</v>
       </c>
       <c r="V94">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
         <v>1.04</v>
       </c>
       <c r="X94">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
         <v>1.27</v>
@@ -15676,10 +15676,10 @@
         <v>1.78</v>
       </c>
       <c r="AC94">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="AD94">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE94">
         <v>1.06</v>
@@ -15815,13 +15815,13 @@
         <v>3.08</v>
       </c>
       <c r="U95">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V95">
         <v>1.44</v>
       </c>
       <c r="W95">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X95">
         <v>1</v>
@@ -15830,13 +15830,13 @@
         <v>1.2</v>
       </c>
       <c r="Z95">
-        <v>3.89</v>
+        <v>3.72</v>
       </c>
       <c r="AA95">
         <v>1.75</v>
       </c>
       <c r="AB95">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC95">
         <v>2.74</v>
@@ -15972,10 +15972,10 @@
         <v>2.38</v>
       </c>
       <c r="S96">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U96">
         <v>2.25</v>
@@ -15993,28 +15993,28 @@
         <v>1.15</v>
       </c>
       <c r="Z96">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA96">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB96">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AC96">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AD96">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE96">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF96">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AG96">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16135,10 +16135,10 @@
         <v>2.27</v>
       </c>
       <c r="S97">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T97">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U97">
         <v>2.5</v>
@@ -16153,7 +16153,7 @@
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z97">
         <v>3.9</v>
@@ -16162,22 +16162,22 @@
         <v>1.81</v>
       </c>
       <c r="AB97">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AC97">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD97">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE97">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF97">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG97">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK97">
         <v>1.47</v>
@@ -16295,13 +16295,13 @@
         <v>2.04</v>
       </c>
       <c r="R98">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="S98">
         <v>1.21</v>
       </c>
       <c r="T98">
-        <v>3.64</v>
+        <v>4.5</v>
       </c>
       <c r="U98">
         <v>2.05</v>
@@ -16319,16 +16319,16 @@
         <v>1.1</v>
       </c>
       <c r="Z98">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA98">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB98">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AC98">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AD98">
         <v>1.74</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,22 +17587,22 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.16</v>
+        <v>1.61</v>
       </c>
       <c r="O106">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P106">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="Q106">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R106">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="S106">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T106">
         <v>4</v>
@@ -17617,34 +17617,34 @@
         <v>1.17</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z106">
-        <v>5.15</v>
+        <v>6.5</v>
       </c>
       <c r="AA106">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB106">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AC106">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AD106">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AE106">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF106">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG106">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AK106">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,22 +17750,22 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="O107">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P107">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q107">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R107">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="S107">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T107">
         <v>4</v>
@@ -17780,50 +17780,50 @@
         <v>1.17</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z107">
-        <v>6.5</v>
+        <v>5.15</v>
       </c>
       <c r="AA107">
+        <v>1.47</v>
+      </c>
+      <c r="AB107">
+        <v>2.52</v>
+      </c>
+      <c r="AC107">
+        <v>2.09</v>
+      </c>
+      <c r="AD107">
+        <v>1.68</v>
+      </c>
+      <c r="AE107">
+        <v>1.25</v>
+      </c>
+      <c r="AF107">
+        <v>1.39</v>
+      </c>
+      <c r="AG107">
+        <v>2.88</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.44</v>
       </c>
-      <c r="AB107">
-        <v>2.75</v>
-      </c>
-      <c r="AC107">
-        <v>2.02</v>
-      </c>
-      <c r="AD107">
-        <v>1.77</v>
-      </c>
-      <c r="AE107">
-        <v>1.31</v>
-      </c>
-      <c r="AF107">
-        <v>1.4</v>
-      </c>
-      <c r="AG107">
-        <v>2.5</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.16</v>
-      </c>
       <c r="AK107">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18088,13 +18088,13 @@
         <v>2.69</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S109">
         <v>1.33</v>
       </c>
       <c r="T109">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U109">
         <v>2.45</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O110">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P110">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q110">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="R110">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="S110">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="U110">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="V110">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W110">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X110">
+        <v>1.01</v>
+      </c>
+      <c r="Y110">
+        <v>1.31</v>
+      </c>
+      <c r="Z110">
+        <v>2.92</v>
+      </c>
+      <c r="AA110">
+        <v>2.06</v>
+      </c>
+      <c r="AB110">
+        <v>1.6</v>
+      </c>
+      <c r="AC110">
+        <v>3.8</v>
+      </c>
+      <c r="AD110">
+        <v>1.19</v>
+      </c>
+      <c r="AE110">
         <v>1.02</v>
       </c>
-      <c r="Y110">
-        <v>1.36</v>
-      </c>
-      <c r="Z110">
-        <v>2.7</v>
-      </c>
-      <c r="AA110">
-        <v>2.2</v>
-      </c>
-      <c r="AB110">
-        <v>1.57</v>
-      </c>
-      <c r="AC110">
-        <v>4.2</v>
-      </c>
-      <c r="AD110">
-        <v>1.16</v>
-      </c>
-      <c r="AE110">
-        <v>1.01</v>
-      </c>
       <c r="AF110">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK110">
         <v>1.91</v>
@@ -18411,16 +18411,16 @@
         <v>3</v>
       </c>
       <c r="Q111">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="R111">
         <v>2</v>
       </c>
       <c r="S111">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T111">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U111">
         <v>3</v>
@@ -18429,16 +18429,16 @@
         <v>1.33</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z111">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AA111">
         <v>2.05</v>
@@ -18447,19 +18447,19 @@
         <v>1.73</v>
       </c>
       <c r="AC111">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD111">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF111">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG111">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK111">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,16 +18565,16 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P112">
         <v>2.45</v>
       </c>
       <c r="Q112">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="R112">
         <v>2.1</v>
@@ -18583,7 +18583,7 @@
         <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U112">
         <v>2.75</v>
@@ -18592,16 +18592,16 @@
         <v>1.4</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X112">
         <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z112">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA112">
         <v>1.85</v>
@@ -18610,19 +18610,19 @@
         <v>1.95</v>
       </c>
       <c r="AC112">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AD112">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE112">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF112">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG112">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>3.2</v>
       </c>
       <c r="Q114">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="R114">
         <v>2.16</v>
@@ -18924,16 +18924,16 @@
         <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z114">
         <v>3.08</v>
       </c>
       <c r="AA114">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AB114">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC114">
         <v>3.28</v>
@@ -18945,7 +18945,7 @@
         <v>1.06</v>
       </c>
       <c r="AF114">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG114">
         <v>1.96</v>
@@ -19069,19 +19069,19 @@
         <v>2.08</v>
       </c>
       <c r="S115">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T115">
         <v>3.01</v>
       </c>
       <c r="U115">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="V115">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X115">
         <v>1.03</v>
@@ -19096,7 +19096,7 @@
         <v>1.85</v>
       </c>
       <c r="AB115">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC115">
         <v>3.27</v>
@@ -19127,7 +19127,7 @@
         <v>1.3</v>
       </c>
       <c r="AK115">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19869,10 +19869,10 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="O120">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P120">
         <v>2.83</v>
@@ -19942,7 +19942,7 @@
         <v>1.35</v>
       </c>
       <c r="AK120">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20735,10 +20735,10 @@
         <v>1.3</v>
       </c>
       <c r="AE125">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF125">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG125">
         <v>2</v>
@@ -20856,10 +20856,10 @@
         <v>2.75</v>
       </c>
       <c r="Q126">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="R126">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S126">
         <v>1.3</v>
@@ -20868,10 +20868,10 @@
         <v>3.2</v>
       </c>
       <c r="U126">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V126">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W126">
         <v>1.11</v>
@@ -20880,16 +20880,16 @@
         <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z126">
-        <v>4.03</v>
+        <v>3.82</v>
       </c>
       <c r="AA126">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB126">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC126">
         <v>2.9</v>
@@ -20901,10 +20901,10 @@
         <v>1.1</v>
       </c>
       <c r="AF126">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG126">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AK126">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21013,7 +21013,7 @@
         <v>3.1</v>
       </c>
       <c r="O127">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P127">
         <v>2.2</v>
@@ -21052,7 +21052,7 @@
         <v>1.72</v>
       </c>
       <c r="AB127">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC127">
         <v>2.8</v>
@@ -21064,10 +21064,10 @@
         <v>1.13</v>
       </c>
       <c r="AF127">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG127">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21369,19 +21369,19 @@
         <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z129">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA129">
         <v>2</v>
       </c>
       <c r="AB129">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC129">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD129">
         <v>1.29</v>
@@ -21409,7 +21409,7 @@
         <v>1.22</v>
       </c>
       <c r="AK129">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21834,37 +21834,37 @@
         <v>5.5</v>
       </c>
       <c r="Q132">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="R132">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S132">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T132">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U132">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="V132">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W132">
         <v>1.08</v>
       </c>
       <c r="X132">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z132">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="AA132">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB132">
         <v>1.79</v>
@@ -21882,7 +21882,7 @@
         <v>1.95</v>
       </c>
       <c r="AG132">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK132">
         <v>2.25</v>
@@ -21994,7 +21994,7 @@
         <v>3.7</v>
       </c>
       <c r="P133">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="Q133">
         <v>2.12</v>
@@ -22009,7 +22009,7 @@
         <v>3.25</v>
       </c>
       <c r="U133">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V133">
         <v>1.47</v>
@@ -22021,28 +22021,28 @@
         <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z133">
-        <v>3.84</v>
+        <v>4.07</v>
       </c>
       <c r="AA133">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB133">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC133">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AD133">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE133">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF133">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG133">
         <v>2.05</v>
@@ -22061,7 +22061,7 @@
         <v>1.25</v>
       </c>
       <c r="AK133">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="O134">
         <v>3.4</v>
@@ -22160,19 +22160,19 @@
         <v>3.6</v>
       </c>
       <c r="Q134">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="R134">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S134">
         <v>1.36</v>
       </c>
       <c r="T134">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="U134">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V134">
         <v>1.38</v>
@@ -22187,10 +22187,10 @@
         <v>1.29</v>
       </c>
       <c r="Z134">
-        <v>3.04</v>
+        <v>3.19</v>
       </c>
       <c r="AA134">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB134">
         <v>1.73</v>
@@ -22208,7 +22208,7 @@
         <v>1.83</v>
       </c>
       <c r="AG134">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22323,55 +22323,55 @@
         <v>3.41</v>
       </c>
       <c r="Q135">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="R135">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="S135">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T135">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U135">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V135">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W135">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X135">
         <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z135">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="AA135">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB135">
         <v>2.02</v>
       </c>
       <c r="AC135">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD135">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE135">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF135">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AG135">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK135">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22483,7 +22483,7 @@
         <v>4.9</v>
       </c>
       <c r="P136">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="Q136">
         <v>1.76</v>
@@ -22498,10 +22498,10 @@
         <v>3.48</v>
       </c>
       <c r="U136">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="V136">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W136">
         <v>1.14</v>
@@ -22531,7 +22531,7 @@
         <v>1.25</v>
       </c>
       <c r="AF136">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG136">
         <v>2.05</v>
@@ -22652,7 +22652,7 @@
         <v>2.6</v>
       </c>
       <c r="R137">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S137">
         <v>1.3</v>
@@ -22661,40 +22661,40 @@
         <v>3.2</v>
       </c>
       <c r="U137">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="V137">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W137">
         <v>1.1</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z137">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="AA137">
         <v>1.83</v>
       </c>
       <c r="AB137">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC137">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD137">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE137">
         <v>1.08</v>
       </c>
       <c r="AF137">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG137">
         <v>2</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK137">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22969,16 +22969,16 @@
         <v>2.26</v>
       </c>
       <c r="O139">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P139">
         <v>2.8</v>
       </c>
       <c r="Q139">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="R139">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S139">
         <v>1.4</v>
@@ -22990,7 +22990,7 @@
         <v>2.9</v>
       </c>
       <c r="V139">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W139">
         <v>1.02</v>
@@ -23011,7 +23011,7 @@
         <v>1.67</v>
       </c>
       <c r="AC139">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AD139">
         <v>1.19</v>
@@ -23020,7 +23020,7 @@
         <v>1.03</v>
       </c>
       <c r="AF139">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG139">
         <v>1.85</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK139">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AL139">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -638,22 +638,22 @@
         <v>2.16</v>
       </c>
       <c r="O2">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="Q2">
         <v>2.54</v>
       </c>
       <c r="R2">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S2">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
         <v>2.6</v>
@@ -671,28 +671,28 @@
         <v>1.26</v>
       </c>
       <c r="Z2">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA2">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB2">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC2">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE2">
         <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
         <v>1.7</v>
@@ -1000,7 +1000,7 @@
         <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB4">
         <v>1.87</v>
@@ -1622,55 +1622,55 @@
         <v>5.04</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="R8">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T8">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="U8">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB8">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC8">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AD8">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3771,7 +3771,7 @@
         <v>2.92</v>
       </c>
       <c r="AA21">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AB21">
         <v>1.67</v>
@@ -4097,7 +4097,7 @@
         <v>3.14</v>
       </c>
       <c r="AA23">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB23">
         <v>1.75</v>
@@ -4393,55 +4393,55 @@
         <v>2.85</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA25">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AB25">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -6853,10 +6853,10 @@
         <v>2.1</v>
       </c>
       <c r="V40">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W40">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -7010,13 +7010,13 @@
         <v>1.38</v>
       </c>
       <c r="T41">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="U41">
         <v>2.72</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
         <v>1.05</v>
@@ -7031,7 +7031,7 @@
         <v>3.14</v>
       </c>
       <c r="AA41">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB41">
         <v>1.79</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O43">
         <v>3.45</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -7991,7 +7991,7 @@
         <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V47">
         <v>1.57</v>
@@ -8631,19 +8631,19 @@
         <v>2.64</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R51">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="U51">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V51">
         <v>1.28</v>
@@ -8664,7 +8664,7 @@
         <v>2.11</v>
       </c>
       <c r="AB51">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC51">
         <v>3.58</v>
@@ -8824,7 +8824,7 @@
         <v>2.75</v>
       </c>
       <c r="AA52">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB52">
         <v>1.9</v>
@@ -8839,10 +8839,10 @@
         <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG52">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>1.33</v>
       </c>
       <c r="T53">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="U53">
         <v>2.26</v>
@@ -8987,25 +8987,25 @@
         <v>3.34</v>
       </c>
       <c r="AA53">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB53">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC53">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AD53">
         <v>1.3</v>
       </c>
       <c r="AE53">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q57">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="R57">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S57">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="U57">
         <v>2.1</v>
@@ -9633,10 +9633,10 @@
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AA57">
         <v>1.44</v>
@@ -9645,19 +9645,19 @@
         <v>2.62</v>
       </c>
       <c r="AC57">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD57">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE57">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF57">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG57">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9778,13 +9778,13 @@
         <v>2.32</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T58">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U58">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V58">
         <v>1.49</v>
@@ -9962,7 +9962,7 @@
         <v>1.14</v>
       </c>
       <c r="Z59">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA59">
         <v>1.61</v>
@@ -9971,13 +9971,13 @@
         <v>2.25</v>
       </c>
       <c r="AC59">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="AD59">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE59">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
         <v>1.53</v>
@@ -10131,7 +10131,7 @@
         <v>1.62</v>
       </c>
       <c r="AB60">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AC60">
         <v>2.43</v>
@@ -10581,40 +10581,40 @@
         <v>2.62</v>
       </c>
       <c r="O63">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="P63">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA63">
         <v>2.2</v>
@@ -10623,19 +10623,19 @@
         <v>1.65</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11109,7 +11109,7 @@
         <v>1.42</v>
       </c>
       <c r="AB66">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC66">
         <v>2.11</v>
@@ -11466,7 +11466,7 @@
         <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12051,7 +12051,7 @@
         <v>3.45</v>
       </c>
       <c r="P72">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q72">
         <v>2.55</v>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O74">
         <v>3.25</v>
@@ -12410,7 +12410,7 @@
         <v>2.7</v>
       </c>
       <c r="AA74">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AB74">
         <v>1.6</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O75">
         <v>3.1</v>
       </c>
       <c r="P75">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -12567,10 +12567,10 @@
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z75">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA75">
         <v>1.9</v>
@@ -12588,10 +12588,10 @@
         <v>1.05</v>
       </c>
       <c r="AF75">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG75">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>5.64</v>
       </c>
       <c r="AA77">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB77">
         <v>2.66</v>
@@ -13219,10 +13219,10 @@
         <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA79">
         <v>1.75</v>
@@ -13234,7 +13234,7 @@
         <v>2.74</v>
       </c>
       <c r="AD79">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE79">
         <v>1.09</v>
@@ -13388,7 +13388,7 @@
         <v>4.29</v>
       </c>
       <c r="AA80">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB80">
         <v>2.14</v>
@@ -13551,10 +13551,10 @@
         <v>4.1</v>
       </c>
       <c r="AA81">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB81">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC81">
         <v>2.79</v>
@@ -13711,7 +13711,7 @@
         <v>1.15</v>
       </c>
       <c r="Z82">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA82">
         <v>1.59</v>
@@ -13726,13 +13726,13 @@
         <v>1.47</v>
       </c>
       <c r="AE82">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF82">
         <v>1.53</v>
       </c>
       <c r="AG82">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
         <v>1.27</v>
@@ -14170,13 +14170,13 @@
         <v>3.7</v>
       </c>
       <c r="P85">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q85">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R85">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="S85">
         <v>1.17</v>
@@ -14203,13 +14203,13 @@
         <v>6.5</v>
       </c>
       <c r="AA85">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB85">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC85">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AD85">
         <v>1.72</v>
@@ -14221,7 +14221,7 @@
         <v>1.36</v>
       </c>
       <c r="AG85">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14333,13 +14333,13 @@
         <v>3.85</v>
       </c>
       <c r="P86">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q86">
         <v>2.06</v>
       </c>
       <c r="R86">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="S86">
         <v>1.22</v>
@@ -14378,13 +14378,13 @@
         <v>1.59</v>
       </c>
       <c r="AE86">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF86">
         <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14662,7 +14662,7 @@
         <v>10</v>
       </c>
       <c r="Q88">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R88">
         <v>2.7</v>
@@ -14698,13 +14698,13 @@
         <v>2.15</v>
       </c>
       <c r="AC88">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AD88">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE88">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF88">
         <v>2.15</v>
@@ -14858,7 +14858,7 @@
         <v>1.47</v>
       </c>
       <c r="AB89">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="AC89">
         <v>2.1</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,80 +14979,80 @@
         </is>
       </c>
       <c r="N90">
+        <v>1.65</v>
+      </c>
+      <c r="O90">
+        <v>3.7</v>
+      </c>
+      <c r="P90">
+        <v>4.6</v>
+      </c>
+      <c r="Q90">
+        <v>2.16</v>
+      </c>
+      <c r="R90">
+        <v>2.25</v>
+      </c>
+      <c r="S90">
+        <v>1.35</v>
+      </c>
+      <c r="T90">
         <v>2.87</v>
       </c>
-      <c r="O90">
-        <v>3.25</v>
-      </c>
-      <c r="P90">
-        <v>2.2</v>
-      </c>
-      <c r="Q90">
-        <v>3.58</v>
-      </c>
-      <c r="R90">
+      <c r="U90">
+        <v>2.65</v>
+      </c>
+      <c r="V90">
+        <v>1.45</v>
+      </c>
+      <c r="W90">
+        <v>1.1</v>
+      </c>
+      <c r="X90">
+        <v>1</v>
+      </c>
+      <c r="Y90">
+        <v>1.19</v>
+      </c>
+      <c r="Z90">
+        <v>4.02</v>
+      </c>
+      <c r="AA90">
+        <v>1.79</v>
+      </c>
+      <c r="AB90">
+        <v>2.03</v>
+      </c>
+      <c r="AC90">
+        <v>2.66</v>
+      </c>
+      <c r="AD90">
+        <v>1.37</v>
+      </c>
+      <c r="AE90">
+        <v>1.12</v>
+      </c>
+      <c r="AF90">
+        <v>1.72</v>
+      </c>
+      <c r="AG90">
+        <v>2</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
+        <v>1.21</v>
+      </c>
+      <c r="AK90">
         <v>2.1</v>
-      </c>
-      <c r="S90">
-        <v>1.33</v>
-      </c>
-      <c r="T90">
-        <v>2.96</v>
-      </c>
-      <c r="U90">
-        <v>2.57</v>
-      </c>
-      <c r="V90">
-        <v>1.4</v>
-      </c>
-      <c r="W90">
-        <v>1.08</v>
-      </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>1.29</v>
-      </c>
-      <c r="Z90">
-        <v>3.54</v>
-      </c>
-      <c r="AA90">
-        <v>1.95</v>
-      </c>
-      <c r="AB90">
-        <v>1.91</v>
-      </c>
-      <c r="AC90">
-        <v>3.3</v>
-      </c>
-      <c r="AD90">
-        <v>1.3</v>
-      </c>
-      <c r="AE90">
-        <v>1.11</v>
-      </c>
-      <c r="AF90">
-        <v>1.7</v>
-      </c>
-      <c r="AG90">
-        <v>2.11</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.3</v>
-      </c>
-      <c r="AK90">
-        <v>1.39</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
+        <v>1.8</v>
+      </c>
+      <c r="O91">
+        <v>3.5</v>
+      </c>
+      <c r="P91">
+        <v>3.9</v>
+      </c>
+      <c r="Q91">
+        <v>2.41</v>
+      </c>
+      <c r="R91">
         <v>2.2</v>
-      </c>
-      <c r="O91">
-        <v>3.1</v>
-      </c>
-      <c r="P91">
-        <v>3.1</v>
-      </c>
-      <c r="Q91">
-        <v>2.88</v>
-      </c>
-      <c r="R91">
-        <v>2</v>
       </c>
       <c r="S91">
         <v>1.42</v>
       </c>
       <c r="T91">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="U91">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="V91">
         <v>1.38</v>
       </c>
       <c r="W91">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AB91">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC91">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="AD91">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE91">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG91">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="O92">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P92">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q92">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="R92">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S92">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T92">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="U92">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="V92">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W92">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X92">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z92">
-        <v>3.99</v>
+        <v>3.04</v>
       </c>
       <c r="AA92">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AB92">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC92">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="AD92">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AE92">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF92">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG92">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
+        <v>2.87</v>
+      </c>
+      <c r="O93">
+        <v>3.25</v>
+      </c>
+      <c r="P93">
+        <v>2.2</v>
+      </c>
+      <c r="Q93">
+        <v>3.58</v>
+      </c>
+      <c r="R93">
+        <v>2.1</v>
+      </c>
+      <c r="S93">
+        <v>1.33</v>
+      </c>
+      <c r="T93">
+        <v>2.96</v>
+      </c>
+      <c r="U93">
         <v>2.7</v>
       </c>
-      <c r="O93">
-        <v>3.4</v>
-      </c>
-      <c r="P93">
-        <v>2.25</v>
-      </c>
-      <c r="Q93">
-        <v>3.02</v>
-      </c>
-      <c r="R93">
-        <v>2.14</v>
-      </c>
-      <c r="S93">
-        <v>1.27</v>
-      </c>
-      <c r="T93">
-        <v>3.32</v>
-      </c>
-      <c r="U93">
-        <v>2.45</v>
-      </c>
       <c r="V93">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z93">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
       <c r="AA93">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB93">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC93">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="AD93">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF93">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG93">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AK93">
         <v>1.39</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="O94">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P94">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q94">
-        <v>2.41</v>
+        <v>3.02</v>
       </c>
       <c r="R94">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S94">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T94">
-        <v>2.59</v>
+        <v>3.32</v>
       </c>
       <c r="U94">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V94">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W94">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X94">
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z94">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA94">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="AB94">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC94">
-        <v>3.74</v>
+        <v>2.52</v>
       </c>
       <c r="AD94">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE94">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF94">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG94">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AK94">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15800,19 +15800,19 @@
         <v>3.25</v>
       </c>
       <c r="P95">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q95">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="R95">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T95">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="U95">
         <v>2.63</v>
@@ -15839,7 +15839,7 @@
         <v>2.05</v>
       </c>
       <c r="AC95">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AD95">
         <v>1.35</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK98">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="O99">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P99">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q99">
         <v>2</v>
@@ -16464,7 +16464,7 @@
         <v>1.14</v>
       </c>
       <c r="T99">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U99">
         <v>1.91</v>
@@ -16482,28 +16482,28 @@
         <v>1.07</v>
       </c>
       <c r="Z99">
-        <v>6.45</v>
+        <v>6.15</v>
       </c>
       <c r="AA99">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB99">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AC99">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AD99">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AE99">
         <v>1.33</v>
       </c>
       <c r="AF99">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AG99">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16615,19 +16615,19 @@
         <v>3.7</v>
       </c>
       <c r="P100">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="Q100">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="R100">
-        <v>2.37</v>
+        <v>2.59</v>
       </c>
       <c r="S100">
         <v>1.21</v>
       </c>
       <c r="T100">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="U100">
         <v>2.1</v>
@@ -16648,25 +16648,25 @@
         <v>5.45</v>
       </c>
       <c r="AA100">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AB100">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AC100">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AD100">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AE100">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF100">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG100">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK100">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O101">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P101">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q101">
         <v>2.1</v>
@@ -16787,7 +16787,7 @@
         <v>2.63</v>
       </c>
       <c r="S101">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T101">
         <v>4.2</v>
@@ -16799,37 +16799,37 @@
         <v>1.8</v>
       </c>
       <c r="W101">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z101">
-        <v>6.15</v>
+        <v>5.75</v>
       </c>
       <c r="AA101">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AB101">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC101">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AD101">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AE101">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AF101">
         <v>1.4</v>
       </c>
       <c r="AG101">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16938,10 +16938,10 @@
         <v>2.3</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P102">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q102">
         <v>2.8</v>
@@ -16953,10 +16953,10 @@
         <v>1.22</v>
       </c>
       <c r="T102">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="U102">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="V102">
         <v>1.58</v>
@@ -16971,13 +16971,13 @@
         <v>1.15</v>
       </c>
       <c r="Z102">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA102">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB102">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AC102">
         <v>2.33</v>
@@ -16989,10 +16989,10 @@
         <v>1.16</v>
       </c>
       <c r="AF102">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG102">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="O103">
         <v>3.5</v>
@@ -17107,16 +17107,16 @@
         <v>2.37</v>
       </c>
       <c r="Q103">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R103">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S103">
         <v>1.17</v>
       </c>
       <c r="T103">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="U103">
         <v>1.95</v>
@@ -17137,22 +17137,22 @@
         <v>6.16</v>
       </c>
       <c r="AA103">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB103">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AC103">
         <v>2</v>
       </c>
       <c r="AD103">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AE103">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF103">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG103">
         <v>3</v>
@@ -17270,10 +17270,10 @@
         <v>3.5</v>
       </c>
       <c r="Q104">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="R104">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S104">
         <v>1.25</v>
@@ -17282,10 +17282,10 @@
         <v>3.5</v>
       </c>
       <c r="U104">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V104">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W104">
         <v>1.12</v>
@@ -17294,28 +17294,28 @@
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z104">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA104">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AB104">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AC104">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AD104">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE104">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF104">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG104">
         <v>2.3</v>
@@ -17424,61 +17424,61 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O105">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P105">
         <v>2.6</v>
       </c>
       <c r="Q105">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="R105">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S105">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T105">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U105">
         <v>1.95</v>
       </c>
       <c r="V105">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="W105">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z105">
-        <v>6.29</v>
+        <v>5.8</v>
       </c>
       <c r="AA105">
+        <v>1.37</v>
+      </c>
+      <c r="AB105">
+        <v>2.66</v>
+      </c>
+      <c r="AC105">
+        <v>2.02</v>
+      </c>
+      <c r="AD105">
+        <v>1.73</v>
+      </c>
+      <c r="AE105">
+        <v>1.29</v>
+      </c>
+      <c r="AF105">
         <v>1.36</v>
-      </c>
-      <c r="AB105">
-        <v>3.1</v>
-      </c>
-      <c r="AC105">
-        <v>1.94</v>
-      </c>
-      <c r="AD105">
-        <v>1.85</v>
-      </c>
-      <c r="AE105">
-        <v>1.36</v>
-      </c>
-      <c r="AF105">
-        <v>1.33</v>
       </c>
       <c r="AG105">
         <v>2.9</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O106">
         <v>4</v>
@@ -17596,7 +17596,7 @@
         <v>3.95</v>
       </c>
       <c r="Q106">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R106">
         <v>2.45</v>
@@ -17605,7 +17605,7 @@
         <v>1.17</v>
       </c>
       <c r="T106">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="U106">
         <v>2</v>
@@ -17623,28 +17623,28 @@
         <v>1.08</v>
       </c>
       <c r="Z106">
-        <v>6.5</v>
+        <v>5.91</v>
       </c>
       <c r="AA106">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB106">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC106">
         <v>2.02</v>
       </c>
       <c r="AD106">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AE106">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AF106">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG106">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK106">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,7 +17750,7 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O107">
         <v>3.6</v>
@@ -17759,7 +17759,7 @@
         <v>2.6</v>
       </c>
       <c r="Q107">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R107">
         <v>2.37</v>
@@ -17789,10 +17789,10 @@
         <v>5.15</v>
       </c>
       <c r="AA107">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB107">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AC107">
         <v>2.09</v>
@@ -17804,10 +17804,10 @@
         <v>1.25</v>
       </c>
       <c r="AF107">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG107">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK107">
         <v>1.57</v>
@@ -17913,22 +17913,22 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O108">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="P108">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q108">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R108">
         <v>2.88</v>
       </c>
       <c r="S108">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T108">
         <v>4.6</v>
@@ -17949,28 +17949,28 @@
         <v>1.06</v>
       </c>
       <c r="Z108">
-        <v>7.5</v>
+        <v>6.55</v>
       </c>
       <c r="AA108">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AB108">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AC108">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AD108">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AE108">
         <v>1.33</v>
       </c>
       <c r="AF108">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG108">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AK108">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18245,7 +18245,7 @@
         <v>3.2</v>
       </c>
       <c r="P110">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q110">
         <v>2.31</v>
@@ -18254,19 +18254,19 @@
         <v>2.03</v>
       </c>
       <c r="S110">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T110">
         <v>2.57</v>
       </c>
       <c r="U110">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="V110">
         <v>1.29</v>
       </c>
       <c r="W110">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
         <v>1.01</v>
@@ -18459,7 +18459,7 @@
         <v>1.7</v>
       </c>
       <c r="AG111">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18577,13 +18577,13 @@
         <v>3.2</v>
       </c>
       <c r="R112">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S112">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T112">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U112">
         <v>2.75</v>
@@ -18592,7 +18592,7 @@
         <v>1.4</v>
       </c>
       <c r="W112">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X112">
         <v>1</v>
@@ -18604,10 +18604,10 @@
         <v>3.74</v>
       </c>
       <c r="AA112">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB112">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC112">
         <v>2.7</v>
@@ -18619,7 +18619,7 @@
         <v>1.11</v>
       </c>
       <c r="AF112">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG112">
         <v>2.25</v>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="AK112">
         <v>1.37</v>
@@ -18903,7 +18903,7 @@
         <v>2.75</v>
       </c>
       <c r="R114">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S114">
         <v>1.38</v>
@@ -19217,80 +19217,80 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O116">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P116">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q116">
+        <v>3.06</v>
+      </c>
+      <c r="R116">
+        <v>2.02</v>
+      </c>
+      <c r="S116">
+        <v>1.38</v>
+      </c>
+      <c r="T116">
+        <v>2.64</v>
+      </c>
+      <c r="U116">
+        <v>2.8</v>
+      </c>
+      <c r="V116">
+        <v>1.36</v>
+      </c>
+      <c r="W116">
+        <v>1.07</v>
+      </c>
+      <c r="X116">
+        <v>1.01</v>
+      </c>
+      <c r="Y116">
+        <v>1.28</v>
+      </c>
+      <c r="Z116">
+        <v>3.05</v>
+      </c>
+      <c r="AA116">
+        <v>1.98</v>
+      </c>
+      <c r="AB116">
+        <v>1.71</v>
+      </c>
+      <c r="AC116">
         <v>3.42</v>
       </c>
-      <c r="R116">
-        <v>1.97</v>
-      </c>
-      <c r="S116">
-        <v>1.41</v>
-      </c>
-      <c r="T116">
-        <v>2.54</v>
-      </c>
-      <c r="U116">
-        <v>3</v>
-      </c>
-      <c r="V116">
+      <c r="AD116">
+        <v>1.23</v>
+      </c>
+      <c r="AE116">
+        <v>1.04</v>
+      </c>
+      <c r="AF116">
+        <v>1.75</v>
+      </c>
+      <c r="AG116">
+        <v>1.93</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ116">
         <v>1.33</v>
       </c>
-      <c r="W116">
-        <v>1.06</v>
-      </c>
-      <c r="X116">
-        <v>1.02</v>
-      </c>
-      <c r="Y116">
-        <v>1.33</v>
-      </c>
-      <c r="Z116">
-        <v>2.83</v>
-      </c>
-      <c r="AA116">
-        <v>2.1</v>
-      </c>
-      <c r="AB116">
-        <v>1.63</v>
-      </c>
-      <c r="AC116">
-        <v>3.8</v>
-      </c>
-      <c r="AD116">
-        <v>1.19</v>
-      </c>
-      <c r="AE116">
-        <v>1.03</v>
-      </c>
-      <c r="AF116">
-        <v>1.82</v>
-      </c>
-      <c r="AG116">
-        <v>1.82</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
+      <c r="AK116">
         <v>1.42</v>
-      </c>
-      <c r="AK116">
-        <v>1.35</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,43 +19380,43 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O117">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q117">
-        <v>4.49</v>
+        <v>4.44</v>
       </c>
       <c r="R117">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="S117">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T117">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="U117">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="V117">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W117">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X117">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z117">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="AA117">
         <v>1.67</v>
@@ -19425,19 +19425,19 @@
         <v>2.15</v>
       </c>
       <c r="AC117">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AD117">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE117">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF117">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG117">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
+        <v>1.21</v>
+      </c>
+      <c r="AK117">
         <v>1.19</v>
-      </c>
-      <c r="AK117">
-        <v>1.18</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19585,7 +19585,7 @@
         <v>1.25</v>
       </c>
       <c r="AB118">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AC118">
         <v>1.69</v>
@@ -19869,10 +19869,10 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="O120">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="P120">
         <v>2.83</v>
@@ -21013,7 +21013,7 @@
         <v>3.1</v>
       </c>
       <c r="O127">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P127">
         <v>2.2</v>
@@ -21375,10 +21375,10 @@
         <v>3.4</v>
       </c>
       <c r="AA129">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB129">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC129">
         <v>3.5</v>
@@ -21541,7 +21541,7 @@
         <v>1.49</v>
       </c>
       <c r="AB130">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC130">
         <v>2.22</v>
@@ -22024,7 +22024,7 @@
         <v>1.2</v>
       </c>
       <c r="Z133">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="AA133">
         <v>1.72</v>
@@ -22160,10 +22160,10 @@
         <v>3.6</v>
       </c>
       <c r="Q134">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="R134">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S134">
         <v>1.36</v>
@@ -22187,7 +22187,7 @@
         <v>1.29</v>
       </c>
       <c r="Z134">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="AA134">
         <v>2.02</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="Q135">
         <v>2.49</v>
@@ -22969,7 +22969,7 @@
         <v>2.26</v>
       </c>
       <c r="O139">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P139">
         <v>2.8</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P4">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q4">
         <v>2.85</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="O25">
         <v>3</v>
       </c>
       <c r="P25">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q25">
         <v>3.5</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="O27">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="P27">
         <v>1.2</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -7828,10 +7828,10 @@
         <v>3.8</v>
       </c>
       <c r="U46">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="V46">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W46">
         <v>1.14</v>
@@ -7846,7 +7846,7 @@
         <v>4.8</v>
       </c>
       <c r="AA46">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB46">
         <v>2.33</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="O52">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="P52">
-        <v>4.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q52">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S52">
+        <v>1.33</v>
+      </c>
+      <c r="T52">
+        <v>2.24</v>
+      </c>
+      <c r="U52">
+        <v>2.26</v>
+      </c>
+      <c r="V52">
         <v>1.32</v>
-      </c>
-      <c r="T52">
-        <v>2.26</v>
-      </c>
-      <c r="U52">
-        <v>2.75</v>
-      </c>
-      <c r="V52">
-        <v>1.33</v>
       </c>
       <c r="W52">
         <v>1.04</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z52">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA52">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB52">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC52">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AD52">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="O53">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="P53">
-        <v>2.58</v>
+        <v>4.66</v>
       </c>
       <c r="Q53">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R53">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
+        <v>1.32</v>
+      </c>
+      <c r="T53">
+        <v>2.26</v>
+      </c>
+      <c r="U53">
+        <v>2.75</v>
+      </c>
+      <c r="V53">
         <v>1.33</v>
-      </c>
-      <c r="T53">
-        <v>2.24</v>
-      </c>
-      <c r="U53">
-        <v>2.26</v>
-      </c>
-      <c r="V53">
-        <v>1.32</v>
       </c>
       <c r="W53">
         <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="AA53">
+        <v>1.9</v>
+      </c>
+      <c r="AB53">
+        <v>1.9</v>
+      </c>
+      <c r="AC53">
+        <v>2.92</v>
+      </c>
+      <c r="AD53">
+        <v>1.31</v>
+      </c>
+      <c r="AE53">
+        <v>1.08</v>
+      </c>
+      <c r="AF53">
+        <v>1.83</v>
+      </c>
+      <c r="AG53">
+        <v>1.85</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.3</v>
+      </c>
+      <c r="AK53">
         <v>1.95</v>
-      </c>
-      <c r="AB53">
-        <v>1.62</v>
-      </c>
-      <c r="AC53">
-        <v>2.7</v>
-      </c>
-      <c r="AD53">
-        <v>1.3</v>
-      </c>
-      <c r="AE53">
-        <v>1.05</v>
-      </c>
-      <c r="AF53">
-        <v>1.67</v>
-      </c>
-      <c r="AG53">
-        <v>2.1</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.44</v>
-      </c>
-      <c r="AK53">
-        <v>1.44</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O76">
         <v>4.8</v>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="O89">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P89">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q89">
-        <v>3.67</v>
+        <v>3.46</v>
       </c>
       <c r="R89">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="S89">
         <v>1.2</v>
@@ -14858,7 +14858,7 @@
         <v>1.47</v>
       </c>
       <c r="AB89">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="AC89">
         <v>2.1</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="O90">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P90">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q90">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="R90">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S90">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T90">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="U90">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="V90">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W90">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X90">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z90">
-        <v>4.02</v>
+        <v>3.04</v>
       </c>
       <c r="AA90">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AB90">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AC90">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="AD90">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AE90">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF90">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG90">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK90">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="O91">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P91">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q91">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="R91">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S91">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T91">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="U91">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V91">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z91">
-        <v>3.25</v>
+        <v>4.02</v>
       </c>
       <c r="AA91">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="AB91">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AC91">
-        <v>3.72</v>
+        <v>2.66</v>
       </c>
       <c r="AD91">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF91">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG91">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK91">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="O92">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q92">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="R92">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="S92">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T92">
-        <v>2.76</v>
+        <v>3.32</v>
       </c>
       <c r="U92">
-        <v>3.12</v>
+        <v>2.45</v>
       </c>
       <c r="V92">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W92">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="AA92">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AB92">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC92">
-        <v>3.34</v>
+        <v>2.52</v>
       </c>
       <c r="AD92">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE92">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF92">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AG92">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AK92">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="O94">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P94">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q94">
-        <v>3.02</v>
+        <v>2.41</v>
       </c>
       <c r="R94">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S94">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="T94">
-        <v>3.32</v>
+        <v>2.59</v>
       </c>
       <c r="U94">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V94">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X94">
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z94">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA94">
-        <v>1.65</v>
+        <v>2.11</v>
       </c>
       <c r="AB94">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC94">
-        <v>2.52</v>
+        <v>3.72</v>
       </c>
       <c r="AD94">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE94">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF94">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG94">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="O121">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P121">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q121">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="R121">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S121">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T121">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U121">
+        <v>2.47</v>
+      </c>
+      <c r="V121">
+        <v>1.53</v>
+      </c>
+      <c r="W121">
+        <v>1.12</v>
+      </c>
+      <c r="X121">
+        <v>1.02</v>
+      </c>
+      <c r="Y121">
+        <v>1.15</v>
+      </c>
+      <c r="Z121">
+        <v>4.35</v>
+      </c>
+      <c r="AA121">
+        <v>1.62</v>
+      </c>
+      <c r="AB121">
         <v>2.25</v>
       </c>
-      <c r="V121">
+      <c r="AC121">
+        <v>2.56</v>
+      </c>
+      <c r="AD121">
+        <v>1.4</v>
+      </c>
+      <c r="AE121">
+        <v>1.18</v>
+      </c>
+      <c r="AF121">
         <v>1.57</v>
       </c>
-      <c r="W121">
-        <v>1.08</v>
-      </c>
-      <c r="X121">
-        <v>1.01</v>
-      </c>
-      <c r="Y121">
-        <v>1.13</v>
-      </c>
-      <c r="Z121">
-        <v>4.5</v>
-      </c>
-      <c r="AA121">
-        <v>1.59</v>
-      </c>
-      <c r="AB121">
-        <v>2.27</v>
-      </c>
-      <c r="AC121">
-        <v>2.41</v>
-      </c>
-      <c r="AD121">
-        <v>1.45</v>
-      </c>
-      <c r="AE121">
-        <v>1.14</v>
-      </c>
-      <c r="AF121">
-        <v>1.55</v>
-      </c>
       <c r="AG121">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK121">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="O122">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P122">
+        <v>1.59</v>
+      </c>
+      <c r="Q122">
+        <v>4.39</v>
+      </c>
+      <c r="R122">
+        <v>2.18</v>
+      </c>
+      <c r="S122">
+        <v>1.3</v>
+      </c>
+      <c r="T122">
         <v>3.2</v>
       </c>
-      <c r="Q122">
-        <v>2.4</v>
-      </c>
-      <c r="R122">
-        <v>2.25</v>
-      </c>
-      <c r="S122">
-        <v>1.26</v>
-      </c>
-      <c r="T122">
-        <v>3.4</v>
-      </c>
       <c r="U122">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V122">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W122">
+        <v>1.09</v>
+      </c>
+      <c r="X122">
+        <v>1.03</v>
+      </c>
+      <c r="Y122">
+        <v>1.17</v>
+      </c>
+      <c r="Z122">
+        <v>3.98</v>
+      </c>
+      <c r="AA122">
+        <v>1.72</v>
+      </c>
+      <c r="AB122">
+        <v>2.08</v>
+      </c>
+      <c r="AC122">
+        <v>2.7</v>
+      </c>
+      <c r="AD122">
+        <v>1.36</v>
+      </c>
+      <c r="AE122">
         <v>1.1</v>
       </c>
-      <c r="X122">
-        <v>1.02</v>
-      </c>
-      <c r="Y122">
-        <v>1.21</v>
-      </c>
-      <c r="Z122">
-        <v>4.35</v>
-      </c>
-      <c r="AA122">
-        <v>1.68</v>
-      </c>
-      <c r="AB122">
-        <v>2.25</v>
-      </c>
-      <c r="AC122">
-        <v>2.56</v>
-      </c>
-      <c r="AD122">
-        <v>1.4</v>
-      </c>
-      <c r="AE122">
-        <v>1.12</v>
-      </c>
       <c r="AF122">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG122">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK122">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>4.5</v>
+        <v>1.61</v>
       </c>
       <c r="O123">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P123">
-        <v>1.56</v>
+        <v>4.15</v>
       </c>
       <c r="Q123">
-        <v>4.39</v>
+        <v>2.06</v>
       </c>
       <c r="R123">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="S123">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T123">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U123">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V123">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W123">
         <v>1.09</v>
       </c>
       <c r="X123">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y123">
         <v>1.17</v>
       </c>
       <c r="Z123">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA123">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB123">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AC123">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD123">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE123">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AF123">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG123">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK123">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,80 +20521,80 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="O124">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P124">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="Q124">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="R124">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S124">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T124">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="U124">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V124">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W124">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X124">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z124">
-        <v>4</v>
+        <v>4.69</v>
       </c>
       <c r="AA124">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB124">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AC124">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AD124">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE124">
+        <v>1.14</v>
+      </c>
+      <c r="AF124">
+        <v>1.55</v>
+      </c>
+      <c r="AG124">
+        <v>2.26</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ124">
         <v>1.19</v>
       </c>
-      <c r="AF124">
-        <v>1.67</v>
-      </c>
-      <c r="AG124">
-        <v>2.08</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>1.21</v>
-      </c>
       <c r="AK124">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21182,10 +21182,10 @@
         <v>10</v>
       </c>
       <c r="Q128">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R128">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="S128">
         <v>1.14</v>
@@ -21206,22 +21206,22 @@
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z128">
-        <v>6.12</v>
+        <v>6.15</v>
       </c>
       <c r="AA128">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB128">
         <v>3.1</v>
       </c>
       <c r="AC128">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD128">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AE128">
         <v>1.32</v>
@@ -21246,7 +21246,7 @@
         <v>1.02</v>
       </c>
       <c r="AK128">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -22480,7 +22480,7 @@
         <v>1.36</v>
       </c>
       <c r="O136">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="P136">
         <v>7.75</v>
@@ -22547,7 +22547,7 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK136">
         <v>3.1</v>
@@ -22821,7 +22821,7 @@
         <v>1.26</v>
       </c>
       <c r="T138">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U138">
         <v>2.4</v>
@@ -22836,13 +22836,13 @@
         <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z138">
         <v>2.9</v>
       </c>
       <c r="AA138">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB138">
         <v>1.96</v>
@@ -22854,7 +22854,7 @@
         <v>1.29</v>
       </c>
       <c r="AE138">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF138">
         <v>1.55</v>
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK138">
         <v>1.17</v>
@@ -23138,7 +23138,7 @@
         <v>2.51</v>
       </c>
       <c r="Q140">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R140">
         <v>2.4</v>
@@ -23177,13 +23177,13 @@
         <v>2.01</v>
       </c>
       <c r="AD140">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE140">
         <v>1.16</v>
       </c>
       <c r="AF140">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG140">
         <v>2.5</v>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AK140">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23346,10 +23346,10 @@
         <v>1.24</v>
       </c>
       <c r="AF141">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG141">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AK141">
         <v>1.53</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1127,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="O5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>1.25</v>
@@ -4097,7 +4097,7 @@
         <v>3.14</v>
       </c>
       <c r="AA23">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB23">
         <v>1.75</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O40">
         <v>3.8</v>
       </c>
       <c r="P40">
-        <v>3.51</v>
+        <v>3.45</v>
       </c>
       <c r="Q40">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R40">
         <v>2.5</v>
@@ -6853,10 +6853,10 @@
         <v>2.1</v>
       </c>
       <c r="V40">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W40">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -7176,10 +7176,10 @@
         <v>2.57</v>
       </c>
       <c r="U42">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="V42">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
         <v>1.01</v>
@@ -7188,13 +7188,13 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z42">
         <v>2.83</v>
       </c>
       <c r="AA42">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AB42">
         <v>1.67</v>
@@ -7321,7 +7321,7 @@
         <v>1.83</v>
       </c>
       <c r="O43">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
         <v>3.4</v>
@@ -7360,10 +7360,10 @@
         <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC43">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AD43">
         <v>1.36</v>
@@ -7976,13 +7976,13 @@
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q47">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
         <v>1.25</v>
@@ -7991,7 +7991,7 @@
         <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V47">
         <v>1.57</v>
@@ -8006,22 +8006,22 @@
         <v>1.14</v>
       </c>
       <c r="Z47">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA47">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB47">
         <v>2.22</v>
       </c>
       <c r="AC47">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD47">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AE47">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF47">
         <v>1.53</v>
@@ -8043,7 +8043,7 @@
         <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="O52">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="P52">
-        <v>2.58</v>
+        <v>4.66</v>
       </c>
       <c r="Q52">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R52">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
+        <v>1.32</v>
+      </c>
+      <c r="T52">
+        <v>2.26</v>
+      </c>
+      <c r="U52">
+        <v>2.75</v>
+      </c>
+      <c r="V52">
         <v>1.33</v>
-      </c>
-      <c r="T52">
-        <v>2.24</v>
-      </c>
-      <c r="U52">
-        <v>2.26</v>
-      </c>
-      <c r="V52">
-        <v>1.32</v>
       </c>
       <c r="W52">
         <v>1.04</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="AA52">
+        <v>1.9</v>
+      </c>
+      <c r="AB52">
+        <v>1.9</v>
+      </c>
+      <c r="AC52">
+        <v>2.92</v>
+      </c>
+      <c r="AD52">
+        <v>1.31</v>
+      </c>
+      <c r="AE52">
+        <v>1.08</v>
+      </c>
+      <c r="AF52">
+        <v>1.83</v>
+      </c>
+      <c r="AG52">
+        <v>1.85</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.3</v>
+      </c>
+      <c r="AK52">
         <v>1.95</v>
-      </c>
-      <c r="AB52">
-        <v>1.62</v>
-      </c>
-      <c r="AC52">
-        <v>2.7</v>
-      </c>
-      <c r="AD52">
-        <v>1.3</v>
-      </c>
-      <c r="AE52">
-        <v>1.05</v>
-      </c>
-      <c r="AF52">
-        <v>1.67</v>
-      </c>
-      <c r="AG52">
-        <v>2.1</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.44</v>
-      </c>
-      <c r="AK52">
-        <v>1.44</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="O53">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="P53">
-        <v>4.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q53">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S53">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T53">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="V53">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W53">
         <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AA53">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB53">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AC53">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AD53">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE53">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK53">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O58">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P58">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q58">
         <v>2.12</v>
@@ -9977,7 +9977,7 @@
         <v>1.44</v>
       </c>
       <c r="AE59">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF59">
         <v>1.53</v>
@@ -10092,10 +10092,10 @@
         <v>2.1</v>
       </c>
       <c r="O60">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P60">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -10128,13 +10128,13 @@
         <v>4.3</v>
       </c>
       <c r="AA60">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB60">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC60">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AD60">
         <v>1.44</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P61">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q61">
         <v>2.15</v>
@@ -10424,7 +10424,7 @@
         <v>3.2</v>
       </c>
       <c r="Q62">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R62">
         <v>2.3</v>
@@ -10454,7 +10454,7 @@
         <v>3.58</v>
       </c>
       <c r="AA62">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB62">
         <v>2</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="O63">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P63">
         <v>2.55</v>
@@ -10617,10 +10617,10 @@
         <v>2.83</v>
       </c>
       <c r="AA63">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB63">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC63">
         <v>3.92</v>
@@ -11082,7 +11082,7 @@
         <v>2.7</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T66">
         <v>4</v>
@@ -11251,13 +11251,13 @@
         <v>3.8</v>
       </c>
       <c r="U67">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V67">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W67">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X67">
         <v>1.02</v>
@@ -11266,22 +11266,22 @@
         <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA67">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB67">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AC67">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AD67">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE67">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF67">
         <v>1.57</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK67">
         <v>1.17</v>
@@ -11396,7 +11396,7 @@
         <v>1.7</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P68">
         <v>4.2</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.87</v>
+        <v>3.03</v>
       </c>
       <c r="O69">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="P69">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q69">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="R69">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S69">
+        <v>1.3</v>
+      </c>
+      <c r="T69">
+        <v>3.12</v>
+      </c>
+      <c r="U69">
+        <v>2.42</v>
+      </c>
+      <c r="V69">
+        <v>1.48</v>
+      </c>
+      <c r="W69">
+        <v>1.07</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
         <v>1.2</v>
       </c>
-      <c r="T69">
-        <v>4</v>
-      </c>
-      <c r="U69">
-        <v>2.1</v>
-      </c>
-      <c r="V69">
-        <v>1.65</v>
-      </c>
-      <c r="W69">
+      <c r="Z69">
+        <v>4.33</v>
+      </c>
+      <c r="AA69">
+        <v>1.67</v>
+      </c>
+      <c r="AB69">
+        <v>2.19</v>
+      </c>
+      <c r="AC69">
+        <v>2.7</v>
+      </c>
+      <c r="AD69">
+        <v>1.44</v>
+      </c>
+      <c r="AE69">
         <v>1.17</v>
       </c>
-      <c r="X69">
-        <v>1.01</v>
-      </c>
-      <c r="Y69">
-        <v>1.1</v>
-      </c>
-      <c r="Z69">
-        <v>6.5</v>
-      </c>
-      <c r="AA69">
-        <v>1.4</v>
-      </c>
-      <c r="AB69">
-        <v>2.88</v>
-      </c>
-      <c r="AC69">
-        <v>2.1</v>
-      </c>
-      <c r="AD69">
-        <v>1.73</v>
-      </c>
-      <c r="AE69">
-        <v>1.3</v>
-      </c>
       <c r="AF69">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK69">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.03</v>
+        <v>2.87</v>
       </c>
       <c r="O70">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="P70">
         <v>2.11</v>
       </c>
       <c r="Q70">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="R70">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="S70">
+        <v>1.2</v>
+      </c>
+      <c r="T70">
+        <v>4</v>
+      </c>
+      <c r="U70">
+        <v>2.1</v>
+      </c>
+      <c r="V70">
+        <v>1.65</v>
+      </c>
+      <c r="W70">
+        <v>1.17</v>
+      </c>
+      <c r="X70">
+        <v>1.01</v>
+      </c>
+      <c r="Y70">
+        <v>1.1</v>
+      </c>
+      <c r="Z70">
+        <v>6.5</v>
+      </c>
+      <c r="AA70">
+        <v>1.4</v>
+      </c>
+      <c r="AB70">
+        <v>2.88</v>
+      </c>
+      <c r="AC70">
+        <v>2.1</v>
+      </c>
+      <c r="AD70">
+        <v>1.73</v>
+      </c>
+      <c r="AE70">
         <v>1.3</v>
       </c>
-      <c r="T70">
-        <v>3.12</v>
-      </c>
-      <c r="U70">
-        <v>2.42</v>
-      </c>
-      <c r="V70">
-        <v>1.48</v>
-      </c>
-      <c r="W70">
-        <v>1.07</v>
-      </c>
-      <c r="X70">
-        <v>1.02</v>
-      </c>
-      <c r="Y70">
-        <v>1.2</v>
-      </c>
-      <c r="Z70">
-        <v>4.33</v>
-      </c>
-      <c r="AA70">
-        <v>1.67</v>
-      </c>
-      <c r="AB70">
-        <v>2.19</v>
-      </c>
-      <c r="AC70">
-        <v>2.7</v>
-      </c>
-      <c r="AD70">
-        <v>1.44</v>
-      </c>
-      <c r="AE70">
-        <v>1.17</v>
-      </c>
       <c r="AF70">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG70">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK70">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12899,7 +12899,7 @@
         <v>5.64</v>
       </c>
       <c r="AA77">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB77">
         <v>2.66</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O83">
         <v>3.48</v>
@@ -14683,13 +14683,13 @@
         <v>1.11</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z88">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA88">
         <v>1.67</v>
@@ -14698,19 +14698,19 @@
         <v>2.15</v>
       </c>
       <c r="AC88">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD88">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE88">
         <v>1.14</v>
       </c>
       <c r="AF88">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AG88">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -15018,10 +15018,10 @@
         <v>3.04</v>
       </c>
       <c r="AA90">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB90">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC90">
         <v>3.34</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
+        <v>2.7</v>
+      </c>
+      <c r="O91">
+        <v>3.47</v>
+      </c>
+      <c r="P91">
+        <v>2.3</v>
+      </c>
+      <c r="Q91">
+        <v>3.02</v>
+      </c>
+      <c r="R91">
+        <v>2.14</v>
+      </c>
+      <c r="S91">
+        <v>1.27</v>
+      </c>
+      <c r="T91">
+        <v>3.32</v>
+      </c>
+      <c r="U91">
+        <v>2.45</v>
+      </c>
+      <c r="V91">
+        <v>1.52</v>
+      </c>
+      <c r="W91">
+        <v>1.11</v>
+      </c>
+      <c r="X91">
+        <v>1.01</v>
+      </c>
+      <c r="Y91">
+        <v>1.2</v>
+      </c>
+      <c r="Z91">
+        <v>4.1</v>
+      </c>
+      <c r="AA91">
         <v>1.65</v>
       </c>
-      <c r="O91">
-        <v>3.7</v>
-      </c>
-      <c r="P91">
-        <v>4.6</v>
-      </c>
-      <c r="Q91">
-        <v>2.16</v>
-      </c>
-      <c r="R91">
-        <v>2.25</v>
-      </c>
-      <c r="S91">
-        <v>1.35</v>
-      </c>
-      <c r="T91">
-        <v>2.87</v>
-      </c>
-      <c r="U91">
-        <v>2.65</v>
-      </c>
-      <c r="V91">
-        <v>1.45</v>
-      </c>
-      <c r="W91">
-        <v>1.1</v>
-      </c>
-      <c r="X91">
-        <v>1</v>
-      </c>
-      <c r="Y91">
-        <v>1.19</v>
-      </c>
-      <c r="Z91">
-        <v>4.02</v>
-      </c>
-      <c r="AA91">
-        <v>1.79</v>
-      </c>
       <c r="AB91">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AC91">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AD91">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE91">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF91">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AK91">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P92">
-        <v>2.3</v>
+        <v>4.55</v>
       </c>
       <c r="Q92">
-        <v>3.02</v>
+        <v>2.16</v>
       </c>
       <c r="R92">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T92">
-        <v>3.32</v>
+        <v>2.87</v>
       </c>
       <c r="U92">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="V92">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z92">
-        <v>4.1</v>
+        <v>4.02</v>
       </c>
       <c r="AA92">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB92">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AC92">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="AD92">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE92">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG92">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AK92">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.87</v>
+        <v>1.83</v>
       </c>
       <c r="O93">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P93">
+        <v>3.9</v>
+      </c>
+      <c r="Q93">
+        <v>2.41</v>
+      </c>
+      <c r="R93">
         <v>2.2</v>
       </c>
-      <c r="Q93">
-        <v>3.58</v>
-      </c>
-      <c r="R93">
-        <v>2.1</v>
-      </c>
       <c r="S93">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T93">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="U93">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V93">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z93">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="AA93">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AB93">
+        <v>1.78</v>
+      </c>
+      <c r="AC93">
+        <v>3.72</v>
+      </c>
+      <c r="AD93">
+        <v>1.26</v>
+      </c>
+      <c r="AE93">
+        <v>1.06</v>
+      </c>
+      <c r="AF93">
         <v>1.85</v>
       </c>
-      <c r="AC93">
-        <v>3.3</v>
-      </c>
-      <c r="AD93">
-        <v>1.3</v>
-      </c>
-      <c r="AE93">
-        <v>1.11</v>
-      </c>
-      <c r="AF93">
-        <v>1.7</v>
-      </c>
       <c r="AG93">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,65 +15631,65 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.8</v>
+        <v>2.87</v>
       </c>
       <c r="O94">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P94">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q94">
-        <v>2.41</v>
+        <v>3.58</v>
       </c>
       <c r="R94">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S94">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T94">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="U94">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V94">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W94">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z94">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="AA94">
+        <v>1.95</v>
+      </c>
+      <c r="AB94">
+        <v>1.91</v>
+      </c>
+      <c r="AC94">
+        <v>2.97</v>
+      </c>
+      <c r="AD94">
+        <v>1.3</v>
+      </c>
+      <c r="AE94">
+        <v>1.11</v>
+      </c>
+      <c r="AF94">
+        <v>1.65</v>
+      </c>
+      <c r="AG94">
         <v>2.11</v>
       </c>
-      <c r="AB94">
-        <v>1.78</v>
-      </c>
-      <c r="AC94">
-        <v>3.72</v>
-      </c>
-      <c r="AD94">
-        <v>1.26</v>
-      </c>
-      <c r="AE94">
-        <v>1.06</v>
-      </c>
-      <c r="AF94">
-        <v>1.85</v>
-      </c>
-      <c r="AG94">
-        <v>1.83</v>
-      </c>
       <c r="AH94" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK94">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O98">
         <v>4.4</v>
@@ -16325,7 +16325,7 @@
         <v>1.44</v>
       </c>
       <c r="AB98">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AC98">
         <v>2.07</v>
@@ -18245,7 +18245,7 @@
         <v>3.2</v>
       </c>
       <c r="P110">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q110">
         <v>2.31</v>
@@ -18296,7 +18296,7 @@
         <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>2.76</v>
       </c>
       <c r="U111">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="V111">
         <v>1.33</v>
@@ -18432,7 +18432,7 @@
         <v>1.04</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
         <v>1.25</v>
@@ -18456,7 +18456,7 @@
         <v>1.06</v>
       </c>
       <c r="AF111">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG111">
         <v>2.05</v>
@@ -18574,7 +18574,7 @@
         <v>2.45</v>
       </c>
       <c r="Q112">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R112">
         <v>2.17</v>
@@ -18601,16 +18601,16 @@
         <v>1.19</v>
       </c>
       <c r="Z112">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="AA112">
         <v>1.8</v>
       </c>
       <c r="AB112">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC112">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD112">
         <v>1.36</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O114">
         <v>3.2</v>
@@ -18909,7 +18909,7 @@
         <v>1.38</v>
       </c>
       <c r="T114">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U114">
         <v>3</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="O116">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q116">
-        <v>3.06</v>
+        <v>4.44</v>
       </c>
       <c r="R116">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="S116">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T116">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="U116">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V116">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W116">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X116">
         <v>1.01</v>
       </c>
       <c r="Y116">
+        <v>1.25</v>
+      </c>
+      <c r="Z116">
+        <v>3.28</v>
+      </c>
+      <c r="AA116">
+        <v>1.67</v>
+      </c>
+      <c r="AB116">
+        <v>2.15</v>
+      </c>
+      <c r="AC116">
+        <v>3.05</v>
+      </c>
+      <c r="AD116">
         <v>1.28</v>
       </c>
-      <c r="Z116">
-        <v>3.05</v>
-      </c>
-      <c r="AA116">
-        <v>1.98</v>
-      </c>
-      <c r="AB116">
-        <v>1.71</v>
-      </c>
-      <c r="AC116">
-        <v>3.42</v>
-      </c>
-      <c r="AD116">
-        <v>1.23</v>
-      </c>
       <c r="AE116">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF116">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG116">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK116">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O117">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P117">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q117">
-        <v>4.44</v>
+        <v>3.06</v>
       </c>
       <c r="R117">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="S117">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T117">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="U117">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V117">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W117">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X117">
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z117">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="AA117">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AB117">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AC117">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AD117">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE117">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF117">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG117">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK117">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19549,7 +19549,7 @@
         <v>5.7</v>
       </c>
       <c r="P118">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q118">
         <v>1.77</v>
@@ -19869,10 +19869,10 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="O120">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P120">
         <v>2.83</v>
@@ -20850,7 +20850,7 @@
         <v>2.46</v>
       </c>
       <c r="O126">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P126">
         <v>2.75</v>
@@ -21378,16 +21378,16 @@
         <v>2.1</v>
       </c>
       <c r="AB129">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC129">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD129">
         <v>1.29</v>
       </c>
       <c r="AE129">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF129">
         <v>1.85</v>
@@ -21825,25 +21825,25 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="O132">
-        <v>3.96</v>
+        <v>3.84</v>
       </c>
       <c r="P132">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q132">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R132">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S132">
         <v>1.36</v>
       </c>
       <c r="T132">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="U132">
         <v>2.67</v>
@@ -21858,22 +21858,22 @@
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z132">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="AA132">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB132">
         <v>1.79</v>
       </c>
       <c r="AC132">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD132">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE132">
         <v>1.06</v>
@@ -21882,7 +21882,7 @@
         <v>1.95</v>
       </c>
       <c r="AG132">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK132">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL132">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -650,13 +650,13 @@
         <v>2.13</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U2">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V2">
         <v>1.44</v>
@@ -668,19 +668,19 @@
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
         <v>3.3</v>
       </c>
       <c r="AA2">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AD2">
         <v>1.38</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q4">
         <v>2.84</v>
@@ -991,10 +991,10 @@
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
         <v>2.97</v>
@@ -1003,7 +1003,7 @@
         <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
         <v>3.42</v>
@@ -1015,10 +1015,10 @@
         <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1145,13 +1145,13 @@
         <v>3.24</v>
       </c>
       <c r="U5">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1163,25 +1163,25 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB5">
         <v>2.38</v>
       </c>
       <c r="AC5">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AD5">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE5">
         <v>1.16</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG5">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="O8">
-        <v>3.71</v>
+        <v>3.43</v>
       </c>
       <c r="P8">
-        <v>5.04</v>
+        <v>5.15</v>
       </c>
       <c r="Q8">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="R8">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="S8">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T8">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="U8">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V8">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
+        <v>1.02</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>1.41</v>
+      </c>
+      <c r="Z8">
+        <v>2.74</v>
+      </c>
+      <c r="AA8">
+        <v>2.1</v>
+      </c>
+      <c r="AB8">
+        <v>1.63</v>
+      </c>
+      <c r="AC8">
+        <v>3.8</v>
+      </c>
+      <c r="AD8">
+        <v>1.19</v>
+      </c>
+      <c r="AE8">
         <v>1.03</v>
       </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>1.3</v>
-      </c>
-      <c r="Z8">
-        <v>2.97</v>
-      </c>
-      <c r="AA8">
-        <v>2.02</v>
-      </c>
-      <c r="AB8">
-        <v>1.68</v>
-      </c>
-      <c r="AC8">
-        <v>3.5</v>
-      </c>
-      <c r="AD8">
-        <v>1.22</v>
-      </c>
-      <c r="AE8">
-        <v>1.04</v>
-      </c>
       <c r="AF8">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK8">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>7.29</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>2.74</v>
       </c>
       <c r="AA22">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
         <v>3.78</v>
@@ -4556,10 +4556,10 @@
         <v>2.1</v>
       </c>
       <c r="Q26">
-        <v>4.32</v>
+        <v>5.08</v>
       </c>
       <c r="R26">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
         <v>1.44</v>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z26">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AA26">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AB26">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4601,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AG26">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AK26">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4906,10 +4906,10 @@
         <v>0</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5069,10 +5069,10 @@
         <v>0</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>2.33</v>
       </c>
       <c r="Q35">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U35">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V35">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="AA35">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB35">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AC35">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD35">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
         <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK35">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O39">
         <v>3.8</v>
@@ -6678,7 +6678,7 @@
         <v>2.05</v>
       </c>
       <c r="R39">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6702,7 +6702,7 @@
         <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>6.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA39">
         <v>1.4</v>
@@ -6711,19 +6711,19 @@
         <v>2.88</v>
       </c>
       <c r="AC39">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AD39">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE39">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF39">
         <v>1.4</v>
       </c>
       <c r="AG39">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.17</v>
       </c>
       <c r="AK39">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>5.07</v>
       </c>
       <c r="Q40">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R40">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T40">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="U40">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="V40">
         <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z40">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA40">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB40">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC40">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD40">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE40">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG40">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK40">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="O41">
         <v>2.98</v>
@@ -7164,7 +7164,7 @@
         <v>3.4</v>
       </c>
       <c r="Q42">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R42">
         <v>2.18</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7665,16 +7665,16 @@
         <v>3.8</v>
       </c>
       <c r="U45">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="V45">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="W45">
         <v>1.14</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
         <v>1.12</v>
@@ -7683,19 +7683,19 @@
         <v>4.8</v>
       </c>
       <c r="AA45">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AB45">
         <v>2.33</v>
       </c>
       <c r="AC45">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD45">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE45">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF45">
         <v>1.46</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P46">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -7828,7 +7828,7 @@
         <v>3.6</v>
       </c>
       <c r="U46">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V46">
         <v>1.57</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O47">
         <v>3.55</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="O49">
-        <v>3.37</v>
+        <v>3.23</v>
       </c>
       <c r="P49">
-        <v>2.89</v>
+        <v>2.41</v>
       </c>
       <c r="Q49">
         <v>2.95</v>
@@ -8332,7 +8332,7 @@
         <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>2.7</v>
+        <v>3.68</v>
       </c>
       <c r="AA49">
         <v>1.87</v>
@@ -8459,61 +8459,61 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="O50">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="P50">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
       </c>
       <c r="R50">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="S50">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>2.29</v>
+        <v>2.71</v>
       </c>
       <c r="U50">
-        <v>2.21</v>
+        <v>2.65</v>
       </c>
       <c r="V50">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>3.39</v>
+        <v>3.19</v>
       </c>
       <c r="AA50">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AB50">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AC50">
-        <v>2.63</v>
+        <v>3.52</v>
       </c>
       <c r="AD50">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE50">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
         <v>2</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="O51">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="P51">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -8788,10 +8788,10 @@
         <v>1.8</v>
       </c>
       <c r="O52">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="P52">
-        <v>4.66</v>
+        <v>4.05</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -8800,10 +8800,10 @@
         <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T52">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="U52">
         <v>2.75</v>
@@ -8815,22 +8815,22 @@
         <v>1.04</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z52">
         <v>3.54</v>
       </c>
       <c r="AA52">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AB52">
         <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AD52">
         <v>1.34</v>
@@ -8839,10 +8839,10 @@
         <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG52">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.18</v>
       </c>
       <c r="AK52">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O54">
         <v>3.55</v>
       </c>
       <c r="P54">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q54">
         <v>2.4</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O56">
         <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -9603,7 +9603,7 @@
         <v>1.58</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P57">
         <v>4.4</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O58">
         <v>3.4</v>
       </c>
       <c r="P58">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q58">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R58">
         <v>2.3</v>
@@ -10098,7 +10098,7 @@
         <v>2.87</v>
       </c>
       <c r="Q60">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R60">
         <v>2.3</v>
@@ -10162,7 +10162,7 @@
         <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>2.55</v>
       </c>
       <c r="Q62">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R62">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S62">
         <v>1.4</v>
@@ -10436,37 +10436,37 @@
         <v>2.62</v>
       </c>
       <c r="U62">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="V62">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W62">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X62">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y62">
         <v>1.33</v>
       </c>
       <c r="Z62">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA62">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB62">
         <v>1.65</v>
       </c>
       <c r="AC62">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AD62">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE62">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF62">
         <v>1.83</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O63">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="P63">
         <v>2.6</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,61 +10741,61 @@
         </is>
       </c>
       <c r="N64">
+        <v>1.5</v>
+      </c>
+      <c r="O64">
+        <v>4.2</v>
+      </c>
+      <c r="P64">
+        <v>4.6</v>
+      </c>
+      <c r="Q64">
+        <v>1.9</v>
+      </c>
+      <c r="R64">
+        <v>2.81</v>
+      </c>
+      <c r="S64">
+        <v>1.15</v>
+      </c>
+      <c r="T64">
+        <v>4.5</v>
+      </c>
+      <c r="U64">
+        <v>2.01</v>
+      </c>
+      <c r="V64">
+        <v>1.78</v>
+      </c>
+      <c r="W64">
+        <v>1.22</v>
+      </c>
+      <c r="X64">
+        <v>1.01</v>
+      </c>
+      <c r="Y64">
+        <v>1.06</v>
+      </c>
+      <c r="Z64">
+        <v>6</v>
+      </c>
+      <c r="AA64">
+        <v>1.33</v>
+      </c>
+      <c r="AB64">
         <v>2.62</v>
       </c>
-      <c r="O64">
-        <v>3.4</v>
-      </c>
-      <c r="P64">
-        <v>2.25</v>
-      </c>
-      <c r="Q64">
-        <v>3.25</v>
-      </c>
-      <c r="R64">
-        <v>2.45</v>
-      </c>
-      <c r="S64">
-        <v>1.24</v>
-      </c>
-      <c r="T64">
-        <v>3.4</v>
-      </c>
-      <c r="U64">
-        <v>2.15</v>
-      </c>
-      <c r="V64">
-        <v>1.62</v>
-      </c>
-      <c r="W64">
-        <v>1.15</v>
-      </c>
-      <c r="X64">
-        <v>1.02</v>
-      </c>
-      <c r="Y64">
-        <v>1.13</v>
-      </c>
-      <c r="Z64">
-        <v>4.55</v>
-      </c>
-      <c r="AA64">
-        <v>1.56</v>
-      </c>
-      <c r="AB64">
-        <v>2.28</v>
-      </c>
       <c r="AC64">
-        <v>2.33</v>
+        <v>1.94</v>
       </c>
       <c r="AD64">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AE64">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AF64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
         <v>2.5</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK64">
-        <v>1.39</v>
+        <v>2.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.5</v>
+        <v>4.33</v>
       </c>
       <c r="O65">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P65">
-        <v>4.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q65">
-        <v>1.95</v>
+        <v>3.85</v>
       </c>
       <c r="R65">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="S65">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T65">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="U65">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="V65">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="W65">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA65">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AB65">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC65">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="AD65">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE65">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AF65">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>2.4</v>
+        <v>1.18</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>4.33</v>
+        <v>1.7</v>
       </c>
       <c r="O66">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P66">
-        <v>1.55</v>
+        <v>4.25</v>
       </c>
       <c r="Q66">
-        <v>3.85</v>
+        <v>2.24</v>
       </c>
       <c r="R66">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="S66">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="T66">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="U66">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="V66">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>4.9</v>
+        <v>3.57</v>
       </c>
       <c r="AA66">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AB66">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="AC66">
-        <v>2.33</v>
+        <v>3.25</v>
       </c>
       <c r="AD66">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AE66">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AF66">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="O67">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>4.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q67">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="R67">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="T67">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U67">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>3.57</v>
+        <v>4.55</v>
       </c>
       <c r="AA67">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AB67">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="AC67">
-        <v>3.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD67">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AE67">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="O68">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="P68">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q68">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="R68">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="S68">
+        <v>1.2</v>
+      </c>
+      <c r="T68">
+        <v>4</v>
+      </c>
+      <c r="U68">
+        <v>2.1</v>
+      </c>
+      <c r="V68">
+        <v>1.65</v>
+      </c>
+      <c r="W68">
+        <v>1.17</v>
+      </c>
+      <c r="X68">
+        <v>1.01</v>
+      </c>
+      <c r="Y68">
+        <v>1.1</v>
+      </c>
+      <c r="Z68">
+        <v>6.5</v>
+      </c>
+      <c r="AA68">
+        <v>1.4</v>
+      </c>
+      <c r="AB68">
+        <v>2.88</v>
+      </c>
+      <c r="AC68">
+        <v>2.1</v>
+      </c>
+      <c r="AD68">
+        <v>1.73</v>
+      </c>
+      <c r="AE68">
         <v>1.3</v>
       </c>
-      <c r="T68">
-        <v>3.12</v>
-      </c>
-      <c r="U68">
-        <v>2.42</v>
-      </c>
-      <c r="V68">
-        <v>1.48</v>
-      </c>
-      <c r="W68">
-        <v>1.07</v>
-      </c>
-      <c r="X68">
-        <v>1.02</v>
-      </c>
-      <c r="Y68">
-        <v>1.2</v>
-      </c>
-      <c r="Z68">
-        <v>4.33</v>
-      </c>
-      <c r="AA68">
-        <v>1.67</v>
-      </c>
-      <c r="AB68">
-        <v>2.19</v>
-      </c>
-      <c r="AC68">
-        <v>2.7</v>
-      </c>
-      <c r="AD68">
-        <v>1.44</v>
-      </c>
-      <c r="AE68">
-        <v>1.17</v>
-      </c>
       <c r="AF68">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK68">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="O69">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
       <c r="P69">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q69">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="R69">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S69">
+        <v>1.3</v>
+      </c>
+      <c r="T69">
+        <v>3.12</v>
+      </c>
+      <c r="U69">
+        <v>2.42</v>
+      </c>
+      <c r="V69">
+        <v>1.48</v>
+      </c>
+      <c r="W69">
+        <v>1.07</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
         <v>1.2</v>
       </c>
-      <c r="T69">
-        <v>4</v>
-      </c>
-      <c r="U69">
-        <v>2.1</v>
-      </c>
-      <c r="V69">
-        <v>1.65</v>
-      </c>
-      <c r="W69">
+      <c r="Z69">
+        <v>4.33</v>
+      </c>
+      <c r="AA69">
+        <v>1.67</v>
+      </c>
+      <c r="AB69">
+        <v>2.19</v>
+      </c>
+      <c r="AC69">
+        <v>2.7</v>
+      </c>
+      <c r="AD69">
+        <v>1.44</v>
+      </c>
+      <c r="AE69">
         <v>1.17</v>
       </c>
-      <c r="X69">
-        <v>1.01</v>
-      </c>
-      <c r="Y69">
-        <v>1.1</v>
-      </c>
-      <c r="Z69">
-        <v>6.5</v>
-      </c>
-      <c r="AA69">
-        <v>1.4</v>
-      </c>
-      <c r="AB69">
-        <v>2.88</v>
-      </c>
-      <c r="AC69">
-        <v>2.1</v>
-      </c>
-      <c r="AD69">
-        <v>1.73</v>
-      </c>
-      <c r="AE69">
-        <v>1.3</v>
-      </c>
       <c r="AF69">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK69">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,71 +11728,71 @@
         <v>1.33</v>
       </c>
       <c r="Q70">
-        <v>6.5</v>
+        <v>6.92</v>
       </c>
       <c r="R70">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T70">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="U70">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="V70">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W70">
+        <v>1.08</v>
+      </c>
+      <c r="X70">
+        <v>1</v>
+      </c>
+      <c r="Y70">
+        <v>1.18</v>
+      </c>
+      <c r="Z70">
+        <v>3.84</v>
+      </c>
+      <c r="AA70">
+        <v>1.72</v>
+      </c>
+      <c r="AB70">
+        <v>2.03</v>
+      </c>
+      <c r="AC70">
+        <v>2.8</v>
+      </c>
+      <c r="AD70">
+        <v>1.4</v>
+      </c>
+      <c r="AE70">
+        <v>1.13</v>
+      </c>
+      <c r="AF70">
+        <v>1.9</v>
+      </c>
+      <c r="AG70">
+        <v>1.85</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>2.59</v>
+      </c>
+      <c r="AK70">
         <v>1.11</v>
-      </c>
-      <c r="X70">
-        <v>1.02</v>
-      </c>
-      <c r="Y70">
-        <v>1.15</v>
-      </c>
-      <c r="Z70">
-        <v>4.3</v>
-      </c>
-      <c r="AA70">
-        <v>1.58</v>
-      </c>
-      <c r="AB70">
-        <v>2.18</v>
-      </c>
-      <c r="AC70">
-        <v>2.39</v>
-      </c>
-      <c r="AD70">
-        <v>1.45</v>
-      </c>
-      <c r="AE70">
-        <v>1.15</v>
-      </c>
-      <c r="AF70">
-        <v>1.8</v>
-      </c>
-      <c r="AG70">
-        <v>1.9</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.12</v>
-      </c>
-      <c r="AK70">
-        <v>1.02</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11885,16 +11885,16 @@
         <v>1.95</v>
       </c>
       <c r="O71">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="P71">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="Q71">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="R71">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S71">
         <v>1.36</v>
@@ -11921,7 +11921,7 @@
         <v>3.53</v>
       </c>
       <c r="AA71">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB71">
         <v>1.97</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AK71">
         <v>1.85</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="O72">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P72">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q72">
         <v>6</v>
@@ -12060,10 +12060,10 @@
         <v>2.89</v>
       </c>
       <c r="S72">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T72">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U72">
         <v>2.09</v>
@@ -12232,7 +12232,7 @@
         <v>3.3</v>
       </c>
       <c r="V73">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W73">
         <v>1.03</v>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK73">
         <v>1.85</v>
@@ -12380,16 +12380,16 @@
         <v>2.55</v>
       </c>
       <c r="Q74">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R74">
         <v>2.1</v>
       </c>
       <c r="S74">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T74">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U74">
         <v>2.88</v>
@@ -12413,7 +12413,7 @@
         <v>1.9</v>
       </c>
       <c r="AB74">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
         <v>3.28</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12576,7 +12576,7 @@
         <v>1.56</v>
       </c>
       <c r="AB75">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AC75">
         <v>2.37</v>
@@ -12736,7 +12736,7 @@
         <v>5.71</v>
       </c>
       <c r="AA76">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB76">
         <v>2.66</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
+        <v>1.7</v>
+      </c>
+      <c r="O78">
+        <v>3.71</v>
+      </c>
+      <c r="P78">
+        <v>3.93</v>
+      </c>
+      <c r="Q78">
+        <v>2.06</v>
+      </c>
+      <c r="R78">
+        <v>2.32</v>
+      </c>
+      <c r="S78">
+        <v>1.25</v>
+      </c>
+      <c r="T78">
+        <v>3.46</v>
+      </c>
+      <c r="U78">
+        <v>2.45</v>
+      </c>
+      <c r="V78">
+        <v>1.5</v>
+      </c>
+      <c r="W78">
+        <v>1.1</v>
+      </c>
+      <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.14</v>
+      </c>
+      <c r="Z78">
+        <v>4.3</v>
+      </c>
+      <c r="AA78">
+        <v>1.66</v>
+      </c>
+      <c r="AB78">
+        <v>2.16</v>
+      </c>
+      <c r="AC78">
+        <v>2.49</v>
+      </c>
+      <c r="AD78">
+        <v>1.42</v>
+      </c>
+      <c r="AE78">
+        <v>1.13</v>
+      </c>
+      <c r="AF78">
+        <v>1.62</v>
+      </c>
+      <c r="AG78">
+        <v>2.14</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.19</v>
+      </c>
+      <c r="AK78">
         <v>2.12</v>
-      </c>
-      <c r="O78">
-        <v>3.55</v>
-      </c>
-      <c r="P78">
-        <v>3.1</v>
-      </c>
-      <c r="Q78">
-        <v>2.69</v>
-      </c>
-      <c r="R78">
-        <v>2.17</v>
-      </c>
-      <c r="S78">
-        <v>1.29</v>
-      </c>
-      <c r="T78">
-        <v>3.2</v>
-      </c>
-      <c r="U78">
-        <v>2.44</v>
-      </c>
-      <c r="V78">
-        <v>1.47</v>
-      </c>
-      <c r="W78">
-        <v>1.06</v>
-      </c>
-      <c r="X78">
-        <v>1.03</v>
-      </c>
-      <c r="Y78">
-        <v>1.2</v>
-      </c>
-      <c r="Z78">
-        <v>4</v>
-      </c>
-      <c r="AA78">
-        <v>1.75</v>
-      </c>
-      <c r="AB78">
-        <v>2.05</v>
-      </c>
-      <c r="AC78">
-        <v>2.74</v>
-      </c>
-      <c r="AD78">
-        <v>1.36</v>
-      </c>
-      <c r="AE78">
-        <v>1.09</v>
-      </c>
-      <c r="AF78">
-        <v>1.61</v>
-      </c>
-      <c r="AG78">
-        <v>2.2</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.22</v>
-      </c>
-      <c r="AK78">
-        <v>1.72</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P79">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="Q79">
-        <v>2.06</v>
+        <v>2.69</v>
       </c>
       <c r="R79">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="S79">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="U79">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V79">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA79">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB79">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AC79">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD79">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE79">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF79">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG79">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13367,7 +13367,7 @@
         <v>1.33</v>
       </c>
       <c r="T80">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="U80">
         <v>2.6</v>
@@ -13376,10 +13376,10 @@
         <v>1.48</v>
       </c>
       <c r="W80">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X80">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
         <v>1.2</v>
@@ -13394,10 +13394,10 @@
         <v>2.1</v>
       </c>
       <c r="AC80">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD80">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE80">
         <v>1.15</v>
@@ -13515,13 +13515,13 @@
         <v>3.25</v>
       </c>
       <c r="O81">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q81">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="R81">
         <v>2.38</v>
@@ -13542,13 +13542,13 @@
         <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
         <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA81">
         <v>1.59</v>
@@ -13563,13 +13563,13 @@
         <v>1.47</v>
       </c>
       <c r="AE81">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF81">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG81">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="O84">
         <v>3.7</v>
       </c>
       <c r="P84">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -14019,7 +14019,7 @@
         <v>1.17</v>
       </c>
       <c r="T84">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U84">
         <v>2.05</v>
@@ -14043,10 +14043,10 @@
         <v>1.36</v>
       </c>
       <c r="AB84">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC84">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AD84">
         <v>1.72</v>
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O85">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P85">
         <v>4.33</v>
@@ -14179,13 +14179,13 @@
         <v>2.44</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U85">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V85">
         <v>1.6</v>
@@ -14194,7 +14194,7 @@
         <v>1.13</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
         <v>1.13</v>
@@ -14203,10 +14203,10 @@
         <v>5.4</v>
       </c>
       <c r="AA85">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AB85">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AC85">
         <v>2.17</v>
@@ -14221,7 +14221,7 @@
         <v>1.53</v>
       </c>
       <c r="AG85">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>2.6</v>
       </c>
       <c r="Q86">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="R86">
         <v>2.04</v>
@@ -14354,13 +14354,13 @@
         <v>1.36</v>
       </c>
       <c r="W86">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X86">
         <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z86">
         <v>3.5</v>
@@ -14372,19 +14372,19 @@
         <v>1.83</v>
       </c>
       <c r="AC86">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD86">
         <v>1.32</v>
       </c>
       <c r="AE86">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG86">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>2.46</v>
       </c>
       <c r="AD87">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE87">
         <v>1.13</v>
@@ -14653,19 +14653,19 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O88">
         <v>3.8</v>
       </c>
       <c r="P88">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q88">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="R88">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S88">
         <v>1.2</v>
@@ -14674,7 +14674,7 @@
         <v>3.9</v>
       </c>
       <c r="U88">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="V88">
         <v>1.67</v>
@@ -14686,16 +14686,16 @@
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z88">
-        <v>5.15</v>
+        <v>5.93</v>
       </c>
       <c r="AA88">
         <v>1.47</v>
       </c>
       <c r="AB88">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AC88">
         <v>2.1</v>
@@ -14846,7 +14846,7 @@
         <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
         <v>1.19</v>
@@ -14858,7 +14858,7 @@
         <v>1.79</v>
       </c>
       <c r="AB89">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC89">
         <v>2.66</v>
@@ -15178,7 +15178,7 @@
         <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA91">
         <v>2.05</v>
@@ -15326,7 +15326,7 @@
         <v>2.96</v>
       </c>
       <c r="U92">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="V92">
         <v>1.4</v>
@@ -15335,7 +15335,7 @@
         <v>1.08</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
         <v>1.25</v>
@@ -15347,10 +15347,10 @@
         <v>1.95</v>
       </c>
       <c r="AB92">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AC92">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AD92">
         <v>1.3</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AK92">
         <v>1.39</v>
@@ -15477,10 +15477,10 @@
         <v>2.3</v>
       </c>
       <c r="Q93">
-        <v>3.02</v>
+        <v>3.33</v>
       </c>
       <c r="R93">
-        <v>2.14</v>
+        <v>2.37</v>
       </c>
       <c r="S93">
         <v>1.27</v>
@@ -15637,7 +15637,7 @@
         <v>3.25</v>
       </c>
       <c r="P94">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="Q94">
         <v>3.83</v>
@@ -15836,7 +15836,7 @@
         <v>1.57</v>
       </c>
       <c r="AB95">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AC95">
         <v>2.35</v>
@@ -15999,7 +15999,7 @@
         <v>1.78</v>
       </c>
       <c r="AB96">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AC96">
         <v>2.92</v>
@@ -16126,7 +16126,7 @@
         <v>4.4</v>
       </c>
       <c r="P97">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q97">
         <v>2.04</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="O98">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P98">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q98">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="R98">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S98">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="T98">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="U98">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="V98">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="W98">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z98">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA98">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB98">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AC98">
         <v>1.92</v>
       </c>
       <c r="AD98">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AE98">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF98">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG98">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK98">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O100">
+        <v>3.75</v>
+      </c>
+      <c r="P100">
         <v>3.9</v>
       </c>
-      <c r="P100">
-        <v>3.75</v>
-      </c>
       <c r="Q100">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R100">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="S100">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T100">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U100">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V100">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="W100">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z100">
-        <v>5.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA100">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB100">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC100">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AD100">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AE100">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF100">
         <v>1.4</v>
       </c>
       <c r="AG100">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK100">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,19 +16772,19 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O101">
         <v>3.64</v>
       </c>
       <c r="P101">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="Q101">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R101">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S101">
         <v>1.22</v>
@@ -16793,7 +16793,7 @@
         <v>3.56</v>
       </c>
       <c r="U101">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V101">
         <v>1.58</v>
@@ -16811,16 +16811,16 @@
         <v>4.7</v>
       </c>
       <c r="AA101">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB101">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AC101">
         <v>2.33</v>
       </c>
       <c r="AD101">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AE101">
         <v>1.16</v>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK101">
         <v>1.57</v>
@@ -16935,10 +16935,10 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
         <v>2.37</v>
@@ -16953,10 +16953,10 @@
         <v>1.17</v>
       </c>
       <c r="T102">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="U102">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V102">
         <v>1.73</v>
@@ -16971,7 +16971,7 @@
         <v>1.11</v>
       </c>
       <c r="Z102">
-        <v>6.16</v>
+        <v>6.26</v>
       </c>
       <c r="AA102">
         <v>1.35</v>
@@ -16983,7 +16983,7 @@
         <v>2</v>
       </c>
       <c r="AD102">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE102">
         <v>1.28</v>
@@ -17264,7 +17264,7 @@
         <v>2.3</v>
       </c>
       <c r="O104">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="P104">
         <v>2.6</v>
@@ -17276,10 +17276,10 @@
         <v>2.45</v>
       </c>
       <c r="S104">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T104">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U104">
         <v>1.95</v>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17430,7 +17430,7 @@
         <v>4</v>
       </c>
       <c r="P105">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="Q105">
         <v>2.1</v>
@@ -17439,19 +17439,19 @@
         <v>2.45</v>
       </c>
       <c r="S105">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T105">
         <v>3.98</v>
       </c>
       <c r="U105">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="V105">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W105">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X105">
         <v>1.01</v>
@@ -17460,7 +17460,7 @@
         <v>1.08</v>
       </c>
       <c r="Z105">
-        <v>5.91</v>
+        <v>5.99</v>
       </c>
       <c r="AA105">
         <v>1.36</v>
@@ -17469,16 +17469,16 @@
         <v>2.7</v>
       </c>
       <c r="AC105">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AD105">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE105">
         <v>1.26</v>
       </c>
       <c r="AF105">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG105">
         <v>2.6</v>
@@ -17497,7 +17497,7 @@
         <v>1.17</v>
       </c>
       <c r="AK105">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O106">
         <v>3.6</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK106">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17789,10 +17789,10 @@
         <v>6.55</v>
       </c>
       <c r="AA107">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB107">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="AC107">
         <v>1.83</v>
@@ -17807,7 +17807,7 @@
         <v>1.77</v>
       </c>
       <c r="AG107">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -18278,10 +18278,10 @@
         <v>3.4</v>
       </c>
       <c r="AA110">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB110">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC110">
         <v>3.14</v>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O111">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P111">
         <v>2.45</v>
@@ -18414,13 +18414,13 @@
         <v>3.22</v>
       </c>
       <c r="R111">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S111">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T111">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="U111">
         <v>2.63</v>
@@ -18429,37 +18429,37 @@
         <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
         <v>1.22</v>
       </c>
       <c r="Z111">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AA111">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB111">
         <v>2.05</v>
       </c>
       <c r="AC111">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="AD111">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE111">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF111">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG111">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK111">
         <v>1.4</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="O112">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="P112">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O113">
         <v>3.2</v>
       </c>
       <c r="P113">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -18761,13 +18761,13 @@
         <v>1.04</v>
       </c>
       <c r="Y113">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z113">
         <v>3.18</v>
       </c>
       <c r="AA113">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AB113">
         <v>1.72</v>
@@ -18927,10 +18927,10 @@
         <v>1.25</v>
       </c>
       <c r="Z114">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA114">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB114">
         <v>1.88</v>
@@ -19054,19 +19054,19 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O115">
         <v>3</v>
       </c>
       <c r="P115">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q115">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="R115">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S115">
         <v>1.38</v>
@@ -19081,10 +19081,10 @@
         <v>1.36</v>
       </c>
       <c r="W115">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y115">
         <v>1.28</v>
@@ -19093,10 +19093,10 @@
         <v>3.05</v>
       </c>
       <c r="AA115">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB115">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC115">
         <v>3.42</v>
@@ -19108,10 +19108,10 @@
         <v>1.04</v>
       </c>
       <c r="AF115">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG115">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK115">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19253,13 +19253,13 @@
         <v>1.25</v>
       </c>
       <c r="Z116">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AA116">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AB116">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC116">
         <v>3.05</v>
@@ -19274,7 +19274,7 @@
         <v>1.7</v>
       </c>
       <c r="AG116">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>3.6</v>
       </c>
       <c r="P119">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="Q119">
         <v>2.82</v>
@@ -19721,16 +19721,16 @@
         <v>2.13</v>
       </c>
       <c r="S119">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T119">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="U119">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V119">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W119">
         <v>1.12</v>
@@ -19742,19 +19742,19 @@
         <v>1.21</v>
       </c>
       <c r="Z119">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="AA119">
         <v>1.76</v>
       </c>
       <c r="AB119">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AC119">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AD119">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE119">
         <v>1.14</v>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AK119">
         <v>1.68</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="O120">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P120">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q120">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="R120">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S120">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T120">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U120">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V120">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W120">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X120">
         <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z120">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="AA120">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB120">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC120">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AD120">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE120">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF120">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG120">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK120">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="O121">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P121">
+        <v>1.59</v>
+      </c>
+      <c r="Q121">
+        <v>4.39</v>
+      </c>
+      <c r="R121">
+        <v>2.18</v>
+      </c>
+      <c r="S121">
+        <v>1.3</v>
+      </c>
+      <c r="T121">
         <v>3.2</v>
       </c>
-      <c r="Q121">
-        <v>2.3</v>
-      </c>
-      <c r="R121">
-        <v>2.2</v>
-      </c>
-      <c r="S121">
-        <v>1.26</v>
-      </c>
-      <c r="T121">
-        <v>3.3</v>
-      </c>
       <c r="U121">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V121">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W121">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X121">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z121">
-        <v>4.35</v>
+        <v>3.98</v>
       </c>
       <c r="AA121">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AB121">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AC121">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AD121">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE121">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF121">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG121">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK121">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>4.3</v>
+        <v>1.83</v>
       </c>
       <c r="O122">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P122">
-        <v>1.59</v>
+        <v>3.45</v>
       </c>
       <c r="Q122">
-        <v>4.39</v>
+        <v>2.31</v>
       </c>
       <c r="R122">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="S122">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T122">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U122">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V122">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W122">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z122">
-        <v>3.98</v>
+        <v>4.69</v>
       </c>
       <c r="AA122">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AB122">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AC122">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AD122">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE122">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF122">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG122">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK122">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="O123">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P123">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="Q123">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="R123">
+        <v>2.24</v>
+      </c>
+      <c r="S123">
+        <v>1.29</v>
+      </c>
+      <c r="T123">
+        <v>3.6</v>
+      </c>
+      <c r="U123">
         <v>2.4</v>
       </c>
-      <c r="S123">
-        <v>1.27</v>
-      </c>
-      <c r="T123">
-        <v>3.32</v>
-      </c>
-      <c r="U123">
-        <v>2.25</v>
-      </c>
       <c r="V123">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W123">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X123">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z123">
-        <v>4.69</v>
+        <v>4</v>
       </c>
       <c r="AA123">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB123">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AC123">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AD123">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE123">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF123">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG123">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK123">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>2.15</v>
       </c>
       <c r="O124">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="P124">
         <v>3.3</v>
@@ -20536,16 +20536,16 @@
         <v>2.12</v>
       </c>
       <c r="S124">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T124">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="U124">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="V124">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W124">
         <v>1.06</v>
@@ -20572,7 +20572,7 @@
         <v>1.3</v>
       </c>
       <c r="AE124">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF124">
         <v>1.7</v>
@@ -20684,19 +20684,19 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="O125">
         <v>3.5</v>
       </c>
       <c r="P125">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="Q125">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R125">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S125">
         <v>1.3</v>
@@ -20705,10 +20705,10 @@
         <v>3.22</v>
       </c>
       <c r="U125">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V125">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W125">
         <v>1.11</v>
@@ -20720,28 +20720,28 @@
         <v>1.22</v>
       </c>
       <c r="Z125">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="AA125">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB125">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC125">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD125">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE125">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF125">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG125">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK125">
         <v>1.53</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O126">
         <v>3.5</v>
       </c>
       <c r="P126">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q126">
         <v>3.24</v>
@@ -20877,13 +20877,13 @@
         <v>1.08</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y126">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z126">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AA126">
         <v>1.72</v>
@@ -20892,13 +20892,13 @@
         <v>2.14</v>
       </c>
       <c r="AC126">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AD126">
         <v>1.44</v>
       </c>
       <c r="AE126">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF126">
         <v>1.59</v>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK126">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21188,7 +21188,7 @@
         <v>2.1</v>
       </c>
       <c r="S128">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T128">
         <v>2.88</v>
@@ -21197,13 +21197,13 @@
         <v>3</v>
       </c>
       <c r="V128">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W128">
         <v>1.05</v>
       </c>
       <c r="X128">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y128">
         <v>1.3</v>
@@ -21224,7 +21224,7 @@
         <v>1.29</v>
       </c>
       <c r="AE128">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF128">
         <v>1.85</v>
@@ -21348,7 +21348,7 @@
         <v>4.5</v>
       </c>
       <c r="R129">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S129">
         <v>1.2</v>
@@ -21393,7 +21393,7 @@
         <v>1.55</v>
       </c>
       <c r="AG129">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21538,10 +21538,10 @@
         <v>0</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC130">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="O132">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="P132">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q132">
         <v>2.12</v>
@@ -21861,25 +21861,25 @@
         <v>1.2</v>
       </c>
       <c r="Z132">
-        <v>3.84</v>
+        <v>2.9</v>
       </c>
       <c r="AA132">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AB132">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC132">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AD132">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE132">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF132">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG132">
         <v>2.05</v>
@@ -21994,7 +21994,7 @@
         <v>3.4</v>
       </c>
       <c r="P133">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q133">
         <v>2.47</v>
@@ -22003,16 +22003,16 @@
         <v>2.07</v>
       </c>
       <c r="S133">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T133">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="U133">
         <v>2.75</v>
       </c>
       <c r="V133">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W133">
         <v>1.06</v>
@@ -22024,7 +22024,7 @@
         <v>1.29</v>
       </c>
       <c r="Z133">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="AA133">
         <v>2.02</v>
@@ -22314,10 +22314,10 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O135">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="P135">
         <v>7.75</v>
@@ -22338,7 +22338,7 @@
         <v>2.17</v>
       </c>
       <c r="V135">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W135">
         <v>1.14</v>
@@ -22359,7 +22359,7 @@
         <v>2.55</v>
       </c>
       <c r="AC135">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AD135">
         <v>1.57</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK135">
         <v>3.1</v>
@@ -22519,10 +22519,10 @@
         <v>1.83</v>
       </c>
       <c r="AB136">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC136">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AD136">
         <v>1.3</v>
@@ -22531,10 +22531,10 @@
         <v>1.08</v>
       </c>
       <c r="AF136">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O138">
         <v>3.2</v>
@@ -22833,7 +22833,7 @@
         <v>1.02</v>
       </c>
       <c r="X138">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y138">
         <v>1.33</v>
@@ -22848,10 +22848,10 @@
         <v>1.67</v>
       </c>
       <c r="AC138">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="AD138">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE138">
         <v>1.03</v>
@@ -22860,7 +22860,7 @@
         <v>1.85</v>
       </c>
       <c r="AG138">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O4">
         <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="Q4">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U4">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
         <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA4">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O5">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P5">
+        <v>1.3</v>
+      </c>
+      <c r="Q5">
+        <v>6.47</v>
+      </c>
+      <c r="R5">
+        <v>2.39</v>
+      </c>
+      <c r="S5">
         <v>1.25</v>
       </c>
-      <c r="Q5">
-        <v>6.09</v>
-      </c>
-      <c r="R5">
-        <v>2.36</v>
-      </c>
-      <c r="S5">
-        <v>1.26</v>
-      </c>
       <c r="T5">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U5">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
         <v>1.11</v>
@@ -1157,28 +1157,28 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="AA5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB5">
         <v>2.38</v>
       </c>
       <c r="AC5">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AD5">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF5">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG5">
         <v>1.75</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z16">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA16">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC16">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="AD16">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF16">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK16">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="O17">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="Q17">
-        <v>6.1</v>
+        <v>2.29</v>
       </c>
       <c r="R17">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="U17">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z17">
-        <v>4.15</v>
+        <v>4.95</v>
       </c>
       <c r="AA17">
+        <v>1.43</v>
+      </c>
+      <c r="AB17">
+        <v>2.46</v>
+      </c>
+      <c r="AC17">
+        <v>2.13</v>
+      </c>
+      <c r="AD17">
         <v>1.61</v>
       </c>
-      <c r="AB17">
-        <v>2.13</v>
-      </c>
-      <c r="AC17">
-        <v>2.49</v>
-      </c>
-      <c r="AD17">
-        <v>1.42</v>
-      </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF17">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>1.94</v>
+        <v>2.53</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>1.05</v>
+        <v>1.82</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="P18">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q18">
+        <v>6.1</v>
+      </c>
+      <c r="R18">
         <v>2.29</v>
       </c>
-      <c r="R18">
-        <v>2.39</v>
-      </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="U18">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z18">
-        <v>4.95</v>
+        <v>4.15</v>
       </c>
       <c r="AA18">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AB18">
-        <v>2.46</v>
+        <v>2.13</v>
       </c>
       <c r="AC18">
-        <v>2.13</v>
+        <v>2.49</v>
       </c>
       <c r="AD18">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="AG18">
-        <v>2.53</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK18">
-        <v>1.82</v>
+        <v>1.05</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O19">
+        <v>3.6</v>
+      </c>
+      <c r="P19">
+        <v>3.9</v>
+      </c>
+      <c r="Q19">
+        <v>2.24</v>
+      </c>
+      <c r="R19">
+        <v>2.17</v>
+      </c>
+      <c r="S19">
+        <v>1.31</v>
+      </c>
+      <c r="T19">
+        <v>2.94</v>
+      </c>
+      <c r="U19">
+        <v>2.48</v>
+      </c>
+      <c r="V19">
+        <v>1.43</v>
+      </c>
+      <c r="W19">
+        <v>1.1</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>1.19</v>
+      </c>
+      <c r="Z19">
         <v>3.8</v>
       </c>
-      <c r="P19">
-        <v>4</v>
-      </c>
-      <c r="Q19">
-        <v>2.2</v>
-      </c>
-      <c r="R19">
-        <v>2.3</v>
-      </c>
-      <c r="S19">
-        <v>1.25</v>
-      </c>
-      <c r="T19">
-        <v>3.3</v>
-      </c>
-      <c r="U19">
-        <v>2.29</v>
-      </c>
-      <c r="V19">
-        <v>1.5</v>
-      </c>
-      <c r="W19">
-        <v>1.13</v>
-      </c>
-      <c r="X19">
-        <v>1.01</v>
-      </c>
-      <c r="Y19">
-        <v>1.14</v>
-      </c>
-      <c r="Z19">
-        <v>4.33</v>
-      </c>
       <c r="AA19">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AC19">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD19">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE19">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,58 +3569,58 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q20">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="R20">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
+        <v>1.09</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.22</v>
+      </c>
+      <c r="Z20">
+        <v>3.5</v>
+      </c>
+      <c r="AA20">
+        <v>1.76</v>
+      </c>
+      <c r="AB20">
+        <v>1.92</v>
+      </c>
+      <c r="AC20">
+        <v>2.83</v>
+      </c>
+      <c r="AD20">
+        <v>1.33</v>
+      </c>
+      <c r="AE20">
         <v>1.1</v>
-      </c>
-      <c r="X20">
-        <v>1.03</v>
-      </c>
-      <c r="Y20">
-        <v>1.19</v>
-      </c>
-      <c r="Z20">
-        <v>3.8</v>
-      </c>
-      <c r="AA20">
-        <v>1.7</v>
-      </c>
-      <c r="AB20">
-        <v>1.99</v>
-      </c>
-      <c r="AC20">
-        <v>2.7</v>
-      </c>
-      <c r="AD20">
-        <v>1.36</v>
-      </c>
-      <c r="AE20">
-        <v>1.11</v>
       </c>
       <c r="AF20">
         <v>1.66</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4230,10 +4230,10 @@
         <v>2.7</v>
       </c>
       <c r="Q24">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S24">
         <v>1.44</v>
@@ -4251,7 +4251,7 @@
         <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
         <v>1.38</v>
@@ -4263,22 +4263,22 @@
         <v>2.19</v>
       </c>
       <c r="AB24">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC24">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AD24">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE24">
         <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG24">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G27">
@@ -4713,61 +4713,61 @@
         <v>2.05</v>
       </c>
       <c r="O27">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P27">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q27">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R27">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="S27">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T27">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="U27">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="V27">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y27">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Z27">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AA27">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="AB27">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AC27">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AD27">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AG27">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK27">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="O28">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P28">
-        <v>3.7</v>
+        <v>2.41</v>
       </c>
       <c r="Q28">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="R28">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="S28">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T28">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="U28">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="V28">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W28">
         <v>1.03</v>
@@ -4906,31 +4906,31 @@
         <v>1.1</v>
       </c>
       <c r="Y28">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z28">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AA28">
         <v>3</v>
       </c>
       <c r="AB28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD28">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AG28">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK28">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,28 +5036,28 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="O29">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P29">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="R29">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="S29">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T29">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="U29">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="V29">
         <v>1.25</v>
@@ -5066,34 +5066,34 @@
         <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Z29">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AA29">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AB29">
         <v>1.39</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AD29">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE29">
         <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AG29">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK29">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,61 +5199,61 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="P30">
-        <v>2.41</v>
+        <v>4.6</v>
       </c>
       <c r="Q30">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="S30">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="T30">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="U30">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="V30">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
         <v>1.1</v>
       </c>
       <c r="Y30">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="Z30">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA30">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AB30">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC30">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AD30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AG30">
         <v>1.53</v>
@@ -5272,7 +5272,7 @@
         <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.31</v>
+        <v>1.95</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.74</v>
+        <v>2.19</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P31">
-        <v>3.94</v>
+        <v>2.65</v>
       </c>
       <c r="Q31">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="R31">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z31">
-        <v>3.08</v>
+        <v>4.11</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB31">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AC31">
-        <v>3.46</v>
+        <v>2.69</v>
       </c>
       <c r="AD31">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF31">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="O32">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.65</v>
+        <v>3.94</v>
       </c>
       <c r="Q32">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="V32">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>4.11</v>
+        <v>3.08</v>
       </c>
       <c r="AA32">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB32">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
-        <v>2.69</v>
+        <v>3.46</v>
       </c>
       <c r="AD32">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="O36">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P36">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q36">
         <v>2.54</v>
@@ -6216,10 +6216,10 @@
         <v>2.44</v>
       </c>
       <c r="AA36">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AB36">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC36">
         <v>4.85</v>
@@ -6231,10 +6231,10 @@
         <v>1.01</v>
       </c>
       <c r="AF36">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AG36">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="O37">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P37">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA37">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB37">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="O39">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>5.07</v>
+        <v>4.05</v>
       </c>
       <c r="Q39">
         <v>2.15</v>
@@ -6711,10 +6711,10 @@
         <v>1.76</v>
       </c>
       <c r="AC39">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
         <v>1.06</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O40">
         <v>2.98</v>
       </c>
       <c r="P40">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="Q40">
         <v>2.49</v>
@@ -7170,16 +7170,16 @@
         <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="U42">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V42">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
         <v>1.1</v>
@@ -7194,10 +7194,10 @@
         <v>3.5</v>
       </c>
       <c r="AA42">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB42">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC42">
         <v>2.88</v>
@@ -7209,10 +7209,10 @@
         <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG42">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7357,10 +7357,10 @@
         <v>3.04</v>
       </c>
       <c r="AA43">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AB43">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC43">
         <v>3.58</v>
@@ -7372,10 +7372,10 @@
         <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG43">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -8009,10 +8009,10 @@
         <v>3.08</v>
       </c>
       <c r="AA47">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AB47">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC47">
         <v>3.28</v>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O48">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="P48">
         <v>2.41</v>
@@ -8172,7 +8172,7 @@
         <v>3.68</v>
       </c>
       <c r="AA48">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB48">
         <v>1.93</v>
@@ -8181,7 +8181,7 @@
         <v>2.63</v>
       </c>
       <c r="AD48">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
         <v>1.05</v>
@@ -8477,7 +8477,7 @@
         <v>1.36</v>
       </c>
       <c r="T50">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="U50">
         <v>2.65</v>
@@ -8504,7 +8504,7 @@
         <v>1.77</v>
       </c>
       <c r="AC50">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="AD50">
         <v>1.27</v>
@@ -8513,7 +8513,7 @@
         <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
         <v>2</v>
@@ -8625,49 +8625,49 @@
         <v>1.8</v>
       </c>
       <c r="O51">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="P51">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Q51">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
         <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
         <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
         <v>3.54</v>
       </c>
       <c r="AA51">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AB51">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD51">
         <v>1.34</v>
@@ -8676,10 +8676,10 @@
         <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8963,22 +8963,22 @@
         <v>2.25</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T53">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="U53">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="V53">
         <v>1.44</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
         <v>1.22</v>
@@ -8987,16 +8987,16 @@
         <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB53">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC53">
         <v>2.78</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE53">
         <v>1.1</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O56">
         <v>3.8</v>
       </c>
       <c r="P56">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="Q56">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="R56">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9458,59 +9458,59 @@
         <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V56">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
+        <v>1.18</v>
+      </c>
+      <c r="Z56">
+        <v>3.9</v>
+      </c>
+      <c r="AA56">
+        <v>1.67</v>
+      </c>
+      <c r="AB56">
+        <v>2.04</v>
+      </c>
+      <c r="AC56">
+        <v>2.66</v>
+      </c>
+      <c r="AD56">
+        <v>1.4</v>
+      </c>
+      <c r="AE56">
+        <v>1.11</v>
+      </c>
+      <c r="AF56">
+        <v>1.67</v>
+      </c>
+      <c r="AG56">
+        <v>2.05</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
         <v>1.16</v>
       </c>
-      <c r="Z56">
-        <v>4.15</v>
-      </c>
-      <c r="AA56">
-        <v>1.61</v>
-      </c>
-      <c r="AB56">
-        <v>2.17</v>
-      </c>
-      <c r="AC56">
-        <v>2.43</v>
-      </c>
-      <c r="AD56">
-        <v>1.44</v>
-      </c>
-      <c r="AE56">
-        <v>1.15</v>
-      </c>
-      <c r="AF56">
-        <v>1.62</v>
-      </c>
-      <c r="AG56">
-        <v>2.12</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.11</v>
-      </c>
       <c r="AK56">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="P57">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="Q57">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S57">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U57">
         <v>2.38</v>
       </c>
       <c r="V57">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z57">
-        <v>4.35</v>
+        <v>4.15</v>
       </c>
       <c r="AA57">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB57">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC57">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AD57">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE57">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF57">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG57">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK57">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="O58">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q58">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="R58">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U58">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V58">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="AA58">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB58">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AC58">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="AD58">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG58">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O59">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P59">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q59">
         <v>2.7</v>
@@ -10294,7 +10294,7 @@
         <v>2.2</v>
       </c>
       <c r="AB61">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC61">
         <v>4</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,61 +10578,61 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.5</v>
+        <v>2.65</v>
       </c>
       <c r="O63">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q63">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="R63">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
+        <v>1.24</v>
+      </c>
+      <c r="T63">
+        <v>3.4</v>
+      </c>
+      <c r="U63">
+        <v>2.15</v>
+      </c>
+      <c r="V63">
+        <v>1.62</v>
+      </c>
+      <c r="W63">
         <v>1.15</v>
       </c>
-      <c r="T63">
-        <v>4.5</v>
-      </c>
-      <c r="U63">
-        <v>2.01</v>
-      </c>
-      <c r="V63">
-        <v>1.78</v>
-      </c>
-      <c r="W63">
-        <v>1.22</v>
-      </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z63">
-        <v>6</v>
+        <v>4.55</v>
       </c>
       <c r="AA63">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AB63">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="AC63">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="AD63">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AE63">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AF63">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
         <v>2.5</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK63">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="O64">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P64">
-        <v>2.25</v>
+        <v>4.25</v>
       </c>
       <c r="Q64">
+        <v>2.24</v>
+      </c>
+      <c r="R64">
+        <v>2.21</v>
+      </c>
+      <c r="S64">
+        <v>1.35</v>
+      </c>
+      <c r="T64">
+        <v>2.73</v>
+      </c>
+      <c r="U64">
+        <v>2.75</v>
+      </c>
+      <c r="V64">
+        <v>1.4</v>
+      </c>
+      <c r="W64">
+        <v>1.08</v>
+      </c>
+      <c r="X64">
+        <v>1.03</v>
+      </c>
+      <c r="Y64">
+        <v>1.28</v>
+      </c>
+      <c r="Z64">
+        <v>3.57</v>
+      </c>
+      <c r="AA64">
+        <v>1.85</v>
+      </c>
+      <c r="AB64">
+        <v>1.88</v>
+      </c>
+      <c r="AC64">
         <v>3.25</v>
       </c>
-      <c r="R64">
-        <v>2.45</v>
-      </c>
-      <c r="S64">
-        <v>1.24</v>
-      </c>
-      <c r="T64">
-        <v>3.4</v>
-      </c>
-      <c r="U64">
-        <v>2.15</v>
-      </c>
-      <c r="V64">
-        <v>1.62</v>
-      </c>
-      <c r="W64">
-        <v>1.15</v>
-      </c>
-      <c r="X64">
-        <v>1.02</v>
-      </c>
-      <c r="Y64">
-        <v>1.13</v>
-      </c>
-      <c r="Z64">
-        <v>4.55</v>
-      </c>
-      <c r="AA64">
-        <v>1.56</v>
-      </c>
-      <c r="AB64">
-        <v>2.28</v>
-      </c>
-      <c r="AC64">
-        <v>2.29</v>
-      </c>
       <c r="AD64">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AE64">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF64">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AG64">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.7</v>
+        <v>4.55</v>
       </c>
       <c r="O65">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="P65">
-        <v>4.25</v>
+        <v>1.57</v>
       </c>
       <c r="Q65">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="R65">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="S65">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="T65">
-        <v>2.73</v>
+        <v>3.8</v>
       </c>
       <c r="U65">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="V65">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>3.57</v>
+        <v>4.9</v>
       </c>
       <c r="AA65">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AB65">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC65">
-        <v>3.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD65">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AE65">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AF65">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,65 +11067,65 @@
         </is>
       </c>
       <c r="N66">
-        <v>4.33</v>
+        <v>1.5</v>
       </c>
       <c r="O66">
         <v>4.2</v>
       </c>
       <c r="P66">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="Q66">
-        <v>3.85</v>
+        <v>1.9</v>
       </c>
       <c r="R66">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="S66">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="T66">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U66">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="V66">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z66">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AA66">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AB66">
+        <v>2.81</v>
+      </c>
+      <c r="AC66">
+        <v>1.89</v>
+      </c>
+      <c r="AD66">
+        <v>1.87</v>
+      </c>
+      <c r="AE66">
+        <v>1.29</v>
+      </c>
+      <c r="AF66">
+        <v>1.5</v>
+      </c>
+      <c r="AG66">
         <v>2.5</v>
       </c>
-      <c r="AC66">
-        <v>2.33</v>
-      </c>
-      <c r="AD66">
-        <v>1.57</v>
-      </c>
-      <c r="AE66">
-        <v>1.23</v>
-      </c>
-      <c r="AF66">
-        <v>1.57</v>
-      </c>
-      <c r="AG66">
-        <v>2.25</v>
-      </c>
       <c r="AH66" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK66">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11242,7 +11242,7 @@
         <v>3.56</v>
       </c>
       <c r="R67">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S67">
         <v>1.2</v>
@@ -11251,37 +11251,37 @@
         <v>4</v>
       </c>
       <c r="U67">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V67">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W67">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA67">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB67">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AC67">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD67">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE67">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF67">
         <v>1.4</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK67">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11399,10 +11399,10 @@
         <v>3.3</v>
       </c>
       <c r="P68">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="Q68">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R68">
         <v>2.3</v>
@@ -11435,7 +11435,7 @@
         <v>1.67</v>
       </c>
       <c r="AB68">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC68">
         <v>2.7</v>
@@ -11725,13 +11725,13 @@
         <v>3.54</v>
       </c>
       <c r="P70">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q70">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R70">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S70">
         <v>1.36</v>
@@ -11792,7 +11792,7 @@
         <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O72">
         <v>3.25</v>
@@ -12060,7 +12060,7 @@
         <v>1.94</v>
       </c>
       <c r="S72">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T72">
         <v>2.62</v>
@@ -12214,7 +12214,7 @@
         <v>3.1</v>
       </c>
       <c r="P73">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -12238,34 +12238,34 @@
         <v>1.06</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z73">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA73">
         <v>1.9</v>
       </c>
       <c r="AB73">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC73">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD73">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE73">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF73">
         <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>1.56</v>
       </c>
       <c r="AB74">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AC74">
         <v>2.37</v>
@@ -12549,7 +12549,7 @@
         <v>2.5</v>
       </c>
       <c r="S75">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T75">
         <v>4</v>
@@ -12564,28 +12564,28 @@
         <v>1.18</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
         <v>1.08</v>
       </c>
       <c r="Z75">
-        <v>5.71</v>
+        <v>5.41</v>
       </c>
       <c r="AA75">
         <v>1.44</v>
       </c>
       <c r="AB75">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="AC75">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AD75">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AE75">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF75">
         <v>1.44</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O77">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="P77">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="Q77">
         <v>2.06</v>
@@ -12878,10 +12878,10 @@
         <v>1.25</v>
       </c>
       <c r="T77">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="U77">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V77">
         <v>1.5</v>
@@ -13044,7 +13044,7 @@
         <v>3.2</v>
       </c>
       <c r="U78">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V78">
         <v>1.47</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="O79">
         <v>3.7</v>
@@ -13201,16 +13201,16 @@
         <v>2.3</v>
       </c>
       <c r="S79">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T79">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="U79">
         <v>2.6</v>
       </c>
       <c r="V79">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W79">
         <v>1.1</v>
@@ -13518,7 +13518,7 @@
         <v>3.48</v>
       </c>
       <c r="P81">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -14170,10 +14170,10 @@
         <v>3.1</v>
       </c>
       <c r="P85">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Q85">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="R85">
         <v>2.04</v>
@@ -14363,7 +14363,7 @@
         <v>1.14</v>
       </c>
       <c r="Z86">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA86">
         <v>1.6</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,68 +14486,68 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N87">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="O87">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="P87">
-        <v>2.02</v>
+        <v>7.35</v>
       </c>
       <c r="Q87">
-        <v>3.66</v>
+        <v>1.67</v>
       </c>
       <c r="R87">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T87">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U87">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="V87">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W87">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z87">
-        <v>5.93</v>
+        <v>5.15</v>
       </c>
       <c r="AA87">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB87">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AC87">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AD87">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE87">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF87">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK87">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G88">
@@ -14649,68 +14649,68 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N88">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="O88">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="P88">
-        <v>7.35</v>
+        <v>2.02</v>
       </c>
       <c r="Q88">
+        <v>3.66</v>
+      </c>
+      <c r="R88">
+        <v>2.45</v>
+      </c>
+      <c r="S88">
+        <v>1.2</v>
+      </c>
+      <c r="T88">
+        <v>3.9</v>
+      </c>
+      <c r="U88">
+        <v>2.09</v>
+      </c>
+      <c r="V88">
         <v>1.67</v>
       </c>
-      <c r="R88">
-        <v>2.62</v>
-      </c>
-      <c r="S88">
-        <v>1.18</v>
-      </c>
-      <c r="T88">
-        <v>3.85</v>
-      </c>
-      <c r="U88">
-        <v>2.07</v>
-      </c>
-      <c r="V88">
-        <v>1.65</v>
-      </c>
       <c r="W88">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z88">
-        <v>5.15</v>
+        <v>5.93</v>
       </c>
       <c r="AA88">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB88">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AC88">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AD88">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE88">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF88">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG88">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AK88">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="O89">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q89">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="R89">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S89">
+        <v>1.42</v>
+      </c>
+      <c r="T89">
+        <v>2.78</v>
+      </c>
+      <c r="U89">
+        <v>3.14</v>
+      </c>
+      <c r="V89">
         <v>1.35</v>
       </c>
-      <c r="T89">
-        <v>2.87</v>
-      </c>
-      <c r="U89">
-        <v>2.66</v>
-      </c>
-      <c r="V89">
-        <v>1.47</v>
-      </c>
       <c r="W89">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z89">
-        <v>4.06</v>
+        <v>3.04</v>
       </c>
       <c r="AA89">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AB89">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC89">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="AD89">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE89">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF89">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG89">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK89">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="O90">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q90">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="R90">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="S90">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T90">
-        <v>2.78</v>
+        <v>3.32</v>
       </c>
       <c r="U90">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="V90">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="W90">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z90">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="AA90">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AB90">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AC90">
-        <v>3.34</v>
+        <v>2.52</v>
       </c>
       <c r="AD90">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE90">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AG90">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AK90">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.87</v>
+        <v>1.81</v>
       </c>
       <c r="O91">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P91">
+        <v>3.52</v>
+      </c>
+      <c r="Q91">
+        <v>2.41</v>
+      </c>
+      <c r="R91">
         <v>2.2</v>
       </c>
-      <c r="Q91">
-        <v>3.58</v>
-      </c>
-      <c r="R91">
-        <v>2.1</v>
-      </c>
       <c r="S91">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T91">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U91">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W91">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
+        <v>1.27</v>
+      </c>
+      <c r="Z91">
+        <v>3.25</v>
+      </c>
+      <c r="AA91">
+        <v>2.04</v>
+      </c>
+      <c r="AB91">
+        <v>1.78</v>
+      </c>
+      <c r="AC91">
+        <v>3.55</v>
+      </c>
+      <c r="AD91">
+        <v>1.29</v>
+      </c>
+      <c r="AE91">
+        <v>1.1</v>
+      </c>
+      <c r="AF91">
+        <v>1.83</v>
+      </c>
+      <c r="AG91">
+        <v>1.85</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
         <v>1.25</v>
       </c>
-      <c r="Z91">
-        <v>3.57</v>
-      </c>
-      <c r="AA91">
-        <v>1.95</v>
-      </c>
-      <c r="AB91">
-        <v>1.83</v>
-      </c>
-      <c r="AC91">
-        <v>3.25</v>
-      </c>
-      <c r="AD91">
-        <v>1.3</v>
-      </c>
-      <c r="AE91">
-        <v>1.12</v>
-      </c>
-      <c r="AF91">
-        <v>1.65</v>
-      </c>
-      <c r="AG91">
-        <v>2.11</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>1.53</v>
-      </c>
       <c r="AK91">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="O92">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P92">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="Q92">
-        <v>2.41</v>
+        <v>2.11</v>
       </c>
       <c r="R92">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T92">
-        <v>2.59</v>
+        <v>2.86</v>
       </c>
       <c r="U92">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V92">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W92">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z92">
-        <v>3.2</v>
+        <v>4.13</v>
       </c>
       <c r="AA92">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AB92">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC92">
-        <v>3.73</v>
+        <v>2.88</v>
       </c>
       <c r="AD92">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE92">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG92">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK92">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="O93">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P93">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q93">
-        <v>3.33</v>
+        <v>3.58</v>
       </c>
       <c r="R93">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="S93">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T93">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="U93">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V93">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
-        <v>4.2</v>
+        <v>3.57</v>
       </c>
       <c r="AA93">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB93">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AC93">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="AD93">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF93">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG93">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AK93">
         <v>1.39</v>
@@ -15637,13 +15637,13 @@
         <v>3.25</v>
       </c>
       <c r="P94">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q94">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="R94">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S94">
         <v>1.33</v>
@@ -15821,7 +15821,7 @@
         <v>1.57</v>
       </c>
       <c r="W95">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X95">
         <v>1.01</v>
@@ -17958,19 +17958,19 @@
         <v>1.95</v>
       </c>
       <c r="AC108">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AD108">
         <v>1.34</v>
       </c>
       <c r="AE108">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF108">
         <v>1.59</v>
       </c>
       <c r="AG108">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -18076,28 +18076,28 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O109">
         <v>3.2</v>
       </c>
       <c r="P109">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q109">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="R109">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="S109">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T109">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="U109">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="V109">
         <v>1.29</v>
@@ -18109,16 +18109,16 @@
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z109">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="AA109">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB109">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC109">
         <v>3.8</v>
@@ -18127,10 +18127,10 @@
         <v>1.19</v>
       </c>
       <c r="AE109">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF109">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG109">
         <v>1.75</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,34 +18239,34 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O110">
         <v>3.2</v>
       </c>
       <c r="P110">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q110">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R110">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="S110">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T110">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="U110">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V110">
         <v>1.42</v>
       </c>
       <c r="W110">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X110">
         <v>1.05</v>
@@ -18275,22 +18275,22 @@
         <v>1.3</v>
       </c>
       <c r="Z110">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA110">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB110">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC110">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD110">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE110">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF110">
         <v>1.71</v>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK110">
         <v>1.7</v>
@@ -18441,16 +18441,16 @@
         <v>3.58</v>
       </c>
       <c r="AA111">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB111">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC111">
         <v>2.78</v>
       </c>
       <c r="AD111">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE111">
         <v>1.14</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.96</v>
+        <v>3.07</v>
       </c>
       <c r="O112">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="P112">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18731,16 +18731,16 @@
         <v>2.26</v>
       </c>
       <c r="O113">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P113">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="Q113">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="R113">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S113">
         <v>1.4</v>
@@ -18761,7 +18761,7 @@
         <v>1.04</v>
       </c>
       <c r="Y113">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z113">
         <v>3.18</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="O114">
         <v>3.25</v>
@@ -19582,7 +19582,7 @@
         <v>3.98</v>
       </c>
       <c r="AA118">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB118">
         <v>2.03</v>
@@ -19712,7 +19712,7 @@
         <v>3.6</v>
       </c>
       <c r="P119">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="Q119">
         <v>2.82</v>
@@ -20850,7 +20850,7 @@
         <v>3</v>
       </c>
       <c r="O126">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P126">
         <v>2.25</v>
@@ -20886,7 +20886,7 @@
         <v>3.9</v>
       </c>
       <c r="AA126">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB126">
         <v>2.14</v>
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK126">
         <v>1.3</v>
@@ -21173,22 +21173,22 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="O128">
         <v>3.6</v>
       </c>
       <c r="P128">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q128">
         <v>2.3</v>
       </c>
       <c r="R128">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S128">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T128">
         <v>2.88</v>
@@ -21206,31 +21206,31 @@
         <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z128">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA128">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB128">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC128">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD128">
         <v>1.29</v>
       </c>
       <c r="AE128">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF128">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG128">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK128">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O129">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P129">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Q129">
         <v>4.5</v>
@@ -21357,10 +21357,10 @@
         <v>4</v>
       </c>
       <c r="U129">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V129">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W129">
         <v>1.14</v>
@@ -21378,10 +21378,10 @@
         <v>1.49</v>
       </c>
       <c r="AB129">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC129">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD129">
         <v>1.62</v>
@@ -21393,7 +21393,7 @@
         <v>1.55</v>
       </c>
       <c r="AG129">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="O130">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P130">
-        <v>3.15</v>
+        <v>2.67</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA130">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB130">
         <v>1.8</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21710,7 +21710,7 @@
         <v>3.2</v>
       </c>
       <c r="AD131">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE131">
         <v>1.06</v>
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O134">
         <v>3.5</v>
       </c>
       <c r="P134">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q134">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="R134">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S134">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T134">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="U134">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V134">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W134">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z134">
-        <v>3.96</v>
+        <v>4.4</v>
       </c>
       <c r="AA134">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB134">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC134">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AD134">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE134">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF134">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG134">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK134">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22341,7 +22341,7 @@
         <v>1.65</v>
       </c>
       <c r="W135">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X135">
         <v>1</v>
@@ -22483,7 +22483,7 @@
         <v>3.3</v>
       </c>
       <c r="P136">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="Q136">
         <v>2.6</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -1459,55 +1459,55 @@
         <v>1.62</v>
       </c>
       <c r="Q7">
-        <v>4.08</v>
+        <v>4.75</v>
       </c>
       <c r="R7">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V7">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>5.2</v>
+        <v>4.85</v>
       </c>
       <c r="AA7">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AB7">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AC7">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD7">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF7">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG7">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O9">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="R9">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S9">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T9">
         <v>2.13</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W9">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Z9">
         <v>2.08</v>
       </c>
       <c r="AA9">
-        <v>3.16</v>
+        <v>2.97</v>
       </c>
       <c r="AB9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AG9">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK9">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,77 +1939,77 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O10">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="Q10">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R10">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S10">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="U10">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="V10">
+        <v>1.26</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
+        <v>1.03</v>
+      </c>
+      <c r="Y10">
+        <v>1.38</v>
+      </c>
+      <c r="Z10">
+        <v>2.62</v>
+      </c>
+      <c r="AA10">
+        <v>2.24</v>
+      </c>
+      <c r="AB10">
+        <v>1.55</v>
+      </c>
+      <c r="AC10">
+        <v>4.2</v>
+      </c>
+      <c r="AD10">
+        <v>1.15</v>
+      </c>
+      <c r="AE10">
+        <v>1.01</v>
+      </c>
+      <c r="AF10">
+        <v>1.95</v>
+      </c>
+      <c r="AG10">
+        <v>1.72</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.27</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>1.37</v>
-      </c>
-      <c r="Z10">
-        <v>2.74</v>
-      </c>
-      <c r="AA10">
-        <v>2.29</v>
-      </c>
-      <c r="AB10">
-        <v>1.52</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>2</v>
-      </c>
-      <c r="AG10">
-        <v>1.69</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.24</v>
       </c>
       <c r="AK10">
         <v>1.57</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O16">
+        <v>3.6</v>
+      </c>
+      <c r="P16">
+        <v>3.9</v>
+      </c>
+      <c r="Q16">
+        <v>2.24</v>
+      </c>
+      <c r="R16">
+        <v>2.17</v>
+      </c>
+      <c r="S16">
+        <v>1.31</v>
+      </c>
+      <c r="T16">
+        <v>2.94</v>
+      </c>
+      <c r="U16">
+        <v>2.48</v>
+      </c>
+      <c r="V16">
+        <v>1.43</v>
+      </c>
+      <c r="W16">
+        <v>1.1</v>
+      </c>
+      <c r="X16">
+        <v>1.03</v>
+      </c>
+      <c r="Y16">
+        <v>1.19</v>
+      </c>
+      <c r="Z16">
         <v>3.8</v>
       </c>
-      <c r="P16">
-        <v>4</v>
-      </c>
-      <c r="Q16">
-        <v>2.2</v>
-      </c>
-      <c r="R16">
-        <v>2.3</v>
-      </c>
-      <c r="S16">
-        <v>1.25</v>
-      </c>
-      <c r="T16">
-        <v>3.3</v>
-      </c>
-      <c r="U16">
-        <v>2.29</v>
-      </c>
-      <c r="V16">
-        <v>1.5</v>
-      </c>
-      <c r="W16">
-        <v>1.13</v>
-      </c>
-      <c r="X16">
-        <v>1.01</v>
-      </c>
-      <c r="Y16">
-        <v>1.14</v>
-      </c>
-      <c r="Z16">
-        <v>4.33</v>
-      </c>
       <c r="AA16">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AC16">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="P17">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q17">
+        <v>6.1</v>
+      </c>
+      <c r="R17">
         <v>2.29</v>
       </c>
-      <c r="R17">
-        <v>2.39</v>
-      </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="U17">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="V17">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>4.95</v>
+        <v>4.15</v>
       </c>
       <c r="AA17">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AB17">
-        <v>2.46</v>
+        <v>2.13</v>
       </c>
       <c r="AC17">
-        <v>2.13</v>
+        <v>2.49</v>
       </c>
       <c r="AD17">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AE17">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="AG17">
-        <v>2.53</v>
+        <v>1.94</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK17">
-        <v>1.82</v>
+        <v>1.05</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="O18">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="Q18">
-        <v>6.1</v>
+        <v>2.29</v>
       </c>
       <c r="R18">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>4.15</v>
+        <v>4.95</v>
       </c>
       <c r="AA18">
+        <v>1.43</v>
+      </c>
+      <c r="AB18">
+        <v>2.46</v>
+      </c>
+      <c r="AC18">
+        <v>2.13</v>
+      </c>
+      <c r="AD18">
         <v>1.61</v>
       </c>
-      <c r="AB18">
-        <v>2.13</v>
-      </c>
-      <c r="AC18">
-        <v>2.49</v>
-      </c>
-      <c r="AD18">
-        <v>1.42</v>
-      </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AG18">
-        <v>1.94</v>
+        <v>2.53</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>1.05</v>
+        <v>1.82</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q19">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R19">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="V19">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA19">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="AD19">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK19">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>1.21</v>
       </c>
       <c r="AE21">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF21">
         <v>1.79</v>
@@ -3904,16 +3904,16 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
         <v>2.05</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U22">
         <v>3.05</v>
@@ -3925,7 +3925,7 @@
         <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
         <v>1.35</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
         <v>1.8</v>
@@ -4073,10 +4073,10 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T23">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="U23">
         <v>2.76</v>
@@ -4088,19 +4088,19 @@
         <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
         <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA23">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC23">
         <v>3.3</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="O24">
         <v>3</v>
       </c>
       <c r="P24">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -4251,7 +4251,7 @@
         <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
         <v>1.38</v>
@@ -4266,7 +4266,7 @@
         <v>1.61</v>
       </c>
       <c r="AC24">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AD24">
         <v>1.16</v>
@@ -4278,7 +4278,7 @@
         <v>1.9</v>
       </c>
       <c r="AG24">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.44</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="O25">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q25">
-        <v>5.72</v>
+        <v>5.15</v>
       </c>
       <c r="R25">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="S25">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T25">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="U25">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="V25">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AA25">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AB25">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="AG25">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>2.8</v>
@@ -4734,7 +4734,7 @@
         <v>4.05</v>
       </c>
       <c r="V27">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W27">
         <v>1.03</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="O28">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="P28">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="Q28">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="R28">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="S28">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="T28">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="U28">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="V28">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y28">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="Z28">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AA28">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AB28">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC28">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD28">
         <v>1.1</v>
       </c>
       <c r="AE28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AG28">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK28">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,28 +5036,28 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P29">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q29">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="R29">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="S29">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="T29">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="U29">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="V29">
         <v>1.25</v>
@@ -5066,34 +5066,34 @@
         <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y29">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Z29">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AA29">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="AB29">
         <v>1.39</v>
       </c>
       <c r="AC29">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AD29">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE29">
         <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AG29">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,61 +5199,61 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="O30">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>2.41</v>
       </c>
       <c r="Q30">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="R30">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="S30">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="T30">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="U30">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="V30">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
         <v>1.1</v>
       </c>
       <c r="Y30">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z30">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AA30">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AB30">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC30">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD30">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF30">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AG30">
         <v>1.53</v>
@@ -5272,7 +5272,7 @@
         <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.95</v>
+        <v>1.31</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="O31">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.65</v>
+        <v>3.94</v>
       </c>
       <c r="Q31">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="R31">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="V31">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
-        <v>4.11</v>
+        <v>3.08</v>
       </c>
       <c r="AA31">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB31">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AC31">
-        <v>2.69</v>
+        <v>3.46</v>
       </c>
       <c r="AD31">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AE31">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.74</v>
+        <v>2.19</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P32">
-        <v>3.94</v>
+        <v>2.65</v>
       </c>
       <c r="Q32">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="R32">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>3.08</v>
+        <v>4.11</v>
       </c>
       <c r="AA32">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AC32">
-        <v>3.46</v>
+        <v>2.69</v>
       </c>
       <c r="AD32">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6047,31 +6047,31 @@
         <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z35">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA35">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
         <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AG35">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>1.7</v>
       </c>
       <c r="O38">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
         <v>3.7</v>
@@ -6853,7 +6853,7 @@
         <v>3.18</v>
       </c>
       <c r="V40">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W40">
         <v>1.01</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O41">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P41">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
       </c>
       <c r="R41">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
         <v>1.33</v>
@@ -7013,7 +7013,7 @@
         <v>3.14</v>
       </c>
       <c r="U41">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V41">
         <v>1.46</v>
@@ -7031,10 +7031,10 @@
         <v>3.7</v>
       </c>
       <c r="AA41">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB41">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC41">
         <v>2.88</v>
@@ -7810,7 +7810,7 @@
         <v>1.95</v>
       </c>
       <c r="O46">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
         <v>3.1</v>
@@ -7819,7 +7819,7 @@
         <v>2.4</v>
       </c>
       <c r="R46">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="S46">
         <v>1.25</v>
@@ -7828,7 +7828,7 @@
         <v>3.6</v>
       </c>
       <c r="U46">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="V46">
         <v>1.59</v>
@@ -7843,16 +7843,16 @@
         <v>1.16</v>
       </c>
       <c r="Z46">
-        <v>4.98</v>
+        <v>5.04</v>
       </c>
       <c r="AA46">
         <v>1.5</v>
       </c>
       <c r="AB46">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC46">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AD46">
         <v>1.6</v>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8148,16 +8148,16 @@
         <v>2.05</v>
       </c>
       <c r="S48">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="U48">
         <v>2.64</v>
       </c>
       <c r="V48">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W48">
         <v>1.04</v>
@@ -8166,16 +8166,16 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="AA48">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB48">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AC48">
         <v>2.63</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O49">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="P49">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -8338,7 +8338,7 @@
         <v>2.11</v>
       </c>
       <c r="AB49">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC49">
         <v>3.58</v>
@@ -8492,7 +8492,7 @@
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z50">
         <v>3.19</v>
@@ -8504,7 +8504,7 @@
         <v>1.77</v>
       </c>
       <c r="AC50">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD50">
         <v>1.27</v>
@@ -8637,7 +8637,7 @@
         <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
         <v>2.88</v>
@@ -8646,7 +8646,7 @@
         <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
         <v>1.04</v>
@@ -8658,13 +8658,13 @@
         <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>3.54</v>
+        <v>4.04</v>
       </c>
       <c r="AA51">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC51">
         <v>3.4</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q54">
         <v>2.57</v>
@@ -9141,7 +9141,7 @@
         <v>1.13</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.16</v>
@@ -9153,7 +9153,7 @@
         <v>1.61</v>
       </c>
       <c r="AB54">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC54">
         <v>2.49</v>
@@ -9277,10 +9277,10 @@
         <v>2</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="Q55">
         <v>2.58</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P56">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q56">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="R56">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9458,59 +9458,59 @@
         <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W56">
+        <v>1.1</v>
+      </c>
+      <c r="X56">
+        <v>1.02</v>
+      </c>
+      <c r="Y56">
+        <v>1.16</v>
+      </c>
+      <c r="Z56">
+        <v>4.15</v>
+      </c>
+      <c r="AA56">
+        <v>1.61</v>
+      </c>
+      <c r="AB56">
+        <v>2.17</v>
+      </c>
+      <c r="AC56">
+        <v>2.43</v>
+      </c>
+      <c r="AD56">
+        <v>1.44</v>
+      </c>
+      <c r="AE56">
+        <v>1.15</v>
+      </c>
+      <c r="AF56">
+        <v>1.62</v>
+      </c>
+      <c r="AG56">
+        <v>2.12</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
         <v>1.11</v>
       </c>
-      <c r="X56">
-        <v>1.03</v>
-      </c>
-      <c r="Y56">
-        <v>1.18</v>
-      </c>
-      <c r="Z56">
-        <v>3.9</v>
-      </c>
-      <c r="AA56">
-        <v>1.67</v>
-      </c>
-      <c r="AB56">
-        <v>2.04</v>
-      </c>
-      <c r="AC56">
-        <v>2.66</v>
-      </c>
-      <c r="AD56">
-        <v>1.4</v>
-      </c>
-      <c r="AE56">
-        <v>1.11</v>
-      </c>
-      <c r="AF56">
-        <v>1.67</v>
-      </c>
-      <c r="AG56">
-        <v>2.05</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.16</v>
-      </c>
       <c r="AK56">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.46</v>
+        <v>2.05</v>
       </c>
       <c r="O57">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="P57">
-        <v>5.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q57">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="R57">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T57">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="U57">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="V57">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W57">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AA57">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB57">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AC57">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AD57">
         <v>1.44</v>
       </c>
       <c r="AE57">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF57">
+        <v>1.49</v>
+      </c>
+      <c r="AG57">
+        <v>2.39</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>1.2</v>
+      </c>
+      <c r="AK57">
         <v>1.62</v>
-      </c>
-      <c r="AG57">
-        <v>2.12</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.11</v>
-      </c>
-      <c r="AK57">
-        <v>2.09</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,65 +9926,65 @@
         </is>
       </c>
       <c r="N59">
+        <v>1.6</v>
+      </c>
+      <c r="O59">
+        <v>3.8</v>
+      </c>
+      <c r="P59">
+        <v>4.3</v>
+      </c>
+      <c r="Q59">
+        <v>2.15</v>
+      </c>
+      <c r="R59">
+        <v>2.25</v>
+      </c>
+      <c r="S59">
+        <v>1.29</v>
+      </c>
+      <c r="T59">
+        <v>3.3</v>
+      </c>
+      <c r="U59">
+        <v>2.45</v>
+      </c>
+      <c r="V59">
+        <v>1.5</v>
+      </c>
+      <c r="W59">
+        <v>1.11</v>
+      </c>
+      <c r="X59">
+        <v>1.03</v>
+      </c>
+      <c r="Y59">
+        <v>1.18</v>
+      </c>
+      <c r="Z59">
+        <v>3.9</v>
+      </c>
+      <c r="AA59">
+        <v>1.67</v>
+      </c>
+      <c r="AB59">
+        <v>2.04</v>
+      </c>
+      <c r="AC59">
+        <v>2.66</v>
+      </c>
+      <c r="AD59">
+        <v>1.4</v>
+      </c>
+      <c r="AE59">
+        <v>1.11</v>
+      </c>
+      <c r="AF59">
+        <v>1.67</v>
+      </c>
+      <c r="AG59">
         <v>2.05</v>
       </c>
-      <c r="O59">
-        <v>3.35</v>
-      </c>
-      <c r="P59">
-        <v>2.95</v>
-      </c>
-      <c r="Q59">
-        <v>2.7</v>
-      </c>
-      <c r="R59">
-        <v>2.3</v>
-      </c>
-      <c r="S59">
-        <v>1.24</v>
-      </c>
-      <c r="T59">
-        <v>3.38</v>
-      </c>
-      <c r="U59">
-        <v>2.22</v>
-      </c>
-      <c r="V59">
-        <v>1.53</v>
-      </c>
-      <c r="W59">
-        <v>1.12</v>
-      </c>
-      <c r="X59">
-        <v>1.02</v>
-      </c>
-      <c r="Y59">
-        <v>1.14</v>
-      </c>
-      <c r="Z59">
-        <v>4.3</v>
-      </c>
-      <c r="AA59">
-        <v>1.6</v>
-      </c>
-      <c r="AB59">
-        <v>2.22</v>
-      </c>
-      <c r="AC59">
-        <v>2.49</v>
-      </c>
-      <c r="AD59">
-        <v>1.44</v>
-      </c>
-      <c r="AE59">
-        <v>1.14</v>
-      </c>
-      <c r="AF59">
-        <v>1.49</v>
-      </c>
-      <c r="AG59">
-        <v>2.39</v>
-      </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK59">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="O60">
         <v>3.4</v>
@@ -10101,7 +10101,7 @@
         <v>2.6</v>
       </c>
       <c r="R60">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S60">
         <v>1.33</v>
@@ -10110,10 +10110,10 @@
         <v>2.97</v>
       </c>
       <c r="U60">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="V60">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W60">
         <v>1.08</v>
@@ -10131,13 +10131,13 @@
         <v>1.85</v>
       </c>
       <c r="AB60">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC60">
         <v>2.83</v>
       </c>
       <c r="AD60">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE60">
         <v>1.09</v>
@@ -10279,7 +10279,7 @@
         <v>1.3</v>
       </c>
       <c r="W61">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
         <v>1.05</v>
@@ -10291,7 +10291,7 @@
         <v>3</v>
       </c>
       <c r="AA61">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB61">
         <v>1.66</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O63">
         <v>3.4</v>
@@ -10587,25 +10587,25 @@
         <v>2.25</v>
       </c>
       <c r="Q63">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S63">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U63">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V63">
         <v>1.62</v>
       </c>
       <c r="W63">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X63">
         <v>1.02</v>
@@ -10617,7 +10617,7 @@
         <v>4.55</v>
       </c>
       <c r="AA63">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB63">
         <v>2.28</v>
@@ -10750,13 +10750,13 @@
         <v>4.25</v>
       </c>
       <c r="Q64">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R64">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="S64">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T64">
         <v>2.73</v>
@@ -10768,7 +10768,7 @@
         <v>1.4</v>
       </c>
       <c r="W64">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X64">
         <v>1.03</v>
@@ -10777,7 +10777,7 @@
         <v>1.28</v>
       </c>
       <c r="Z64">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="AA64">
         <v>1.85</v>
@@ -10910,13 +10910,13 @@
         <v>4.33</v>
       </c>
       <c r="P65">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q65">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="R65">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="S65">
         <v>1.19</v>
@@ -10946,10 +10946,10 @@
         <v>1.46</v>
       </c>
       <c r="AB65">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC65">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD65">
         <v>1.57</v>
@@ -10961,7 +10961,7 @@
         <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11070,19 +11070,19 @@
         <v>1.5</v>
       </c>
       <c r="O66">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P66">
         <v>4.6</v>
       </c>
       <c r="Q66">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R66">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S66">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T66">
         <v>4.5</v>
@@ -11118,13 +11118,13 @@
         <v>1.87</v>
       </c>
       <c r="AE66">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AF66">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.15</v>
       </c>
       <c r="AK66">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="O69">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P69">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Q69">
         <v>6.87</v>
@@ -11610,7 +11610,7 @@
         <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG69">
         <v>1.85</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>2.56</v>
+        <v>1.11</v>
       </c>
       <c r="AK69">
         <v>1.11</v>
@@ -11725,19 +11725,19 @@
         <v>3.54</v>
       </c>
       <c r="P70">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q70">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R70">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S70">
         <v>1.36</v>
       </c>
       <c r="T70">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="U70">
         <v>2.67</v>
@@ -11752,22 +11752,22 @@
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z70">
         <v>3.53</v>
       </c>
       <c r="AA70">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB70">
         <v>1.97</v>
       </c>
       <c r="AC70">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="AD70">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE70">
         <v>1.13</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O71">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="P71">
         <v>7</v>
@@ -11894,7 +11894,7 @@
         <v>7</v>
       </c>
       <c r="R71">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="S71">
         <v>1.2</v>
@@ -11903,10 +11903,10 @@
         <v>4.4</v>
       </c>
       <c r="U71">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V71">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W71">
         <v>1.21</v>
@@ -11918,19 +11918,19 @@
         <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>6.31</v>
+        <v>6.62</v>
       </c>
       <c r="AA71">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AB71">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AC71">
+        <v>1.86</v>
+      </c>
+      <c r="AD71">
         <v>1.88</v>
-      </c>
-      <c r="AD71">
-        <v>1.87</v>
       </c>
       <c r="AE71">
         <v>1.3</v>
@@ -11939,7 +11939,7 @@
         <v>1.62</v>
       </c>
       <c r="AG71">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12054,10 +12054,10 @@
         <v>3.9</v>
       </c>
       <c r="Q72">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R72">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S72">
         <v>1.4</v>
@@ -12084,7 +12084,7 @@
         <v>2.7</v>
       </c>
       <c r="AA72">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AB72">
         <v>1.6</v>
@@ -12093,7 +12093,7 @@
         <v>4.15</v>
       </c>
       <c r="AD72">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE72">
         <v>1.01</v>
@@ -12404,7 +12404,7 @@
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z74">
         <v>4.5</v>
@@ -12416,7 +12416,7 @@
         <v>2.31</v>
       </c>
       <c r="AC74">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AD74">
         <v>1.54</v>
@@ -12444,7 +12444,7 @@
         <v>1.08</v>
       </c>
       <c r="AK74">
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12549,16 +12549,16 @@
         <v>2.5</v>
       </c>
       <c r="S75">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T75">
         <v>4</v>
       </c>
       <c r="U75">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="V75">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W75">
         <v>1.18</v>
@@ -12570,7 +12570,7 @@
         <v>1.08</v>
       </c>
       <c r="Z75">
-        <v>5.41</v>
+        <v>5.48</v>
       </c>
       <c r="AA75">
         <v>1.44</v>
@@ -12863,13 +12863,13 @@
         <v>1.65</v>
       </c>
       <c r="O77">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P77">
         <v>3.92</v>
       </c>
       <c r="Q77">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="R77">
         <v>2.32</v>
@@ -12896,13 +12896,13 @@
         <v>1.14</v>
       </c>
       <c r="Z77">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AA77">
         <v>1.66</v>
       </c>
       <c r="AB77">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC77">
         <v>2.49</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK77">
         <v>2.12</v>
@@ -13032,10 +13032,10 @@
         <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="R78">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
         <v>1.29</v>
@@ -13201,13 +13201,13 @@
         <v>2.3</v>
       </c>
       <c r="S79">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U79">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="V79">
         <v>1.49</v>
@@ -13515,10 +13515,10 @@
         <v>2.2</v>
       </c>
       <c r="O81">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P81">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q81">
         <v>2.75</v>
@@ -13557,7 +13557,7 @@
         <v>1.97</v>
       </c>
       <c r="AC81">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="AD81">
         <v>1.33</v>
@@ -14167,13 +14167,13 @@
         <v>2.45</v>
       </c>
       <c r="O85">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P85">
         <v>2.59</v>
       </c>
       <c r="Q85">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R85">
         <v>2.04</v>
@@ -14200,7 +14200,7 @@
         <v>1.29</v>
       </c>
       <c r="Z85">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA85">
         <v>1.93</v>
@@ -14212,7 +14212,7 @@
         <v>3.14</v>
       </c>
       <c r="AD85">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE85">
         <v>1.06</v>
@@ -14327,16 +14327,16 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="O86">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P86">
         <v>10</v>
       </c>
       <c r="Q86">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="R86">
         <v>2.7</v>
@@ -14360,31 +14360,31 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA86">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB86">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC86">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AD86">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE86">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF86">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AG86">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK86">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14493,7 +14493,7 @@
         <v>1.33</v>
       </c>
       <c r="O87">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P87">
         <v>7.35</v>
@@ -14517,7 +14517,7 @@
         <v>1.65</v>
       </c>
       <c r="W87">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X87">
         <v>1.02</v>
@@ -14547,7 +14547,7 @@
         <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>2.02</v>
       </c>
       <c r="Q88">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="R88">
         <v>2.45</v>
@@ -14674,7 +14674,7 @@
         <v>3.9</v>
       </c>
       <c r="U88">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="V88">
         <v>1.67</v>
@@ -14695,16 +14695,16 @@
         <v>1.47</v>
       </c>
       <c r="AB88">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AC88">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD88">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE88">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF88">
         <v>1.4</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AK88">
         <v>1.3</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="O89">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P89">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="Q89">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="R89">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S89">
         <v>1.42</v>
       </c>
       <c r="T89">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="U89">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="V89">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W89">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z89">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA89">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB89">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC89">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD89">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF89">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG89">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK89">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q90">
-        <v>3.33</v>
+        <v>3.58</v>
       </c>
       <c r="R90">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T90">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="U90">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V90">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W90">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z90">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA90">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB90">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AC90">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="AD90">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF90">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG90">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AK90">
         <v>1.39</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="O91">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="P91">
-        <v>3.52</v>
+        <v>2.35</v>
       </c>
       <c r="Q91">
-        <v>2.41</v>
+        <v>3.37</v>
       </c>
       <c r="R91">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="S91">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T91">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="U91">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="V91">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA91">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="AB91">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC91">
-        <v>3.55</v>
+        <v>2.52</v>
       </c>
       <c r="AD91">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE91">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF91">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG91">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AK91">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.58</v>
+        <v>2.29</v>
       </c>
       <c r="O92">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P92">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q92">
-        <v>2.11</v>
+        <v>2.88</v>
       </c>
       <c r="R92">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S92">
+        <v>1.43</v>
+      </c>
+      <c r="T92">
+        <v>2.79</v>
+      </c>
+      <c r="U92">
+        <v>3.16</v>
+      </c>
+      <c r="V92">
         <v>1.35</v>
       </c>
-      <c r="T92">
-        <v>2.86</v>
-      </c>
-      <c r="U92">
-        <v>2.63</v>
-      </c>
-      <c r="V92">
-        <v>1.46</v>
-      </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X92">
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z92">
-        <v>4.13</v>
+        <v>3.04</v>
       </c>
       <c r="AA92">
-        <v>1.71</v>
+        <v>2.01</v>
       </c>
       <c r="AB92">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC92">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD92">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE92">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF92">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG92">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="O93">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P93">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="Q93">
-        <v>3.58</v>
+        <v>2.11</v>
       </c>
       <c r="R93">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S93">
         <v>1.35</v>
       </c>
       <c r="T93">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U93">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="V93">
+        <v>1.49</v>
+      </c>
+      <c r="W93">
+        <v>1.11</v>
+      </c>
+      <c r="X93">
+        <v>1.02</v>
+      </c>
+      <c r="Y93">
+        <v>1.18</v>
+      </c>
+      <c r="Z93">
+        <v>4.17</v>
+      </c>
+      <c r="AA93">
+        <v>1.78</v>
+      </c>
+      <c r="AB93">
+        <v>1.97</v>
+      </c>
+      <c r="AC93">
+        <v>2.88</v>
+      </c>
+      <c r="AD93">
         <v>1.4</v>
-      </c>
-      <c r="W93">
-        <v>1.08</v>
-      </c>
-      <c r="X93">
-        <v>1.01</v>
-      </c>
-      <c r="Y93">
-        <v>1.25</v>
-      </c>
-      <c r="Z93">
-        <v>3.57</v>
-      </c>
-      <c r="AA93">
-        <v>1.95</v>
-      </c>
-      <c r="AB93">
-        <v>1.83</v>
-      </c>
-      <c r="AC93">
-        <v>3.25</v>
-      </c>
-      <c r="AD93">
-        <v>1.3</v>
       </c>
       <c r="AE93">
         <v>1.12</v>
       </c>
       <c r="AF93">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG93">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="AK93">
-        <v>1.39</v>
+        <v>2.24</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15637,25 +15637,25 @@
         <v>3.25</v>
       </c>
       <c r="P94">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q94">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="R94">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S94">
         <v>1.33</v>
       </c>
       <c r="T94">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="U94">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V94">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W94">
         <v>1.11</v>
@@ -15673,10 +15673,10 @@
         <v>1.75</v>
       </c>
       <c r="AB94">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC94">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AD94">
         <v>1.35</v>
@@ -15688,7 +15688,7 @@
         <v>1.61</v>
       </c>
       <c r="AG94">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>1.57</v>
       </c>
       <c r="AB95">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AC95">
         <v>2.35</v>
@@ -15966,22 +15966,22 @@
         <v>2.6</v>
       </c>
       <c r="Q96">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="R96">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S96">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T96">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U96">
         <v>2.5</v>
       </c>
       <c r="V96">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W96">
         <v>1.08</v>
@@ -15993,13 +15993,13 @@
         <v>1.25</v>
       </c>
       <c r="Z96">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AA96">
         <v>1.78</v>
       </c>
       <c r="AB96">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC96">
         <v>2.92</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK96">
         <v>1.47</v>
@@ -16159,7 +16159,7 @@
         <v>5.89</v>
       </c>
       <c r="AA97">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB97">
         <v>2.66</v>
@@ -17955,7 +17955,7 @@
         <v>1.76</v>
       </c>
       <c r="AB108">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC108">
         <v>3.13</v>
@@ -17964,7 +17964,7 @@
         <v>1.34</v>
       </c>
       <c r="AE108">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF108">
         <v>1.59</v>
@@ -17986,7 +17986,7 @@
         <v>1.27</v>
       </c>
       <c r="AK108">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,28 +18076,28 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O109">
         <v>3.2</v>
       </c>
       <c r="P109">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q109">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="R109">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S109">
         <v>1.43</v>
       </c>
       <c r="T109">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="U109">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="V109">
         <v>1.29</v>
@@ -18127,7 +18127,7 @@
         <v>1.19</v>
       </c>
       <c r="AE109">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF109">
         <v>1.92</v>
@@ -18254,10 +18254,10 @@
         <v>2.11</v>
       </c>
       <c r="S110">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U110">
         <v>2.62</v>
@@ -18269,10 +18269,10 @@
         <v>1.05</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z110">
         <v>3.6</v>
@@ -18281,7 +18281,7 @@
         <v>1.84</v>
       </c>
       <c r="AB110">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC110">
         <v>3.08</v>
@@ -18312,7 +18312,7 @@
         <v>1.29</v>
       </c>
       <c r="AK110">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O111">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P111">
         <v>2.45</v>
@@ -18420,7 +18420,7 @@
         <v>1.36</v>
       </c>
       <c r="T111">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="U111">
         <v>2.63</v>
@@ -18441,19 +18441,19 @@
         <v>3.58</v>
       </c>
       <c r="AA111">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB111">
         <v>2</v>
       </c>
       <c r="AC111">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AD111">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE111">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF111">
         <v>1.6</v>
@@ -18737,10 +18737,10 @@
         <v>2.85</v>
       </c>
       <c r="Q113">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R113">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S113">
         <v>1.4</v>
@@ -18770,7 +18770,7 @@
         <v>1.98</v>
       </c>
       <c r="AB113">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC113">
         <v>3.4</v>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
         <v>1.63</v>
@@ -18900,7 +18900,7 @@
         <v>2.3</v>
       </c>
       <c r="Q114">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="R114">
         <v>2.08</v>
@@ -18909,7 +18909,7 @@
         <v>1.3</v>
       </c>
       <c r="T114">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="U114">
         <v>2.75</v>
@@ -18933,10 +18933,10 @@
         <v>1.84</v>
       </c>
       <c r="AB114">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC114">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="AD114">
         <v>1.3</v>
@@ -18964,7 +18964,7 @@
         <v>1.3</v>
       </c>
       <c r="AK114">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="O115">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P115">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="Q115">
-        <v>2.97</v>
+        <v>4.44</v>
       </c>
       <c r="R115">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="S115">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="U115">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V115">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W115">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
+        <v>1.25</v>
+      </c>
+      <c r="Z115">
+        <v>3.8</v>
+      </c>
+      <c r="AA115">
+        <v>1.87</v>
+      </c>
+      <c r="AB115">
+        <v>1.9</v>
+      </c>
+      <c r="AC115">
+        <v>3.05</v>
+      </c>
+      <c r="AD115">
         <v>1.28</v>
       </c>
-      <c r="Z115">
-        <v>3.05</v>
-      </c>
-      <c r="AA115">
-        <v>1.96</v>
-      </c>
-      <c r="AB115">
-        <v>1.72</v>
-      </c>
-      <c r="AC115">
-        <v>3.42</v>
-      </c>
-      <c r="AD115">
-        <v>1.23</v>
-      </c>
       <c r="AE115">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG115">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AK115">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="O116">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P116">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="Q116">
-        <v>4.44</v>
+        <v>2.97</v>
       </c>
       <c r="R116">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="S116">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T116">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="U116">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V116">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W116">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y116">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z116">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA116">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AB116">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC116">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AD116">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE116">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG116">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AK116">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19386,7 +19386,7 @@
         <v>5.7</v>
       </c>
       <c r="P117">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q117">
         <v>1.77</v>
@@ -19404,7 +19404,7 @@
         <v>1.86</v>
       </c>
       <c r="V117">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="W117">
         <v>1.25</v>
@@ -19422,7 +19422,7 @@
         <v>1.25</v>
       </c>
       <c r="AB117">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AC117">
         <v>1.69</v>
@@ -19616,7 +19616,7 @@
         <v>1.13</v>
       </c>
       <c r="AK118">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="O119">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P119">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="Q119">
         <v>2.82</v>
@@ -19724,7 +19724,7 @@
         <v>1.3</v>
       </c>
       <c r="T119">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U119">
         <v>2.42</v>
@@ -20524,7 +20524,7 @@
         <v>2.15</v>
       </c>
       <c r="O124">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P124">
         <v>3.4</v>
@@ -20551,13 +20551,13 @@
         <v>1.06</v>
       </c>
       <c r="X124">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z124">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA124">
         <v>1.9</v>
@@ -20702,7 +20702,7 @@
         <v>1.3</v>
       </c>
       <c r="T125">
-        <v>3.22</v>
+        <v>2.82</v>
       </c>
       <c r="U125">
         <v>2.47</v>
@@ -20757,7 +20757,7 @@
         <v>1.44</v>
       </c>
       <c r="AK125">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20856,10 +20856,10 @@
         <v>2.25</v>
       </c>
       <c r="Q126">
-        <v>3.24</v>
+        <v>3.07</v>
       </c>
       <c r="R126">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="S126">
         <v>1.3</v>
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK126">
         <v>1.3</v>
@@ -21212,7 +21212,7 @@
         <v>3.25</v>
       </c>
       <c r="AA128">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AB128">
         <v>1.77</v>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK128">
         <v>2.1</v>
@@ -21357,10 +21357,10 @@
         <v>4</v>
       </c>
       <c r="U129">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V129">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W129">
         <v>1.14</v>
@@ -21381,7 +21381,7 @@
         <v>2.5</v>
       </c>
       <c r="AC129">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AD129">
         <v>1.62</v>
@@ -21499,28 +21499,28 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O130">
+        <v>3</v>
+      </c>
+      <c r="P130">
         <v>3.1</v>
       </c>
-      <c r="P130">
-        <v>2.67</v>
-      </c>
       <c r="Q130">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R130">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="S130">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T130">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="U130">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V130">
         <v>1.4</v>
@@ -21529,34 +21529,34 @@
         <v>1.06</v>
       </c>
       <c r="X130">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z130">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="AA130">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB130">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC130">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD130">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE130">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF130">
         <v>1.73</v>
       </c>
       <c r="AG130">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK130">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21674,7 +21674,7 @@
         <v>2.2</v>
       </c>
       <c r="R131">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S131">
         <v>1.36</v>
@@ -21695,7 +21695,7 @@
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z131">
         <v>3.3</v>
@@ -21873,7 +21873,7 @@
         <v>2.38</v>
       </c>
       <c r="AD132">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE132">
         <v>1.08</v>
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P134">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q134">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R134">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S134">
+        <v>1.3</v>
+      </c>
+      <c r="T134">
+        <v>3.24</v>
+      </c>
+      <c r="U134">
+        <v>2.45</v>
+      </c>
+      <c r="V134">
+        <v>1.5</v>
+      </c>
+      <c r="W134">
+        <v>1.11</v>
+      </c>
+      <c r="X134">
+        <v>1.03</v>
+      </c>
+      <c r="Y134">
+        <v>1.2</v>
+      </c>
+      <c r="Z134">
+        <v>4.1</v>
+      </c>
+      <c r="AA134">
+        <v>1.72</v>
+      </c>
+      <c r="AB134">
+        <v>2.04</v>
+      </c>
+      <c r="AC134">
+        <v>2.75</v>
+      </c>
+      <c r="AD134">
+        <v>1.4</v>
+      </c>
+      <c r="AE134">
+        <v>1.13</v>
+      </c>
+      <c r="AF134">
+        <v>1.62</v>
+      </c>
+      <c r="AG134">
+        <v>2.15</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
         <v>1.25</v>
       </c>
-      <c r="T134">
-        <v>3.5</v>
-      </c>
-      <c r="U134">
-        <v>2.3</v>
-      </c>
-      <c r="V134">
-        <v>1.55</v>
-      </c>
-      <c r="W134">
-        <v>1.14</v>
-      </c>
-      <c r="X134">
-        <v>1.01</v>
-      </c>
-      <c r="Y134">
-        <v>1.18</v>
-      </c>
-      <c r="Z134">
-        <v>4.4</v>
-      </c>
-      <c r="AA134">
-        <v>1.63</v>
-      </c>
-      <c r="AB134">
-        <v>2.1</v>
-      </c>
-      <c r="AC134">
-        <v>2.61</v>
-      </c>
-      <c r="AD134">
-        <v>1.44</v>
-      </c>
-      <c r="AE134">
-        <v>1.14</v>
-      </c>
-      <c r="AF134">
-        <v>1.55</v>
-      </c>
-      <c r="AG134">
-        <v>2.3</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.29</v>
-      </c>
       <c r="AK134">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>2.17</v>
       </c>
       <c r="V135">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W135">
         <v>1.17</v>
@@ -22359,7 +22359,7 @@
         <v>2.55</v>
       </c>
       <c r="AC135">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="AD135">
         <v>1.57</v>
@@ -22516,16 +22516,16 @@
         <v>3.6</v>
       </c>
       <c r="AA136">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB136">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC136">
         <v>3.09</v>
       </c>
       <c r="AD136">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE136">
         <v>1.08</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="O2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="R2">
         <v>2.13</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="U2">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -668,19 +668,19 @@
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
         <v>3.3</v>
       </c>
       <c r="AA2">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC2">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AD2">
         <v>1.38</v>
@@ -708,7 +708,7 @@
         <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>2.6</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R4">
         <v>1.99</v>
@@ -1000,7 +1000,7 @@
         <v>2.92</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
         <v>1.65</v>
@@ -1160,16 +1160,16 @@
         <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>4.72</v>
+        <v>4.77</v>
       </c>
       <c r="AA5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AC5">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD5">
         <v>1.52</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O6">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
         <v>2.58</v>
@@ -1338,13 +1338,13 @@
         <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AG6">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
+        <v>4.4</v>
+      </c>
+      <c r="O7">
         <v>4.2</v>
       </c>
-      <c r="O7">
-        <v>4.1</v>
-      </c>
       <c r="P7">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Q7">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="R7">
         <v>2.65</v>
@@ -1489,25 +1489,25 @@
         <v>4.85</v>
       </c>
       <c r="AA7">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB7">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD7">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE7">
         <v>1.25</v>
       </c>
       <c r="AF7">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="O8">
-        <v>3.43</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>5.15</v>
+        <v>6.25</v>
       </c>
       <c r="Q8">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="R8">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="T8">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="U8">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
         <v>1.02</v>
@@ -1646,19 +1646,19 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z8">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA8">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB8">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AC8">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AD8">
         <v>1.19</v>
@@ -1667,10 +1667,10 @@
         <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AG8">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>2.9</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q9">
         <v>2.74</v>
@@ -1803,7 +1803,7 @@
         <v>1.18</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1.08</v>
@@ -1827,7 +1827,7 @@
         <v>1.05</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
         <v>2.51</v>
@@ -1945,7 +1945,7 @@
         <v>3.1</v>
       </c>
       <c r="P10">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q10">
         <v>2.8</v>
@@ -2105,7 +2105,7 @@
         <v>1.25</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P11">
         <v>9.5</v>
@@ -2114,7 +2114,7 @@
         <v>1.75</v>
       </c>
       <c r="R11">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S11">
         <v>1.3</v>
@@ -2129,7 +2129,7 @@
         <v>1.43</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
         <v>2.45</v>
@@ -2440,52 +2440,52 @@
         <v>2.88</v>
       </c>
       <c r="R13">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
         <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="V13">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z13">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AA13">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AB13">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AC13">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AD13">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AG13">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AK13">
         <v>1.44</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="O14">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>7.29</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
         <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U14">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
         <v>1.11</v>
@@ -2627,28 +2627,28 @@
         <v>1.15</v>
       </c>
       <c r="Z14">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA14">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC14">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AD14">
         <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AG14">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK14">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="O15">
         <v>3.4</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q15">
-        <v>3.63</v>
+        <v>3.3</v>
       </c>
       <c r="R15">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
         <v>1.28</v>
@@ -2775,10 +2775,10 @@
         <v>3.12</v>
       </c>
       <c r="U15">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="W15">
         <v>1.12</v>
@@ -2796,13 +2796,13 @@
         <v>1.61</v>
       </c>
       <c r="AB15">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AC15">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AD15">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE15">
         <v>1.14</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="AK15">
         <v>1.29</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
         <v>3.9</v>
       </c>
       <c r="Q16">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R16">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U16">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
         <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC16">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O17">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Q17">
-        <v>6.1</v>
+        <v>4.97</v>
       </c>
       <c r="R17">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="S17">
         <v>1.28</v>
@@ -3107,7 +3107,7 @@
         <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3134,10 +3134,10 @@
         <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
+        <v>1.85</v>
+      </c>
+      <c r="O18">
+        <v>3.4</v>
+      </c>
+      <c r="P18">
+        <v>3.5</v>
+      </c>
+      <c r="Q18">
+        <v>2.38</v>
+      </c>
+      <c r="R18">
+        <v>2.25</v>
+      </c>
+      <c r="S18">
+        <v>1.34</v>
+      </c>
+      <c r="T18">
+        <v>3.02</v>
+      </c>
+      <c r="U18">
+        <v>2.59</v>
+      </c>
+      <c r="V18">
+        <v>1.44</v>
+      </c>
+      <c r="W18">
+        <v>1.09</v>
+      </c>
+      <c r="X18">
+        <v>1.03</v>
+      </c>
+      <c r="Y18">
+        <v>1.22</v>
+      </c>
+      <c r="Z18">
+        <v>4.2</v>
+      </c>
+      <c r="AA18">
+        <v>1.81</v>
+      </c>
+      <c r="AB18">
+        <v>1.98</v>
+      </c>
+      <c r="AC18">
+        <v>2.88</v>
+      </c>
+      <c r="AD18">
+        <v>1.4</v>
+      </c>
+      <c r="AE18">
+        <v>1.14</v>
+      </c>
+      <c r="AF18">
+        <v>1.62</v>
+      </c>
+      <c r="AG18">
+        <v>2.2</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.3</v>
+      </c>
+      <c r="AK18">
         <v>1.83</v>
-      </c>
-      <c r="O18">
-        <v>3.75</v>
-      </c>
-      <c r="P18">
-        <v>3.25</v>
-      </c>
-      <c r="Q18">
-        <v>2.29</v>
-      </c>
-      <c r="R18">
-        <v>2.39</v>
-      </c>
-      <c r="S18">
-        <v>1.22</v>
-      </c>
-      <c r="T18">
-        <v>3.8</v>
-      </c>
-      <c r="U18">
-        <v>2.06</v>
-      </c>
-      <c r="V18">
-        <v>1.65</v>
-      </c>
-      <c r="W18">
-        <v>1.16</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.11</v>
-      </c>
-      <c r="Z18">
-        <v>4.95</v>
-      </c>
-      <c r="AA18">
-        <v>1.43</v>
-      </c>
-      <c r="AB18">
-        <v>2.46</v>
-      </c>
-      <c r="AC18">
-        <v>2.13</v>
-      </c>
-      <c r="AD18">
-        <v>1.61</v>
-      </c>
-      <c r="AE18">
-        <v>1.22</v>
-      </c>
-      <c r="AF18">
-        <v>1.44</v>
-      </c>
-      <c r="AG18">
-        <v>2.53</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.17</v>
-      </c>
-      <c r="AK18">
-        <v>1.82</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="O19">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q19">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="U19">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z19">
-        <v>4.33</v>
+        <v>5.4</v>
       </c>
       <c r="AA19">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AC19">
-        <v>2.42</v>
+        <v>1.99</v>
       </c>
       <c r="AD19">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AE19">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q20">
+        <v>2.15</v>
+      </c>
+      <c r="R20">
         <v>2.4</v>
       </c>
-      <c r="R20">
-        <v>2.16</v>
-      </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA20">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC20">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF20">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG20">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>1.21</v>
       </c>
       <c r="AE21">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
         <v>1.79</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q22">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
         <v>2.05</v>
@@ -3916,16 +3916,16 @@
         <v>2.62</v>
       </c>
       <c r="U22">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
         <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
         <v>1.35</v>
@@ -3937,7 +3937,7 @@
         <v>2.12</v>
       </c>
       <c r="AB22">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC22">
         <v>3.78</v>
@@ -3949,10 +3949,10 @@
         <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q23">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S23">
         <v>1.39</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P25">
         <v>1.8</v>
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
         <v>2.8</v>
       </c>
       <c r="P27">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q27">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R27">
         <v>1.85</v>
       </c>
       <c r="S27">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="T27">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="U27">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="V27">
         <v>1.22</v>
@@ -4743,28 +4743,28 @@
         <v>1.1</v>
       </c>
       <c r="Y27">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z27">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AA27">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AB27">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD27">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AG27">
         <v>1.55</v>
@@ -4927,10 +4927,10 @@
         <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG28">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O29">
         <v>3</v>
@@ -5211,7 +5211,7 @@
         <v>3.9</v>
       </c>
       <c r="R30">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="S30">
         <v>1.67</v>
@@ -5220,16 +5220,16 @@
         <v>2.03</v>
       </c>
       <c r="U30">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V30">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W30">
         <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y30">
         <v>1.62</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q33">
         <v>2.61</v>
@@ -5890,7 +5890,7 @@
         <v>3.1</v>
       </c>
       <c r="AA34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB34">
         <v>1.61</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O35">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
         <v>2.2</v>
@@ -6047,10 +6047,10 @@
         <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA35">
         <v>1.95</v>
@@ -6059,19 +6059,19 @@
         <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD35">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6186,10 +6186,10 @@
         <v>4.2</v>
       </c>
       <c r="Q36">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="R36">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S36">
         <v>1.51</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O37">
         <v>2.8</v>
       </c>
       <c r="P37">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R37">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S37">
         <v>1.53</v>
@@ -6379,7 +6379,7 @@
         <v>2.32</v>
       </c>
       <c r="AA37">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AB37">
         <v>1.35</v>
@@ -6506,16 +6506,16 @@
         <v>1.7</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P38">
         <v>3.7</v>
       </c>
       <c r="Q38">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="R38">
-        <v>2.68</v>
+        <v>2.41</v>
       </c>
       <c r="S38">
         <v>1.2</v>
@@ -6708,7 +6708,7 @@
         <v>2</v>
       </c>
       <c r="AB39">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
@@ -7164,7 +7164,7 @@
         <v>7.2</v>
       </c>
       <c r="Q42">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R42">
         <v>2.3</v>
@@ -7176,7 +7176,7 @@
         <v>3</v>
       </c>
       <c r="U42">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V42">
         <v>1.44</v>
@@ -7194,7 +7194,7 @@
         <v>3.5</v>
       </c>
       <c r="AA42">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB42">
         <v>1.9</v>
@@ -7212,7 +7212,7 @@
         <v>2</v>
       </c>
       <c r="AG42">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Q43">
-        <v>6.12</v>
+        <v>5.5</v>
       </c>
       <c r="R43">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
         <v>1.38</v>
@@ -7372,7 +7372,7 @@
         <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG43">
         <v>1.75</v>
@@ -7650,7 +7650,7 @@
         <v>3.4</v>
       </c>
       <c r="P45">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q45">
         <v>3.25</v>
@@ -7674,7 +7674,7 @@
         <v>1.12</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
         <v>1.16</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q46">
         <v>2.4</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="O48">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P48">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
         <v>1.38</v>
@@ -8169,7 +8169,7 @@
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="AA48">
         <v>1.69</v>
@@ -8187,7 +8187,7 @@
         <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG48">
         <v>2.1</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="O49">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="P49">
         <v>2.31</v>
       </c>
       <c r="Q49">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R49">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S49">
         <v>1.37</v>
@@ -8335,10 +8335,10 @@
         <v>3.02</v>
       </c>
       <c r="AA49">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AB49">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC49">
         <v>3.58</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O51">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="P51">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -8646,7 +8646,7 @@
         <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W51">
         <v>1.04</v>
@@ -8658,10 +8658,10 @@
         <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>4.04</v>
+        <v>3.46</v>
       </c>
       <c r="AA51">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB51">
         <v>1.87</v>
@@ -8670,13 +8670,13 @@
         <v>3.4</v>
       </c>
       <c r="AD51">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
         <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG51">
         <v>1.9</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
         <v>2</v>
@@ -9277,7 +9277,7 @@
         <v>2</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P55">
         <v>2.7</v>
@@ -9446,10 +9446,10 @@
         <v>5.4</v>
       </c>
       <c r="Q56">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="R56">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O57">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P57">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q57">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R57">
         <v>2.3</v>
       </c>
       <c r="S57">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="U57">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="V57">
         <v>1.53</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
         <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA57">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB57">
         <v>2.22</v>
       </c>
       <c r="AC57">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AD57">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE57">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF57">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AG57">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="O58">
         <v>3.4</v>
       </c>
       <c r="P58">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q58">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R58">
         <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T58">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U58">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="V58">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W58">
         <v>1.12</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
         <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AA58">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB58">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AC58">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AD58">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE58">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF58">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG58">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9935,10 +9935,10 @@
         <v>4.3</v>
       </c>
       <c r="Q59">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R59">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S59">
         <v>1.29</v>
@@ -10098,7 +10098,7 @@
         <v>3.2</v>
       </c>
       <c r="Q60">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R60">
         <v>2.31</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O62">
         <v>3.36</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O63">
         <v>3.4</v>
@@ -10587,7 +10587,7 @@
         <v>2.25</v>
       </c>
       <c r="Q63">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="R63">
         <v>2.38</v>
@@ -10741,25 +10741,25 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O64">
         <v>3.65</v>
       </c>
       <c r="P64">
-        <v>4.25</v>
+        <v>4.55</v>
       </c>
       <c r="Q64">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="R64">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="S64">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T64">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="U64">
         <v>2.75</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="O65">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P65">
         <v>1.55</v>
       </c>
       <c r="Q65">
-        <v>3.83</v>
+        <v>4.18</v>
       </c>
       <c r="R65">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S65">
         <v>1.19</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK65">
         <v>1.18</v>
@@ -11070,7 +11070,7 @@
         <v>1.5</v>
       </c>
       <c r="O66">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P66">
         <v>4.6</v>
@@ -11112,7 +11112,7 @@
         <v>2.81</v>
       </c>
       <c r="AC66">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AD66">
         <v>1.87</v>
@@ -11121,7 +11121,7 @@
         <v>1.36</v>
       </c>
       <c r="AF66">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG66">
         <v>2.63</v>
@@ -11251,13 +11251,13 @@
         <v>4</v>
       </c>
       <c r="U67">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V67">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W67">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X67">
         <v>1.01</v>
@@ -11284,10 +11284,10 @@
         <v>1.25</v>
       </c>
       <c r="AF67">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG67">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.18</v>
+        <v>1.77</v>
       </c>
       <c r="AK67">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P68">
         <v>2.16</v>
@@ -11466,7 +11466,7 @@
         <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11562,7 +11562,7 @@
         <v>4.2</v>
       </c>
       <c r="P69">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q69">
         <v>6.87</v>
@@ -11610,7 +11610,7 @@
         <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG69">
         <v>1.85</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK69">
         <v>1.11</v>
@@ -11725,19 +11725,19 @@
         <v>3.54</v>
       </c>
       <c r="P70">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q70">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="R70">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S70">
         <v>1.36</v>
       </c>
       <c r="T70">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="U70">
         <v>2.67</v>
@@ -11752,22 +11752,22 @@
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z70">
         <v>3.53</v>
       </c>
       <c r="AA70">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB70">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AC70">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="AD70">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE70">
         <v>1.13</v>
@@ -11897,7 +11897,7 @@
         <v>3.07</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T71">
         <v>4.4</v>
@@ -11927,7 +11927,7 @@
         <v>3.2</v>
       </c>
       <c r="AC71">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AD71">
         <v>1.88</v>
@@ -11939,7 +11939,7 @@
         <v>1.62</v>
       </c>
       <c r="AG71">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>3.4</v>
+        <v>1.07</v>
       </c>
       <c r="AK71">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12534,31 +12534,31 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="O75">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P75">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q75">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R75">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S75">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T75">
         <v>4</v>
       </c>
       <c r="U75">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="V75">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W75">
         <v>1.18</v>
@@ -12567,10 +12567,10 @@
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z75">
-        <v>5.48</v>
+        <v>5.35</v>
       </c>
       <c r="AA75">
         <v>1.44</v>
@@ -12579,10 +12579,10 @@
         <v>2.2</v>
       </c>
       <c r="AC75">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD75">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE75">
         <v>1.29</v>
@@ -12591,7 +12591,7 @@
         <v>1.44</v>
       </c>
       <c r="AG75">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK75">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK77">
         <v>2.12</v>
@@ -13041,16 +13041,16 @@
         <v>1.29</v>
       </c>
       <c r="T78">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U78">
         <v>2.5</v>
       </c>
       <c r="V78">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
         <v>1.03</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
         <v>1.72</v>
@@ -13186,49 +13186,49 @@
         </is>
       </c>
       <c r="N79">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P79">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Q79">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="R79">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S79">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T79">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U79">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="V79">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W79">
         <v>1.1</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y79">
         <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA79">
         <v>1.7</v>
       </c>
       <c r="AB79">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AC79">
         <v>2.88</v>
@@ -13240,10 +13240,10 @@
         <v>1.15</v>
       </c>
       <c r="AF79">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG79">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
+        <v>1.22</v>
+      </c>
+      <c r="AK79">
         <v>1.2</v>
-      </c>
-      <c r="AK79">
-        <v>1.18</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P80">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q80">
         <v>3.84</v>
@@ -13385,7 +13385,7 @@
         <v>1.15</v>
       </c>
       <c r="Z80">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA80">
         <v>1.59</v>
@@ -13422,7 +13422,7 @@
         <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13515,7 +13515,7 @@
         <v>2.2</v>
       </c>
       <c r="O81">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
         <v>3.15</v>
@@ -13542,7 +13542,7 @@
         <v>1.07</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
         <v>1.22</v>
@@ -13551,10 +13551,10 @@
         <v>3.5</v>
       </c>
       <c r="AA81">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB81">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC81">
         <v>3.28</v>
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
+        <v>1.24</v>
+      </c>
+      <c r="O82">
+        <v>5.9</v>
+      </c>
+      <c r="P82">
+        <v>11</v>
+      </c>
+      <c r="Q82">
+        <v>1.57</v>
+      </c>
+      <c r="R82">
+        <v>2.7</v>
+      </c>
+      <c r="S82">
         <v>1.22</v>
       </c>
-      <c r="O82">
-        <v>5.35</v>
-      </c>
-      <c r="P82">
-        <v>8.6</v>
-      </c>
-      <c r="Q82">
-        <v>0</v>
-      </c>
-      <c r="R82">
-        <v>0</v>
-      </c>
-      <c r="S82">
-        <v>0</v>
-      </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,28 +13838,28 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O83">
         <v>3.7</v>
       </c>
       <c r="P83">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="Q83">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R83">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="S83">
         <v>1.17</v>
       </c>
       <c r="T83">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="U83">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V83">
         <v>1.7</v>
@@ -13877,16 +13877,16 @@
         <v>6.5</v>
       </c>
       <c r="AA83">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB83">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AC83">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AD83">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE83">
         <v>1.29</v>
@@ -13911,7 +13911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O84">
         <v>3.9</v>
@@ -14022,13 +14022,13 @@
         <v>3.7</v>
       </c>
       <c r="U84">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V84">
         <v>1.6</v>
       </c>
       <c r="W84">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X84">
         <v>1.01</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O85">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Q85">
         <v>3.2</v>
@@ -14330,13 +14330,13 @@
         <v>1.21</v>
       </c>
       <c r="O86">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P86">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Q86">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R86">
         <v>2.7</v>
@@ -14360,10 +14360,10 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z86">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA86">
         <v>1.57</v>
@@ -14372,19 +14372,19 @@
         <v>2.25</v>
       </c>
       <c r="AC86">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="AD86">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE86">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF86">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AG86">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK86">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,68 +14486,68 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N87">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="O87">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="P87">
-        <v>7.35</v>
+        <v>2.02</v>
       </c>
       <c r="Q87">
+        <v>3.1</v>
+      </c>
+      <c r="R87">
+        <v>2.45</v>
+      </c>
+      <c r="S87">
+        <v>1.2</v>
+      </c>
+      <c r="T87">
+        <v>3.9</v>
+      </c>
+      <c r="U87">
+        <v>2.02</v>
+      </c>
+      <c r="V87">
         <v>1.67</v>
       </c>
-      <c r="R87">
-        <v>2.62</v>
-      </c>
-      <c r="S87">
-        <v>1.18</v>
-      </c>
-      <c r="T87">
-        <v>3.85</v>
-      </c>
-      <c r="U87">
-        <v>2.07</v>
-      </c>
-      <c r="V87">
-        <v>1.65</v>
-      </c>
       <c r="W87">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z87">
-        <v>5.15</v>
+        <v>5.93</v>
       </c>
       <c r="AA87">
         <v>1.44</v>
       </c>
       <c r="AB87">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="AC87">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD87">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE87">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF87">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG87">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.06</v>
+        <v>1.73</v>
       </c>
       <c r="AK87">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G88">
@@ -14649,68 +14649,68 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N88">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="O88">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="P88">
-        <v>2.02</v>
+        <v>7.35</v>
       </c>
       <c r="Q88">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="R88">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T88">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U88">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="V88">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>5.93</v>
+        <v>5.15</v>
       </c>
       <c r="AA88">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB88">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AC88">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD88">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AE88">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF88">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG88">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.73</v>
+        <v>1.06</v>
       </c>
       <c r="AK88">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="O89">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P89">
-        <v>3.52</v>
+        <v>2.35</v>
       </c>
       <c r="Q89">
-        <v>2.41</v>
+        <v>3.37</v>
       </c>
       <c r="R89">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="S89">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="T89">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="U89">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="V89">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W89">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z89">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA89">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB89">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC89">
-        <v>3.58</v>
+        <v>2.52</v>
       </c>
       <c r="AD89">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE89">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG89">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AK89">
-        <v>1.99</v>
+        <v>1.38</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,80 +14979,80 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.87</v>
+        <v>2.32</v>
       </c>
       <c r="O90">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P90">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q90">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S90">
+        <v>1.4</v>
+      </c>
+      <c r="T90">
+        <v>2.79</v>
+      </c>
+      <c r="U90">
+        <v>2.9</v>
+      </c>
+      <c r="V90">
         <v>1.35</v>
       </c>
-      <c r="T90">
-        <v>2.96</v>
-      </c>
-      <c r="U90">
-        <v>2.59</v>
-      </c>
-      <c r="V90">
-        <v>1.4</v>
-      </c>
       <c r="W90">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z90">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="AA90">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AB90">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC90">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AD90">
+        <v>1.24</v>
+      </c>
+      <c r="AE90">
+        <v>1.05</v>
+      </c>
+      <c r="AF90">
+        <v>1.8</v>
+      </c>
+      <c r="AG90">
+        <v>1.93</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
         <v>1.3</v>
       </c>
-      <c r="AE90">
-        <v>1.12</v>
-      </c>
-      <c r="AF90">
-        <v>1.7</v>
-      </c>
-      <c r="AG90">
-        <v>2.11</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.53</v>
-      </c>
       <c r="AK90">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.7</v>
+        <v>1.81</v>
       </c>
       <c r="O91">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="P91">
-        <v>2.35</v>
+        <v>3.52</v>
       </c>
       <c r="Q91">
-        <v>3.37</v>
+        <v>2.41</v>
       </c>
       <c r="R91">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S91">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="T91">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="U91">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="V91">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W91">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB91">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC91">
-        <v>2.52</v>
+        <v>3.58</v>
       </c>
       <c r="AD91">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE91">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF91">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG91">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AK91">
-        <v>1.38</v>
+        <v>1.99</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.29</v>
+        <v>1.42</v>
       </c>
       <c r="O92">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P92">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="Q92">
+        <v>2.11</v>
+      </c>
+      <c r="R92">
+        <v>2.23</v>
+      </c>
+      <c r="S92">
+        <v>1.35</v>
+      </c>
+      <c r="T92">
         <v>2.88</v>
       </c>
-      <c r="R92">
-        <v>2</v>
-      </c>
-      <c r="S92">
-        <v>1.43</v>
-      </c>
-      <c r="T92">
-        <v>2.79</v>
-      </c>
       <c r="U92">
-        <v>3.16</v>
+        <v>2.61</v>
       </c>
       <c r="V92">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W92">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z92">
-        <v>3.04</v>
+        <v>4.17</v>
       </c>
       <c r="AA92">
+        <v>1.81</v>
+      </c>
+      <c r="AB92">
         <v>2.01</v>
       </c>
-      <c r="AB92">
-        <v>1.75</v>
-      </c>
       <c r="AC92">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="AD92">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE92">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG92">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK92">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="O93">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P93">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q93">
-        <v>2.11</v>
+        <v>3.3</v>
       </c>
       <c r="R93">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S93">
         <v>1.35</v>
       </c>
       <c r="T93">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="U93">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="V93">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
-        <v>4.17</v>
+        <v>3.6</v>
       </c>
       <c r="AA93">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB93">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AC93">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AD93">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
         <v>1.12</v>
       </c>
       <c r="AF93">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG93">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="AK93">
-        <v>2.24</v>
+        <v>1.35</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15806,7 +15806,7 @@
         <v>3</v>
       </c>
       <c r="R95">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
         <v>1.25</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="O97">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P97">
         <v>4.6</v>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O98">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P98">
         <v>3.4</v>
@@ -16295,52 +16295,52 @@
         <v>2.25</v>
       </c>
       <c r="R98">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S98">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T98">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U98">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="V98">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="W98">
         <v>1.17</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z98">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="AA98">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB98">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AC98">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AD98">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE98">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF98">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG98">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16455,10 +16455,10 @@
         <v>3.14</v>
       </c>
       <c r="Q99">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R99">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="S99">
         <v>1.21</v>
@@ -16485,7 +16485,7 @@
         <v>5.45</v>
       </c>
       <c r="AA99">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB99">
         <v>2.59</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="O100">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="P100">
-        <v>3.9</v>
+        <v>2.81</v>
       </c>
       <c r="Q100">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="R100">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="S100">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T100">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U100">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="V100">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="W100">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z100">
-        <v>5.45</v>
+        <v>4.7</v>
       </c>
       <c r="AA100">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AB100">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="AC100">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD100">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AE100">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF100">
+        <v>1.45</v>
+      </c>
+      <c r="AG100">
+        <v>2.5</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
         <v>1.4</v>
       </c>
-      <c r="AG100">
-        <v>2.6</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>1.19</v>
-      </c>
       <c r="AK100">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="O101">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P101">
-        <v>2.74</v>
+        <v>2.37</v>
       </c>
       <c r="Q101">
-        <v>2.71</v>
+        <v>2.91</v>
       </c>
       <c r="R101">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S101">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T101">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="U101">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="V101">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="W101">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z101">
-        <v>4.7</v>
+        <v>6.36</v>
       </c>
       <c r="AA101">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AB101">
-        <v>2.33</v>
+        <v>2.74</v>
       </c>
       <c r="AC101">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="AD101">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AE101">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AF101">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AG101">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="O102">
         <v>3.6</v>
       </c>
       <c r="P102">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="Q102">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="R102">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S102">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T102">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="U102">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="V102">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="W102">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z102">
-        <v>6.26</v>
+        <v>4.4</v>
       </c>
       <c r="AA102">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AB102">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AC102">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AD102">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AE102">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AF102">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AG102">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="O103">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="P103">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q103">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="R103">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S103">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T103">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U103">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="V103">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="W103">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X103">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z103">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AA103">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AB103">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="AC103">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AD103">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AE103">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AF103">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AG103">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O104">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="P104">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q104">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R104">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="S104">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T104">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U104">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V104">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W104">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X104">
         <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z104">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA104">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB104">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC104">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD104">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE104">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF104">
         <v>1.36</v>
       </c>
       <c r="AG104">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,31 +17424,31 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="O105">
+        <v>3.75</v>
+      </c>
+      <c r="P105">
+        <v>3.9</v>
+      </c>
+      <c r="Q105">
+        <v>2.17</v>
+      </c>
+      <c r="R105">
+        <v>2.44</v>
+      </c>
+      <c r="S105">
+        <v>1.2</v>
+      </c>
+      <c r="T105">
         <v>4</v>
       </c>
-      <c r="P105">
-        <v>4.25</v>
-      </c>
-      <c r="Q105">
-        <v>2.1</v>
-      </c>
-      <c r="R105">
-        <v>2.45</v>
-      </c>
-      <c r="S105">
-        <v>1.18</v>
-      </c>
-      <c r="T105">
-        <v>3.98</v>
-      </c>
       <c r="U105">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="V105">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W105">
         <v>1.15</v>
@@ -17460,25 +17460,25 @@
         <v>1.08</v>
       </c>
       <c r="Z105">
-        <v>5.99</v>
+        <v>5.45</v>
       </c>
       <c r="AA105">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB105">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC105">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AD105">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AE105">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF105">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG105">
         <v>2.6</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK105">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="O106">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P106">
-        <v>2.6</v>
+        <v>4.05</v>
       </c>
       <c r="Q106">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="R106">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="S106">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T106">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="U106">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V106">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W106">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z106">
-        <v>5.15</v>
+        <v>6.14</v>
       </c>
       <c r="AA106">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB106">
         <v>2.7</v>
       </c>
       <c r="AC106">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AD106">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE106">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF106">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG106">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK106">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17823,7 +17823,7 @@
         <v>1.02</v>
       </c>
       <c r="AK107">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17928,10 +17928,10 @@
         <v>2.11</v>
       </c>
       <c r="S108">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T108">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="U108">
         <v>2.45</v>
@@ -17958,7 +17958,7 @@
         <v>1.94</v>
       </c>
       <c r="AC108">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AD108">
         <v>1.34</v>
@@ -17967,7 +17967,7 @@
         <v>1.12</v>
       </c>
       <c r="AF108">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AG108">
         <v>2.05</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,31 +18076,31 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="O109">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P109">
-        <v>4.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q109">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S109">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T109">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="U109">
-        <v>3.06</v>
+        <v>2.63</v>
       </c>
       <c r="V109">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="W109">
         <v>1.07</v>
@@ -18109,31 +18109,31 @@
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z109">
-        <v>2.98</v>
+        <v>3.58</v>
       </c>
       <c r="AA109">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AB109">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AC109">
-        <v>3.8</v>
+        <v>2.81</v>
       </c>
       <c r="AD109">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AE109">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF109">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AG109">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK109">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,31 +18402,31 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="O111">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="Q111">
-        <v>3.22</v>
+        <v>2.38</v>
       </c>
       <c r="R111">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T111">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="U111">
-        <v>2.63</v>
+        <v>3.06</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W111">
         <v>1.07</v>
@@ -18435,31 +18435,31 @@
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z111">
-        <v>3.58</v>
+        <v>2.98</v>
       </c>
       <c r="AA111">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="AB111">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AC111">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="AD111">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AE111">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF111">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AG111">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="P112">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="O113">
         <v>3.1</v>
@@ -18767,7 +18767,7 @@
         <v>3.18</v>
       </c>
       <c r="AA113">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AB113">
         <v>1.76</v>
@@ -18782,7 +18782,7 @@
         <v>1.09</v>
       </c>
       <c r="AF113">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG113">
         <v>1.96</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="O114">
         <v>3.25</v>
@@ -18900,7 +18900,7 @@
         <v>2.3</v>
       </c>
       <c r="Q114">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="R114">
         <v>2.08</v>
@@ -18909,7 +18909,7 @@
         <v>1.3</v>
       </c>
       <c r="T114">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="U114">
         <v>2.75</v>
@@ -18927,7 +18927,7 @@
         <v>1.25</v>
       </c>
       <c r="Z114">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA114">
         <v>1.84</v>
@@ -18936,7 +18936,7 @@
         <v>1.92</v>
       </c>
       <c r="AC114">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="AD114">
         <v>1.3</v>
@@ -18964,7 +18964,7 @@
         <v>1.3</v>
       </c>
       <c r="AK114">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19066,7 +19066,7 @@
         <v>4.44</v>
       </c>
       <c r="R115">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="S115">
         <v>1.33</v>
@@ -19075,10 +19075,10 @@
         <v>2.86</v>
       </c>
       <c r="U115">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="V115">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W115">
         <v>1.08</v>
@@ -19093,10 +19093,10 @@
         <v>3.8</v>
       </c>
       <c r="AA115">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB115">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC115">
         <v>3.05</v>
@@ -19247,7 +19247,7 @@
         <v>1.05</v>
       </c>
       <c r="X116">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y116">
         <v>1.28</v>
@@ -19271,7 +19271,7 @@
         <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG116">
         <v>1.95</v>
@@ -19380,19 +19380,19 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O117">
         <v>5.7</v>
       </c>
       <c r="P117">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q117">
         <v>1.77</v>
       </c>
       <c r="R117">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="S117">
         <v>1.11</v>
@@ -19425,10 +19425,10 @@
         <v>3.5</v>
       </c>
       <c r="AC117">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AD117">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AE117">
         <v>1.52</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AK117">
         <v>3.12</v>
@@ -19715,7 +19715,7 @@
         <v>3.1</v>
       </c>
       <c r="Q119">
-        <v>2.82</v>
+        <v>2.49</v>
       </c>
       <c r="R119">
         <v>2.13</v>
@@ -19724,7 +19724,7 @@
         <v>1.3</v>
       </c>
       <c r="T119">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U119">
         <v>2.42</v>
@@ -20536,22 +20536,22 @@
         <v>2.12</v>
       </c>
       <c r="S124">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T124">
         <v>2.99</v>
       </c>
       <c r="U124">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="V124">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W124">
         <v>1.06</v>
       </c>
       <c r="X124">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y124">
         <v>1.3</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK124">
         <v>1.73</v>
@@ -20693,10 +20693,10 @@
         <v>2.64</v>
       </c>
       <c r="Q125">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R125">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S125">
         <v>1.3</v>
@@ -20708,7 +20708,7 @@
         <v>2.47</v>
       </c>
       <c r="V125">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W125">
         <v>1.1</v>
@@ -20738,7 +20738,7 @@
         <v>1.12</v>
       </c>
       <c r="AF125">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG125">
         <v>2.15</v>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AK125">
         <v>1.44</v>
@@ -20856,10 +20856,10 @@
         <v>2.25</v>
       </c>
       <c r="Q126">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="R126">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S126">
         <v>1.3</v>
@@ -21176,16 +21176,16 @@
         <v>1.57</v>
       </c>
       <c r="O128">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P128">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q128">
         <v>2.3</v>
       </c>
       <c r="R128">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S128">
         <v>1.46</v>
@@ -21194,7 +21194,7 @@
         <v>2.88</v>
       </c>
       <c r="U128">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V128">
         <v>1.38</v>
@@ -21212,10 +21212,10 @@
         <v>3.25</v>
       </c>
       <c r="AA128">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AB128">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC128">
         <v>3.5</v>
@@ -21224,13 +21224,13 @@
         <v>1.29</v>
       </c>
       <c r="AE128">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF128">
         <v>1.91</v>
       </c>
       <c r="AG128">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>1.21</v>
       </c>
       <c r="AK128">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21339,7 +21339,7 @@
         <v>4.75</v>
       </c>
       <c r="O129">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P129">
         <v>1.6</v>
@@ -21378,10 +21378,10 @@
         <v>1.49</v>
       </c>
       <c r="AB129">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC129">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AD129">
         <v>1.62</v>
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O130">
         <v>3</v>
@@ -21671,10 +21671,10 @@
         <v>5</v>
       </c>
       <c r="Q131">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R131">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S131">
         <v>1.36</v>
@@ -21704,7 +21704,7 @@
         <v>1.93</v>
       </c>
       <c r="AB131">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC131">
         <v>3.2</v>
@@ -21735,7 +21735,7 @@
         <v>1.13</v>
       </c>
       <c r="AK131">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21988,16 +21988,16 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="O133">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P133">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="Q133">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="R133">
         <v>2.07</v>
@@ -22006,13 +22006,13 @@
         <v>1.4</v>
       </c>
       <c r="T133">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="U133">
         <v>2.75</v>
       </c>
       <c r="V133">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W133">
         <v>1.06</v>
@@ -22024,7 +22024,7 @@
         <v>1.29</v>
       </c>
       <c r="Z133">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="AA133">
         <v>2.02</v>
@@ -22045,7 +22045,7 @@
         <v>1.83</v>
       </c>
       <c r="AG133">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>4.1</v>
       </c>
       <c r="AA134">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB134">
         <v>2.04</v>
@@ -22317,7 +22317,7 @@
         <v>1.37</v>
       </c>
       <c r="O135">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="P135">
         <v>7.75</v>
@@ -22341,7 +22341,7 @@
         <v>1.62</v>
       </c>
       <c r="W135">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X135">
         <v>1</v>
@@ -22359,7 +22359,7 @@
         <v>2.55</v>
       </c>
       <c r="AC135">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AD135">
         <v>1.57</v>
@@ -22368,7 +22368,7 @@
         <v>1.22</v>
       </c>
       <c r="AF135">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG135">
         <v>2.05</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK135">
         <v>3.1</v>
@@ -22477,7 +22477,7 @@
         </is>
       </c>
       <c r="N136">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O136">
         <v>3.3</v>
@@ -22522,7 +22522,7 @@
         <v>1.86</v>
       </c>
       <c r="AC136">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AD136">
         <v>1.31</v>
@@ -22812,7 +22812,7 @@
         <v>2.8</v>
       </c>
       <c r="Q138">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="R138">
         <v>2</v>
@@ -22848,10 +22848,10 @@
         <v>1.67</v>
       </c>
       <c r="AC138">
-        <v>3.68</v>
+        <v>3.91</v>
       </c>
       <c r="AD138">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE138">
         <v>1.03</v>
@@ -22876,7 +22876,7 @@
         <v>1.26</v>
       </c>
       <c r="AK138">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AL138">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
         <v>3.12</v>
@@ -1172,7 +1172,7 @@
         <v>2.43</v>
       </c>
       <c r="AD5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE5">
         <v>1.17</v>
@@ -1453,13 +1453,13 @@
         <v>4.4</v>
       </c>
       <c r="O7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P7">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="R7">
         <v>2.65</v>
@@ -1489,22 +1489,22 @@
         <v>4.85</v>
       </c>
       <c r="AA7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB7">
         <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD7">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE7">
         <v>1.25</v>
       </c>
       <c r="AF7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
         <v>2.48</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O11">
         <v>4.6</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,65 +3243,65 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P18">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q18">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="R18">
+        <v>2.4</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
+        <v>3.3</v>
+      </c>
+      <c r="U18">
+        <v>2.29</v>
+      </c>
+      <c r="V18">
+        <v>1.53</v>
+      </c>
+      <c r="W18">
+        <v>1.13</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.2</v>
+      </c>
+      <c r="Z18">
+        <v>4.5</v>
+      </c>
+      <c r="AA18">
+        <v>1.57</v>
+      </c>
+      <c r="AB18">
+        <v>2.2</v>
+      </c>
+      <c r="AC18">
+        <v>2.55</v>
+      </c>
+      <c r="AD18">
+        <v>1.5</v>
+      </c>
+      <c r="AE18">
+        <v>1.2</v>
+      </c>
+      <c r="AF18">
+        <v>1.6</v>
+      </c>
+      <c r="AG18">
         <v>2.25</v>
       </c>
-      <c r="S18">
-        <v>1.34</v>
-      </c>
-      <c r="T18">
-        <v>3.02</v>
-      </c>
-      <c r="U18">
-        <v>2.59</v>
-      </c>
-      <c r="V18">
-        <v>1.44</v>
-      </c>
-      <c r="W18">
-        <v>1.09</v>
-      </c>
-      <c r="X18">
-        <v>1.03</v>
-      </c>
-      <c r="Y18">
-        <v>1.22</v>
-      </c>
-      <c r="Z18">
-        <v>4.2</v>
-      </c>
-      <c r="AA18">
-        <v>1.81</v>
-      </c>
-      <c r="AB18">
-        <v>1.98</v>
-      </c>
-      <c r="AC18">
-        <v>2.88</v>
-      </c>
-      <c r="AD18">
-        <v>1.4</v>
-      </c>
-      <c r="AE18">
-        <v>1.14</v>
-      </c>
-      <c r="AF18">
-        <v>1.62</v>
-      </c>
-      <c r="AG18">
-        <v>2.2</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q20">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U20">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="V20">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB20">
+        <v>1.98</v>
+      </c>
+      <c r="AC20">
+        <v>2.88</v>
+      </c>
+      <c r="AD20">
+        <v>1.4</v>
+      </c>
+      <c r="AE20">
+        <v>1.14</v>
+      </c>
+      <c r="AF20">
+        <v>1.62</v>
+      </c>
+      <c r="AG20">
         <v>2.2</v>
       </c>
-      <c r="AC20">
-        <v>2.55</v>
-      </c>
-      <c r="AD20">
-        <v>1.5</v>
-      </c>
-      <c r="AE20">
-        <v>1.2</v>
-      </c>
-      <c r="AF20">
-        <v>1.6</v>
-      </c>
-      <c r="AG20">
-        <v>2.25</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4115,7 +4115,7 @@
         <v>1.7</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -4236,16 +4236,16 @@
         <v>1.93</v>
       </c>
       <c r="S24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="U24">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="V24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4254,10 +4254,10 @@
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z24">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AA24">
         <v>2.19</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O25">
         <v>3.1</v>
@@ -4553,7 +4553,7 @@
         <v>6.05</v>
       </c>
       <c r="P26">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB26">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O27">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P27">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -4767,7 +4767,7 @@
         <v>2.39</v>
       </c>
       <c r="AG27">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.4</v>
       </c>
       <c r="AK27">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="O28">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P28">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q28">
         <v>2.84</v>
@@ -4894,7 +4894,7 @@
         <v>2.19</v>
       </c>
       <c r="U28">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V28">
         <v>1.25</v>
@@ -4924,7 +4924,7 @@
         <v>1.1</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
         <v>2.2</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O29">
         <v>3</v>
@@ -5051,7 +5051,7 @@
         <v>1.91</v>
       </c>
       <c r="S29">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="T29">
         <v>2.23</v>
@@ -5075,10 +5075,10 @@
         <v>2.45</v>
       </c>
       <c r="AA29">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AB29">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -5208,16 +5208,16 @@
         <v>2.41</v>
       </c>
       <c r="Q30">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="R30">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S30">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="T30">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -5232,10 +5232,10 @@
         <v>1.13</v>
       </c>
       <c r="Y30">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z30">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA30">
         <v>3</v>
@@ -5272,7 +5272,7 @@
         <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>3.94</v>
+        <v>2.87</v>
       </c>
       <c r="Q31">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="R31">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
+        <v>1.3</v>
+      </c>
+      <c r="T31">
+        <v>3.2</v>
+      </c>
+      <c r="U31">
+        <v>2.45</v>
+      </c>
+      <c r="V31">
+        <v>1.44</v>
+      </c>
+      <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>1.2</v>
+      </c>
+      <c r="Z31">
+        <v>3.76</v>
+      </c>
+      <c r="AA31">
+        <v>1.73</v>
+      </c>
+      <c r="AB31">
+        <v>2</v>
+      </c>
+      <c r="AC31">
+        <v>2.78</v>
+      </c>
+      <c r="AD31">
         <v>1.37</v>
       </c>
-      <c r="T31">
-        <v>2.69</v>
-      </c>
-      <c r="U31">
-        <v>2.77</v>
-      </c>
-      <c r="V31">
-        <v>1.35</v>
-      </c>
-      <c r="W31">
-        <v>1.07</v>
-      </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>1.3</v>
-      </c>
-      <c r="Z31">
-        <v>3.08</v>
-      </c>
-      <c r="AA31">
-        <v>2</v>
-      </c>
-      <c r="AB31">
-        <v>1.8</v>
-      </c>
-      <c r="AC31">
-        <v>3.46</v>
-      </c>
-      <c r="AD31">
-        <v>1.24</v>
-      </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P32">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q32">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="V32">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>4.11</v>
+        <v>3.08</v>
       </c>
       <c r="AA32">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB32">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AC32">
-        <v>2.69</v>
+        <v>3.46</v>
       </c>
       <c r="AD32">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="O36">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P36">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="S36">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="T36">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U36">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="V36">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W36">
         <v>1.02</v>
       </c>
       <c r="X36">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y36">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="Z36">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="AA36">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AB36">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AC36">
-        <v>4.85</v>
+        <v>5.7</v>
       </c>
       <c r="AD36">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF36">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AG36">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK36">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="O37">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P37">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q37">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="R37">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="S37">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="T37">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U37">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="V37">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W37">
         <v>1.02</v>
       </c>
       <c r="X37">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="Z37">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="AA37">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="AB37">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC37">
-        <v>5.7</v>
+        <v>4.85</v>
       </c>
       <c r="AD37">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF37">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AG37">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK37">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         <v>2.1</v>
       </c>
       <c r="V38">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W38">
         <v>1.18</v>
@@ -6551,7 +6551,7 @@
         <v>1.96</v>
       </c>
       <c r="AD38">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE38">
         <v>1.28</v>
@@ -6666,28 +6666,28 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O39">
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="Q39">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="R39">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
         <v>1.39</v>
       </c>
       <c r="T39">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="U39">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="V39">
         <v>1.36</v>
@@ -6711,10 +6711,10 @@
         <v>1.72</v>
       </c>
       <c r="AC39">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE39">
         <v>1.06</v>
@@ -6995,10 +6995,10 @@
         <v>1.85</v>
       </c>
       <c r="O41">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -7013,7 +7013,7 @@
         <v>3.14</v>
       </c>
       <c r="U41">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="V41">
         <v>1.46</v>
@@ -7022,7 +7022,7 @@
         <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
         <v>1.2</v>
@@ -7034,7 +7034,7 @@
         <v>1.81</v>
       </c>
       <c r="AB41">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AC41">
         <v>2.88</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="O42">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P42">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Q42">
         <v>1.85</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="O43">
         <v>3.5</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="O44">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="P44">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q44">
         <v>2.38</v>
@@ -7505,10 +7505,10 @@
         <v>2.33</v>
       </c>
       <c r="V44">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W44">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X44">
         <v>1.02</v>
@@ -7517,41 +7517,41 @@
         <v>1.12</v>
       </c>
       <c r="Z44">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AA44">
         <v>1.54</v>
       </c>
       <c r="AB44">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AC44">
         <v>2.33</v>
       </c>
       <c r="AD44">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AE44">
+        <v>1.23</v>
+      </c>
+      <c r="AF44">
+        <v>1.49</v>
+      </c>
+      <c r="AG44">
+        <v>2.38</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.22</v>
-      </c>
-      <c r="AF44">
-        <v>1.46</v>
-      </c>
-      <c r="AG44">
-        <v>2.45</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.3</v>
       </c>
       <c r="AK44">
         <v>1.83</v>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O45">
         <v>3.4</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="O50">
-        <v>3.31</v>
+        <v>3.48</v>
       </c>
       <c r="P50">
-        <v>2.66</v>
+        <v>3.88</v>
       </c>
       <c r="Q50">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
         <v>1.36</v>
@@ -8480,59 +8480,59 @@
         <v>2.88</v>
       </c>
       <c r="U50">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V50">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>3.19</v>
+        <v>3.46</v>
       </c>
       <c r="AA50">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB50">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC50">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD50">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG50">
+        <v>1.9</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.2</v>
+      </c>
+      <c r="AK50">
         <v>2</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.26</v>
-      </c>
-      <c r="AK50">
-        <v>1.4</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="O51">
-        <v>3.48</v>
+        <v>3.31</v>
       </c>
       <c r="P51">
-        <v>3.88</v>
+        <v>2.66</v>
       </c>
       <c r="Q51">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S51">
         <v>1.36</v>
@@ -8643,43 +8643,43 @@
         <v>2.88</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V51">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z51">
-        <v>3.46</v>
+        <v>3.19</v>
       </c>
       <c r="AA51">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB51">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC51">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O52">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="P52">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB52">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O53">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
         <v>3.35</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="O56">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P56">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q56">
         <v>2.05</v>
       </c>
       <c r="R56">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9458,59 +9458,59 @@
         <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V56">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
+        <v>1.18</v>
+      </c>
+      <c r="Z56">
+        <v>3.9</v>
+      </c>
+      <c r="AA56">
+        <v>1.67</v>
+      </c>
+      <c r="AB56">
+        <v>2.04</v>
+      </c>
+      <c r="AC56">
+        <v>2.66</v>
+      </c>
+      <c r="AD56">
+        <v>1.4</v>
+      </c>
+      <c r="AE56">
+        <v>1.11</v>
+      </c>
+      <c r="AF56">
+        <v>1.67</v>
+      </c>
+      <c r="AG56">
+        <v>2.05</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
         <v>1.16</v>
       </c>
-      <c r="Z56">
-        <v>4.15</v>
-      </c>
-      <c r="AA56">
-        <v>1.61</v>
-      </c>
-      <c r="AB56">
-        <v>2.17</v>
-      </c>
-      <c r="AC56">
-        <v>2.43</v>
-      </c>
-      <c r="AD56">
-        <v>1.44</v>
-      </c>
-      <c r="AE56">
-        <v>1.15</v>
-      </c>
-      <c r="AF56">
-        <v>1.62</v>
-      </c>
-      <c r="AG56">
-        <v>2.12</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.11</v>
-      </c>
       <c r="AK56">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="O57">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q57">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R57">
         <v>2.3</v>
       </c>
       <c r="S57">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T57">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U57">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="V57">
         <v>1.53</v>
       </c>
       <c r="W57">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
         <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA57">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB57">
         <v>2.22</v>
       </c>
       <c r="AC57">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD57">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE57">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF57">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG57">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="O58">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="P58">
-        <v>2.95</v>
+        <v>5.4</v>
       </c>
       <c r="Q58">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="R58">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S58">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T58">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="U58">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="V58">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W58">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z58">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA58">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB58">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AC58">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD58">
         <v>1.44</v>
       </c>
       <c r="AE58">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF58">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AG58">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK58">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="O59">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P59">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q59">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="R59">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U59">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V59">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W59">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z59">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA59">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AB59">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="AC59">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AD59">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE59">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF59">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG59">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O61">
         <v>3.1</v>
       </c>
       <c r="P61">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q61">
         <v>3.7</v>
@@ -10291,7 +10291,7 @@
         <v>3</v>
       </c>
       <c r="AA61">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB61">
         <v>1.66</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="O64">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="P64">
-        <v>4.55</v>
+        <v>1.55</v>
       </c>
       <c r="Q64">
-        <v>2.23</v>
+        <v>4.18</v>
       </c>
       <c r="R64">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="S64">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="T64">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="U64">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="V64">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="W64">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z64">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AA64">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AB64">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AC64">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="AD64">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AE64">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AF64">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG64">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK64">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
+        <v>1.5</v>
+      </c>
+      <c r="O65">
+        <v>4.3</v>
+      </c>
+      <c r="P65">
+        <v>4.6</v>
+      </c>
+      <c r="Q65">
+        <v>1.92</v>
+      </c>
+      <c r="R65">
+        <v>2.84</v>
+      </c>
+      <c r="S65">
+        <v>1.2</v>
+      </c>
+      <c r="T65">
         <v>4.5</v>
       </c>
-      <c r="O65">
-        <v>4.2</v>
-      </c>
-      <c r="P65">
-        <v>1.55</v>
-      </c>
-      <c r="Q65">
-        <v>4.18</v>
-      </c>
-      <c r="R65">
-        <v>2.38</v>
-      </c>
-      <c r="S65">
-        <v>1.19</v>
-      </c>
-      <c r="T65">
-        <v>3.8</v>
-      </c>
       <c r="U65">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="V65">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z65">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AA65">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AB65">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="AC65">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="AD65">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AE65">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AF65">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG65">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.15</v>
       </c>
       <c r="AK65">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="O66">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="P66">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="Q66">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="R66">
-        <v>2.84</v>
+        <v>2.37</v>
       </c>
       <c r="S66">
+        <v>1.37</v>
+      </c>
+      <c r="T66">
+        <v>2.76</v>
+      </c>
+      <c r="U66">
+        <v>2.75</v>
+      </c>
+      <c r="V66">
+        <v>1.4</v>
+      </c>
+      <c r="W66">
+        <v>1.06</v>
+      </c>
+      <c r="X66">
+        <v>1.03</v>
+      </c>
+      <c r="Y66">
+        <v>1.28</v>
+      </c>
+      <c r="Z66">
+        <v>3.6</v>
+      </c>
+      <c r="AA66">
+        <v>1.85</v>
+      </c>
+      <c r="AB66">
+        <v>1.88</v>
+      </c>
+      <c r="AC66">
+        <v>3.25</v>
+      </c>
+      <c r="AD66">
+        <v>1.34</v>
+      </c>
+      <c r="AE66">
+        <v>1.07</v>
+      </c>
+      <c r="AF66">
+        <v>1.75</v>
+      </c>
+      <c r="AG66">
+        <v>1.9</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.2</v>
       </c>
-      <c r="T66">
-        <v>4.5</v>
-      </c>
-      <c r="U66">
-        <v>2.01</v>
-      </c>
-      <c r="V66">
-        <v>1.78</v>
-      </c>
-      <c r="W66">
-        <v>1.22</v>
-      </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.06</v>
-      </c>
-      <c r="Z66">
-        <v>6</v>
-      </c>
-      <c r="AA66">
-        <v>1.33</v>
-      </c>
-      <c r="AB66">
-        <v>2.81</v>
-      </c>
-      <c r="AC66">
-        <v>1.9</v>
-      </c>
-      <c r="AD66">
-        <v>1.87</v>
-      </c>
-      <c r="AE66">
-        <v>1.36</v>
-      </c>
-      <c r="AF66">
-        <v>1.5</v>
-      </c>
-      <c r="AG66">
-        <v>2.63</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.15</v>
-      </c>
       <c r="AK66">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,31 +11230,31 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q67">
-        <v>3.56</v>
+        <v>3.68</v>
       </c>
       <c r="R67">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S67">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U67">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V67">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W67">
         <v>1.14</v>
@@ -11263,31 +11263,31 @@
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z67">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA67">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB67">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AC67">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD67">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AE67">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF67">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AK67">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="O68">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P68">
         <v>2.16</v>
@@ -11466,7 +11466,7 @@
         <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11885,7 +11885,7 @@
         <v>1.27</v>
       </c>
       <c r="O71">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P71">
         <v>7</v>
@@ -11939,7 +11939,7 @@
         <v>1.62</v>
       </c>
       <c r="AG71">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.07</v>
+        <v>3.4</v>
       </c>
       <c r="AK71">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12078,13 +12078,13 @@
         <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z72">
         <v>2.7</v>
       </c>
       <c r="AA72">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="AB72">
         <v>1.6</v>
@@ -12093,7 +12093,7 @@
         <v>4.15</v>
       </c>
       <c r="AD72">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE72">
         <v>1.01</v>
@@ -12102,7 +12102,7 @@
         <v>1.98</v>
       </c>
       <c r="AG72">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>12.1</v>
+        <v>22</v>
       </c>
       <c r="O76">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="P76">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Q76">
-        <v>11.2</v>
+        <v>14.7</v>
       </c>
       <c r="R76">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="S76">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T76">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="U76">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="V76">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="W76">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X76">
         <v>1</v>
       </c>
       <c r="Y76">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z76">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA76">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AB76">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AC76">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AD76">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AE76">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AF76">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="AG76">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,68 +14486,68 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N87">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="O87">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="P87">
-        <v>2.02</v>
+        <v>7.35</v>
       </c>
       <c r="Q87">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="R87">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T87">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U87">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="V87">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W87">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z87">
-        <v>5.93</v>
+        <v>5.15</v>
       </c>
       <c r="AA87">
         <v>1.44</v>
       </c>
       <c r="AB87">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AC87">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD87">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AE87">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF87">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.73</v>
+        <v>1.06</v>
       </c>
       <c r="AK87">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G88">
@@ -14649,68 +14649,68 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N88">
-        <v>1.33</v>
+        <v>3.05</v>
       </c>
       <c r="O88">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="P88">
-        <v>7.35</v>
+        <v>2.04</v>
       </c>
       <c r="Q88">
+        <v>3.1</v>
+      </c>
+      <c r="R88">
+        <v>2.45</v>
+      </c>
+      <c r="S88">
+        <v>1.2</v>
+      </c>
+      <c r="T88">
+        <v>3.9</v>
+      </c>
+      <c r="U88">
+        <v>2.02</v>
+      </c>
+      <c r="V88">
         <v>1.67</v>
       </c>
-      <c r="R88">
-        <v>2.62</v>
-      </c>
-      <c r="S88">
-        <v>1.18</v>
-      </c>
-      <c r="T88">
-        <v>3.85</v>
-      </c>
-      <c r="U88">
-        <v>2.07</v>
-      </c>
-      <c r="V88">
-        <v>1.65</v>
-      </c>
       <c r="W88">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z88">
-        <v>5.15</v>
+        <v>5.93</v>
       </c>
       <c r="AA88">
         <v>1.44</v>
       </c>
       <c r="AB88">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="AC88">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD88">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE88">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF88">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG88">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.06</v>
+        <v>1.73</v>
       </c>
       <c r="AK88">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.7</v>
+        <v>1.81</v>
       </c>
       <c r="O89">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P89">
-        <v>2.35</v>
+        <v>3.52</v>
       </c>
       <c r="Q89">
-        <v>3.37</v>
+        <v>2.41</v>
       </c>
       <c r="R89">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S89">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="T89">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="U89">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="V89">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W89">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z89">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA89">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB89">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC89">
-        <v>2.52</v>
+        <v>3.58</v>
       </c>
       <c r="AD89">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF89">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG89">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AK89">
-        <v>1.38</v>
+        <v>1.99</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,80 +14979,80 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.32</v>
+        <v>2.87</v>
       </c>
       <c r="O90">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q90">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="R90">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S90">
+        <v>1.35</v>
+      </c>
+      <c r="T90">
+        <v>2.96</v>
+      </c>
+      <c r="U90">
+        <v>2.59</v>
+      </c>
+      <c r="V90">
         <v>1.4</v>
       </c>
-      <c r="T90">
-        <v>2.79</v>
-      </c>
-      <c r="U90">
-        <v>2.9</v>
-      </c>
-      <c r="V90">
+      <c r="W90">
+        <v>1.08</v>
+      </c>
+      <c r="X90">
+        <v>1.01</v>
+      </c>
+      <c r="Y90">
+        <v>1.25</v>
+      </c>
+      <c r="Z90">
+        <v>3.6</v>
+      </c>
+      <c r="AA90">
+        <v>1.95</v>
+      </c>
+      <c r="AB90">
+        <v>1.83</v>
+      </c>
+      <c r="AC90">
+        <v>3.25</v>
+      </c>
+      <c r="AD90">
+        <v>1.3</v>
+      </c>
+      <c r="AE90">
+        <v>1.12</v>
+      </c>
+      <c r="AF90">
+        <v>1.7</v>
+      </c>
+      <c r="AG90">
+        <v>2.11</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
+        <v>1.53</v>
+      </c>
+      <c r="AK90">
         <v>1.35</v>
-      </c>
-      <c r="W90">
-        <v>1.07</v>
-      </c>
-      <c r="X90">
-        <v>1.02</v>
-      </c>
-      <c r="Y90">
-        <v>1.29</v>
-      </c>
-      <c r="Z90">
-        <v>3.04</v>
-      </c>
-      <c r="AA90">
-        <v>2.01</v>
-      </c>
-      <c r="AB90">
-        <v>1.75</v>
-      </c>
-      <c r="AC90">
-        <v>3.34</v>
-      </c>
-      <c r="AD90">
-        <v>1.24</v>
-      </c>
-      <c r="AE90">
-        <v>1.05</v>
-      </c>
-      <c r="AF90">
-        <v>1.8</v>
-      </c>
-      <c r="AG90">
-        <v>1.93</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.3</v>
-      </c>
-      <c r="AK90">
-        <v>1.62</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="O91">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P91">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="Q91">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="R91">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S91">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
+        <v>2.79</v>
+      </c>
+      <c r="U91">
         <v>2.9</v>
       </c>
-      <c r="U91">
-        <v>2.75</v>
-      </c>
       <c r="V91">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z91">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA91">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB91">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC91">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD91">
+        <v>1.24</v>
+      </c>
+      <c r="AE91">
+        <v>1.05</v>
+      </c>
+      <c r="AF91">
+        <v>1.8</v>
+      </c>
+      <c r="AG91">
+        <v>1.93</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
         <v>1.3</v>
       </c>
-      <c r="AE91">
-        <v>1.1</v>
-      </c>
-      <c r="AF91">
-        <v>1.83</v>
-      </c>
-      <c r="AG91">
-        <v>1.85</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>1.21</v>
-      </c>
       <c r="AK91">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.42</v>
+        <v>2.7</v>
       </c>
       <c r="O92">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>5.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q92">
-        <v>2.11</v>
+        <v>3.37</v>
       </c>
       <c r="R92">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="S92">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="T92">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="U92">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
       <c r="V92">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W92">
         <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="AA92">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB92">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AC92">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="AD92">
         <v>1.4</v>
       </c>
       <c r="AE92">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF92">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG92">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AK92">
-        <v>2.23</v>
+        <v>1.38</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.87</v>
+        <v>1.42</v>
       </c>
       <c r="O93">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P93">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="Q93">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="R93">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="S93">
         <v>1.35</v>
       </c>
       <c r="T93">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U93">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="V93">
+        <v>1.5</v>
+      </c>
+      <c r="W93">
+        <v>1.11</v>
+      </c>
+      <c r="X93">
+        <v>1.02</v>
+      </c>
+      <c r="Y93">
+        <v>1.18</v>
+      </c>
+      <c r="Z93">
+        <v>4.17</v>
+      </c>
+      <c r="AA93">
+        <v>1.81</v>
+      </c>
+      <c r="AB93">
+        <v>2.01</v>
+      </c>
+      <c r="AC93">
+        <v>2.88</v>
+      </c>
+      <c r="AD93">
         <v>1.4</v>
-      </c>
-      <c r="W93">
-        <v>1.08</v>
-      </c>
-      <c r="X93">
-        <v>1.01</v>
-      </c>
-      <c r="Y93">
-        <v>1.25</v>
-      </c>
-      <c r="Z93">
-        <v>3.6</v>
-      </c>
-      <c r="AA93">
-        <v>1.95</v>
-      </c>
-      <c r="AB93">
-        <v>1.83</v>
-      </c>
-      <c r="AC93">
-        <v>3.25</v>
-      </c>
-      <c r="AD93">
-        <v>1.3</v>
       </c>
       <c r="AE93">
         <v>1.12</v>
       </c>
       <c r="AF93">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG93">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AK93">
-        <v>1.35</v>
+        <v>2.23</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16011,7 +16011,7 @@
         <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG96">
         <v>2.15</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="O97">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="P97">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q97">
         <v>2.04</v>
@@ -16159,7 +16159,7 @@
         <v>5.89</v>
       </c>
       <c r="AA97">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB97">
         <v>2.66</v>
@@ -16177,7 +16177,7 @@
         <v>1.45</v>
       </c>
       <c r="AG97">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.15</v>
       </c>
       <c r="AK97">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="O99">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P99">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="Q99">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="R99">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="S99">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T99">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="U99">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V99">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W99">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X99">
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z99">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="AA99">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB99">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC99">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD99">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE99">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF99">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG99">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK99">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O100">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="P100">
-        <v>2.81</v>
+        <v>3.9</v>
       </c>
       <c r="Q100">
-        <v>2.71</v>
+        <v>2.17</v>
       </c>
       <c r="R100">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T100">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="U100">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="V100">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="W100">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z100">
-        <v>4.7</v>
+        <v>5.45</v>
       </c>
       <c r="AA100">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AB100">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="AC100">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AD100">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AE100">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF100">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG100">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AK100">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="P102">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q102">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="R102">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S102">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T102">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U102">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="V102">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="W102">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z102">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA102">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AB102">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AC102">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AD102">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AE102">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AF102">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AG102">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O103">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="P103">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="Q103">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="R103">
         <v>2.45</v>
       </c>
       <c r="S103">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T103">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="U103">
         <v>2.1</v>
       </c>
       <c r="V103">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W103">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
         <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z103">
-        <v>5.8</v>
+        <v>5.45</v>
       </c>
       <c r="AA103">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB103">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AC103">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AD103">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE103">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF103">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG103">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK103">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O104">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="P104">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="Q104">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="R104">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="S104">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T104">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U104">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="V104">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="W104">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X104">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z104">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="AA104">
+        <v>1.55</v>
+      </c>
+      <c r="AB104">
+        <v>2.33</v>
+      </c>
+      <c r="AC104">
+        <v>2.33</v>
+      </c>
+      <c r="AD104">
+        <v>1.48</v>
+      </c>
+      <c r="AE104">
+        <v>1.16</v>
+      </c>
+      <c r="AF104">
+        <v>1.45</v>
+      </c>
+      <c r="AG104">
+        <v>2.5</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.4</v>
       </c>
-      <c r="AB104">
-        <v>2.7</v>
-      </c>
-      <c r="AC104">
-        <v>2.05</v>
-      </c>
-      <c r="AD104">
-        <v>1.71</v>
-      </c>
-      <c r="AE104">
-        <v>1.26</v>
-      </c>
-      <c r="AF104">
-        <v>1.36</v>
-      </c>
-      <c r="AG104">
-        <v>2.81</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.22</v>
-      </c>
       <c r="AK104">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="O105">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P105">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q105">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="R105">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="S105">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T105">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U105">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="V105">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="W105">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z105">
-        <v>5.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA105">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="AB105">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AC105">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AD105">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AE105">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF105">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AG105">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,31 +18076,31 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="O109">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P109">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="Q109">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="R109">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S109">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T109">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="U109">
-        <v>2.63</v>
+        <v>3.06</v>
       </c>
       <c r="V109">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W109">
         <v>1.07</v>
@@ -18109,31 +18109,31 @@
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z109">
-        <v>3.58</v>
+        <v>2.98</v>
       </c>
       <c r="AA109">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AB109">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AC109">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="AD109">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AE109">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF109">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AG109">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
+        <v>2.5</v>
+      </c>
+      <c r="O110">
+        <v>3.1</v>
+      </c>
+      <c r="P110">
+        <v>2.45</v>
+      </c>
+      <c r="Q110">
+        <v>3.1</v>
+      </c>
+      <c r="R110">
+        <v>2.15</v>
+      </c>
+      <c r="S110">
+        <v>1.36</v>
+      </c>
+      <c r="T110">
+        <v>2.82</v>
+      </c>
+      <c r="U110">
+        <v>2.63</v>
+      </c>
+      <c r="V110">
+        <v>1.44</v>
+      </c>
+      <c r="W110">
+        <v>1.07</v>
+      </c>
+      <c r="X110">
+        <v>1.01</v>
+      </c>
+      <c r="Y110">
+        <v>1.22</v>
+      </c>
+      <c r="Z110">
+        <v>3.58</v>
+      </c>
+      <c r="AA110">
+        <v>1.8</v>
+      </c>
+      <c r="AB110">
         <v>2</v>
       </c>
-      <c r="O110">
-        <v>3.2</v>
-      </c>
-      <c r="P110">
-        <v>3.3</v>
-      </c>
-      <c r="Q110">
-        <v>2.4</v>
-      </c>
-      <c r="R110">
-        <v>2.11</v>
-      </c>
-      <c r="S110">
+      <c r="AC110">
+        <v>2.81</v>
+      </c>
+      <c r="AD110">
         <v>1.33</v>
       </c>
-      <c r="T110">
-        <v>2.9</v>
-      </c>
-      <c r="U110">
-        <v>2.62</v>
-      </c>
-      <c r="V110">
-        <v>1.42</v>
-      </c>
-      <c r="W110">
-        <v>1.05</v>
-      </c>
-      <c r="X110">
-        <v>1.04</v>
-      </c>
-      <c r="Y110">
-        <v>1.29</v>
-      </c>
-      <c r="Z110">
-        <v>3.6</v>
-      </c>
-      <c r="AA110">
-        <v>1.84</v>
-      </c>
-      <c r="AB110">
-        <v>1.83</v>
-      </c>
-      <c r="AC110">
-        <v>3.08</v>
-      </c>
-      <c r="AD110">
-        <v>1.28</v>
-      </c>
       <c r="AE110">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG110">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.29</v>
       </c>
       <c r="AK110">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="O111">
         <v>3.2</v>
       </c>
       <c r="P111">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q111">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R111">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S111">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="U111">
-        <v>3.06</v>
+        <v>2.62</v>
       </c>
       <c r="V111">
+        <v>1.42</v>
+      </c>
+      <c r="W111">
+        <v>1.05</v>
+      </c>
+      <c r="X111">
+        <v>1.04</v>
+      </c>
+      <c r="Y111">
         <v>1.29</v>
       </c>
-      <c r="W111">
-        <v>1.07</v>
-      </c>
-      <c r="X111">
-        <v>1.01</v>
-      </c>
-      <c r="Y111">
-        <v>1.36</v>
-      </c>
       <c r="Z111">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="AA111">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AB111">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC111">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="AD111">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE111">
         <v>1.07</v>
       </c>
       <c r="AF111">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AG111">
+        <v>1.98</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.29</v>
+      </c>
+      <c r="AK111">
         <v>1.75</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.25</v>
-      </c>
-      <c r="AK111">
-        <v>1.85</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19380,19 +19380,19 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="O117">
         <v>5.7</v>
       </c>
       <c r="P117">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q117">
         <v>1.77</v>
       </c>
       <c r="R117">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="S117">
         <v>1.11</v>
@@ -19416,13 +19416,13 @@
         <v>1.06</v>
       </c>
       <c r="Z117">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AA117">
         <v>1.25</v>
       </c>
       <c r="AB117">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC117">
         <v>1.71</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK117">
         <v>3.12</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="O120">
+        <v>3.65</v>
+      </c>
+      <c r="P120">
         <v>3.6</v>
-      </c>
-      <c r="P120">
-        <v>3.3</v>
       </c>
       <c r="Q120">
         <v>2.3</v>
@@ -19887,10 +19887,10 @@
         <v>1.26</v>
       </c>
       <c r="T120">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U120">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="V120">
         <v>1.53</v>
@@ -19905,19 +19905,19 @@
         <v>1.15</v>
       </c>
       <c r="Z120">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA120">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AB120">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC120">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD120">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE120">
         <v>1.19</v>
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK120">
         <v>1.85</v>
@@ -20032,22 +20032,22 @@
         </is>
       </c>
       <c r="N121">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O121">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P121">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="Q121">
-        <v>4.39</v>
+        <v>4.59</v>
       </c>
       <c r="R121">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S121">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T121">
         <v>3.2</v>
@@ -20105,7 +20105,7 @@
         <v>1.2</v>
       </c>
       <c r="AK121">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,16 +20195,16 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O122">
         <v>3.5</v>
       </c>
       <c r="P122">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q122">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="R122">
         <v>2.4</v>
@@ -20228,22 +20228,22 @@
         <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z122">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="AA122">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB122">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AC122">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AD122">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE122">
         <v>1.14</v>
@@ -20252,7 +20252,7 @@
         <v>1.55</v>
       </c>
       <c r="AG122">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>1.19</v>
       </c>
       <c r="AK122">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,19 +20358,19 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O123">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P123">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="Q123">
         <v>2.06</v>
       </c>
       <c r="R123">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="S123">
         <v>1.29</v>
@@ -20403,7 +20403,7 @@
         <v>2.2</v>
       </c>
       <c r="AC123">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD123">
         <v>1.49</v>
@@ -20527,7 +20527,7 @@
         <v>3.35</v>
       </c>
       <c r="P124">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q124">
         <v>2.74</v>
@@ -20551,10 +20551,10 @@
         <v>1.06</v>
       </c>
       <c r="X124">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z124">
         <v>3.4</v>
@@ -20684,7 +20684,7 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O125">
         <v>3.5</v>
@@ -21010,19 +21010,19 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O127">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="P127">
-        <v>9.9</v>
+        <v>12</v>
       </c>
       <c r="Q127">
         <v>1.48</v>
       </c>
       <c r="R127">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="S127">
         <v>1.14</v>
@@ -21058,10 +21058,10 @@
         <v>1.95</v>
       </c>
       <c r="AD127">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AE127">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF127">
         <v>2.1</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="O135">
         <v>5</v>
       </c>
       <c r="P135">
-        <v>7.75</v>
+        <v>7.25</v>
       </c>
       <c r="Q135">
         <v>1.76</v>
@@ -22338,7 +22338,7 @@
         <v>2.17</v>
       </c>
       <c r="V135">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W135">
         <v>1.15</v>
@@ -22359,7 +22359,7 @@
         <v>2.55</v>
       </c>
       <c r="AC135">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD135">
         <v>1.57</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK135">
         <v>3.1</v>
@@ -22649,10 +22649,10 @@
         <v>1.62</v>
       </c>
       <c r="Q137">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="R137">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S137">
         <v>1.26</v>
@@ -22679,10 +22679,10 @@
         <v>3</v>
       </c>
       <c r="AA137">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB137">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AC137">
         <v>2.25</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AK137">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22993,16 +22993,16 @@
         <v>1.44</v>
       </c>
       <c r="W139">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X139">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y139">
         <v>1.19</v>
       </c>
       <c r="Z139">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA139">
         <v>1.73</v>
@@ -23011,7 +23011,7 @@
         <v>1.95</v>
       </c>
       <c r="AC139">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD139">
         <v>1.33</v>
@@ -23020,7 +23020,7 @@
         <v>1.09</v>
       </c>
       <c r="AF139">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG139">
         <v>2.15</v>
@@ -23129,19 +23129,19 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="O140">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="P140">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="Q140">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="R140">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S140">
         <v>1.2</v>
@@ -23150,7 +23150,7 @@
         <v>3.9</v>
       </c>
       <c r="U140">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V140">
         <v>1.68</v>
@@ -23174,10 +23174,10 @@
         <v>2.62</v>
       </c>
       <c r="AC140">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD140">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE140">
         <v>1.24</v>
@@ -23202,7 +23202,7 @@
         <v>1.47</v>
       </c>
       <c r="AK140">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL140">
         <v>0</v>

--- a/jogos_2026-10-23.xlsx
+++ b/jogos_2026-10-23.xlsx
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
         <v>3.1</v>
@@ -1015,10 +1015,10 @@
         <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="O5">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="P5">
         <v>1.3</v>
@@ -1145,10 +1145,10 @@
         <v>3.4</v>
       </c>
       <c r="U5">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W5">
         <v>1.11</v>
@@ -1160,16 +1160,16 @@
         <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>4.77</v>
+        <v>4.52</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB5">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AD5">
         <v>1.53</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O9">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
       <c r="Q9">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="R9">
         <v>1.77</v>
@@ -1833,7 +1833,7 @@
         <v>2.51</v>
       </c>
       <c r="AG9">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1954,16 +1954,16 @@
         <v>1.94</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T10">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
         <v>3.24</v>
       </c>
       <c r="V10">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W10">
         <v>1.01</v>
@@ -1972,7 +1972,7 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
         <v>2.62</v>
@@ -1996,7 +1996,7 @@
         <v>1.95</v>
       </c>
       <c r="AG10">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AK10">
         <v>1.57</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P11">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R11">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S11">
         <v>1.3</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="O12">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="P12">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB12">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -3759,7 +3759,7 @@
         <v>1.31</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1.03</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O22">
         <v>3.2</v>
       </c>
       <c r="P22">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q22">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R22">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S22">
         <v>1.4</v>
@@ -3916,7 +3916,7 @@
         <v>2.62</v>
       </c>
       <c r="U22">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V22">
         <v>1.33</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O23">
+        <v>3.2</v>
+      </c>
+      <c r="P23">
         <v>3.25</v>
       </c>
-      <c r="P23">
-        <v>3.2</v>
-      </c>
       <c r="Q23">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R23">
         <v>2.15</v>
@@ -4091,7 +4091,7 @@
         <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z23">
         <v>3.4</v>
@@ -4112,7 +4112,7 @@
         <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
         <v>2</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,55 +4221,55 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O24">
         <v>3.1</v>
       </c>
       <c r="P24">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
       </c>
       <c r="R24">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T24">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U24">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
         <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z24">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="AA24">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AB24">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC24">
         <v>4.15</v>
       </c>
       <c r="AD24">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE24">
         <v>1.06</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O25">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P25">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q25">
         <v>5.15</v>
@@ -4411,7 +4411,7 @@
         <v>1.27</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4441,7 +4441,7 @@
         <v>2.12</v>
       </c>
       <c r="AG25">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="AK25">
         <v>1.13</v>
@@ -4553,7 +4553,7 @@
         <v>6.05</v>
       </c>
       <c r="P26">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB26">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>1.64</v>
       </c>
       <c r="T27">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="U27">
         <v>3.98</v>
@@ -4743,25 +4743,25 @@
         <v>1.1</v>
       </c>
       <c r="Y27">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z27">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA27">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AB27">
         <v>1.37</v>
       </c>
       <c r="AC27">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AD27">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
         <v>2.39</v>
@@ -4873,52 +4873,52 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P28">
         <v>3.8</v>
       </c>
       <c r="Q28">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="S28">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T28">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="U28">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V28">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W28">
         <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Z28">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AA28">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AB28">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AC28">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="AD28">
         <v>1.1</v>
@@ -4930,7 +4930,7 @@
         <v>2.2</v>
       </c>
       <c r="AG28">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK28">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P29">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -5051,10 +5051,10 @@
         <v>1.91</v>
       </c>
       <c r="S29">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="T29">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="U29">
         <v>3.7</v>
@@ -5075,10 +5075,10 @@
         <v>2.45</v>
       </c>
       <c r="AA29">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="AB29">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -5090,10 +5090,10 @@
         <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AG29">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
+        <v>2.6</v>
+      </c>
+      <c r="O30">
+        <v>2.55</v>
+      </c>
+      <c r="P30">
         <v>3.05</v>
       </c>
-      <c r="O30">
-        <v>2.73</v>
-      </c>
-      <c r="P30">
-        <v>2.41</v>
-      </c>
       <c r="Q30">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="R30">
         <v>1.8</v>
@@ -5217,13 +5217,13 @@
         <v>1.68</v>
       </c>
       <c r="T30">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="U30">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V30">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W30">
         <v>1.03</v>
@@ -5272,7 +5272,7 @@
         <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O31">
+        <v>3.25</v>
+      </c>
+      <c r="P31">
         <v>3.4</v>
       </c>
-      <c r="P31">
-        <v>2.87</v>
-      </c>
       <c r="Q31">
+        <v>2.56</v>
+      </c>
+      <c r="R31">
+        <v>1.99</v>
+      </c>
+      <c r="S31">
+        <v>1.37</v>
+      </c>
+      <c r="T31">
         <v>2.69</v>
       </c>
-      <c r="R31">
-        <v>2.2</v>
-      </c>
-      <c r="S31">
+      <c r="U31">
+        <v>2.77</v>
+      </c>
+      <c r="V31">
+        <v>1.35</v>
+      </c>
+      <c r="W31">
+        <v>1.07</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
         <v>1.3</v>
       </c>
-      <c r="T31">
-        <v>3.2</v>
-      </c>
-      <c r="U31">
-        <v>2.45</v>
-      </c>
-      <c r="V31">
-        <v>1.44</v>
-      </c>
-      <c r="W31">
-        <v>1.1</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>1.2</v>
-      </c>
       <c r="Z31">
-        <v>3.76</v>
+        <v>3.08</v>
       </c>
       <c r="AA31">
+        <v>2.05</v>
+      </c>
+      <c r="AB31">
+        <v>1.75</v>
+      </c>
+      <c r="AC31">
+        <v>3.46</v>
+      </c>
+      <c r="AD31">
+        <v>1.24</v>
+      </c>
+      <c r="AE31">
+        <v>1.08</v>
+      </c>
+      <c r="AF31">
+        <v>1.8</v>
+      </c>
+      <c r="AG31">
+        <v>1.95</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.25</v>
+      </c>
+      <c r="AK31">
         <v>1.73</v>
-      </c>
-      <c r="AB31">
-        <v>2</v>
-      </c>
-      <c r="AC31">
-        <v>2.78</v>
-      </c>
-      <c r="AD31">
-        <v>1.37</v>
-      </c>
-      <c r="AE31">
-        <v>1.11</v>
-      </c>
-      <c r="AF31">
-        <v>1.57</v>
-      </c>
-      <c r="AG31">
-        <v>2.2</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.29</v>
-      </c>
-      <c r="AK31">
-        <v>1.6</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O32">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q32">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="R32">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
+        <v>1.3</v>
+      </c>
+      <c r="T32">
+        <v>3.2</v>
+      </c>
+      <c r="U32">
+        <v>2.45</v>
+      </c>
+      <c r="V32">
+        <v>1.44</v>
+      </c>
+      <c r="W32">
+        <v>1.1</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.2</v>
+      </c>
+      <c r="Z32">
+        <v>3.76</v>
+      </c>
+      <c r="AA32">
+        <v>1.73</v>
+      </c>
+      <c r="AB32">
+        <v>2</v>
+      </c>
+      <c r="AC32">
+        <v>2.78</v>
+      </c>
+      <c r="AD32">
         <v>1.37</v>
       </c>
-      <c r="T32">
-        <v>2.69</v>
-      </c>
-      <c r="U32">
-        <v>2.77</v>
-      </c>
-      <c r="V32">
-        <v>1.35</v>
-      </c>
-      <c r="W32">
-        <v>1.07</v>
-      </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>1.3</v>
-      </c>
-      <c r="Z32">
-        <v>3.08</v>
-      </c>
-      <c r="AA32">
-        <v>2.05</v>
-      </c>
-      <c r="AB32">
-        <v>1.75</v>
-      </c>
-      <c r="AC32">
-        <v>3.46</v>
-      </c>
-      <c r="AD32">
-        <v>1.24</v>
-      </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,28 +5691,28 @@
         <v>2</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q33">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T33">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="U33">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W33">
         <v>1.1</v>
@@ -5721,31 +5721,31 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA33">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC33">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="AD33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O34">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O38">
         <v>3.85</v>
       </c>
       <c r="P38">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q38">
         <v>2.16</v>
@@ -6521,7 +6521,7 @@
         <v>1.2</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="U38">
         <v>2.1</v>
@@ -6530,7 +6530,7 @@
         <v>1.76</v>
       </c>
       <c r="W38">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
         <v>1.01</v>
@@ -6672,19 +6672,19 @@
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="Q39">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S39">
         <v>1.39</v>
       </c>
       <c r="T39">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="U39">
         <v>2.76</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O40">
         <v>2.98</v>
@@ -6838,10 +6838,10 @@
         <v>3.38</v>
       </c>
       <c r="Q40">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="R40">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="S40">
         <v>1.43</v>
@@ -6865,19 +6865,19 @@
         <v>1.36</v>
       </c>
       <c r="Z40">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="AA40">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AB40">
         <v>1.67</v>
       </c>
       <c r="AC40">
-        <v>3.95</v>
+        <v>4.07</v>
       </c>
       <c r="AD40">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE40">
         <v>1.02</v>
@@ -6886,7 +6886,7 @@
         <v>1.95</v>
       </c>
       <c r="AG40">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>3</v>
       </c>
       <c r="U42">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V42">
         <v>1.44</v>
@@ -7185,7 +7185,7 @@
         <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
         <v>1.22</v>
@@ -7209,10 +7209,10 @@
         <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG42">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q43">
-        <v>5.5</v>
+        <v>6.12</v>
       </c>
       <c r="R43">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S43">
         <v>1.38</v>
@@ -7348,7 +7348,7 @@
         <v>1.06</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y43">
         <v>1.29</v>
@@ -7363,10 +7363,10 @@
         <v>1.69</v>
       </c>
       <c r="AC43">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD43">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE43">
         <v>1.08</v>
@@ -7375,7 +7375,7 @@
         <v>2</v>
       </c>
       <c r="AG43">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O44">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P44">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q44">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R44">
         <v>2.4</v>
@@ -7502,13 +7502,13 @@
         <v>3.8</v>
       </c>
       <c r="U44">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="V44">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W44">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
         <v>1.02</v>
@@ -7517,13 +7517,13 @@
         <v>1.12</v>
       </c>
       <c r="Z44">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AA44">
         <v>1.54</v>
       </c>
       <c r="AB44">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AC44">
         <v>2.33</v>
@@ -7532,7 +7532,7 @@
         <v>1.51</v>
       </c>
       <c r="AE44">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF44">
         <v>1.49</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P45">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q45">
         <v>3.25</v>
@@ -7665,7 +7665,7 @@
         <v>3.4</v>
       </c>
       <c r="U45">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V45">
         <v>1.53</v>
@@ -7683,7 +7683,7 @@
         <v>4.15</v>
       </c>
       <c r="AA45">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB45">
         <v>2.13</v>
@@ -7692,7 +7692,7 @@
         <v>2.52</v>
       </c>
       <c r="AD45">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AE45">
         <v>1.13</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
         <v>1.31</v>
@@ -7970,55 +7970,55 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O47">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P47">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q47">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="R47">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T47">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="U47">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="V47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W47">
         <v>1.05</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z47">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="AA47">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AB47">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC47">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD47">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE47">
         <v>1.06</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK47">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8139,19 +8139,19 @@
         <v>3.25</v>
       </c>
       <c r="P48">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q48">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R48">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S48">
         <v>1.38</v>
       </c>
       <c r="T48">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="U48">
         <v>2.64</v>
@@ -8172,10 +8172,10 @@
         <v>3.68</v>
       </c>
       <c r="AA48">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="AB48">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC48">
         <v>2.63</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK48">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="O49">
         <v>3.03</v>
       </c>
       <c r="P49">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="Q49">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S49">
         <v>1.37</v>
@@ -8341,10 +8341,10 @@
         <v>1.5</v>
       </c>
       <c r="AC49">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="AD49">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE49">
         <v>1.03</v>
@@ -8459,52 +8459,52 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O50">
         <v>3.48</v>
       </c>
       <c r="P50">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T50">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="V50">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W50">
         <v>1.04</v>
       </c>
       <c r="X50">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z50">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="AA50">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB50">
         <v>1.87</v>
       </c>
       <c r="AC50">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AD50">
         <v>1.32</v>
@@ -8516,7 +8516,7 @@
         <v>1.83</v>
       </c>
       <c r="AG50">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8625,10 +8625,10 @@
         <v>2.66</v>
       </c>
       <c r="O51">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -8652,7 +8652,7 @@
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
         <v>1.31</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK51">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8960,19 +8960,19 @@
         <v>2.4</v>
       </c>
       <c r="R53">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U53">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="V53">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W53">
         <v>1.06</v>
@@ -8987,10 +8987,10 @@
         <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC53">
         <v>2.78</v>
@@ -9277,7 +9277,7 @@
         <v>2</v>
       </c>
       <c r="O55">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P55">
         <v>2.7</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P56">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q56">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9458,43 +9458,43 @@
         <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AA56">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB56">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AC56">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AD56">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE56">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF56">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG56">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.16</v>
       </c>
       <c r="AK56">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="Q57">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S57">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="U57">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="V57">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z57">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA57">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB57">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="AC57">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="AD57">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE57">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF57">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG57">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK57">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,65 +9763,65 @@
         </is>
       </c>
       <c r="N58">
+        <v>1.95</v>
+      </c>
+      <c r="O58">
+        <v>3.45</v>
+      </c>
+      <c r="P58">
+        <v>3.4</v>
+      </c>
+      <c r="Q58">
+        <v>2.38</v>
+      </c>
+      <c r="R58">
+        <v>2.38</v>
+      </c>
+      <c r="S58">
+        <v>1.25</v>
+      </c>
+      <c r="T58">
+        <v>3.4</v>
+      </c>
+      <c r="U58">
+        <v>2.25</v>
+      </c>
+      <c r="V58">
+        <v>1.57</v>
+      </c>
+      <c r="W58">
+        <v>1.13</v>
+      </c>
+      <c r="X58">
+        <v>1.01</v>
+      </c>
+      <c r="Y58">
+        <v>1.14</v>
+      </c>
+      <c r="Z58">
+        <v>4.4</v>
+      </c>
+      <c r="AA58">
+        <v>1.56</v>
+      </c>
+      <c r="AB58">
+        <v>2.22</v>
+      </c>
+      <c r="AC58">
+        <v>2.38</v>
+      </c>
+      <c r="AD58">
         <v>1.46</v>
       </c>
-      <c r="O58">
-        <v>4.1</v>
-      </c>
-      <c r="P58">
-        <v>5.4</v>
-      </c>
-      <c r="Q58">
-        <v>2.12</v>
-      </c>
-      <c r="R58">
-        <v>2.32</v>
-      </c>
-      <c r="S58">
-        <v>1.29</v>
-      </c>
-      <c r="T58">
-        <v>3.3</v>
-      </c>
-      <c r="U58">
+      <c r="AE58">
+        <v>1.2</v>
+      </c>
+      <c r="AF58">
+        <v>1.52</v>
+      </c>
+      <c r="AG58">
         <v>2.38</v>
       </c>
-      <c r="V58">
-        <v>1.49</v>
-      </c>
-      <c r="W58">
-        <v>1.1</v>
-      </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.16</v>
-      </c>
-      <c r="Z58">
-        <v>4.15</v>
-      </c>
-      <c r="AA58">
-        <v>1.61</v>
-      </c>
-      <c r="AB58">
-        <v>2.17</v>
-      </c>
-      <c r="AC58">
-        <v>2.43</v>
-      </c>
-      <c r="AD58">
-        <v>1.44</v>
-      </c>
-      <c r="AE58">
-        <v>1.15</v>
-      </c>
-      <c r="AF58">
-        <v>1.62</v>
-      </c>
-      <c r="AG58">
-        <v>2.12</v>
-      </c>
       <c r="AH58" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,61 +9926,61 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="O59">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P59">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q59">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="R59">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S59">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T59">
         <v>3.4</v>
       </c>
       <c r="U59">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V59">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W59">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
         <v>1.14</v>
       </c>
       <c r="Z59">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA59">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB59">
         <v>2.22</v>
       </c>
       <c r="AC59">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD59">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE59">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG59">
         <v>2.38</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10255,13 +10255,13 @@
         <v>2.75</v>
       </c>
       <c r="O61">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P61">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q61">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="R61">
         <v>1.96</v>
@@ -10291,10 +10291,10 @@
         <v>3</v>
       </c>
       <c r="AA61">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB61">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC61">
         <v>4</v>
@@ -10306,10 +10306,10 @@
         <v>1.05</v>
       </c>
       <c r="AF61">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG61">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O63">
         <v>3.4</v>
@@ -10587,7 +10587,7 @@
         <v>2.25</v>
       </c>
       <c r="Q63">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="R63">
         <v>2.38</v>
@@ -10623,7 +10623,7 @@
         <v>2.28</v>
       </c>
       <c r="AC63">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD63">
         <v>1.55</v>
@@ -10753,7 +10753,7 @@
         <v>4.18</v>
       </c>
       <c r="R64">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S64">
         <v>1.19</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O66">
         <v>3.65</v>
@@ -11079,13 +11079,13 @@
         <v>2.23</v>
       </c>
       <c r="R66">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="S66">
         <v>1.37</v>
       </c>
       <c r="T66">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="U66">
         <v>2.75</v>
@@ -11103,7 +11103,7 @@
         <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="AA66">
         <v>1.85</v>
@@ -11284,10 +11284,10 @@
         <v>1.3</v>
       </c>
       <c r="AF67">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG67">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AK67">
         <v>1.31</v>
@@ -11402,22 +11402,22 @@
         <v>2.16</v>
       </c>
       <c r="Q68">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R68">
         <v>2.3</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T68">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="U68">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="V68">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W68">
         <v>1.07</v>
@@ -11435,7 +11435,7 @@
         <v>1.67</v>
       </c>
       <c r="AB68">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AC68">
         <v>2.7</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AK68">
         <v>1.28</v>
@@ -11559,7 +11559,7 @@
         <v>6</v>
       </c>
       <c r="O69">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P69">
         <v>1.41</v>
@@ -11571,7 +11571,7 @@
         <v>2.38</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T69">
         <v>3.2</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="AK69">
         <v>1.11</v>
@@ -11722,13 +11722,13 @@
         <v>1.95</v>
       </c>
       <c r="O70">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
         <v>3.15</v>
       </c>
       <c r="Q70">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="R70">
         <v>2.31</v>
@@ -11752,16 +11752,16 @@
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z70">
         <v>3.53</v>
       </c>
       <c r="AA70">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB70">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC70">
         <v>3.24</v>
@@ -12057,7 +12057,7 @@
         <v>2.46</v>
       </c>
       <c r="R72">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S72">
         <v>1.4</v>
@@ -12078,16 +12078,16 @@
         <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z72">
         <v>2.7</v>
       </c>
       <c r="AA72">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AB72">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC72">
         <v>4.15</v>
@@ -12096,13 +12096,13 @@
         <v>1.16</v>
       </c>
       <c r="AE72">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF72">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG72">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>3.1</v>
       </c>
       <c r="P73">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -12549,7 +12549,7 @@
         <v>2.44</v>
       </c>
       <c r="S75">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T75">
         <v>4</v>
@@ -12561,7 +12561,7 @@
         <v>1.65</v>
       </c>
       <c r="W75">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X75">
         <v>1.02</v>
@@ -12573,10 +12573,10 @@
         <v>5.35</v>
       </c>
       <c r="AA75">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB75">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC75">
         <v>2.15</v>
@@ -12591,7 +12591,7 @@
         <v>1.44</v>
       </c>
       <c r="AG75">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12863,10 +12863,10 @@
         <v>1.65</v>
       </c>
       <c r="O77">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P77">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="Q77">
         <v>2.21</v>
@@ -12896,7 +12896,7 @@
         <v>1.14</v>
       </c>
       <c r="Z77">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="AA77">
         <v>1.66</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="O78">
         <v>3.55</v>
@@ -13032,7 +13032,7 @@
         <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="R78">
         <v>2.15</v>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O79">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
         <v>1.75</v>
@@ -13201,31 +13201,31 @@
         <v>2.25</v>
       </c>
       <c r="S79">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T79">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U79">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="V79">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W79">
         <v>1.1</v>
       </c>
       <c r="X79">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z79">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA79">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB79">
         <v>1.99</v>
@@ -13234,7 +13234,7 @@
         <v>2.88</v>
       </c>
       <c r="AD79">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE79">
         <v>1.15</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
+        <v>1.2</v>
+      </c>
+      <c r="AK79">
         <v>1.22</v>
-      </c>
-      <c r="AK79">
-        <v>1.2</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13515,7 +13515,7 @@
         <v>2.2</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P81">
         <v>3.15</v>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O86">
         <v>5.25</v>
@@ -14363,7 +14363,7 @@
         <v>1.14</v>
       </c>
       <c r="Z86">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA86">
         <v>1.57</v>
@@ -14372,10 +14372,10 @@
         <v>2.25</v>
       </c>
       <c r="AC86">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AD86">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE86">
         <v>1.13</v>
@@ -14384,7 +14384,7 @@
         <v>2.23</v>
       </c>
       <c r="AG86">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,68 +14486,68 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N87">
-        <v>1.33</v>
+        <v>3.05</v>
       </c>
       <c r="O87">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="P87">
-        <v>7.35</v>
+        <v>2.04</v>
       </c>
       <c r="Q87">
+        <v>3.1</v>
+      </c>
+      <c r="R87">
+        <v>2.45</v>
+      </c>
+      <c r="S87">
+        <v>1.2</v>
+      </c>
+      <c r="T87">
+        <v>3.9</v>
+      </c>
+      <c r="U87">
+        <v>2.02</v>
+      </c>
+      <c r="V87">
         <v>1.67</v>
       </c>
-      <c r="R87">
-        <v>2.62</v>
-      </c>
-      <c r="S87">
+      <c r="W87">
         <v>1.18</v>
-      </c>
-      <c r="T87">
-        <v>3.85</v>
-      </c>
-      <c r="U87">
-        <v>2.07</v>
-      </c>
-      <c r="V87">
-        <v>1.65</v>
-      </c>
-      <c r="W87">
-        <v>1.15</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z87">
-        <v>5.15</v>
+        <v>5.93</v>
       </c>
       <c r="AA87">
         <v>1.44</v>
       </c>
       <c r="AB87">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AC87">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD87">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE87">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF87">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG87">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="AK87">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.05</v>
+        <v>1.33</v>
       </c>
       <c r="O88">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="P88">
-        <v>2.04</v>
+        <v>7.35</v>
       </c>
       <c r="Q88">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="R88">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T88">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U88">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="V88">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>5.93</v>
+        <v>5.15</v>
       </c>
       <c r="AA88">
         <v>1.44</v>
       </c>
       <c r="AB88">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AC88">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD88">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AE88">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF88">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG88">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.73</v>
+        <v>1.06</v>
       </c>
       <c r="AK88">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,80 +14816,80 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="O89">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>3.52</v>
+        <v>2.95</v>
       </c>
       <c r="Q89">
-        <v>2.41</v>
+        <v>2.96</v>
       </c>
       <c r="R89">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S89">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
+        <v>2.8</v>
+      </c>
+      <c r="U89">
         <v>2.9</v>
       </c>
-      <c r="U89">
-        <v>2.75</v>
-      </c>
       <c r="V89">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W89">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z89">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA89">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB89">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC89">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD89">
+        <v>1.24</v>
+      </c>
+      <c r="AE89">
+        <v>1.06</v>
+      </c>
+      <c r="AF89">
+        <v>1.76</v>
+      </c>
+      <c r="AG89">
+        <v>1.93</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
         <v>1.3</v>
       </c>
-      <c r="AE89">
-        <v>1.1</v>
-      </c>
-      <c r="AF89">
-        <v>1.83</v>
-      </c>
-      <c r="AG89">
-        <v>1.85</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>1.21</v>
-      </c>
       <c r="AK89">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.87</v>
+        <v>1.81</v>
       </c>
       <c r="O90">
+        <v>3.3</v>
+      </c>
+      <c r="P90">
+        <v>3.52</v>
+      </c>
+      <c r="Q90">
+        <v>2.4</v>
+      </c>
+      <c r="R90">
+        <v>2.1</v>
+      </c>
+      <c r="S90">
+        <v>1.4</v>
+      </c>
+      <c r="T90">
+        <v>2.58</v>
+      </c>
+      <c r="U90">
+        <v>2.9</v>
+      </c>
+      <c r="V90">
+        <v>1.37</v>
+      </c>
+      <c r="W90">
+        <v>1.04</v>
+      </c>
+      <c r="X90">
+        <v>1.04</v>
+      </c>
+      <c r="Y90">
+        <v>1.27</v>
+      </c>
+      <c r="Z90">
         <v>3.25</v>
       </c>
-      <c r="P90">
-        <v>2.2</v>
-      </c>
-      <c r="Q90">
-        <v>3.3</v>
-      </c>
-      <c r="R90">
-        <v>2.08</v>
-      </c>
-      <c r="S90">
-        <v>1.35</v>
-      </c>
-      <c r="T90">
-        <v>2.96</v>
-      </c>
-      <c r="U90">
-        <v>2.59</v>
-      </c>
-      <c r="V90">
-        <v>1.4</v>
-      </c>
-      <c r="W90">
-        <v>1.08</v>
-      </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>1.25</v>
-      </c>
-      <c r="Z90">
-        <v>3.6</v>
-      </c>
       <c r="AA90">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AB90">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC90">
-        <v>3.25</v>
+        <v>3.89</v>
       </c>
       <c r="AD90">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE90">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF90">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG90">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AK90">
-        <v>1.35</v>
+        <v>1.97</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,61 +15142,61 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.32</v>
+        <v>1.65</v>
       </c>
       <c r="O91">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="P91">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q91">
+        <v>2.1</v>
+      </c>
+      <c r="R91">
+        <v>2.23</v>
+      </c>
+      <c r="S91">
+        <v>1.35</v>
+      </c>
+      <c r="T91">
         <v>2.88</v>
       </c>
-      <c r="R91">
-        <v>2</v>
-      </c>
-      <c r="S91">
-        <v>1.4</v>
-      </c>
-      <c r="T91">
-        <v>2.79</v>
-      </c>
       <c r="U91">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="V91">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W91">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X91">
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z91">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="AA91">
+        <v>1.81</v>
+      </c>
+      <c r="AB91">
         <v>2.01</v>
       </c>
-      <c r="AB91">
-        <v>1.75</v>
-      </c>
       <c r="AC91">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="AD91">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AE91">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF91">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG91">
         <v>1.93</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK91">
-        <v>1.62</v>
+        <v>2.32</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P92">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q92">
-        <v>3.37</v>
+        <v>3.19</v>
       </c>
       <c r="R92">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
+        <v>1.35</v>
+      </c>
+      <c r="T92">
+        <v>2.73</v>
+      </c>
+      <c r="U92">
+        <v>2.59</v>
+      </c>
+      <c r="V92">
+        <v>1.4</v>
+      </c>
+      <c r="W92">
+        <v>1.08</v>
+      </c>
+      <c r="X92">
+        <v>1.04</v>
+      </c>
+      <c r="Y92">
+        <v>1.25</v>
+      </c>
+      <c r="Z92">
+        <v>3.63</v>
+      </c>
+      <c r="AA92">
+        <v>1.95</v>
+      </c>
+      <c r="AB92">
+        <v>1.85</v>
+      </c>
+      <c r="AC92">
+        <v>2.97</v>
+      </c>
+      <c r="AD92">
+        <v>1.33</v>
+      </c>
+      <c r="AE92">
+        <v>1.12</v>
+      </c>
+      <c r="AF92">
+        <v>1.7</v>
+      </c>
+      <c r="AG92">
+        <v>2.11</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
         <v>1.27</v>
       </c>
-      <c r="T92">
-        <v>3.32</v>
-      </c>
-      <c r="U92">
-        <v>2.34</v>
-      </c>
-      <c r="V92">
-        <v>1.52</v>
-      </c>
-      <c r="W92">
-        <v>1.11</v>
-      </c>
-      <c r="X92">
-        <v>1.01</v>
-      </c>
-      <c r="Y92">
-        <v>1.2</v>
-      </c>
-      <c r="Z92">
-        <v>4.2</v>
-      </c>
-      <c r="AA92">
-        <v>1.65</v>
-      </c>
-      <c r="AB92">
-        <v>2.15</v>
-      </c>
-      <c r="AC92">
-        <v>2.52</v>
-      </c>
-      <c r="AD92">
-        <v>1.4</v>
-      </c>
-      <c r="AE92">
-        <v>1.13</v>
-      </c>
-      <c r="AF92">
-        <v>1.57</v>
-      </c>
-      <c r="AG92">
-        <v>2.3</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.55</v>
-      </c>
       <c r="AK92">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.42</v>
+        <v>2.7</v>
       </c>
       <c r="O93">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="P93">
-        <v>5.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q93">
-        <v>2.11</v>
+        <v>3.39</v>
       </c>
       <c r="R93">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S93">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="U93">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V93">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W93">
         <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
         <v>1.18</v>
       </c>
       <c r="Z93">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
       <c r="AA93">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB93">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AC93">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AD93">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE93">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF93">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG93">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AK93">
-        <v>2.23</v>
+        <v>1.38</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O99">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P99">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="Q99">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="R99">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="S99">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T99">
         <v>4</v>
       </c>
       <c r="U99">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V99">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W99">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z99">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="AA99">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB99">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC99">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD99">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AE99">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF99">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG99">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK99">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O100">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="P100">
-        <v>3.9</v>
+        <v>2.81</v>
       </c>
       <c r="Q100">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="R100">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="S100">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T100">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U100">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="V100">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="W100">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z100">
-        <v>5.45</v>
+        <v>4.7</v>
       </c>
       <c r="AA100">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AB100">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="AC100">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD100">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AE100">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF100">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG100">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AK100">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="O101">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="P101">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="Q101">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="R101">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S101">
+        <v>1.22</v>
+      </c>
+      <c r="T101">
+        <v>4</v>
+      </c>
+      <c r="U101">
+        <v>2.1</v>
+      </c>
+      <c r="V101">
+        <v>1.69</v>
+      </c>
+      <c r="W101">
         <v>1.17</v>
       </c>
-      <c r="T101">
-        <v>4.1</v>
-      </c>
-      <c r="U101">
-        <v>1.97</v>
-      </c>
-      <c r="V101">
-        <v>1.72</v>
-      </c>
-      <c r="W101">
-        <v>1.18</v>
-      </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z101">
-        <v>6.36</v>
+        <v>5.8</v>
       </c>
       <c r="AA101">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AB101">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AC101">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AD101">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE101">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF101">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG101">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="O102">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q102">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="R102">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S102">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T102">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U102">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="V102">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W102">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z102">
-        <v>5.8</v>
+        <v>6.36</v>
       </c>
       <c r="AA102">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AB102">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AC102">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AD102">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE102">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF102">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG102">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="O103">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P103">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="Q103">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="R103">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="S103">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T103">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="U103">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V103">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W103">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X103">
         <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z103">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="AA103">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB103">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC103">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD103">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE103">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF103">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG103">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O104">
+        <v>3.7</v>
+      </c>
+      <c r="P104">
+        <v>3.14</v>
+      </c>
+      <c r="Q104">
+        <v>2.48</v>
+      </c>
+      <c r="R104">
+        <v>2.45</v>
+      </c>
+      <c r="S104">
+        <v>1.21</v>
+      </c>
+      <c r="T104">
         <v>3.64</v>
       </c>
-      <c r="P104">
-        <v>2.81</v>
-      </c>
-      <c r="Q104">
-        <v>2.71</v>
-      </c>
-      <c r="R104">
-        <v>2.48</v>
-      </c>
-      <c r="S104">
-        <v>1.22</v>
-      </c>
-      <c r="T104">
-        <v>3.56</v>
-      </c>
       <c r="U104">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="V104">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="W104">
+        <v>1.14</v>
+      </c>
+      <c r="X104">
+        <v>1.02</v>
+      </c>
+      <c r="Y104">
         <v>1.12</v>
       </c>
-      <c r="X104">
-        <v>1.01</v>
-      </c>
-      <c r="Y104">
-        <v>1.15</v>
-      </c>
       <c r="Z104">
-        <v>4.7</v>
+        <v>5.45</v>
       </c>
       <c r="AA104">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB104">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="AC104">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="AD104">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AE104">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF104">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK104">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17955,7 +17955,7 @@
         <v>1.76</v>
       </c>
       <c r="AB108">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC108">
         <v>3.2</v>
@@ -17964,7 +17964,7 @@
         <v>1.34</v>
       </c>
       <c r="AE108">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF108">
         <v>1.7</v>
@@ -17986,7 +17986,7 @@
         <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="O109">
         <v>3.2</v>
       </c>
       <c r="P109">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q109">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S109">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T109">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="U109">
-        <v>3.06</v>
+        <v>2.62</v>
       </c>
       <c r="V109">
+        <v>1.42</v>
+      </c>
+      <c r="W109">
+        <v>1.05</v>
+      </c>
+      <c r="X109">
+        <v>1.04</v>
+      </c>
+      <c r="Y109">
         <v>1.29</v>
       </c>
-      <c r="W109">
-        <v>1.07</v>
-      </c>
-      <c r="X109">
-        <v>1.01</v>
-      </c>
-      <c r="Y109">
-        <v>1.36</v>
-      </c>
       <c r="Z109">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="AA109">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AB109">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC109">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="AD109">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE109">
         <v>1.07</v>
       </c>
       <c r="AF109">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AG109">
+        <v>1.98</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
+        <v>1.29</v>
+      </c>
+      <c r="AK109">
         <v>1.75</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.25</v>
-      </c>
-      <c r="AK109">
-        <v>1.85</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,31 +18239,31 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="O110">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P110">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="Q110">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="R110">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S110">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T110">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="U110">
-        <v>2.63</v>
+        <v>3.06</v>
       </c>
       <c r="V110">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W110">
         <v>1.07</v>
@@ -18272,31 +18272,31 @@
         <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z110">
-        <v>3.58</v>
+        <v>2.98</v>
       </c>
       <c r="AA110">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AB110">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AC110">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="AD110">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AE110">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF110">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AG110">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
+        <v>2.5</v>
+      </c>
+      <c r="O111">
+        <v>3.1</v>
+      </c>
+      <c r="P111">
+        <v>2.45</v>
+      </c>
+      <c r="Q111">
+        <v>3.1</v>
+      </c>
+      <c r="R111">
+        <v>2.25</v>
+      </c>
+      <c r="S111">
+        <v>1.36</v>
+      </c>
+      <c r="T111">
+        <v>2.82</v>
+      </c>
+      <c r="U111">
+        <v>2.63</v>
+      </c>
+      <c r="V111">
+        <v>1.44</v>
+      </c>
+      <c r="W111">
+        <v>1.07</v>
+      </c>
+      <c r="X111">
+        <v>1.01</v>
+      </c>
+      <c r="Y111">
+        <v>1.22</v>
+      </c>
+      <c r="Z111">
+        <v>3.58</v>
+      </c>
+      <c r="AA111">
+        <v>1.74</v>
+      </c>
+      <c r="AB111">
         <v>2</v>
       </c>
-      <c r="O111">
-        <v>3.2</v>
-      </c>
-      <c r="P111">
-        <v>3.3</v>
-      </c>
-      <c r="Q111">
-        <v>2.4</v>
-      </c>
-      <c r="R111">
-        <v>2.11</v>
-      </c>
-      <c r="S111">
+      <c r="AC111">
+        <v>2.81</v>
+      </c>
+      <c r="AD111">
         <v>1.33</v>
       </c>
-      <c r="T111">
-        <v>2.9</v>
-      </c>
-      <c r="U111">
-        <v>2.62</v>
-      </c>
-      <c r="V111">
-        <v>1.42</v>
-      </c>
-      <c r="W111">
-        <v>1.05</v>
-      </c>
-      <c r="X111">
-        <v>1.04</v>
-      </c>
-      <c r="Y111">
-        <v>1.29</v>
-      </c>
-      <c r="Z111">
-        <v>3.6</v>
-      </c>
-      <c r="AA111">
-        <v>1.84</v>
-      </c>
-      <c r="AB111">
-        <v>1.83</v>
-      </c>
-      <c r="AC111">
-        <v>3.08</v>
-      </c>
-      <c r="AD111">
-        <v>1.28</v>
-      </c>
       <c r="AE111">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF111">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG111">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.29</v>
       </c>
       <c r="AK111">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,10 +18565,10 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="O112">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="P112">
         <v>1.91</v>
@@ -18728,16 +18728,16 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O113">
         <v>3.1</v>
       </c>
       <c r="P113">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="Q113">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="R113">
         <v>2.19</v>
@@ -18767,7 +18767,7 @@
         <v>3.18</v>
       </c>
       <c r="AA113">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AB113">
         <v>1.76</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="O114">
         <v>3.25</v>
@@ -18964,7 +18964,7 @@
         <v>1.3</v>
       </c>
       <c r="AK114">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19380,19 +19380,19 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O117">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="P117">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q117">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R117">
-        <v>3.17</v>
+        <v>2.96</v>
       </c>
       <c r="S117">
         <v>1.11</v>
@@ -19422,7 +19422,7 @@
         <v>1.25</v>
       </c>
       <c r="AB117">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AC117">
         <v>1.71</v>
@@ -19434,7 +19434,7 @@
         <v>1.52</v>
       </c>
       <c r="AF117">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG117">
         <v>2.7</v>
@@ -19453,7 +19453,7 @@
         <v>1.11</v>
       </c>
       <c r="AK117">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19552,7 +19552,7 @@
         <v>1.44</v>
       </c>
       <c r="Q118">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="R118">
         <v>2.33</v>
@@ -19570,7 +19570,7 @@
         <v>1.44</v>
       </c>
       <c r="W118">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X118">
         <v>1.03</v>
@@ -19582,19 +19582,19 @@
         <v>3.98</v>
       </c>
       <c r="AA118">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB118">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AC118">
         <v>2.7</v>
       </c>
       <c r="AD118">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE118">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF118">
         <v>1.8</v>
@@ -19616,7 +19616,7 @@
         <v>1.13</v>
       </c>
       <c r="AK118">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19715,7 +19715,7 @@
         <v>3.1</v>
       </c>
       <c r="Q119">
-        <v>2.49</v>
+        <v>2.82</v>
       </c>
       <c r="R119">
         <v>2.13</v>
@@ -19724,7 +19724,7 @@
         <v>1.3</v>
       </c>
       <c r="T119">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="U119">
         <v>2.42</v>
@@ -20850,7 +20850,7 @@
         <v>3</v>
       </c>
       <c r="O126">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P126">
         <v>2.25</v>
@@ -20862,10 +20862,10 @@
         <v>2.15</v>
       </c>
       <c r="S126">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T126">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U126">
         <v>2.55</v>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK126">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21176,13 +21176,13 @@
         <v>1.57</v>
       </c>
       <c r="O128">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P128">
         <v>5.25</v>
       </c>
       <c r="Q128">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R128">
         <v>2.12</v>
@@ -21191,7 +21191,7 @@
         <v>1.46</v>
       </c>
       <c r="T128">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U128">
         <v>2.88</v>
@@ -21200,31 +21200,31 @@
         <v>1.38</v>
       </c>
       <c r="W128">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X128">
         <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z128">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA128">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AB128">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC128">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD128">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE128">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF128">
         <v>1.91</v>
@@ -21339,7 +21339,7 @@
         <v>4.75</v>
       </c>
       <c r="O129">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P129">
         <v>1.6</v>
@@ -21375,13 +21375,13 @@
         <v>4.9</v>
       </c>
       <c r="AA129">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB129">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC129">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AD129">
         <v>1.62</v>
@@ -21409,7 +21409,7 @@
         <v>1.17</v>
       </c>
       <c r="AK129">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O130">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P130">
-        <v>3.1</v>
+        <v>2.7</v>
       </